--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1858">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356557846069</t>
+    <t xml:space="preserve">12.2356538772583</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956901550293</t>
+    <t xml:space="preserve">12.195689201355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5895690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097309112549</t>
+    <t xml:space="preserve">11.5895700454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097299575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0766973495483</t>
+    <t xml:space="preserve">11.076696395874</t>
   </si>
   <si>
     <t xml:space="preserve">11.136643409729</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">10.6770582199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3107204437256</t>
+    <t xml:space="preserve">10.3107194900513</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907381057739</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.737003326416</t>
+    <t xml:space="preserve">10.7370042800903</t>
   </si>
   <si>
     <t xml:space="preserve">10.3906488418579</t>
@@ -95,43 +95,43 @@
     <t xml:space="preserve">10.5438442230225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257435798645</t>
+    <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
     <t xml:space="preserve">10.2707557678223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4838972091675</t>
+    <t xml:space="preserve">10.4838981628418</t>
   </si>
   <si>
     <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1042385101318</t>
+    <t xml:space="preserve">10.1042394638062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8702163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7170219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77786731719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9110803604126</t>
+    <t xml:space="preserve">10.7170209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77786636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91107940673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.54474258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77120494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.217472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639148712158</t>
+    <t xml:space="preserve">9.77120590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2174711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171102523804</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">10.417290687561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7703075408936</t>
+    <t xml:space="preserve">10.7703056335449</t>
   </si>
   <si>
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436595916748</t>
+    <t xml:space="preserve">9.96436500549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236833572388</t>
+    <t xml:space="preserve">10.7236824035645</t>
   </si>
   <si>
     <t xml:space="preserve">10.9434843063354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.436372756958</t>
+    <t xml:space="preserve">11.4363737106323</t>
   </si>
   <si>
     <t xml:space="preserve">11.3431243896484</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">11.6495161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0624771118164</t>
+    <t xml:space="preserve">11.2898387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0624780654907</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289943695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.475438117981</t>
+    <t xml:space="preserve">12.2289934158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4754371643066</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3422250747681</t>
+    <t xml:space="preserve">12.3422260284424</t>
   </si>
   <si>
     <t xml:space="preserve">12.4621171951294</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">12.6019926071167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823692321777</t>
+    <t xml:space="preserve">12.1823701858521</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961393356323</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.075798034668</t>
+    <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
     <t xml:space="preserve">11.9159421920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1890287399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.496319770813</t>
+    <t xml:space="preserve">12.1890296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4963188171387</t>
   </si>
   <si>
     <t xml:space="preserve">11.0633764266968</t>
@@ -224,40 +224,40 @@
     <t xml:space="preserve">11.6561756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.955906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2689580917358</t>
+    <t xml:space="preserve">11.9559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2689590454102</t>
   </si>
   <si>
     <t xml:space="preserve">12.8217926025391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9217023849487</t>
+    <t xml:space="preserve">12.9217042922974</t>
   </si>
   <si>
     <t xml:space="preserve">12.9350261688232</t>
   </si>
   <si>
-    <t xml:space="preserve">13.101541519165</t>
+    <t xml:space="preserve">13.1015424728394</t>
   </si>
   <si>
     <t xml:space="preserve">13.1281833648682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2480773925781</t>
+    <t xml:space="preserve">13.2480764389038</t>
   </si>
   <si>
     <t xml:space="preserve">13.1947898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1814708709717</t>
+    <t xml:space="preserve">13.1814699172974</t>
   </si>
   <si>
     <t xml:space="preserve">13.16148853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3613080978394</t>
+    <t xml:space="preserve">13.361307144165</t>
   </si>
   <si>
     <t xml:space="preserve">13.2347555160522</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">13.3946123123169</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0882186889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9816493988037</t>
+    <t xml:space="preserve">13.0882205963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.981650352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.6885805130005</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">12.5620279312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881739616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482578277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088306427002</t>
+    <t xml:space="preserve">12.8817386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482568740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088315963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7218828201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685098648071</t>
+    <t xml:space="preserve">12.4221525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7218837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685089111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.9150419235229</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134407043457</t>
+    <t xml:space="preserve">13.1344079971313</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5159864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6230993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226821899414</t>
+    <t xml:space="preserve">13.5159873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6230983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226812362671</t>
   </si>
   <si>
     <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4222640991211</t>
+    <t xml:space="preserve">13.4222660064697</t>
   </si>
   <si>
     <t xml:space="preserve">13.3620147705078</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">13.3553218841553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0741567611694</t>
+    <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
     <t xml:space="preserve">12.993824005127</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749900817871</t>
+    <t xml:space="preserve">13.2749891281128</t>
   </si>
   <si>
     <t xml:space="preserve">13.194655418396</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">11.7218885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0766935348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524095535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925764083862</t>
+    <t xml:space="preserve">12.0766925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524105072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925754547119</t>
   </si>
   <si>
     <t xml:space="preserve">12.4515790939331</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">13.1410999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8850889205933</t>
+    <t xml:space="preserve">10.8850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.1487054824829</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177295684814</t>
+    <t xml:space="preserve">10.4834260940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177286148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4432601928711</t>
+    <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">11.0122842788696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.811450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9252557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8783960342407</t>
+    <t xml:space="preserve">10.8114500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9252548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1754837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88762474060059</t>
+    <t xml:space="preserve">10.175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88762378692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.06421375274658</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">8.93032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313110351562</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479488372803</t>
+    <t xml:space="preserve">9.20479583740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.37215518951416</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115692138672</t>
+    <t xml:space="preserve">9.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">9.37884998321533</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23157405853271</t>
+    <t xml:space="preserve">9.2315731048584</t>
   </si>
   <si>
     <t xml:space="preserve">9.6332368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79390335083008</t>
+    <t xml:space="preserve">9.79390239715576</t>
   </si>
   <si>
     <t xml:space="preserve">9.55959796905518</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">9.51273822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43909931182861</t>
+    <t xml:space="preserve">9.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.56629371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.49265575408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.53951549530029</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">9.8273754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76043128967285</t>
+    <t xml:space="preserve">9.76043033599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.78720855712891</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">9.6734037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07760238647461</t>
+    <t xml:space="preserve">9.07760334014893</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -557,40 +557,40 @@
     <t xml:space="preserve">9.31190490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17801761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36546039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24496364593506</t>
+    <t xml:space="preserve">9.17801856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3654613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3855447769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24496269226074</t>
   </si>
   <si>
     <t xml:space="preserve">9.03743553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72279930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007617950439</t>
+    <t xml:space="preserve">8.70941066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72279834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007713317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78304958343506</t>
+    <t xml:space="preserve">8.74957656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78304862976074</t>
   </si>
   <si>
     <t xml:space="preserve">8.78974342346191</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.66924381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33452415466309</t>
+    <t xml:space="preserve">8.33452320098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.20063591003418</t>
@@ -611,52 +611,52 @@
     <t xml:space="preserve">8.10022068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83913898468018</t>
+    <t xml:space="preserve">8.1203031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83913803100586</t>
   </si>
   <si>
     <t xml:space="preserve">7.86591672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6316123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491798400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508436203003</t>
+    <t xml:space="preserve">7.84583330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63161277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491846084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508483886719</t>
   </si>
   <si>
     <t xml:space="preserve">7.74541664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71194553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69186162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500093460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516635894775</t>
+    <t xml:space="preserve">7.71194648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.651695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516683578491</t>
   </si>
   <si>
     <t xml:space="preserve">7.9596381187439</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21149063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963598251343</t>
+    <t xml:space="preserve">9.21149158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99635887146</t>
   </si>
   <si>
     <t xml:space="preserve">12.1168575286865</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967363357544</t>
+    <t xml:space="preserve">11.8691654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499143600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615617752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569847106934</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">13.957818031311</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7904567718506</t>
+    <t xml:space="preserve">13.7904577255249</t>
   </si>
   <si>
     <t xml:space="preserve">14.6004800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3126211166382</t>
+    <t xml:space="preserve">14.01806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582342147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3126201629639</t>
   </si>
   <si>
     <t xml:space="preserve">14.2858428955078</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">13.817234992981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101240158081</t>
+    <t xml:space="preserve">13.7101259231567</t>
   </si>
   <si>
     <t xml:space="preserve">13.455738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2415170669556</t>
+    <t xml:space="preserve">13.2415161132812</t>
   </si>
   <si>
     <t xml:space="preserve">13.1544885635376</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">12.7528266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8264646530151</t>
+    <t xml:space="preserve">12.8264636993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.9737405776978</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">12.9067974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1611843109131</t>
+    <t xml:space="preserve">13.1611833572388</t>
   </si>
   <si>
     <t xml:space="preserve">13.0540733337402</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">13.2147388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1879634857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812677383423</t>
+    <t xml:space="preserve">13.1879625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812686920166</t>
   </si>
   <si>
     <t xml:space="preserve">13.033989906311</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">12.9871292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.007212638855</t>
+    <t xml:space="preserve">13.0072135925293</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">13.3754053115845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4758214950562</t>
+    <t xml:space="preserve">13.4758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">13.3486280441284</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406856536865</t>
+    <t xml:space="preserve">13.0406866073608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666296005249</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">12.8867130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9335746765137</t>
+    <t xml:space="preserve">12.933575630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.8398532867432</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.9001045227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9536581039429</t>
+    <t xml:space="preserve">12.9536571502686</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532438278198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8197689056396</t>
+    <t xml:space="preserve">12.819769859314</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858825683594</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">12.3109951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3310794830322</t>
+    <t xml:space="preserve">12.3310785293579</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047174453735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708311080933</t>
+    <t xml:space="preserve">12.2708301544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1436347961426</t>
+    <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
     <t xml:space="preserve">12.7862977981567</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9469633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5653839111328</t>
+    <t xml:space="preserve">12.946964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5653848648071</t>
   </si>
   <si>
     <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637201309204</t>
+    <t xml:space="preserve">12.1637191772461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043012619019</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">12.3913297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649667739868</t>
+    <t xml:space="preserve">12.558690071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649677276611</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574405670166</t>
+    <t xml:space="preserve">12.2574396133423</t>
   </si>
   <si>
     <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4181070327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1971912384033</t>
+    <t xml:space="preserve">12.4181060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.197190284729</t>
   </si>
   <si>
     <t xml:space="preserve">12.1034698486328</t>
@@ -953,28 +953,28 @@
     <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0633039474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519943237305</t>
+    <t xml:space="preserve">12.063304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519933700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.6724939346313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3176898956299</t>
+    <t xml:space="preserve">12.3176889419556</t>
   </si>
   <si>
     <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030536651611</t>
+    <t xml:space="preserve">12.0030546188354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813064575195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6147794723511</t>
+    <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076684951782</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880002975464</t>
+    <t xml:space="preserve">11.5879993438721</t>
   </si>
   <si>
     <t xml:space="preserve">11.7085008621216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942789077759</t>
+    <t xml:space="preserve">11.6817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942798614502</t>
   </si>
   <si>
     <t xml:space="preserve">11.5210571289062</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6616401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6348600387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7687492370605</t>
+    <t xml:space="preserve">11.661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6348609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
     <t xml:space="preserve">11.7018060684204</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">11.2265043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7779808044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7043399810791</t>
+    <t xml:space="preserve">10.777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7043409347534</t>
   </si>
   <si>
     <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9453392028809</t>
+    <t xml:space="preserve">10.9453401565552</t>
   </si>
   <si>
     <t xml:space="preserve">11.1394758224487</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4206399917603</t>
+    <t xml:space="preserve">11.4206390380859</t>
   </si>
   <si>
     <t xml:space="preserve">11.5411405563354</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198095321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3001413345337</t>
+    <t xml:space="preserve">11.2198085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.300142288208</t>
   </si>
   <si>
     <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4608087539673</t>
+    <t xml:space="preserve">11.4608097076416</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541130065918</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">11.3336153030396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536958694458</t>
+    <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
     <t xml:space="preserve">11.1595602035522</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721174240112</t>
+    <t xml:space="preserve">10.9721155166626</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897037506104</t>
+    <t xml:space="preserve">10.3897047042847</t>
   </si>
   <si>
     <t xml:space="preserve">10.3093719482422</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">10.1620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156496047974</t>
+    <t xml:space="preserve">10.2156505584717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3361482620239</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625102996826</t>
+    <t xml:space="preserve">10.2625112533569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3428430557251</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">10.3562326431274</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076309204102</t>
+    <t xml:space="preserve">9.8407621383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059814453125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80729198455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68679141998291</t>
+    <t xml:space="preserve">9.80729103088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74704170227051</t>
+    <t xml:space="preserve">9.74704265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">9.75373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70018196105957</t>
+    <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650785446167</t>
+    <t xml:space="preserve">10.7110357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507863998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700365066528</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188871383667</t>
+    <t xml:space="preserve">10.3763151168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1888723373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.275899887085</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">10.128623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2223453521729</t>
+    <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2357330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5102024078369</t>
+    <t xml:space="preserve">10.5570640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089557647705</t>
+    <t xml:space="preserve">10.2089548110962</t>
   </si>
   <si>
     <t xml:space="preserve">9.6533203125</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">9.52612686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62654209136963</t>
+    <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959823608398</t>
+    <t xml:space="preserve">9.8474588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436754226685</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9988946914673</t>
+    <t xml:space="preserve">10.998893737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2465877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0859212875366</t>
+    <t xml:space="preserve">11.1796436309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2465858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0859203338623</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">10.463342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871877670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2892866134644</t>
+    <t xml:space="preserve">10.1554002761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2892875671387</t>
   </si>
   <si>
     <t xml:space="preserve">10.2658576965332</t>
@@ -1322,25 +1322,25 @@
     <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616590499878</t>
+    <t xml:space="preserve">10.8616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.6407451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106185913086</t>
+    <t xml:space="preserve">10.6106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5771465301514</t>
+    <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
     <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6139659881592</t>
+    <t xml:space="preserve">10.6139650344849</t>
   </si>
   <si>
     <t xml:space="preserve">10.6240072250366</t>
@@ -1352,31 +1352,31 @@
     <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9821586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269393920898</t>
+    <t xml:space="preserve">10.9821577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269403457642</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261079788208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3394956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3629264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1520528793335</t>
+    <t xml:space="preserve">10.403094291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3394966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.36292552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1520519256592</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821775436401</t>
+    <t xml:space="preserve">10.1821784973145</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452667236328</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">10.0349016189575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9788103103638</t>
+    <t xml:space="preserve">10.0951509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9788112640381</t>
   </si>
   <si>
     <t xml:space="preserve">11.1060047149658</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.082573890686</t>
+    <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">10.952033996582</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">11.0290184020996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0758800506592</t>
+    <t xml:space="preserve">11.0758790969849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2867546081543</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">10.3729677200317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1721363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2457752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0683727264404</t>
+    <t xml:space="preserve">10.172137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.245774269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0683736801147</t>
   </si>
   <si>
     <t xml:space="preserve">9.74369525909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28847503662109</t>
+    <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
     <t xml:space="preserve">9.34537792205811</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">9.67005634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72695922851562</t>
+    <t xml:space="preserve">9.72695827484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">9.6165018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54286289215088</t>
+    <t xml:space="preserve">9.54286193847656</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298851013184</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">9.5026969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49600219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62319564819336</t>
+    <t xml:space="preserve">9.47926616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49600124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62319469451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">8.60564804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932819366455</t>
+    <t xml:space="preserve">8.68932723999023</t>
   </si>
   <si>
     <t xml:space="preserve">8.72949409484863</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186557769775</t>
+    <t xml:space="preserve">9.30186462402344</t>
   </si>
   <si>
     <t xml:space="preserve">9.22487926483154</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785171508789</t>
+    <t xml:space="preserve">9.13785076141357</t>
   </si>
   <si>
     <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39558601379395</t>
+    <t xml:space="preserve">9.39558696746826</t>
   </si>
   <si>
     <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61315441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71691799163818</t>
+    <t xml:space="preserve">9.6131534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71691703796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73284149169922</t>
+    <t xml:space="preserve">8.7328405380249</t>
   </si>
   <si>
     <t xml:space="preserve">8.80647945404053</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338138580322</t>
+    <t xml:space="preserve">8.85334014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338043212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003398895264</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.82656288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58891201019287</t>
+    <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
     <t xml:space="preserve">8.29770469665527</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2508430480957</t>
+    <t xml:space="preserve">8.25084400177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78639602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945095062256</t>
+    <t xml:space="preserve">8.78639698028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71945190429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635478973389</t>
@@ -1643,22 +1643,22 @@
     <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1345043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00730991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01065921783447</t>
+    <t xml:space="preserve">9.13450527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00731182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
     <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20814418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22822570800781</t>
+    <t xml:space="preserve">9.20814228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22822666168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.94706153869629</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735210418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12781047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03408908843994</t>
+    <t xml:space="preserve">9.01735305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12780952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03408813476562</t>
   </si>
   <si>
     <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8499927520752</t>
+    <t xml:space="preserve">8.59560585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907886505127</t>
+    <t xml:space="preserve">8.62907791137695</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">9.30855941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50604438781738</t>
+    <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.46587753295898</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3110933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34456539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32448387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49184322357178</t>
+    <t xml:space="preserve">8.31109428405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34456634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32448291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514842987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49184226989746</t>
   </si>
   <si>
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810199737549</t>
+    <t xml:space="preserve">9.19810104370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">8.75627040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82321548461914</t>
+    <t xml:space="preserve">8.82321643829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.84329891204834</t>
@@ -1778,10 +1778,10 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169776916504</t>
+    <t xml:space="preserve">9.42236423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169872283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.29851722717285</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">9.44914054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91105556488037</t>
+    <t xml:space="preserve">9.91105461120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.8441104888916</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">9.44244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41901683807373</t>
+    <t xml:space="preserve">9.41901588439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.60646057128906</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2717399597168</t>
+    <t xml:space="preserve">9.27174091339111</t>
   </si>
   <si>
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275806427002</t>
+    <t xml:space="preserve">8.7127571105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.8098258972168</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">9.27843284606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947425842285</t>
+    <t xml:space="preserve">9.52947330474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42905902862549</t>
+    <t xml:space="preserve">9.42905807495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.36211395263672</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">9.15124130249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128349304199</t>
+    <t xml:space="preserve">9.16128253936768</t>
   </si>
   <si>
     <t xml:space="preserve">9.14789390563965</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">9.43240642547607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39223861694336</t>
+    <t xml:space="preserve">9.39223766326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.33533668518066</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69014072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73700046539307</t>
+    <t xml:space="preserve">9.69013977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50939083099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73699951171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.79724979400635</t>
@@ -1907,22 +1907,22 @@
     <t xml:space="preserve">9.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90770721435547</t>
+    <t xml:space="preserve">9.90770816802979</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77716732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7102222442627</t>
+    <t xml:space="preserve">9.77716636657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71022319793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.62989139556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38889122009277</t>
+    <t xml:space="preserve">9.38889217376709</t>
   </si>
   <si>
     <t xml:space="preserve">9.45248794555664</t>
@@ -1937,37 +1937,37 @@
     <t xml:space="preserve">8.76631259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62572956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953628540039</t>
+    <t xml:space="preserve">8.62573051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953533172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.77300643920898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75961780548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02404689788818</t>
+    <t xml:space="preserve">8.75961875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0240478515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.40562725067139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63993167877197</t>
+    <t xml:space="preserve">9.63993072509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94787406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76712512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66670989990234</t>
+    <t xml:space="preserve">9.94787311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76712608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
     <t xml:space="preserve">9.53282070159912</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35542011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20144844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10103225708008</t>
+    <t xml:space="preserve">9.35541915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20144939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94371318817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053359985352</t>
+    <t xml:space="preserve">8.9437141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98053455352783</t>
   </si>
   <si>
     <t xml:space="preserve">8.99057483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342357635498</t>
+    <t xml:space="preserve">8.87342262268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67928600311279</t>
+    <t xml:space="preserve">8.68263339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67928504943848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86084651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82402801513672</t>
+    <t xml:space="preserve">9.86084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8240270614624</t>
   </si>
   <si>
     <t xml:space="preserve">9.81063842773438</t>
@@ -2024,19 +2024,19 @@
     <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30521106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15793514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1746711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08764362335205</t>
+    <t xml:space="preserve">9.30521202087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15793609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16797733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17467021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08764457702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">8.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288272857666</t>
+    <t xml:space="preserve">8.74288368225098</t>
   </si>
   <si>
     <t xml:space="preserve">8.7930908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250873565674</t>
+    <t xml:space="preserve">8.65250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">8.88681221008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0039644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05417156219482</t>
+    <t xml:space="preserve">9.00396347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05417251586914</t>
   </si>
   <si>
     <t xml:space="preserve">9.060866355896</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">8.97383975982666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
+    <t xml:space="preserve">9.11776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094787597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.96714496612549</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726867675781</t>
+    <t xml:space="preserve">8.99726963043213</t>
   </si>
   <si>
     <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06756114959717</t>
+    <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40146827697754</t>
+    <t xml:space="preserve">8.64246559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40146732330322</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">8.28431701660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410797119141</t>
+    <t xml:space="preserve">8.23410892486572</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377521514893</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">7.9897632598877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06005382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01653957366943</t>
+    <t xml:space="preserve">8.0600528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.03327655792236</t>
@@ -2156,13 +2156,13 @@
     <t xml:space="preserve">7.96633148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03997039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94290113449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558349609375</t>
+    <t xml:space="preserve">8.03997135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94290161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558301925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">7.1295313835144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22325372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300487518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07263040542603</t>
+    <t xml:space="preserve">7.22325325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300392150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">6.87514638900757</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">6.72786903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57222414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15884494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55802297592163</t>
+    <t xml:space="preserve">6.57222461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15884447097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55802345275879</t>
   </si>
   <si>
     <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4509129524231</t>
+    <t xml:space="preserve">5.45091247558594</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05928993225098</t>
+    <t xml:space="preserve">4.74800062179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05929040908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27183771133423</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693183898926</t>
+    <t xml:space="preserve">5.69693231582642</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311710357666</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">6.05842876434326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23917818069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29440641403198</t>
+    <t xml:space="preserve">6.23917865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515535354614</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">6.6174111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53038454055786</t>
+    <t xml:space="preserve">6.5303840637207</t>
   </si>
   <si>
     <t xml:space="preserve">6.64753675460815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56720352172852</t>
+    <t xml:space="preserve">6.56720399856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.54377317428589</t>
@@ -2270,37 +2270,37 @@
     <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09190130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03834676742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1789288520813</t>
+    <t xml:space="preserve">6.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03834629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00487422943115</t>
+    <t xml:space="preserve">6.00487375259399</t>
   </si>
   <si>
     <t xml:space="preserve">6.20235872268677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25926160812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32620477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628820419312</t>
+    <t xml:space="preserve">6.25926113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32620525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628772735596</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20905351638794</t>
+    <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826286315918</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01156854629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813819885254</t>
+    <t xml:space="preserve">6.01156806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433290481567</t>
+    <t xml:space="preserve">5.87433338165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747220993042</t>
@@ -2339,19 +2339,19 @@
     <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75302219390869</t>
+    <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
     <t xml:space="preserve">4.91368770599365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774185180664</t>
+    <t xml:space="preserve">5.08774137496948</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.188157081604</t>
+    <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.34212923049927</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22163009643555</t>
+    <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74379253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044609069824</t>
+    <t xml:space="preserve">5.74379301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044561386108</t>
   </si>
   <si>
     <t xml:space="preserve">5.89106941223145</t>
@@ -2384,49 +2384,49 @@
     <t xml:space="preserve">5.60655736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29526853561401</t>
+    <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.2082405090332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19819927215576</t>
+    <t xml:space="preserve">5.1981987953186</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861545562744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2852258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23836517333984</t>
+    <t xml:space="preserve">5.28522634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23836469650269</t>
   </si>
   <si>
     <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2785325050354</t>
+    <t xml:space="preserve">5.27853202819824</t>
   </si>
   <si>
     <t xml:space="preserve">5.23167133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204580307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3253927230835</t>
+    <t xml:space="preserve">5.35886430740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32539319992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22832441329956</t>
+    <t xml:space="preserve">5.2283239364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.04422807693481</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">4.97059011459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046497344971</t>
+    <t xml:space="preserve">4.94046545028687</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">5.08104753494263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13125514984131</t>
+    <t xml:space="preserve">5.13125562667847</t>
   </si>
   <si>
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790822982788</t>
+    <t xml:space="preserve">5.12790775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">5.11786651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12121343612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092191696167</t>
+    <t xml:space="preserve">5.12121391296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092239379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10447788238525</t>
+    <t xml:space="preserve">5.1044774055481</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
@@ -2477,31 +2477,31 @@
     <t xml:space="preserve">4.96389532089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41576719284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38899040222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48940515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36890649795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32873964309692</t>
+    <t xml:space="preserve">5.41576671600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38898992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48940563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36890697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">5.5764331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961277008057</t>
+    <t xml:space="preserve">5.53961324691772</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568376541138</t>
+    <t xml:space="preserve">5.39568424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221218109131</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">5.36555957794189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34547662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3053092956543</t>
+    <t xml:space="preserve">5.3454761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30530977249146</t>
   </si>
   <si>
     <t xml:space="preserve">5.27518510818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09108877182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60320997238159</t>
+    <t xml:space="preserve">5.09108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60321044921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537288665771</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">6.15215063095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934455871582</t>
+    <t xml:space="preserve">6.27934503555298</t>
   </si>
   <si>
     <t xml:space="preserve">6.22244167327881</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">6.19566488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880418777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524869918823</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375082015991</t>
+    <t xml:space="preserve">5.89441680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375034332275</t>
   </si>
   <si>
     <t xml:space="preserve">5.62664079666138</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48605871200562</t>
+    <t xml:space="preserve">5.4860577583313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271131515503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287721633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65341806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040437698364</t>
+    <t xml:space="preserve">5.52287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65341758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7304048538208</t>
   </si>
   <si>
     <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70362663269043</t>
+    <t xml:space="preserve">5.70362615585327</t>
   </si>
   <si>
     <t xml:space="preserve">5.65676498413086</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">5.55634927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46262788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47266960144043</t>
+    <t xml:space="preserve">5.46262741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47267007827759</t>
   </si>
   <si>
     <t xml:space="preserve">5.50948858261108</t>
@@ -2603,28 +2603,28 @@
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894773483276</t>
+    <t xml:space="preserve">5.37894821166992</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95385360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88021564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94381237030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07769966125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2182822227478</t>
+    <t xml:space="preserve">4.92372941970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95385408401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88021516799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94381189346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07770013809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21828269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.15468597412109</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09859561920166</t>
+    <t xml:space="preserve">6.0985951423645</t>
   </si>
   <si>
     <t xml:space="preserve">6.44335651397705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59398174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8082013130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63749504089355</t>
+    <t xml:space="preserve">6.59398126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80820178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6374945640564</t>
   </si>
   <si>
     <t xml:space="preserve">6.58728647232056</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">6.67766094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41323232650757</t>
+    <t xml:space="preserve">6.41323184967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.64418935775757</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">6.7814245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7613410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10275459289551</t>
+    <t xml:space="preserve">6.76134061813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10275554656982</t>
   </si>
   <si>
     <t xml:space="preserve">7.36383628845215</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">7.12283897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08936595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961576461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0558934211731</t>
+    <t xml:space="preserve">7.08936643600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556161880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986604690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589437484741</t>
   </si>
   <si>
     <t xml:space="preserve">7.00233936309814</t>
@@ -2711,31 +2711,31 @@
     <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944986343384</t>
+    <t xml:space="preserve">7.10944938659668</t>
   </si>
   <si>
     <t xml:space="preserve">7.07597780227661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9822564125061</t>
+    <t xml:space="preserve">6.98225736618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.14292144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200708389282</t>
+    <t xml:space="preserve">7.09606122970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200660705566</t>
   </si>
   <si>
     <t xml:space="preserve">6.96886730194092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90192317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11614465713501</t>
+    <t xml:space="preserve">6.90192365646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572751998901</t>
@@ -2744,61 +2744,61 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581094741821</t>
+    <t xml:space="preserve">7.03581047058105</t>
   </si>
   <si>
     <t xml:space="preserve">6.90861749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08267211914062</t>
+    <t xml:space="preserve">7.08267116546631</t>
   </si>
   <si>
     <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15631055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25003147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011489868164</t>
+    <t xml:space="preserve">7.15631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2500319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011442184448</t>
   </si>
   <si>
     <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55127954483032</t>
+    <t xml:space="preserve">7.55128002166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41069650650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3906135559082</t>
+    <t xml:space="preserve">7.4106969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56466960906982</t>
+    <t xml:space="preserve">7.56466865539551</t>
   </si>
   <si>
     <t xml:space="preserve">7.51111364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53789091110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6115288734436</t>
+    <t xml:space="preserve">7.53789138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61152935028076</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880575180054</t>
+    <t xml:space="preserve">7.7588062286377</t>
   </si>
   <si>
     <t xml:space="preserve">7.8525276184082</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849487304688</t>
+    <t xml:space="preserve">8.48849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485595703125</t>
+    <t xml:space="preserve">8.41485691070557</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">8.45502376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32782936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236171722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277694702148</t>
+    <t xml:space="preserve">8.26758098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32783126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81236124038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277742385864</t>
   </si>
   <si>
     <t xml:space="preserve">7.89938879013062</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93448543548584</t>
+    <t xml:space="preserve">9.55290412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93448448181152</t>
   </si>
   <si>
     <t xml:space="preserve">9.99473476409912</t>
@@ -2900,25 +2900,25 @@
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381896972656</t>
+    <t xml:space="preserve">9.77381992340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.73365306854248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5168972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039247512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6775636672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440916061401</t>
+    <t xml:space="preserve">10.5168981552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.677562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440906524658</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">9.93489170074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94969654083252</t>
+    <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63876914978027</t>
+    <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">9.43888759613037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57954502105713</t>
+    <t xml:space="preserve">9.57954406738281</t>
   </si>
   <si>
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462173461914</t>
+    <t xml:space="preserve">9.76462078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">9.89787673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97931003570557</t>
+    <t xml:space="preserve">9.97931098937988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98671245574951</t>
@@ -2984,22 +2984,22 @@
     <t xml:space="preserve">10.0903549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047241210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75721836090088</t>
+    <t xml:space="preserve">9.89047336578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7572193145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904102325439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85345935821533</t>
+    <t xml:space="preserve">9.85345840454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7720251083374</t>
+    <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0533399581909</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6017541885376</t>
+    <t xml:space="preserve">9.60175514221191</t>
   </si>
   <si>
     <t xml:space="preserve">9.54993343353271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52032089233398</t>
+    <t xml:space="preserve">9.5203218460083</t>
   </si>
   <si>
     <t xml:space="preserve">9.4018726348877</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26121425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14276504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10575008392334</t>
+    <t xml:space="preserve">9.33524513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26121520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14276599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10575103759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11315250396729</t>
+    <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">9.31303691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35745525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26861763000488</t>
+    <t xml:space="preserve">9.35745429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26861667633057</t>
   </si>
   <si>
     <t xml:space="preserve">9.15016841888428</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98730182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09834766387939</t>
+    <t xml:space="preserve">8.98730278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09834671020508</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885166168213</t>
+    <t xml:space="preserve">8.86885261535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.75040340423584</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33078384399414</t>
+    <t xml:space="preserve">4.33078336715698</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723415374756</t>
+    <t xml:space="preserve">4.69723463058472</t>
   </si>
   <si>
     <t xml:space="preserve">4.58248710632324</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1938271522522</t>
+    <t xml:space="preserve">4.19382762908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.16791677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17161798477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2456488609314</t>
+    <t xml:space="preserve">4.17161846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24564933776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.24934959411621</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018516540527</t>
+    <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233510971069</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41962003707886</t>
+    <t xml:space="preserve">4.41962051391602</t>
   </si>
   <si>
     <t xml:space="preserve">4.35669422149658</t>
@@ -3227,34 +3227,34 @@
     <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36039543151855</t>
+    <t xml:space="preserve">4.36039590835571</t>
   </si>
   <si>
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758710861206</t>
+    <t xml:space="preserve">4.10499048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.17902088165283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93842220306396</t>
+    <t xml:space="preserve">3.93842244148254</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057262420654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687093734741</t>
+    <t xml:space="preserve">4.05687141418457</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576635360718</t>
+    <t xml:space="preserve">4.04576587677002</t>
   </si>
   <si>
     <t xml:space="preserve">3.85328698158264</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51644825935364</t>
+    <t xml:space="preserve">3.51644802093506</t>
   </si>
   <si>
     <t xml:space="preserve">3.86069059371948</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206466674805</t>
+    <t xml:space="preserve">4.04206514358521</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654246330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95322799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05316925048828</t>
+    <t xml:space="preserve">3.90510869026184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433329582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654222488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95322823524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05316877365112</t>
   </si>
   <si>
     <t xml:space="preserve">4.01615428924561</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">3.88660097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8643913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036092758179</t>
+    <t xml:space="preserve">3.86439108848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036116600037</t>
   </si>
   <si>
     <t xml:space="preserve">3.73483824729919</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">3.62009072303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61638975143433</t>
+    <t xml:space="preserve">3.61638951301575</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42391014099121</t>
+    <t xml:space="preserve">3.42391037940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.33137178421021</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">2.98342871665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93345808982849</t>
+    <t xml:space="preserve">2.93345832824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3407,19 +3407,19 @@
     <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81130766868591</t>
+    <t xml:space="preserve">2.81130790710449</t>
   </si>
   <si>
     <t xml:space="preserve">2.86497974395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683082580566</t>
+    <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90569663047791</t>
+    <t xml:space="preserve">2.90569686889648</t>
   </si>
   <si>
     <t xml:space="preserve">2.86868143081665</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014457702637</t>
+    <t xml:space="preserve">2.90014433860779</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82426309585571</t>
+    <t xml:space="preserve">2.82426333427429</t>
   </si>
   <si>
     <t xml:space="preserve">2.83721852302551</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515645980835</t>
+    <t xml:space="preserve">2.56515622138977</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">2.46706604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47817063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45596170425415</t>
+    <t xml:space="preserve">2.47817087173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45596146583557</t>
   </si>
   <si>
     <t xml:space="preserve">2.48927521705627</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742413520813</t>
+    <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
     <t xml:space="preserve">2.27273607254028</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">2.25792980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34861707687378</t>
+    <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34676671028137</t>
+    <t xml:space="preserve">2.34676647186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790066719055</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">2.18760085105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29679560661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2856912612915</t>
+    <t xml:space="preserve">2.29679584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28569149971008</t>
   </si>
   <si>
     <t xml:space="preserve">2.30234837532043</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">2.35416984558105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34121417999268</t>
+    <t xml:space="preserve">2.34121441841125</t>
   </si>
   <si>
     <t xml:space="preserve">2.25422835350037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26718378067017</t>
+    <t xml:space="preserve">2.26718354225159</t>
   </si>
   <si>
     <t xml:space="preserve">2.28754210472107</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458691596985</t>
+    <t xml:space="preserve">2.27458667755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276568412781</t>
+    <t xml:space="preserve">2.22276544570923</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18204855918884</t>
+    <t xml:space="preserve">2.18204879760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15798902511597</t>
+    <t xml:space="preserve">2.15798878669739</t>
   </si>
   <si>
     <t xml:space="preserve">2.14873504638672</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765959739685</t>
+    <t xml:space="preserve">2.08765983581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688444137573</t>
+    <t xml:space="preserve">2.14688420295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810651779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186683177948</t>
+    <t xml:space="preserve">1.95810627937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186695098877</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
@@ -5583,6 +5583,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.11399984359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07999992370605</t>
   </si>
 </sst>
 </file>
@@ -70687,7 +70690,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495833333</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>438109</v>
@@ -70708,6 +70711,32 @@
         <v>1856</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494212963</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>389712</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>4.18400001525879</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>4.03599977493286</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>4.07999992370605</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="1860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="1861">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356548309326</t>
+    <t xml:space="preserve">12.2356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">12.1956901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895700454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097309112549</t>
+    <t xml:space="preserve">11.7027997970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895690917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097318649292</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101800918579</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">11.0766973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3107204437256</t>
+    <t xml:space="preserve">11.1366443634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.677056312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3107194900513</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907381057739</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507743835449</t>
+    <t xml:space="preserve">10.2507753372192</t>
   </si>
   <si>
     <t xml:space="preserve">10.7370042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3906488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239511489868</t>
+    <t xml:space="preserve">10.3906478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239521026611</t>
   </si>
   <si>
     <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2574338912964</t>
+    <t xml:space="preserve">10.257435798645</t>
   </si>
   <si>
     <t xml:space="preserve">10.2707557678223</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">10.1042394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8702173233032</t>
+    <t xml:space="preserve">10.8702163696289</t>
   </si>
   <si>
     <t xml:space="preserve">10.7170209884644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77786636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91107940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2174711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639148712158</t>
+    <t xml:space="preserve">9.77786731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91108131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54474353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2174701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171102523804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172925949097</t>
+    <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703065872192</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4905586242676</t>
+    <t xml:space="preserve">9.96436500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4905576705933</t>
   </si>
   <si>
     <t xml:space="preserve">10.7236824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9434843063354</t>
+    <t xml:space="preserve">10.9434833526611</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363737106323</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">11.6495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.062479019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2289934158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554567337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422260284424</t>
+    <t xml:space="preserve">11.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0624780654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2289943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.475438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422250747681</t>
   </si>
   <si>
     <t xml:space="preserve">12.4621171951294</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823701858521</t>
+    <t xml:space="preserve">12.6019916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823682785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695867538452</t>
+    <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.915940284729</t>
+    <t xml:space="preserve">11.9159412384033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1890306472778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.496319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0633754730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.955906867981</t>
+    <t xml:space="preserve">11.4963207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0633773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561765670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9559078216553</t>
   </si>
   <si>
     <t xml:space="preserve">12.2689580917358</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350242614746</t>
+    <t xml:space="preserve">12.9350261688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.101541519165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1281852722168</t>
+    <t xml:space="preserve">13.1281843185425</t>
   </si>
   <si>
     <t xml:space="preserve">13.2480764389038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1947908401489</t>
+    <t xml:space="preserve">13.1947917938232</t>
   </si>
   <si>
     <t xml:space="preserve">13.1814708709717</t>
@@ -257,37 +257,37 @@
     <t xml:space="preserve">13.16148853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.361307144165</t>
+    <t xml:space="preserve">13.3613090515137</t>
   </si>
   <si>
     <t xml:space="preserve">13.2347555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3946113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882196426392</t>
+    <t xml:space="preserve">13.3946123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882215499878</t>
   </si>
   <si>
     <t xml:space="preserve">12.981650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6885786056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5620269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8817405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884010314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482578277588</t>
+    <t xml:space="preserve">12.6885795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5620288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482568740845</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
@@ -296,55 +296,55 @@
     <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.721884727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887939453125</t>
+    <t xml:space="preserve">12.4221525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7218837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150438308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159873962402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230974197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226812362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561552047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222640991211</t>
+    <t xml:space="preserve">13.6230983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222650527954</t>
   </si>
   <si>
     <t xml:space="preserve">13.3620157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3553218841553</t>
+    <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9938249588013</t>
+    <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
@@ -356,37 +356,37 @@
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6591053009033</t>
+    <t xml:space="preserve">12.6591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">12.0833873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8156099319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524105072021</t>
+    <t xml:space="preserve">11.8156108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7218894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524095535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850908279419</t>
+    <t xml:space="preserve">12.4515800476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850889205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.1487054824829</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">10.4231758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8382291793823</t>
+    <t xml:space="preserve">10.8382301330566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4834260940552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177305221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2290391921997</t>
+    <t xml:space="preserve">10.7177295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2290382385254</t>
   </si>
   <si>
     <t xml:space="preserve">10.4164810180664</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7445058822632</t>
+    <t xml:space="preserve">10.7445077896118</t>
   </si>
   <si>
     <t xml:space="preserve">11.1193933486938</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0189762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0122833251953</t>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1260890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0189771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0122842788696</t>
   </si>
   <si>
     <t xml:space="preserve">10.8114500045776</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7645893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0616779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.175482749939</t>
+    <t xml:space="preserve">10.7645902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0616788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1754837036133</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762474060059</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">8.93032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93702030181885</t>
+    <t xml:space="preserve">8.93701934814453</t>
   </si>
   <si>
     <t xml:space="preserve">9.20479583740234</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31860065460205</t>
+    <t xml:space="preserve">9.23826885223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13115787506104</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">9.19140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315731048584</t>
+    <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.63323783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79390239715576</t>
+    <t xml:space="preserve">9.79390335083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.55959796905518</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78720760345459</t>
+    <t xml:space="preserve">9.78720855712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.87423515319824</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">9.67340469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07760334014893</t>
+    <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31190490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801856994629</t>
+    <t xml:space="preserve">9.3119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
   </si>
   <si>
     <t xml:space="preserve">9.35207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3654613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3855447769165</t>
+    <t xml:space="preserve">9.36546039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38554382324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.24496269226074</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">8.70941066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007713317871</t>
+    <t xml:space="preserve">8.72279930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007617950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.7696590423584</t>
@@ -590,73 +590,73 @@
     <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78304862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7897424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71610450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66924381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452320098877</t>
+    <t xml:space="preserve">8.78304958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78974437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71610546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.20063591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1002197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82575035095215</t>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1203031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82575082778931</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583330154419</t>
+    <t xml:space="preserve">7.86591577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.63161277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62491846084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508388519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74541664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69186210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500141143799</t>
+    <t xml:space="preserve">7.62491893768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508436203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74541759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7119460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500188827515</t>
   </si>
   <si>
     <t xml:space="preserve">7.65169620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68516778945923</t>
+    <t xml:space="preserve">7.68516731262207</t>
   </si>
   <si>
     <t xml:space="preserve">7.9596381187439</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92363166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21149063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963598251343</t>
+    <t xml:space="preserve">8.9236307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21148872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99635887146</t>
   </si>
   <si>
     <t xml:space="preserve">12.1168594360352</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">12.0499143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8615627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833080291748</t>
+    <t xml:space="preserve">14.8615608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833061218262</t>
   </si>
   <si>
     <t xml:space="preserve">13.7971525192261</t>
@@ -707,67 +707,67 @@
     <t xml:space="preserve">13.7569847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004800796509</t>
+    <t xml:space="preserve">13.8975687026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908739089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904558181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004781723022</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180683135986</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0582342147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917043685913</t>
+    <t xml:space="preserve">14.058235168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917062759399</t>
   </si>
   <si>
     <t xml:space="preserve">14.3126201629639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2858438491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1385669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251764297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101249694824</t>
+    <t xml:space="preserve">14.2858428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1385650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
     <t xml:space="preserve">13.4557371139526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2415189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544895172119</t>
+    <t xml:space="preserve">13.2415180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544904708862</t>
   </si>
   <si>
     <t xml:space="preserve">13.2549047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2080450057983</t>
+    <t xml:space="preserve">13.2080430984497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9268798828125</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">12.8264636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9737405776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611833572388</t>
+    <t xml:space="preserve">12.9737415313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611862182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.0540742874146</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">12.9134931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879634857178</t>
+    <t xml:space="preserve">13.2147388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879625320435</t>
   </si>
   <si>
     <t xml:space="preserve">13.3419332504272</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">13.1812686920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599367141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.007212638855</t>
+    <t xml:space="preserve">13.033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8599348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072135925293</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
@@ -824,67 +824,67 @@
     <t xml:space="preserve">13.0206022262573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.920184135437</t>
+    <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758195877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3486270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214345932007</t>
+    <t xml:space="preserve">13.3754034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758214950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3486289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214336395264</t>
   </si>
   <si>
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406856536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8666315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8867139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8398523330688</t>
+    <t xml:space="preserve">13.0406837463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8666305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8867149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9335737228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
     <t xml:space="preserve">12.9001035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9536590576172</t>
+    <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.819769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3109951019287</t>
+    <t xml:space="preserve">12.8197689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3109941482544</t>
   </si>
   <si>
     <t xml:space="preserve">12.3310794830322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4047183990479</t>
+    <t xml:space="preserve">12.4047174453735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2708301544189</t>
@@ -893,109 +893,109 @@
     <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6750297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624715805054</t>
+    <t xml:space="preserve">11.6750288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624696731567</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862997055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800191879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9469652175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3043012619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5586891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6189384460449</t>
+    <t xml:space="preserve">12.1436347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800210952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9469633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637201309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3043003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913288116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5586881637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2842197418213</t>
+    <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1034698486328</t>
+    <t xml:space="preserve">12.1971921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1034708023071</t>
   </si>
   <si>
     <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0633039474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519933700562</t>
+    <t xml:space="preserve">12.0633020401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519952774048</t>
   </si>
   <si>
     <t xml:space="preserve">12.672492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8089151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030536651611</t>
+    <t xml:space="preserve">12.3176898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8089160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030546188354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813055038452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6147785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5076694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6549463272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5880012512207</t>
+    <t xml:space="preserve">11.6147775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5076684951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6549453735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5880002975464</t>
   </si>
   <si>
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942798614502</t>
+    <t xml:space="preserve">11.6817216873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.5210561752319</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">11.661639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.634861946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7687492370605</t>
+    <t xml:space="preserve">11.6348628997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
     <t xml:space="preserve">11.7018051147461</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3804750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7043409347534</t>
+    <t xml:space="preserve">11.3804759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2265043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7980613708496</t>
@@ -1040,25 +1040,25 @@
     <t xml:space="preserve">11.1394758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1930303573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0658397674561</t>
+    <t xml:space="preserve">11.1930322647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0658388137817</t>
   </si>
   <si>
     <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528663635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0993099212646</t>
+    <t xml:space="preserve">11.0591440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.099310874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.1997261047363</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">11.4206399917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5411396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5679187774658</t>
+    <t xml:space="preserve">11.5411415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5679197311401</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1091,46 +1091,46 @@
     <t xml:space="preserve">11.4608087539673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3336143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3536958694458</t>
+    <t xml:space="preserve">11.4541139602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
     <t xml:space="preserve">11.1595592498779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5302867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3897037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093709945679</t>
+    <t xml:space="preserve">11.0524492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3897047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093719482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.1620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3361482620239</t>
+    <t xml:space="preserve">10.2156505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3361492156982</t>
   </si>
   <si>
     <t xml:space="preserve">10.4901208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625112533569</t>
+    <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3428430557251</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">9.71356964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026538848877</t>
+    <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74034786224365</t>
+    <t xml:space="preserve">9.74034690856934</t>
   </si>
   <si>
     <t xml:space="preserve">9.75373554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70018196105957</t>
+    <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650785446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700384140015</t>
+    <t xml:space="preserve">10.7110347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
     <t xml:space="preserve">10.6708679199219</t>
@@ -1190,40 +1190,40 @@
     <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1888723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759008407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1286220550537</t>
+    <t xml:space="preserve">10.188871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.128623008728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
+    <t xml:space="preserve">10.2357339859009</t>
   </si>
   <si>
     <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102024078369</t>
+    <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52612686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62654304504395</t>
+    <t xml:space="preserve">10.2089567184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52612590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62654209136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436754226685</t>
+    <t xml:space="preserve">10.5436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
@@ -1247,13 +1247,13 @@
     <t xml:space="preserve">10.8583116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855051040649</t>
+    <t xml:space="preserve">10.9855041503906</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587278366089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7311191558838</t>
+    <t xml:space="preserve">10.7311172485352</t>
   </si>
   <si>
     <t xml:space="preserve">10.82483959198</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">10.9654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725336074829</t>
+    <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
     <t xml:space="preserve">10.998893737793</t>
@@ -1274,40 +1274,40 @@
     <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2465858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0859203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9185609817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9118661880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9051742553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8917846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7512006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0390596389771</t>
+    <t xml:space="preserve">11.2465867996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0859212875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9185619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9118671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9051723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8917837142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7512016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
     <t xml:space="preserve">10.7277708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.463342666626</t>
+    <t xml:space="preserve">10.4633417129517</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">10.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3696212768555</t>
+    <t xml:space="preserve">10.3696203231812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135507583618</t>
@@ -1325,22 +1325,22 @@
     <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6407442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5503702163696</t>
+    <t xml:space="preserve">10.8616580963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6407451629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5503692626953</t>
   </si>
   <si>
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
+    <t xml:space="preserve">10.533634185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4097862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1729488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9821577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269393920898</t>
+    <t xml:space="preserve">10.4097881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.172947883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.982159614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269403457642</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261070251465</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3629264831543</t>
+    <t xml:space="preserve">10.36292552948</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.202260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821775436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94452571868896</t>
+    <t xml:space="preserve">10.2022609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349016189575</t>
@@ -1391,16 +1391,16 @@
     <t xml:space="preserve">10.0951499938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0357141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762962341309</t>
+    <t xml:space="preserve">10.9788103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1060056686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0357122421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0223245620728</t>
+    <t xml:space="preserve">11.0223236083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.9553804397583</t>
@@ -1424,37 +1424,37 @@
     <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9520330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0290193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0758790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.28675365448</t>
+    <t xml:space="preserve">10.952033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0290184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0758800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.506856918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729667663574</t>
+    <t xml:space="preserve">10.9352960586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5068559646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729677200317</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2457752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0683736801147</t>
+    <t xml:space="preserve">10.245774269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0683727264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.74369525909424</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">9.48596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6165018081665</t>
+    <t xml:space="preserve">9.58637714385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">9.54286289215088</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">9.57298755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56964015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50269603729248</t>
+    <t xml:space="preserve">9.56964111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50269508361816</t>
   </si>
   <si>
     <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49600219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62319469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60980606079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83660411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60564804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949409484863</t>
+    <t xml:space="preserve">9.49600315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62319660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6098051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83660316467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60564708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949314117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.89350605010986</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512954711914</t>
+    <t xml:space="preserve">9.22488021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
     <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785076141357</t>
+    <t xml:space="preserve">9.13785266876221</t>
   </si>
   <si>
     <t xml:space="preserve">9.45583629608154</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">9.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28178119659424</t>
+    <t xml:space="preserve">9.28178215026855</t>
   </si>
   <si>
     <t xml:space="preserve">9.61315441131592</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46922588348389</t>
+    <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37550354003906</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">9.26504611968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647945404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015865325928</t>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92028331756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88011837005615</t>
+    <t xml:space="preserve">8.92028427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88011646270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.82656288146973</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29770469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27427387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24080371856689</t>
+    <t xml:space="preserve">8.29770565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27427577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.25084400177002</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175979614258</t>
+    <t xml:space="preserve">8.47175884246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78639602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77635383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16462898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">8.78639507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71945095062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77635478973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16462993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00731182098389</t>
@@ -1655,34 +1655,34 @@
     <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01400470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20814323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22822666168213</t>
+    <t xml:space="preserve">9.01400566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20814418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0006160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735305786133</t>
+    <t xml:space="preserve">9.00061702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735210418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66589546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59560489654541</t>
+    <t xml:space="preserve">9.03408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66589641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.8499927520752</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">8.53535652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47510719299316</t>
+    <t xml:space="preserve">8.47510623931885</t>
   </si>
   <si>
     <t xml:space="preserve">8.30105209350586</t>
@@ -1700,79 +1700,79 @@
     <t xml:space="preserve">8.62907791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75292301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90689563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30855941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50604343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11107444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.294358253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3110933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34456634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32448291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93367195129395</t>
+    <t xml:space="preserve">8.7529239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90689468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29516983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30855846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50604438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31109428405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34456539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32448387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49184322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93367385864258</t>
   </si>
   <si>
     <t xml:space="preserve">9.19810104370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2349214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25753974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56548023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75627040863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82321643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84329891204834</t>
+    <t xml:space="preserve">9.23492050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70271682739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25753879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5654821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5018835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82321548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">8.74622917175293</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169872283936</t>
+    <t xml:space="preserve">9.42236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169776916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91105461120605</t>
+    <t xml:space="preserve">9.44914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91105556488037</t>
   </si>
   <si>
     <t xml:space="preserve">9.84411144256592</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60645961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95456790924072</t>
+    <t xml:space="preserve">9.60646057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95456886291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.41566848754883</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27174091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54874420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71275806427002</t>
+    <t xml:space="preserve">9.2717399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54874515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7127571105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
@@ -1838,31 +1838,31 @@
     <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27843379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42905902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3621129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24830913543701</t>
+    <t xml:space="preserve">9.27843284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42905807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36211490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2483081817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4257116317749</t>
+    <t xml:space="preserve">9.55625247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42571067810059</t>
   </si>
   <si>
     <t xml:space="preserve">9.15124034881592</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">9.16128158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14789295196533</t>
+    <t xml:space="preserve">9.14789390563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.43240547180176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39223766326904</t>
+    <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
     <t xml:space="preserve">9.33533573150635</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454555511475</t>
+    <t xml:space="preserve">9.14454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73030567169189</t>
+    <t xml:space="preserve">9.73030662536621</t>
   </si>
   <si>
     <t xml:space="preserve">9.69013977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50939083099365</t>
+    <t xml:space="preserve">9.50938987731934</t>
   </si>
   <si>
     <t xml:space="preserve">9.73700046539307</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92109489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90770816802979</t>
+    <t xml:space="preserve">9.9210958480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90770721435547</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
@@ -1922,43 +1922,43 @@
     <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62989044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62573146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77300643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961780548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02404689788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40562725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63993167877197</t>
+    <t xml:space="preserve">9.62989139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38889122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7730073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02404594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63993072509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">9.94787406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76712512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66670894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53282165527344</t>
+    <t xml:space="preserve">9.76712608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66670989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
     <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35541915893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20144939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10103225708008</t>
+    <t xml:space="preserve">9.35542011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20144844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.02739429473877</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">8.99057579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90354919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68263339996338</t>
+    <t xml:space="preserve">8.87342357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90354824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68263244628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.67928600311279</t>
@@ -2021,70 +2021,70 @@
     <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063938140869</t>
+    <t xml:space="preserve">9.81064033508301</t>
   </si>
   <si>
     <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30521202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15793609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17467021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08764362335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04413032531738</t>
+    <t xml:space="preserve">9.30521106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15793514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16797542572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08764457702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0441312789917</t>
   </si>
   <si>
     <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288368225098</t>
+    <t xml:space="preserve">8.88346576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681221008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0039644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05417251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.060866355896</t>
+    <t xml:space="preserve">8.65250873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05417156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06086540222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776828765869</t>
+    <t xml:space="preserve">8.97383880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776733398438</t>
   </si>
   <si>
     <t xml:space="preserve">9.08094882965088</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95040893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020084381104</t>
+    <t xml:space="preserve">8.95040798187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92697811126709</t>
+    <t xml:space="preserve">8.99726867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.829909324646</t>
+    <t xml:space="preserve">8.82990837097168</t>
   </si>
   <si>
     <t xml:space="preserve">8.64246654510498</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">8.40146827697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33787155151367</t>
+    <t xml:space="preserve">8.33787059783936</t>
   </si>
   <si>
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410892486572</t>
+    <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
@@ -2138,37 +2138,37 @@
     <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01654148101807</t>
+    <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95629024505615</t>
+    <t xml:space="preserve">7.94624853134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
     <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02323436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96633243560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03997135162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94290161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67177820205688</t>
+    <t xml:space="preserve">8.02323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96633148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03997039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9429030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6717791557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.12953233718872</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793214797974</t>
+    <t xml:space="preserve">7.54793167114258</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07263040542603</t>
+    <t xml:space="preserve">7.07262992858887</t>
   </si>
   <si>
     <t xml:space="preserve">6.87514543533325</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">6.72786855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57222366333008</t>
+    <t xml:space="preserve">6.57222414016724</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55802345275879</t>
+    <t xml:space="preserve">6.15884494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55802249908447</t>
   </si>
   <si>
     <t xml:space="preserve">5.57977962493896</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800109863281</t>
+    <t xml:space="preserve">4.74800157546997</t>
   </si>
   <si>
     <t xml:space="preserve">5.05929040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27183771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69023752212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69693231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98311758041382</t>
+    <t xml:space="preserve">5.27183723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6902379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69693183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98311805725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.05842971801758</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47515487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49356460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753675460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
+    <t xml:space="preserve">6.4751558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49356508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5303840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
     <t xml:space="preserve">6.42662143707275</t>
@@ -2273,34 +2273,34 @@
     <t xml:space="preserve">6.3596773147583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09190130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03834629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892789840698</t>
+    <t xml:space="preserve">6.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03834676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00487375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20235919952393</t>
+    <t xml:space="preserve">6.00487422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20235872268677</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620525360107</t>
+    <t xml:space="preserve">6.32620477676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28603887557983</t>
+    <t xml:space="preserve">6.28603839874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.20905303955078</t>
@@ -2309,46 +2309,46 @@
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520650863647</t>
+    <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156806945801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89776420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813724517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87433290481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82747316360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68354272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6601128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0843939781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87017393112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75302171707153</t>
+    <t xml:space="preserve">5.8977632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813772201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05508184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87433338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82747268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68354320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66011238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87017345428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75302219390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.91368770599365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774137496948</t>
+    <t xml:space="preserve">5.08774185180664</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34212827682495</t>
+    <t xml:space="preserve">5.34212923049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.15803289413452</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37225294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74379301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044561386108</t>
+    <t xml:space="preserve">5.37225389480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74379253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044513702393</t>
   </si>
   <si>
     <t xml:space="preserve">5.89106893539429</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">5.82077789306641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60655689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2952675819397</t>
+    <t xml:space="preserve">5.60655736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.2082405090332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1981987953186</t>
+    <t xml:space="preserve">5.19819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861497879028</t>
@@ -2402,10 +2402,10 @@
     <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30196189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23836517333984</t>
+    <t xml:space="preserve">5.30196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.238365650177</t>
   </si>
   <si>
     <t xml:space="preserve">5.33208751678467</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">5.27853202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23167133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35886526107788</t>
+    <t xml:space="preserve">5.23167085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35886478424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.32204580307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3253927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28187894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22832441329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04422807693481</t>
+    <t xml:space="preserve">5.32539319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28187942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22832345962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.97059011459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046545028687</t>
+    <t xml:space="preserve">4.94046497344971</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">5.08104705810547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11451959609985</t>
+    <t xml:space="preserve">5.13125514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.12790775299072</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
+    <t xml:space="preserve">5.11786699295044</t>
   </si>
   <si>
     <t xml:space="preserve">5.12121391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98063135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1044774055481</t>
+    <t xml:space="preserve">5.05092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98063182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10447835922241</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
@@ -2483,22 +2483,22 @@
     <t xml:space="preserve">5.41576719284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38898944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48940563201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32874011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53961324691772</t>
+    <t xml:space="preserve">5.38898992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48940515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36890649795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32874059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57643270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53961277008057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
@@ -2507,73 +2507,73 @@
     <t xml:space="preserve">5.39568424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36221218109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38229465484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36555957794189</t>
+    <t xml:space="preserve">5.36221170425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38229513168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36555862426758</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30530977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27518510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09108877182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60320997238159</t>
+    <t xml:space="preserve">5.3053092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27518463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09108829498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60321044921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537336349487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215063095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1956639289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1488037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.15215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27934408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19566440582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14880418777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524774551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375082015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62664079666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48605823516846</t>
+    <t xml:space="preserve">5.89441680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62663984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61325216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4860577583313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287769317627</t>
+    <t xml:space="preserve">5.52287721633911</t>
   </si>
   <si>
     <t xml:space="preserve">5.65341806411743</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">5.70027923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70362615585327</t>
+    <t xml:space="preserve">5.70362663269043</t>
   </si>
   <si>
     <t xml:space="preserve">5.65676546096802</t>
@@ -2600,22 +2600,22 @@
     <t xml:space="preserve">5.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45258712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37894773483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10113000869751</t>
+    <t xml:space="preserve">5.50948858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45258617401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37894821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
     <t xml:space="preserve">4.92372941970825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95385408401489</t>
+    <t xml:space="preserve">4.95385360717773</t>
   </si>
   <si>
     <t xml:space="preserve">4.88021564483643</t>
@@ -2627,31 +2627,31 @@
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21828269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55300235748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86094427108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02830457687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09859561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44335699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80820226669312</t>
+    <t xml:space="preserve">5.2182822227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55300283432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8609447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02830410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09859609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44335746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
     <t xml:space="preserve">6.6374945640564</t>
@@ -2660,85 +2660,85 @@
     <t xml:space="preserve">6.58728647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7211742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766094207764</t>
+    <t xml:space="preserve">6.72117376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766141891479</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418983459473</t>
+    <t xml:space="preserve">6.64418840408325</t>
   </si>
   <si>
     <t xml:space="preserve">6.78142404556274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76134061813354</t>
+    <t xml:space="preserve">6.7613410949707</t>
   </si>
   <si>
     <t xml:space="preserve">7.10275506973267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283802032471</t>
+    <t xml:space="preserve">7.36383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647741317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283897399902</t>
   </si>
   <si>
     <t xml:space="preserve">7.08936643600464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97556161880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986604690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05589485168457</t>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961576461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589389801025</t>
   </si>
   <si>
     <t xml:space="preserve">7.00233936309814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86175727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0692834854126</t>
+    <t xml:space="preserve">6.86175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06928253173828</t>
   </si>
   <si>
     <t xml:space="preserve">7.10944938659668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07597780227661</t>
+    <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
     <t xml:space="preserve">6.98225593566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14292192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96886682510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90192365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11614370346069</t>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96886730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90192270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572799682617</t>
@@ -2747,40 +2747,40 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581190109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622665405273</t>
+    <t xml:space="preserve">7.03581094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267259597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622617721558</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2500319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55127906799316</t>
+    <t xml:space="preserve">7.25003099441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366895675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4106969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39061450958252</t>
+    <t xml:space="preserve">7.41069746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.470947265625</t>
@@ -2795,31 +2795,31 @@
     <t xml:space="preserve">7.53789138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61152982711792</t>
+    <t xml:space="preserve">7.6115288734436</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252666473389</t>
+    <t xml:space="preserve">7.75880575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252714157104</t>
   </si>
   <si>
     <t xml:space="preserve">8.07344341278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18055248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37469005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6625509262085</t>
+    <t xml:space="preserve">8.32113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1805534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37469100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.89685344696045</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849678039551</t>
+    <t xml:space="preserve">8.48849487304688</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485691070557</t>
+    <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">8.28766345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45502376556396</t>
+    <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
     <t xml:space="preserve">8.18724727630615</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32783031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938831329346</t>
+    <t xml:space="preserve">8.26758098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32782936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938879013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049140930176</t>
+    <t xml:space="preserve">8.97049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009853363037</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9947338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96126270294189</t>
+    <t xml:space="preserve">9.99473476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96126365661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.94118022918701</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4767303466797</t>
+    <t xml:space="preserve">10.6039247512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476731300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.6775636672974</t>
@@ -2930,10 +2930,10 @@
     <t xml:space="preserve">9.84605503082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3346576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.186595916748</t>
+    <t xml:space="preserve">10.3346567153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1865949630737</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755491256714</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
+    <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80904102325439</t>
+    <t xml:space="preserve">9.80903911590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.85345840454102</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0533399581909</t>
+    <t xml:space="preserve">9.7720251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">9.60175514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5499324798584</t>
+    <t xml:space="preserve">9.54993343353271</t>
   </si>
   <si>
     <t xml:space="preserve">9.52032089233398</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">9.40187168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524513244629</t>
+    <t xml:space="preserve">9.40927505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575008392334</t>
+    <t xml:space="preserve">9.10575103759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">9.4166784286499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30563259124756</t>
+    <t xml:space="preserve">9.30563163757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.17237854003906</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199108123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17978096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11315441131592</t>
+    <t xml:space="preserve">9.20199012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17978000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.3130350112915</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">9.03171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02431678771973</t>
+    <t xml:space="preserve">9.02431583404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99470520019531</t>
+    <t xml:space="preserve">9.09834766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.994704246521</t>
   </si>
   <si>
     <t xml:space="preserve">9.80163669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0237274169922</t>
+    <t xml:space="preserve">10.0237283706665</t>
   </si>
   <si>
     <t xml:space="preserve">9.9571008682251</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60915660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32784175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46109676361084</t>
+    <t xml:space="preserve">9.60915756225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32784271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772426605225</t>
+    <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885166168213</t>
@@ -3143,31 +3143,31 @@
     <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92067337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93548107147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8096284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33078336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40481424331665</t>
+    <t xml:space="preserve">8.92067432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93548011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77261257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33078384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5898904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62690591812134</t>
+    <t xml:space="preserve">4.58989000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62690544128418</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128927230835</t>
+    <t xml:space="preserve">4.10128879547119</t>
   </si>
   <si>
     <t xml:space="preserve">4.13090133666992</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24564933776855</t>
+    <t xml:space="preserve">4.2456488609314</t>
   </si>
   <si>
     <t xml:space="preserve">4.24935007095337</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12720012664795</t>
+    <t xml:space="preserve">4.12719964981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033668518066</t>
+    <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35669422149658</t>
+    <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
     <t xml:space="preserve">4.39741134643555</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499048233032</t>
+    <t xml:space="preserve">4.10499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758758544922</t>
@@ -3245,40 +3245,40 @@
     <t xml:space="preserve">4.17902135848999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93842196464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06057262420654</t>
+    <t xml:space="preserve">3.93842220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
     <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87549638748169</t>
+    <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
     <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85328698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.588627576828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51644802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86069011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07537889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04206514358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15681219100952</t>
+    <t xml:space="preserve">3.85328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51644825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86069059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07537841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04206418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15681171417236</t>
   </si>
   <si>
     <t xml:space="preserve">4.34558963775635</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94952702522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433281898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654174804688</t>
+    <t xml:space="preserve">3.94952654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433234214783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86439156532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036068916321</t>
+    <t xml:space="preserve">4.01985549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8643913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
     <t xml:space="preserve">3.73483824729919</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">3.53310513496399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55716490745544</t>
+    <t xml:space="preserve">3.55716514587402</t>
   </si>
   <si>
     <t xml:space="preserve">3.52014994621277</t>
@@ -3338,25 +3338,25 @@
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459717750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57382154464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62009072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
+    <t xml:space="preserve">3.51459765434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5738217830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6200909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42391014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.42391037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33137226104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20181822776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26474452018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10187792778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.14999747276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20181846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2647442817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10187745094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">2.98342895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3410,16 +3410,16 @@
     <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81130790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8649799823761</t>
+    <t xml:space="preserve">2.81130766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86497974395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503872871399</t>
+    <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3443,22 +3443,22 @@
     <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82426333427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83721852302551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76318788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772395133972</t>
+    <t xml:space="preserve">2.82426309585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83721828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.763188123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">2.52999210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49852895736694</t>
+    <t xml:space="preserve">2.49852919578552</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515622138977</t>
+    <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">2.47817063331604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45596146583557</t>
+    <t xml:space="preserve">2.45596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">2.48927521705627</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27273607254028</t>
+    <t xml:space="preserve">2.2727358341217</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41339373588562</t>
+    <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676671028137</t>
@@ -3557,22 +3557,22 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607919692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276520729065</t>
+    <t xml:space="preserve">2.25607895851135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.182049036026</t>
+    <t xml:space="preserve">2.18204879760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
@@ -3581,31 +3581,31 @@
     <t xml:space="preserve">2.2912437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24867630004883</t>
+    <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
     <t xml:space="preserve">2.21351170539856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13022756576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15798854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14873480796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11727213859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08765983581543</t>
+    <t xml:space="preserve">2.1302273273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15798878669739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14873504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.117271900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08765959739685</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688444137573</t>
+    <t xml:space="preserve">2.14688420295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434608459473</t>
+    <t xml:space="preserve">2.05434632301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912250518799</t>
+    <t xml:space="preserve">2.11912274360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652564048767</t>
@@ -3638,28 +3638,28 @@
     <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810627937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186671257019</t>
+    <t xml:space="preserve">1.95810651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132355690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638417720795</t>
+    <t xml:space="preserve">1.90132343769073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91036570072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077330589294</t>
+    <t xml:space="preserve">1.91036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953665733337</t>
@@ -3671,13 +3671,13 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679899692535</t>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556932449341</t>
+    <t xml:space="preserve">1.8955694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79199540615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85857880115509</t>
+    <t xml:space="preserve">1.79199552536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">1.95311069488525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.958864569664</t>
+    <t xml:space="preserve">1.95886468887329</t>
   </si>
   <si>
     <t xml:space="preserve">2.00078773498535</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">1.98023724555969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03942251205444</t>
+    <t xml:space="preserve">2.03942227363586</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559084892273</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">2.07970118522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0048975944519</t>
+    <t xml:space="preserve">2.00489735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.99749958515167</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2420494556427</t>
+    <t xml:space="preserve">2.24204921722412</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">2.14135241508484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573763847351</t>
+    <t xml:space="preserve">2.15573740005493</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">2.28520512580872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34480118751526</t>
+    <t xml:space="preserve">2.34480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">2.2728750705719</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30781054496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34685659408569</t>
+    <t xml:space="preserve">2.30781030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34685635566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.35096621513367</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821424484253</t>
+    <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
     <t xml:space="preserve">2.25848960876465</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21944379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24615955352783</t>
+    <t xml:space="preserve">2.14546227455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21944403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24615931510925</t>
   </si>
   <si>
     <t xml:space="preserve">2.26670980453491</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">2.25437951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30986547470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35507655143738</t>
+    <t xml:space="preserve">2.30986571311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3550763130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.41056251525879</t>
@@ -3845,34 +3845,34 @@
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52769994735718</t>
+    <t xml:space="preserve">2.54619550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52770018577576</t>
   </si>
   <si>
     <t xml:space="preserve">2.55236029624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53797507286072</t>
+    <t xml:space="preserve">2.5379753112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.54003024101257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45988368988037</t>
+    <t xml:space="preserve">2.45988345146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153491973877</t>
+    <t xml:space="preserve">2.52153468132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51125955581665</t>
+    <t xml:space="preserve">2.51125979423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
@@ -3917,10 +3917,10 @@
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250708580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66744256019592</t>
+    <t xml:space="preserve">2.63250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674427986145</t>
   </si>
   <si>
     <t xml:space="preserve">2.67155265808105</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">2.7414243221283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70443320274353</t>
+    <t xml:space="preserve">2.70443344116211</t>
   </si>
   <si>
     <t xml:space="preserve">2.72498393058777</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78868985176086</t>
+    <t xml:space="preserve">2.78869009017944</t>
   </si>
   <si>
     <t xml:space="preserve">2.77019476890564</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62634181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648860931396</t>
+    <t xml:space="preserve">2.60784649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6263415813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524107933044</t>
+    <t xml:space="preserve">2.58524084091187</t>
   </si>
   <si>
     <t xml:space="preserve">2.58935141563416</t>
@@ -4013,10 +4013,10 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048787117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97158861160278</t>
+    <t xml:space="preserve">2.93048810958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97158885002136</t>
   </si>
   <si>
     <t xml:space="preserve">2.91404747962952</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035929679871</t>
+    <t xml:space="preserve">3.00035953521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.99419403076172</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773590087891</t>
+    <t xml:space="preserve">2.82773566246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.74553418159485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61606645584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68388295173645</t>
+    <t xml:space="preserve">2.61606669425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">2.84212112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77224969863892</t>
+    <t xml:space="preserve">2.7722499370575</t>
   </si>
   <si>
     <t xml:space="preserve">2.78457975387573</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89555215835571</t>
+    <t xml:space="preserve">2.89555239677429</t>
   </si>
   <si>
     <t xml:space="preserve">3.10927653312683</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.9633686542511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93665313720703</t>
+    <t xml:space="preserve">2.93665289878845</t>
   </si>
   <si>
     <t xml:space="preserve">2.89966225624084</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034108161926</t>
+    <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
     <t xml:space="preserve">2.86883687973022</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">2.9818639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0126895904541</t>
+    <t xml:space="preserve">3.01268935203552</t>
   </si>
   <si>
     <t xml:space="preserve">2.94281816482544</t>
@@ -5592,6 +5592,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.10200023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11999988555908</t>
   </si>
 </sst>
 </file>
@@ -70826,7 +70829,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6496296296</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>506423</v>
@@ -70847,6 +70850,32 @@
         <v>1859</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910069444</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>225372</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>4.10400009155273</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>4.11600017547607</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="1860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="1861">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356538772583</t>
+    <t xml:space="preserve">12.2356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">12.1956901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7027988433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097309112549</t>
+    <t xml:space="preserve">11.7028007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895681381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097318649292</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101800918579</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">11.0766973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.136643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302545547485</t>
+    <t xml:space="preserve">11.1366424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302526473999</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3107213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2907390594482</t>
+    <t xml:space="preserve">10.3107204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2907381057739</t>
   </si>
   <si>
     <t xml:space="preserve">9.65797424316406</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7370042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3906478881836</t>
+    <t xml:space="preserve">10.737003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
     <t xml:space="preserve">10.4239511489868</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2574348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2707567214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4838962554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2973985671997</t>
+    <t xml:space="preserve">10.257435798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2707557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4838981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
     <t xml:space="preserve">10.1042394638062</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.77786731719971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91108131408691</t>
+    <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
     <t xml:space="preserve">9.54474353790283</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.217472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639139175415</t>
+    <t xml:space="preserve">10.2174701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171112060547</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9643669128418</t>
+    <t xml:space="preserve">9.96436595916748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">11.3431253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6495151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0624771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2289934158325</t>
+    <t xml:space="preserve">11.6495141983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0624761581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2289943695068</t>
   </si>
   <si>
     <t xml:space="preserve">12.4754390716553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4554567337036</t>
+    <t xml:space="preserve">12.4554586410522</t>
   </si>
   <si>
     <t xml:space="preserve">12.3422260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4621181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823701858521</t>
+    <t xml:space="preserve">12.4621171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019906997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823692321777</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961402893066</t>
@@ -206,64 +206,64 @@
     <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.075798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.915940284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1890287399292</t>
+    <t xml:space="preserve">12.0757970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9159421920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1890277862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0633773803711</t>
+    <t xml:space="preserve">11.0633754730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.6561756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9559049606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.921703338623</t>
+    <t xml:space="preserve">11.9559087753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2689580917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217023849487</t>
   </si>
   <si>
     <t xml:space="preserve">12.9350252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
+    <t xml:space="preserve">13.1015434265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480754852295</t>
   </si>
   <si>
     <t xml:space="preserve">13.1947908401489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.181468963623</t>
+    <t xml:space="preserve">13.1814708709717</t>
   </si>
   <si>
     <t xml:space="preserve">13.16148853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.361307144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946113586426</t>
+    <t xml:space="preserve">13.3613090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
@@ -275,52 +275,52 @@
     <t xml:space="preserve">12.6885786056519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8817405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884010314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482587814331</t>
+    <t xml:space="preserve">12.5620288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482559204102</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488874435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.721884727478</t>
+    <t xml:space="preserve">12.3755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7218837738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.7685089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9150428771973</t>
+    <t xml:space="preserve">12.9150438308716</t>
   </si>
   <si>
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.134407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159883499146</t>
+    <t xml:space="preserve">13.1344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">13.6230983734131</t>
@@ -329,67 +329,67 @@
     <t xml:space="preserve">13.5226821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5561542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0741586685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9938249588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017683029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2749900817871</t>
+    <t xml:space="preserve">13.5561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620157241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3553228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2749881744385</t>
   </si>
   <si>
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6591053009033</t>
+    <t xml:space="preserve">12.6591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">12.0833864212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8156099319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766935348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524105072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487064361572</t>
+    <t xml:space="preserve">11.8156108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7218894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524095535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487054824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834260940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177295684814</t>
+    <t xml:space="preserve">10.4834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177305221558</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4164819717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0482892990112</t>
+    <t xml:space="preserve">10.4164810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
     <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7445068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1193943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4741954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599763870239</t>
+    <t xml:space="preserve">10.7445058822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1193933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.474196434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599754333496</t>
   </si>
   <si>
     <t xml:space="preserve">11.126088142395</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">11.0189762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.811450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9252557754517</t>
+    <t xml:space="preserve">11.0122842788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8114500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9252548217773</t>
   </si>
   <si>
     <t xml:space="preserve">10.8783950805664</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">10.7645902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0616779327393</t>
+    <t xml:space="preserve">10.0616788864136</t>
   </si>
   <si>
     <t xml:space="preserve">10.1754837036133</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06421279907227</t>
+    <t xml:space="preserve">9.06421375274658</t>
   </si>
   <si>
     <t xml:space="preserve">8.93032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313110351562</t>
@@ -473,25 +473,25 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37215614318848</t>
+    <t xml:space="preserve">9.20479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37215518951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23826789855957</t>
+    <t xml:space="preserve">9.33868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23826885223389</t>
   </si>
   <si>
     <t xml:space="preserve">9.31860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115692138672</t>
+    <t xml:space="preserve">9.13115882873535</t>
   </si>
   <si>
     <t xml:space="preserve">9.37884998321533</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">9.63323783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43910026550293</t>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51273822784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43909931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.56629371643066</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">9.49265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53951549530029</t>
+    <t xml:space="preserve">9.53951644897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.8273754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76043033599854</t>
+    <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
     <t xml:space="preserve">9.78720855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87423610687256</t>
+    <t xml:space="preserve">9.87423419952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.6734037399292</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
+    <t xml:space="preserve">9.07090759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08429527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31190586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207366943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.36546039581299</t>
@@ -572,22 +572,22 @@
     <t xml:space="preserve">9.24496173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03743457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72280025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007617950439</t>
+    <t xml:space="preserve">9.03743553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72279930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007522583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957656860352</t>
+    <t xml:space="preserve">8.74957752227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304862976074</t>
@@ -596,52 +596,52 @@
     <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71610450744629</t>
+    <t xml:space="preserve">8.71610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">8.66924381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33452320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2006368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1002197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1203031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227781295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82575035095215</t>
+    <t xml:space="preserve">8.33452415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20063591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12030410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82575082778931</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583377838135</t>
+    <t xml:space="preserve">7.86591577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583282470703</t>
   </si>
   <si>
     <t xml:space="preserve">7.6316123008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62491750717163</t>
+    <t xml:space="preserve">7.62491798400879</t>
   </si>
   <si>
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194553375244</t>
+    <t xml:space="preserve">7.74541759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7119460105896</t>
   </si>
   <si>
     <t xml:space="preserve">7.69186162948608</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">7.48433542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95963764190674</t>
+    <t xml:space="preserve">7.64500188827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963907241821</t>
   </si>
   <si>
     <t xml:space="preserve">8.12699794769287</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9236307144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963598251343</t>
+    <t xml:space="preserve">8.92363166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21149063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99635887146</t>
   </si>
   <si>
     <t xml:space="preserve">12.1168594360352</t>
@@ -686,40 +686,40 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499134063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967363357544</t>
+    <t xml:space="preserve">11.8691663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569856643677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975667953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235145568848</t>
+    <t xml:space="preserve">13.8975687026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235126495361</t>
   </si>
   <si>
     <t xml:space="preserve">13.8908739089966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.957818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904567718506</t>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904577255249</t>
   </si>
   <si>
     <t xml:space="preserve">14.6004800796509</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">14.0180673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0582332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712066650391</t>
+    <t xml:space="preserve">14.0582342147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712057113647</t>
   </si>
   <si>
     <t xml:space="preserve">14.0917053222656</t>
@@ -740,91 +740,91 @@
     <t xml:space="preserve">14.3126201629639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2858438491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1385669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557371139526</t>
+    <t xml:space="preserve">14.2858428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1385660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557390213013</t>
   </si>
   <si>
     <t xml:space="preserve">13.2415180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544904708862</t>
+    <t xml:space="preserve">13.1544895172119</t>
   </si>
   <si>
     <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.208044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268808364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264656066895</t>
+    <t xml:space="preserve">13.2080430984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528257369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264646530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611852645874</t>
+    <t xml:space="preserve">12.9067974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611862182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.0540733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9134931564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2147388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812696456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599367141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0473804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0206031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.920184135437</t>
+    <t xml:space="preserve">12.9134922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339908599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.859935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.007212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0473794937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0206022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201850891113</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934097290039</t>
@@ -839,46 +839,46 @@
     <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1745719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406866073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8666305541992</t>
+    <t xml:space="preserve">13.1745729446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406837463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8666315078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8867130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8398523330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536590576172</t>
+    <t xml:space="preserve">12.933575630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8398532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8197708129883</t>
+    <t xml:space="preserve">12.8197689056396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386056900024</t>
+    <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
     <t xml:space="preserve">12.3109951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3310804367065</t>
+    <t xml:space="preserve">12.3310794830322</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6750297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624715805054</t>
+    <t xml:space="preserve">11.67502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624696731567</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771078109741</t>
@@ -902,37 +902,37 @@
     <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862997055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800191879272</t>
+    <t xml:space="preserve">12.7862977981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.946964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637201309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3043012619019</t>
+    <t xml:space="preserve">12.5653848648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637182235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3043022155762</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586891174316</t>
+    <t xml:space="preserve">12.558687210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.4649667739868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6189393997192</t>
+    <t xml:space="preserve">12.6189384460449</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971921920776</t>
+    <t xml:space="preserve">12.1971912384033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1034698486328</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.672492980957</t>
+    <t xml:space="preserve">12.6724948883057</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176908493042</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">11.8089151382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030527114868</t>
+    <t xml:space="preserve">12.0030536651611</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813055038452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6147785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5076684951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6549444198608</t>
+    <t xml:space="preserve">11.6147775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5076694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6549453735352</t>
   </si>
   <si>
     <t xml:space="preserve">11.5880012512207</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5210561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151947021484</t>
+    <t xml:space="preserve">11.6817216873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5210571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151937484741</t>
   </si>
   <si>
     <t xml:space="preserve">11.661639213562</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7018051147461</t>
+    <t xml:space="preserve">11.7018060684204</t>
   </si>
   <si>
     <t xml:space="preserve">11.4474201202393</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7980613708496</t>
+    <t xml:space="preserve">10.7980623245239</t>
   </si>
   <si>
     <t xml:space="preserve">10.9453392028809</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0658388137817</t>
+    <t xml:space="preserve">11.1461706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0658397674561</t>
   </si>
   <si>
     <t xml:space="preserve">11.1327819824219</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">11.0993099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.199725151062</t>
+    <t xml:space="preserve">11.1997261047363</t>
   </si>
   <si>
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112699508667</t>
+    <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206409454346</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">11.2198095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.300142288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4608087539673</t>
+    <t xml:space="preserve">11.3001413345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4005575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541130065918</t>
@@ -1094,37 +1094,37 @@
     <t xml:space="preserve">11.3336133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1595592498779</t>
+    <t xml:space="preserve">11.3536958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1595602035522</t>
   </si>
   <si>
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5302867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3897047042847</t>
+    <t xml:space="preserve">10.9721155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3897037506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3093709945679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1620950698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2156505584717</t>
+    <t xml:space="preserve">10.1620941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2156496047974</t>
   </si>
   <si>
     <t xml:space="preserve">10.3361482620239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490119934082</t>
+    <t xml:space="preserve">10.4901208877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
@@ -1133,25 +1133,25 @@
     <t xml:space="preserve">10.3428440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3562316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84076404571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80059814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80729103088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68679237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71356964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72026538848877</t>
+    <t xml:space="preserve">10.3562326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80059719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80729007720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68679332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7135705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704265594482</t>
@@ -1160,37 +1160,37 @@
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70018100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5235929489136</t>
+    <t xml:space="preserve">9.75373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70018196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650785446167</t>
+    <t xml:space="preserve">10.6507863998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708688735962</t>
+    <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1888723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2758989334106</t>
+    <t xml:space="preserve">10.3763151168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2759008407593</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.316065788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2089548110962</t>
+    <t xml:space="preserve">10.3160648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2089567184448</t>
   </si>
   <si>
     <t xml:space="preserve">9.6533203125</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">9.52612590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62654304504395</t>
+    <t xml:space="preserve">9.62654209136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8474588394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959833145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7712841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5972299575806</t>
+    <t xml:space="preserve">9.84745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5436744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7712850570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5972290039062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8583116531372</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">10.9654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9988946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0926151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1796436309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2465858459473</t>
+    <t xml:space="preserve">11.0725326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9988956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0926160812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1796426773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
     <t xml:space="preserve">11.0859212875366</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.9118661880493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051742553711</t>
+    <t xml:space="preserve">10.9051733016968</t>
   </si>
   <si>
     <t xml:space="preserve">10.8917837142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7512006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0390596389771</t>
+    <t xml:space="preserve">10.7512016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
     <t xml:space="preserve">10.7277708053589</t>
@@ -1307,25 +1307,25 @@
     <t xml:space="preserve">10.5871887207031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2892875671387</t>
+    <t xml:space="preserve">10.289288520813</t>
   </si>
   <si>
     <t xml:space="preserve">10.2658567428589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3696203231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135507583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.620659828186</t>
+    <t xml:space="preserve">10.3696212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
     <t xml:space="preserve">10.8616590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6407432556152</t>
+    <t xml:space="preserve">10.6407442092896</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106185913086</t>
@@ -1337,40 +1337,40 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6240072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4097871780396</t>
+    <t xml:space="preserve">10.533634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6240081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4097881317139</t>
   </si>
   <si>
     <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9821586608887</t>
+    <t xml:space="preserve">10.982159614563</t>
   </si>
   <si>
     <t xml:space="preserve">10.5269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261070251465</t>
+    <t xml:space="preserve">10.3261079788208</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3629274368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1520519256592</t>
+    <t xml:space="preserve">10.3394947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3629264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1520528793335</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
@@ -1382,25 +1382,25 @@
     <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0349016189575</t>
+    <t xml:space="preserve">10.0349006652832</t>
   </si>
   <si>
     <t xml:space="preserve">10.0951509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9788112640381</t>
+    <t xml:space="preserve">10.9788103103638</t>
   </si>
   <si>
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357141494751</t>
+    <t xml:space="preserve">11.0357131958008</t>
   </si>
   <si>
     <t xml:space="preserve">11.1762962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8717002868652</t>
+    <t xml:space="preserve">10.8717012405396</t>
   </si>
   <si>
     <t xml:space="preserve">10.868353843689</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.952033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0290203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0758800506592</t>
+    <t xml:space="preserve">10.9520330429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0290193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0758790969849</t>
   </si>
   <si>
     <t xml:space="preserve">11.28675365448</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352970123291</t>
+    <t xml:space="preserve">10.9352960586548</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
@@ -1448,43 +1448,43 @@
     <t xml:space="preserve">10.1721353530884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2457733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0683727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74369430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34537792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6700553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72695922851562</t>
+    <t xml:space="preserve">10.2457752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0683736801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74369525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34537887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67005634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72695827484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48596000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58637714385986</t>
+    <t xml:space="preserve">9.57633399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54286289215088</t>
+    <t xml:space="preserve">9.54286193847656</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298851013184</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49600219726562</t>
+    <t xml:space="preserve">9.49600315093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.62319564819336</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7294921875</t>
+    <t xml:space="preserve">8.68932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949314117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.89350605010986</t>
@@ -1529,19 +1529,19 @@
     <t xml:space="preserve">9.30186462402344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21483707427979</t>
+    <t xml:space="preserve">9.22487926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.13785171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45583438873291</t>
+    <t xml:space="preserve">9.45583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
@@ -1550,28 +1550,28 @@
     <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61315441131592</t>
+    <t xml:space="preserve">9.6131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46922397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37550258636475</t>
+    <t xml:space="preserve">9.46922492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31525421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7328405380249</t>
+    <t xml:space="preserve">9.31525325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26504611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73284149169922</t>
   </si>
   <si>
     <t xml:space="preserve">8.80647945404053</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0206995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85334014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86003398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92028427124023</t>
+    <t xml:space="preserve">9.02070045471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86003494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92028331756592</t>
   </si>
   <si>
     <t xml:space="preserve">8.88011741638184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82656383514404</t>
+    <t xml:space="preserve">8.82656192779541</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27427387237549</t>
+    <t xml:space="preserve">8.2742748260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25084400177002</t>
+    <t xml:space="preserve">8.2508430480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870391845703</t>
+    <t xml:space="preserve">8.47175788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
     <t xml:space="preserve">8.78639602661133</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00731182098389</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00061511993408</t>
+    <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735210418701</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408908843994</t>
+    <t xml:space="preserve">9.03408813476562</t>
   </si>
   <si>
     <t xml:space="preserve">8.66589736938477</t>
@@ -1682,52 +1682,52 @@
     <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84999179840088</t>
+    <t xml:space="preserve">8.84999370574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47510623931885</t>
+    <t xml:space="preserve">8.47510719299316</t>
   </si>
   <si>
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75292491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90689563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30855751037598</t>
+    <t xml:space="preserve">8.62907791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75292301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90689468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29516983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111473083496</t>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111568450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.294358253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31109428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34456634521484</t>
+    <t xml:space="preserve">8.29435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3110933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34456539154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.32448387145996</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">9.19810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">8.56548118591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5018835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75627040863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82321453094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84329795837402</t>
+    <t xml:space="preserve">8.50188446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82321548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84329891204834</t>
   </si>
   <si>
     <t xml:space="preserve">8.74622917175293</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29851818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44914150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91105461120605</t>
+    <t xml:space="preserve">9.42236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29851722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44914054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91105556488037</t>
   </si>
   <si>
     <t xml:space="preserve">9.8441104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52277946472168</t>
+    <t xml:space="preserve">9.522780418396</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">9.4424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41901588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.41901683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456790924072</t>
@@ -1817,13 +1817,13 @@
     <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35876655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54874515533447</t>
+    <t xml:space="preserve">9.35876750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27174091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54874610900879</t>
   </si>
   <si>
     <t xml:space="preserve">8.71275806427002</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">9.52947425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51943302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42905807495117</t>
+    <t xml:space="preserve">9.51943206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42905902862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.36211395263672</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625247955322</t>
+    <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.42571067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789295196533</t>
+    <t xml:space="preserve">9.1512393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128253936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789390563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.43240451812744</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24161529541016</t>
+    <t xml:space="preserve">9.33533668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.14454555511475</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73030567169189</t>
+    <t xml:space="preserve">9.73030662536621</t>
   </si>
   <si>
     <t xml:space="preserve">9.69013977050781</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79724979400635</t>
+    <t xml:space="preserve">9.79725074768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.92109680175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90770816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92779064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77716541290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71022319793701</t>
+    <t xml:space="preserve">9.90770721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92779159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77716636657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.62988948822021</t>
@@ -1925,28 +1925,28 @@
     <t xml:space="preserve">9.38889217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500297546387</t>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500392913818</t>
   </si>
   <si>
     <t xml:space="preserve">8.76296615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76631259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62572956085205</t>
+    <t xml:space="preserve">8.76631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62573051452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77300643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961875915527</t>
+    <t xml:space="preserve">8.7730073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404689788818</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">9.4056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63993263244629</t>
+    <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53282165527344</t>
+    <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
     <t xml:space="preserve">9.60311317443848</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20144844055176</t>
+    <t xml:space="preserve">9.20144748687744</t>
   </si>
   <si>
     <t xml:space="preserve">9.10103321075439</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94371318817139</t>
+    <t xml:space="preserve">8.9437141418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.98053359985352</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068061828613</t>
+    <t xml:space="preserve">9.81063938140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.30521202087402</t>
@@ -2036,40 +2036,40 @@
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764457702637</t>
+    <t xml:space="preserve">9.08764362335205</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09099006652832</t>
+    <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
     <t xml:space="preserve">8.88346576690674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65250778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681221008301</t>
+    <t xml:space="preserve">8.74288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79308986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65250873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681125640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05417156219482</t>
+    <t xml:space="preserve">9.05417060852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.060866355896</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">9.15458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9671459197998</t>
+    <t xml:space="preserve">8.97383785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0809497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020179748535</t>
+    <t xml:space="preserve">8.90020084381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">8.99726867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92697811126709</t>
+    <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
@@ -2114,25 +2114,25 @@
     <t xml:space="preserve">8.64246559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40146827697754</t>
+    <t xml:space="preserve">8.40146923065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28431701660156</t>
+    <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98976278305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0600528717041</t>
+    <t xml:space="preserve">8.15377616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9897632598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
@@ -2141,55 +2141,55 @@
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95629024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93286085128784</t>
+    <t xml:space="preserve">7.94624900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95629119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96633291244507</t>
+    <t xml:space="preserve">7.96633148193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67177867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12953186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2232551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300487518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222414016724</t>
+    <t xml:space="preserve">7.9429030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6717791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12953281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22325468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300439834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514638900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222461700439</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256681442261</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">6.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55802345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45091247558594</t>
+    <t xml:space="preserve">5.55802297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57978010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2213,55 +2213,55 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05929088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183771133423</t>
+    <t xml:space="preserve">4.74800157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05929040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183723449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98311758041382</t>
+    <t xml:space="preserve">5.69693183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98311805725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.05842971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29440689086914</t>
+    <t xml:space="preserve">6.23917722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29440641403198</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.647536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
+    <t xml:space="preserve">6.49356460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6174111366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5303840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64753723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
     <t xml:space="preserve">6.4266209602356</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09190130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03834676742554</t>
+    <t xml:space="preserve">6.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03834629058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.17892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85759735107422</t>
+    <t xml:space="preserve">5.85759687423706</t>
   </si>
   <si>
     <t xml:space="preserve">6.00487422943115</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">6.20235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25926113128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32620525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628820419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28603935241699</t>
+    <t xml:space="preserve">6.25926160812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32620477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
     <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08520650863647</t>
+    <t xml:space="preserve">6.01826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156806945801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89776420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813724517822</t>
+    <t xml:space="preserve">5.89776372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508184432983</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82747220993042</t>
+    <t xml:space="preserve">5.82747268676758</t>
   </si>
   <si>
     <t xml:space="preserve">5.68354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66011238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0843939781189</t>
+    <t xml:space="preserve">5.66011190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08439445495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2351,34 +2351,34 @@
     <t xml:space="preserve">5.17142200469971</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18815803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34212875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15803289413452</t>
+    <t xml:space="preserve">5.18815755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34212923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15803241729736</t>
   </si>
   <si>
     <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37225341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74379253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044513702393</t>
+    <t xml:space="preserve">5.37225294113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74379301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044466018677</t>
   </si>
   <si>
     <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94127702713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82077741622925</t>
+    <t xml:space="preserve">5.94127798080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82077789306641</t>
   </si>
   <si>
     <t xml:space="preserve">5.60655736923218</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20824098587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1981987953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29861497879028</t>
+    <t xml:space="preserve">5.2082405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19819927215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29861450195312</t>
   </si>
   <si>
     <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30196285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23836517333984</t>
+    <t xml:space="preserve">5.30196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.238365650177</t>
   </si>
   <si>
     <t xml:space="preserve">5.33208703994751</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">5.23167133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3253927230835</t>
+    <t xml:space="preserve">5.35886526107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204580307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32539319992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">5.2283239364624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04422807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97058963775635</t>
+    <t xml:space="preserve">5.04422760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97058916091919</t>
   </si>
   <si>
     <t xml:space="preserve">4.94046497344971</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104753494263</t>
+    <t xml:space="preserve">5.08104705810547</t>
   </si>
   <si>
     <t xml:space="preserve">5.13125514984131</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790822982788</t>
+    <t xml:space="preserve">5.12790775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
@@ -2468,25 +2468,25 @@
     <t xml:space="preserve">4.98063182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1044774055481</t>
+    <t xml:space="preserve">5.10447835922241</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96389532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41576766967773</t>
+    <t xml:space="preserve">4.96389579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41576719284058</t>
   </si>
   <si>
     <t xml:space="preserve">5.38898992538452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48940563201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36890697479248</t>
+    <t xml:space="preserve">5.48940515518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961277008057</t>
+    <t xml:space="preserve">5.53961324691772</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568424224854</t>
+    <t xml:space="preserve">5.39568471908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221218109131</t>
@@ -2525,34 +2525,34 @@
     <t xml:space="preserve">5.09108877182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60321044921875</t>
+    <t xml:space="preserve">5.60320997238159</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215063095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244215011597</t>
+    <t xml:space="preserve">6.15215110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2793436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244167327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70697259902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89441633224487</t>
+    <t xml:space="preserve">6.14880418777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524774551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7069730758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375082015991</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48605823516846</t>
+    <t xml:space="preserve">5.4860577583313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65341758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040437698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.52287721633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65341806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5563497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46262788772583</t>
+    <t xml:space="preserve">5.55634927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46262741088867</t>
   </si>
   <si>
     <t xml:space="preserve">5.47266960144043</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">5.50948810577393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258712768555</t>
+    <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894773483276</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95385408401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88021516799927</t>
+    <t xml:space="preserve">4.92372894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95385360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88021564483643</t>
   </si>
   <si>
     <t xml:space="preserve">4.94381237030029</t>
@@ -2633,109 +2633,109 @@
     <t xml:space="preserve">5.55300235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86094427108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02830457687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09859609603882</t>
+    <t xml:space="preserve">5.8609447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02830410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09859561920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.44335651397705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59398126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80820226669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63749504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5872859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72117471694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41323280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
+    <t xml:space="preserve">6.59398174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80820178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63749408721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58728647232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72117376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766141891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41323232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.7613410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275554656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383581161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936548233032</t>
+    <t xml:space="preserve">7.10275459289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283849716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0893669128418</t>
   </si>
   <si>
     <t xml:space="preserve">6.97556209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2098650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961576461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05589389801025</t>
+    <t xml:space="preserve">7.20986557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589532852173</t>
   </si>
   <si>
     <t xml:space="preserve">7.00233888626099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86175727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0692834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10944890975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07597684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98225545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14292192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606170654297</t>
+    <t xml:space="preserve">6.86175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06928300857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10944986343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98225593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606122970581</t>
   </si>
   <si>
     <t xml:space="preserve">6.92200660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96886777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90192365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11614465713501</t>
+    <t xml:space="preserve">6.9688663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90192270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11614370346069</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572799682617</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267164230347</t>
+    <t xml:space="preserve">7.03581047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267211914062</t>
   </si>
   <si>
     <t xml:space="preserve">7.13622665405273</t>
@@ -2759,55 +2759,55 @@
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25003147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011442184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366943359375</t>
+    <t xml:space="preserve">7.25003242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
     <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47764110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4106969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39061498641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47094631195068</t>
+    <t xml:space="preserve">7.47764158248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41069746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.470947265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.56466865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5111141204834</t>
+    <t xml:space="preserve">7.51111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.53789138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6115288734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61822414398193</t>
+    <t xml:space="preserve">7.61152982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61822462081909</t>
   </si>
   <si>
     <t xml:space="preserve">7.75880575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8525276184082</t>
+    <t xml:space="preserve">7.85252714157104</t>
   </si>
   <si>
     <t xml:space="preserve">8.07344245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32113647460938</t>
+    <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.1805534362793</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89685249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91693592071533</t>
+    <t xml:space="preserve">8.89685440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.48849582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7361888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41485691070557</t>
+    <t xml:space="preserve">8.73618793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724632263184</t>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758098602295</t>
+    <t xml:space="preserve">8.26758003234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.32782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8123607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938879013062</t>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938831329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980354309082</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">8.97049140930176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68009853363037</t>
+    <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
     <t xml:space="preserve">9.55290508270264</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9947338104248</t>
+    <t xml:space="preserve">9.99473571777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126365661621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9411792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0081233978271</t>
+    <t xml:space="preserve">9.94117832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0081224441528</t>
   </si>
   <si>
     <t xml:space="preserve">10.0282068252563</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">9.77381992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7336540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168962478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4767303466797</t>
+    <t xml:space="preserve">9.73365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039247512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476731300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.677562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.84605503082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3346557617188</t>
+    <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
     <t xml:space="preserve">10.186595916748</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90528011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63876914978027</t>
+    <t xml:space="preserve">9.9052791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59435176849365</t>
+    <t xml:space="preserve">9.59435081481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.43888759613037</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">9.57954502105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578411102295</t>
+    <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83865165710449</t>
+    <t xml:space="preserve">9.79423332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83865261077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7572193145752</t>
+    <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533399581909</t>
+    <t xml:space="preserve">10.0533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">9.4018726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927600860596</t>
+    <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
     <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26121520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14276599884033</t>
+    <t xml:space="preserve">9.26121425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14276504516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.10575008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655437469482</t>
+    <t xml:space="preserve">8.99655532836914</t>
   </si>
   <si>
     <t xml:space="preserve">9.34634971618652</t>
@@ -3056,40 +3056,40 @@
     <t xml:space="preserve">9.17237758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24640846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20199108123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17978000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1131534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23160266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01691341400146</t>
+    <t xml:space="preserve">9.2464075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20199012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17978096008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11315250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23160171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01691436767578</t>
   </si>
   <si>
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3130350112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35745334625244</t>
+    <t xml:space="preserve">9.15757179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31303596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35745429992676</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016746520996</t>
+    <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.03171920776367</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834671020508</t>
+    <t xml:space="preserve">9.09834766387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.668381690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32784175872803</t>
+    <t xml:space="preserve">9.32784271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.46109676361084</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">9.52772426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75040435791016</t>
+    <t xml:space="preserve">8.86885166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33078336715698</t>
+    <t xml:space="preserve">8.77261257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33078384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58989000320435</t>
+    <t xml:space="preserve">4.5898904800415</t>
   </si>
   <si>
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723463058472</t>
+    <t xml:space="preserve">4.69723415374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.5824875831604</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128879547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090085983276</t>
+    <t xml:space="preserve">4.10128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090133666992</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1938271522522</t>
+    <t xml:space="preserve">4.19382667541504</t>
   </si>
   <si>
     <t xml:space="preserve">4.16791677474976</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12719964981079</t>
+    <t xml:space="preserve">4.12720012664795</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018421173096</t>
+    <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233510971069</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36039590835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15311098098755</t>
+    <t xml:space="preserve">4.39741086959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36039543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
     <t xml:space="preserve">4.10499095916748</t>
@@ -3239,28 +3239,28 @@
     <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17902135848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93842196464539</t>
+    <t xml:space="preserve">4.17902088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687046051025</t>
+    <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58862805366516</t>
+    <t xml:space="preserve">4.04576683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.07537889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206466674805</t>
+    <t xml:space="preserve">4.04206418991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94952702522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510821342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433258056641</t>
+    <t xml:space="preserve">3.94952654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433281898499</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95322823524475</t>
+    <t xml:space="preserve">3.95322799682617</t>
   </si>
   <si>
     <t xml:space="preserve">4.05316925048828</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660049438477</t>
+    <t xml:space="preserve">4.01985549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660097122192</t>
   </si>
   <si>
     <t xml:space="preserve">3.86439180374146</t>
@@ -3323,46 +3323,46 @@
     <t xml:space="preserve">3.50164246559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53310537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716490745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52014994621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48313450813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51459717750549</t>
+    <t xml:space="preserve">3.53310513496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52015018463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48313474655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51459765434265</t>
   </si>
   <si>
     <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62009072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70152425765991</t>
+    <t xml:space="preserve">3.6200909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137178421021</t>
+    <t xml:space="preserve">3.33137226104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358119010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1092803478241</t>
+    <t xml:space="preserve">3.35358095169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10928058624268</t>
   </si>
   <si>
     <t xml:space="preserve">3.24623703956604</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10187768936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.10187745094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">3.007488489151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98342871665955</t>
+    <t xml:space="preserve">2.98342895507812</t>
   </si>
   <si>
     <t xml:space="preserve">2.93345808982849</t>
@@ -3404,25 +3404,25 @@
     <t xml:space="preserve">2.93530893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8723828792572</t>
+    <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8649799823761</t>
+    <t xml:space="preserve">2.86497974395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503872871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90569686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86868166923523</t>
+    <t xml:space="preserve">2.76503896713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90569663047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86868143081665</t>
   </si>
   <si>
     <t xml:space="preserve">2.92420434951782</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85387563705444</t>
+    <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
     <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059125900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82426333427429</t>
+    <t xml:space="preserve">2.77059102058411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82426309585571</t>
   </si>
   <si>
     <t xml:space="preserve">2.83721852302551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76318788528442</t>
+    <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60772395133972</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">2.52999186515808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49852871894836</t>
+    <t xml:space="preserve">2.49852895736694</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61512732505798</t>
+    <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
     <t xml:space="preserve">2.57811188697815</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44855809211731</t>
+    <t xml:space="preserve">2.44855833053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.47446918487549</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">2.48927521705627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52629065513611</t>
+    <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742437362671</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">2.25792980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34861731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41339373588562</t>
+    <t xml:space="preserve">2.34861707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676671028137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790066719055</t>
+    <t xml:space="preserve">2.30790042877197</t>
   </si>
   <si>
     <t xml:space="preserve">2.19685482978821</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18760108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29679608345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28569149971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30234837532043</t>
+    <t xml:space="preserve">2.18760085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29679584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2856912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30234813690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35416984558105</t>
@@ -3542,19 +3542,19 @@
     <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25422835350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26718401908875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28754186630249</t>
+    <t xml:space="preserve">2.25422859191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26718378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28754210472107</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276544570923</t>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">2.18204879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26533317565918</t>
+    <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
     <t xml:space="preserve">2.2912437915802</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
+    <t xml:space="preserve">2.08765959739685</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688420295715</t>
+    <t xml:space="preserve">2.14688444137573</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434632301331</t>
+    <t xml:space="preserve">2.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912250518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652587890625</t>
+    <t xml:space="preserve">2.11912274360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652564048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.07285380363464</t>
@@ -3635,28 +3635,28 @@
     <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810639858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186695098877</t>
+    <t xml:space="preserve">1.95810651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132367610931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638429641724</t>
+    <t xml:space="preserve">1.90132355690002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638417720795</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91036558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077318668365</t>
+    <t xml:space="preserve">1.91036570072174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077330589294</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953665733337</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679887771606</t>
+    <t xml:space="preserve">1.86679899692535</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8955694437027</t>
+    <t xml:space="preserve">1.89556932449341</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.770623087883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556234836578</t>
+    <t xml:space="preserve">1.77062296867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8585786819458</t>
+    <t xml:space="preserve">1.85857880115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311045646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95886468887329</t>
+    <t xml:space="preserve">1.95311069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.958864569664</t>
   </si>
   <si>
     <t xml:space="preserve">2.00078773498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03695631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03942203521729</t>
+    <t xml:space="preserve">2.03695607185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98023724555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03942251205444</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559084892273</t>
+    <t xml:space="preserve">2.07559108734131</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204897880554</t>
+    <t xml:space="preserve">2.2420494556427</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573740005493</t>
+    <t xml:space="preserve">2.14135241508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573763847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">2.30781054496765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34685635566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35096645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3427460193634</t>
+    <t xml:space="preserve">2.34685659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35096621513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34274625778198</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821448326111</t>
+    <t xml:space="preserve">2.24821424484253</t>
   </si>
   <si>
     <t xml:space="preserve">2.25848960876465</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546227455139</t>
+    <t xml:space="preserve">2.14546251296997</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944379806519</t>
@@ -3833,37 +3833,37 @@
     <t xml:space="preserve">2.30986547470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3550763130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41056227684021</t>
+    <t xml:space="preserve">2.35507655143738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41056251525879</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619550704956</t>
+    <t xml:space="preserve">2.54619526863098</t>
   </si>
   <si>
     <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55236053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5379753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54003000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45988345146179</t>
+    <t xml:space="preserve">2.55236029624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53797507286072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54003024101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45988368988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153468132019</t>
+    <t xml:space="preserve">2.52153491973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5585253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55647015571594</t>
+    <t xml:space="preserve">2.55852556228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55647039413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786423683167</t>
+    <t xml:space="preserve">2.75786447525024</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087383270264</t>
+    <t xml:space="preserve">2.72087359428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674427986145</t>
+    <t xml:space="preserve">2.63250708580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66744256019592</t>
   </si>
   <si>
     <t xml:space="preserve">2.67155265808105</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74142408370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70443344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72498369216919</t>
+    <t xml:space="preserve">2.7414243221283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70443320274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3953,25 +3953,25 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77019453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703886032104</t>
+    <t xml:space="preserve">2.78868985176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77019476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703909873962</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60784649848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6263415813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648837089539</t>
+    <t xml:space="preserve">2.6078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62634181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648860931396</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428689002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59757161140442</t>
+    <t xml:space="preserve">2.62428712844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59757137298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057915687561</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">2.58524107933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58935117721558</t>
+    <t xml:space="preserve">2.58935141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048810958862</t>
+    <t xml:space="preserve">2.93048787117004</t>
   </si>
   <si>
     <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9140477180481</t>
+    <t xml:space="preserve">2.91404747962952</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99419379234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99830436706543</t>
+    <t xml:space="preserve">3.00035929679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99419403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99830412864685</t>
   </si>
   <si>
     <t xml:space="preserve">2.89760732650757</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553442001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61606669425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68388319015503</t>
+    <t xml:space="preserve">2.82773590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553418159485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61606645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68388295173645</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896545410156</t>
+    <t xml:space="preserve">2.79896521568298</t>
   </si>
   <si>
     <t xml:space="preserve">2.7907452583313</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93459796905518</t>
+    <t xml:space="preserve">2.9345977306366</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">2.77224969863892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78457999229431</t>
+    <t xml:space="preserve">2.78457975387573</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979106903076</t>
+    <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
     <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10927629470825</t>
+    <t xml:space="preserve">3.10927653312683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034132003784</t>
+    <t xml:space="preserve">2.85034108161926</t>
   </si>
   <si>
     <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82568073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92226791381836</t>
+    <t xml:space="preserve">2.82568097114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92226767539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.88733220100403</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995559692383</t>
+    <t xml:space="preserve">3.05995535850525</t>
   </si>
   <si>
     <t xml:space="preserve">2.9818639755249</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94281792640686</t>
+    <t xml:space="preserve">2.94281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">2.92432260513306</t>
@@ -5592,6 +5592,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.11999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07399988174438</t>
   </si>
 </sst>
 </file>
@@ -70878,7 +70881,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909953704</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>325698</v>
@@ -70899,6 +70902,32 @@
         <v>1819</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6909953704</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>296084</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>4.13600015640259</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>4.06400012969971</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>4.06400012969971</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>4.07399988174438</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="1862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1863">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356557846069</t>
+    <t xml:space="preserve">12.2356548309326</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.195689201355</t>
+    <t xml:space="preserve">12.1956901550293</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
@@ -53,34 +53,34 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101800918579</t>
+    <t xml:space="preserve">11.4097299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101781845093</t>
   </si>
   <si>
     <t xml:space="preserve">11.0766973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.136643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770572662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3107194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2907390594482</t>
+    <t xml:space="preserve">11.1366424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770582199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3107204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2907381057739</t>
   </si>
   <si>
     <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507743835449</t>
+    <t xml:space="preserve">10.2507753372192</t>
   </si>
   <si>
     <t xml:space="preserve">10.7370042800903</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438432693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.257435798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2707567214966</t>
+    <t xml:space="preserve">10.4239511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2707557678223</t>
   </si>
   <si>
     <t xml:space="preserve">10.4838972091675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973985671997</t>
+    <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
     <t xml:space="preserve">10.1042394638062</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120685577393</t>
+    <t xml:space="preserve">9.54474353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4639167785645</t>
+    <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171112060547</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">10.7703075408936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9301614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96436595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4905576705933</t>
+    <t xml:space="preserve">10.9301624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96436500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
     <t xml:space="preserve">10.7236824035645</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">11.3431253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6495151519775</t>
+    <t xml:space="preserve">11.6495170593262</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0624771118164</t>
+    <t xml:space="preserve">12.0624780654907</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289934158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.475438117981</t>
+    <t xml:space="preserve">12.2289953231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4754371643066</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3422260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4621171951294</t>
+    <t xml:space="preserve">12.3422269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4621162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.5553665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823692321777</t>
+    <t xml:space="preserve">12.6019926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823711395264</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961402893066</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">11.9159421920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1890296936035</t>
+    <t xml:space="preserve">12.1890287399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">11.0633764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6561756134033</t>
+    <t xml:space="preserve">11.6561765670776</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559078216553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217935562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.921703338623</t>
+    <t xml:space="preserve">12.2689571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217042922974</t>
   </si>
   <si>
     <t xml:space="preserve">12.9350252151489</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">13.1015424728394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
+    <t xml:space="preserve">13.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480773925781</t>
   </si>
   <si>
     <t xml:space="preserve">13.1947917938232</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">13.1814699172974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1614894866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613080978394</t>
+    <t xml:space="preserve">13.16148853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3613090515137</t>
   </si>
   <si>
     <t xml:space="preserve">13.2347555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3946132659912</t>
+    <t xml:space="preserve">13.3946113586426</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9816493988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5620279312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8817415237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617563247681</t>
+    <t xml:space="preserve">12.981650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6885786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5620288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617572784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.8884000778198</t>
@@ -293,70 +293,70 @@
     <t xml:space="preserve">12.4088315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221525192261</t>
+    <t xml:space="preserve">12.3755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221515655518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7218828201294</t>
+    <t xml:space="preserve">12.7218837738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.7685089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9150438308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887929916382</t>
+    <t xml:space="preserve">12.9150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.134407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159883499146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230974197388</t>
+    <t xml:space="preserve">13.6230993270874</t>
   </si>
   <si>
     <t xml:space="preserve">13.5226821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5561532974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620166778564</t>
+    <t xml:space="preserve">13.5561542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620157241821</t>
   </si>
   <si>
     <t xml:space="preserve">13.3553218841553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0741577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9938230514526</t>
+    <t xml:space="preserve">13.0741567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749891281128</t>
+    <t xml:space="preserve">13.2749881744385</t>
   </si>
   <si>
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.659104347229</t>
+    <t xml:space="preserve">12.6591024398804</t>
   </si>
   <si>
     <t xml:space="preserve">12.0833864212036</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620544433594</t>
+    <t xml:space="preserve">11.7620553970337</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218894958496</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">12.6524095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6925754547119</t>
+    <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
     <t xml:space="preserve">12.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1411008834839</t>
+    <t xml:space="preserve">13.1410999298096</t>
   </si>
   <si>
     <t xml:space="preserve">10.8850889205933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1487064361572</t>
+    <t xml:space="preserve">10.1487054824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834260940552</t>
+    <t xml:space="preserve">10.4834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">10.7177305221558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2290391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4164819717407</t>
+    <t xml:space="preserve">10.2290382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4164810180664</t>
   </si>
   <si>
     <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4432592391968</t>
+    <t xml:space="preserve">10.4432601928711</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193943023682</t>
+    <t xml:space="preserve">11.1193933486938</t>
   </si>
   <si>
     <t xml:space="preserve">11.474196434021</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">11.126088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0189771652222</t>
+    <t xml:space="preserve">11.0189762115479</t>
   </si>
   <si>
     <t xml:space="preserve">11.0122842788696</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">10.0616788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1754837036133</t>
+    <t xml:space="preserve">10.1754846572876</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762474060059</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">8.67593860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80313205718994</t>
+    <t xml:space="preserve">8.80313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">8.93702030181885</t>
@@ -485,40 +485,40 @@
     <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23826789855957</t>
+    <t xml:space="preserve">9.23826885223389</t>
   </si>
   <si>
     <t xml:space="preserve">9.31860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37885093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19140625</t>
+    <t xml:space="preserve">9.13115787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37884998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
     <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6332368850708</t>
+    <t xml:space="preserve">9.63323783874512</t>
   </si>
   <si>
     <t xml:space="preserve">9.79390335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55959892272949</t>
+    <t xml:space="preserve">9.55959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43910026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629276275635</t>
+    <t xml:space="preserve">9.43909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">9.87423515319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6734037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760334014893</t>
+    <t xml:space="preserve">9.67340278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">9.07090759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08429718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801856994629</t>
+    <t xml:space="preserve">9.08429622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31190586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
   </si>
   <si>
     <t xml:space="preserve">9.35207271575928</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3855447769165</t>
+    <t xml:space="preserve">9.38554573059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.24496269226074</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">9.03743553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70941066741943</t>
+    <t xml:space="preserve">8.70940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">8.72279930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87007617950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76966094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74957656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78304862976074</t>
+    <t xml:space="preserve">8.87007522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76965999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74957752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78304958343506</t>
   </si>
   <si>
     <t xml:space="preserve">8.78974342346191</t>
@@ -605,64 +605,64 @@
     <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2006368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1203031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227828979492</t>
+    <t xml:space="preserve">8.20063591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12030410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227876663208</t>
   </si>
   <si>
     <t xml:space="preserve">7.82575082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83913850784302</t>
+    <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
     <t xml:space="preserve">7.86591577529907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84583330154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63161277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491798400879</t>
+    <t xml:space="preserve">7.84583377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6316123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491703033447</t>
   </si>
   <si>
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541711807251</t>
+    <t xml:space="preserve">7.74541759490967</t>
   </si>
   <si>
     <t xml:space="preserve">7.71194553375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69186210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433637619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.651695728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516778945923</t>
+    <t xml:space="preserve">7.69186162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500188827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169715881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516731262207</t>
   </si>
   <si>
     <t xml:space="preserve">7.9596381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12699794769287</t>
+    <t xml:space="preserve">8.12699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.38138484954834</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21149063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768486022949</t>
+    <t xml:space="preserve">9.2114896774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768676757812</t>
   </si>
   <si>
     <t xml:space="preserve">11.99635887146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1168584823608</t>
+    <t xml:space="preserve">12.1168594360352</t>
   </si>
   <si>
     <t xml:space="preserve">11.9294147491455</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">11.8691654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0499143600464</t>
+    <t xml:space="preserve">12.0499153137207</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2833070755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971525192261</t>
+    <t xml:space="preserve">15.2833080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971534729004</t>
   </si>
   <si>
     <t xml:space="preserve">13.6967363357544</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">13.7569847106934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975677490234</t>
+    <t xml:space="preserve">13.8975687026978</t>
   </si>
   <si>
     <t xml:space="preserve">13.7235136032104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8908729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180673599243</t>
+    <t xml:space="preserve">13.8908720016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.957818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180683135986</t>
   </si>
   <si>
     <t xml:space="preserve">14.0582332611084</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">13.9712066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0917043685913</t>
+    <t xml:space="preserve">14.0917062759399</t>
   </si>
   <si>
     <t xml:space="preserve">14.3126211166382</t>
@@ -746,40 +746,40 @@
     <t xml:space="preserve">14.1385669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8172340393066</t>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817234992981</t>
   </si>
   <si>
     <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544895172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549047470093</t>
+    <t xml:space="preserve">13.455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544904708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.2080450057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9268789291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528257369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737415313721</t>
+    <t xml:space="preserve">12.9268808364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067974090576</t>
@@ -791,31 +791,31 @@
     <t xml:space="preserve">13.0540733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9134922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072135925293</t>
+    <t xml:space="preserve">12.9134931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2147388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419332504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.859935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.007212638855</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">12.9201850891113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8934078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3754024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758205413818</t>
+    <t xml:space="preserve">12.8934087753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3754034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758214950562</t>
   </si>
   <si>
     <t xml:space="preserve">13.3486280441284</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406856536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8666305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8867139816284</t>
+    <t xml:space="preserve">13.0406837463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8666315078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8867130279541</t>
   </si>
   <si>
     <t xml:space="preserve">12.9335746765137</t>
@@ -857,34 +857,34 @@
     <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001035690308</t>
+    <t xml:space="preserve">12.9001045227051</t>
   </si>
   <si>
     <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8532428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.819769859314</t>
+    <t xml:space="preserve">12.8532419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197689056396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3109941482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3310804367065</t>
+    <t xml:space="preserve">12.5386047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3109951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3310794830322</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708301544189</t>
+    <t xml:space="preserve">12.2708311080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">11.67502784729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8624696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1771078109741</t>
+    <t xml:space="preserve">11.8624706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
     <t xml:space="preserve">12.1436347961426</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">12.7862977981567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8800210952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9469652175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5653829574585</t>
+    <t xml:space="preserve">12.8800201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9469633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637191772461</t>
+    <t xml:space="preserve">12.1637182235718</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043012619019</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">12.5586881637573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4649677276611</t>
+    <t xml:space="preserve">12.4649667739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2842197418213</t>
+    <t xml:space="preserve">12.2574405670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181070327759</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">12.1034698486328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0900812149048</t>
+    <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0633029937744</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.672492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3176908493042</t>
+    <t xml:space="preserve">12.6724939346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3176898956299</t>
   </si>
   <si>
     <t xml:space="preserve">11.8089151382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030546188354</t>
+    <t xml:space="preserve">12.0030536651611</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813055038452</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076684951782</t>
+    <t xml:space="preserve">11.5076694488525</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549453735352</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817226409912</t>
+    <t xml:space="preserve">11.6817216873169</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5210561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151947021484</t>
+    <t xml:space="preserve">11.5210571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151937484741</t>
   </si>
   <si>
     <t xml:space="preserve">11.661639213562</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7018060684204</t>
+    <t xml:space="preserve">11.7018070220947</t>
   </si>
   <si>
     <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3804750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2265033721924</t>
+    <t xml:space="preserve">11.3804759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">10.777979850769</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9453401565552</t>
+    <t xml:space="preserve">10.9453392028809</t>
   </si>
   <si>
     <t xml:space="preserve">11.1394758224487</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">11.1461706161499</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591440200806</t>
+    <t xml:space="preserve">11.0591449737549</t>
   </si>
   <si>
     <t xml:space="preserve">11.1528654098511</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4206399917603</t>
+    <t xml:space="preserve">11.4206409454346</t>
   </si>
   <si>
     <t xml:space="preserve">11.5411405563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5679187774658</t>
+    <t xml:space="preserve">11.5679197311401</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4608087539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541139602661</t>
+    <t xml:space="preserve">11.4005575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.460807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541130065918</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536968231201</t>
+    <t xml:space="preserve">11.3536958694458</t>
   </si>
   <si>
     <t xml:space="preserve">11.1595602035522</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721155166626</t>
+    <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897047042847</t>
+    <t xml:space="preserve">10.3897037506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3093719482422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1620941162109</t>
+    <t xml:space="preserve">10.1620950698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.2156496047974</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2625112533569</t>
+    <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3428440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3562316894531</t>
+    <t xml:space="preserve">10.3562326431274</t>
   </si>
   <si>
     <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80059719085693</t>
+    <t xml:space="preserve">9.80059814453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68679332733154</t>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">9.74704265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74034690856934</t>
+    <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
     <t xml:space="preserve">9.75373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70018100738525</t>
+    <t xml:space="preserve">9.70018196105957</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">10.7110347747803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6507863998413</t>
+    <t xml:space="preserve">10.650785446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708688735962</t>
+    <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.664174079895</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1888723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759008407593</t>
+    <t xml:space="preserve">10.188871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
@@ -1202,28 +1202,28 @@
     <t xml:space="preserve">10.2357330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5102033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.316065788269</t>
+    <t xml:space="preserve">10.5570640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5102024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160648345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.2089567184448</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52612781524658</t>
+    <t xml:space="preserve">9.65332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52612590789795</t>
   </si>
   <si>
     <t xml:space="preserve">9.62654209136963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83406925201416</t>
+    <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
     <t xml:space="preserve">9.84745788574219</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">10.2959823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436744689941</t>
+    <t xml:space="preserve">10.5436754226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">10.5972299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8583116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9855041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9587287902832</t>
+    <t xml:space="preserve">10.8583106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9855051040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9587278366089</t>
   </si>
   <si>
     <t xml:space="preserve">10.7311182022095</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">10.8248405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654216766357</t>
+    <t xml:space="preserve">10.9654226303101</t>
   </si>
   <si>
     <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9988946914673</t>
+    <t xml:space="preserve">10.9988956451416</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926160812378</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2465858459473</t>
+    <t xml:space="preserve">11.2465877532959</t>
   </si>
   <si>
     <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9185600280762</t>
+    <t xml:space="preserve">10.9185609817505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9118671417236</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">10.9051733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8917846679688</t>
+    <t xml:space="preserve">10.8917837142944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512016296387</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.463342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.7277708053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633417129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1319,13 +1319,13 @@
     <t xml:space="preserve">10.5135498046875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6206617355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6407442092896</t>
+    <t xml:space="preserve">10.6206607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8616590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6407451629639</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106185913086</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5771474838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.533634185791</t>
+    <t xml:space="preserve">10.5771465301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4097871780396</t>
+    <t xml:space="preserve">10.4097881317139</t>
   </si>
   <si>
     <t xml:space="preserve">11.1729488372803</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.36292552948</t>
+    <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94452571868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0349006652832</t>
+    <t xml:space="preserve">10.1821775436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0349016189575</t>
   </si>
   <si>
     <t xml:space="preserve">10.0951499938965</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762952804565</t>
+    <t xml:space="preserve">11.0357141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0223236083984</t>
+    <t xml:space="preserve">11.0223245620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.955379486084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256719589233</t>
+    <t xml:space="preserve">11.025671005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9520330429077</t>
+    <t xml:space="preserve">10.952033996582</t>
   </si>
   <si>
     <t xml:space="preserve">11.0290193557739</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">11.28675365448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3135299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9352960586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5068550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1721363067627</t>
+    <t xml:space="preserve">11.313530921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9352970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5068559646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1721353530884</t>
   </si>
   <si>
     <t xml:space="preserve">10.2457752227783</t>
@@ -1454,37 +1454,37 @@
     <t xml:space="preserve">10.0683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74369525909424</t>
+    <t xml:space="preserve">9.74369430541992</t>
   </si>
   <si>
     <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537887573242</t>
+    <t xml:space="preserve">9.34537792205811</t>
   </si>
   <si>
     <t xml:space="preserve">9.67005634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72695732116699</t>
+    <t xml:space="preserve">9.72695827484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633495330811</t>
+    <t xml:space="preserve">9.57633399963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.48596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637714385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5428638458252</t>
+    <t xml:space="preserve">9.58637619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6165018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54286289215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298851013184</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">9.56964111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50269508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4792652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49600124359131</t>
+    <t xml:space="preserve">9.5026969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49600315093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60980701446533</t>
+    <t xml:space="preserve">9.6098051071167</t>
   </si>
   <si>
     <t xml:space="preserve">8.83660316467285</t>
@@ -1514,25 +1514,25 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14119815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30186557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512763977051</t>
+    <t xml:space="preserve">8.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949409484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14119911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30186462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22487926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
     <t xml:space="preserve">9.2148380279541</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">9.45583629608154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39558696746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28178215026855</t>
+    <t xml:space="preserve">9.39558601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
     <t xml:space="preserve">9.61315441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691703796387</t>
+    <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
@@ -1562,49 +1562,49 @@
     <t xml:space="preserve">9.37550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54620933532715</t>
+    <t xml:space="preserve">9.54621028900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.31525325775146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26504611968994</t>
+    <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.73284149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89016056060791</t>
+    <t xml:space="preserve">8.80647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8533411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338043212891</t>
+    <t xml:space="preserve">8.85333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92028427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88011646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82656192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58891010284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29770565032959</t>
+    <t xml:space="preserve">8.92028331756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88011741638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82656288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58891201019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29770469665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.2742748260498</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25084400177002</t>
+    <t xml:space="preserve">8.2508430480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">8.35795497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47845458984375</t>
+    <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.47175884246826</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">8.78639602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71945190429688</t>
+    <t xml:space="preserve">8.71945095062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16462993621826</t>
+    <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
     <t xml:space="preserve">9.1345043182373</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">9.00731086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01065826416016</t>
+    <t xml:space="preserve">9.01065921783447</t>
   </si>
   <si>
     <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20814323425293</t>
+    <t xml:space="preserve">9.20814418792725</t>
   </si>
   <si>
     <t xml:space="preserve">9.22822570800781</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735305786133</t>
+    <t xml:space="preserve">9.01735210418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.12781047821045</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66589736938477</t>
+    <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8499927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53535556793213</t>
+    <t xml:space="preserve">8.84999370574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">8.47510623931885</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907886505127</t>
+    <t xml:space="preserve">8.62907791137695</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90689563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517078399658</t>
+    <t xml:space="preserve">8.90689468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29516983032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855941772461</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">9.50604438781738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111568450928</t>
+    <t xml:space="preserve">9.46587753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29435729980469</t>
+    <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
     <t xml:space="preserve">8.3110933303833</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">9.23492050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70271682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56548118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5018835067749</t>
+    <t xml:space="preserve">8.70271587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25753879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5654821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188446044922</t>
   </si>
   <si>
     <t xml:space="preserve">8.75627136230469</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">8.82321548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84329700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74622821807861</t>
+    <t xml:space="preserve">8.84329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236423492432</t>
+    <t xml:space="preserve">9.42236328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.26169776916504</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">9.45918273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44244575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41901588439941</t>
+    <t xml:space="preserve">9.4424467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95456886291504</t>
+    <t xml:space="preserve">9.95456790924072</t>
   </si>
   <si>
     <t xml:space="preserve">9.41566848754883</t>
@@ -1820,34 +1820,34 @@
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2717399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54874610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7127571105957</t>
+    <t xml:space="preserve">9.27174091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54874515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.8098258972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10437870025635</t>
+    <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843284606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947330474854</t>
+    <t xml:space="preserve">9.52947425842285</t>
   </si>
   <si>
     <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42905807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36211490631104</t>
+    <t xml:space="preserve">9.42905902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">9.24830913543701</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625247955322</t>
+    <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.42571067810059</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533573150635</t>
+    <t xml:space="preserve">9.33533668518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.24161529541016</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">9.73030662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69013977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50939083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73700141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79725074768066</t>
+    <t xml:space="preserve">9.69014072418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50938987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73700046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.9210958480835</t>
@@ -1910,43 +1910,43 @@
     <t xml:space="preserve">9.90770626068115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92779064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77716636657715</t>
+    <t xml:space="preserve">9.92779159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77716732025146</t>
   </si>
   <si>
     <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62988948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38889217376709</t>
+    <t xml:space="preserve">9.62989044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
     <t xml:space="preserve">9.45248794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25500297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.76631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62573051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7730073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961875915527</t>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77300643920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404689788818</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">9.76712512969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66670799255371</t>
+    <t xml:space="preserve">9.66670989990234</t>
   </si>
   <si>
     <t xml:space="preserve">9.53282070159912</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20144844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10103321075439</t>
+    <t xml:space="preserve">9.20144748687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10103225708008</t>
   </si>
   <si>
     <t xml:space="preserve">9.02739429473877</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">8.98053359985352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99057579040527</t>
+    <t xml:space="preserve">8.99057483673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.87342357635498</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">9.86084651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8240270614624</t>
+    <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
     <t xml:space="preserve">9.81063842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068061828613</t>
+    <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.30521106719971</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">9.15793514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16797637939453</t>
+    <t xml:space="preserve">9.16797542572021</t>
   </si>
   <si>
     <t xml:space="preserve">9.1746711730957</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88346576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288272857666</t>
+    <t xml:space="preserve">8.88346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250778198242</t>
+    <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677001953125</t>
+    <t xml:space="preserve">8.87677097320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681125640869</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05417156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06086540222168</t>
+    <t xml:space="preserve">9.05417060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.060866355896</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776828765869</t>
+    <t xml:space="preserve">9.11776733398438</t>
   </si>
   <si>
     <t xml:space="preserve">9.0809497833252</t>
@@ -2114,40 +2114,40 @@
     <t xml:space="preserve">8.64246654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40146732330322</t>
+    <t xml:space="preserve">8.40146923065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28431701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23410892486572</t>
+    <t xml:space="preserve">8.28431606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98976278305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06005382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01654052734375</t>
+    <t xml:space="preserve">7.9897632598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06005477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01653957366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624948501587</t>
+    <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
     <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93285989761353</t>
+    <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
@@ -2159,43 +2159,43 @@
     <t xml:space="preserve">8.03997039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290256500244</t>
+    <t xml:space="preserve">7.94290208816528</t>
   </si>
   <si>
     <t xml:space="preserve">7.78558349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12953186035156</t>
+    <t xml:space="preserve">7.67177820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12953233718872</t>
   </si>
   <si>
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300439834595</t>
+    <t xml:space="preserve">7.54793262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.07263040542603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87514591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786855697632</t>
+    <t xml:space="preserve">6.87514638900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786903381348</t>
   </si>
   <si>
     <t xml:space="preserve">6.57222414016724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25256681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1588454246521</t>
+    <t xml:space="preserve">6.25256729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15884494781494</t>
   </si>
   <si>
     <t xml:space="preserve">5.55802297592163</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45091247558594</t>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2213,73 +2213,73 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800062179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05929040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69023752212524</t>
+    <t xml:space="preserve">4.74800157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05928993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6902379989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98311758041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05842924118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23917722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29440689086914</t>
+    <t xml:space="preserve">5.98311805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05842971801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23917770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29440641403198</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515535354614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5303840637207</t>
+    <t xml:space="preserve">6.49356460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53038454055786</t>
   </si>
   <si>
     <t xml:space="preserve">6.64753675460815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56720399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3596773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0919017791748</t>
+    <t xml:space="preserve">6.56720352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35967683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
     <t xml:space="preserve">6.03834629058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85759735107422</t>
+    <t xml:space="preserve">6.17892789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85759687423706</t>
   </si>
   <si>
     <t xml:space="preserve">6.00487422943115</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">6.32620477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34628772735596</t>
+    <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520698547363</t>
+    <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156806945801</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">5.89776372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98813819885254</t>
+    <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433338165283</t>
+    <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747268676758</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0843939781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87017345428467</t>
+    <t xml:space="preserve">5.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
     <t xml:space="preserve">4.75302219390869</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">4.91368770599365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774185180664</t>
+    <t xml:space="preserve">5.0877423286438</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142200469971</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34212875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15803289413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22162961959839</t>
+    <t xml:space="preserve">5.34212923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15803241729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22163009643555</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">5.74044513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89106893539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94127750396729</t>
+    <t xml:space="preserve">5.89106941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94127798080444</t>
   </si>
   <si>
     <t xml:space="preserve">5.82077789306641</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">5.60655736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29526805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20824098587036</t>
+    <t xml:space="preserve">5.29526853561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2082405090332</t>
   </si>
   <si>
     <t xml:space="preserve">5.19819927215576</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">5.29861497879028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28522682189941</t>
+    <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
     <t xml:space="preserve">5.30196237564087</t>
@@ -2408,25 +2408,25 @@
     <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27853155136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23167133331299</t>
+    <t xml:space="preserve">5.27853202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23167085647583</t>
   </si>
   <si>
     <t xml:space="preserve">5.35886526107788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32204532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32539319992065</t>
+    <t xml:space="preserve">5.32204580307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3253927230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2283239364624</t>
+    <t xml:space="preserve">5.22832441329956</t>
   </si>
   <si>
     <t xml:space="preserve">5.04422807693481</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">4.97058963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046545028687</t>
+    <t xml:space="preserve">4.94046497344971</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13125562667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11451959609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12790775299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12456035614014</t>
+    <t xml:space="preserve">5.08104753494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13125514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1145191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12790822982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
     <t xml:space="preserve">5.11786651611328</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">5.0375337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96389532089233</t>
+    <t xml:space="preserve">4.96389579772949</t>
   </si>
   <si>
     <t xml:space="preserve">5.41576719284058</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961324691772</t>
+    <t xml:space="preserve">5.53961277008057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3454761505127</t>
+    <t xml:space="preserve">5.34547662734985</t>
   </si>
   <si>
     <t xml:space="preserve">5.3053092956543</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">5.27518510818481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09108829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60321092605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12537336349487</t>
+    <t xml:space="preserve">5.09108877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60320997238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
     <t xml:space="preserve">6.15215063095093</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">6.14880418777466</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.09524774551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441680908203</t>
+    <t xml:space="preserve">5.89441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375129699707</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4860577583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48271083831787</t>
+    <t xml:space="preserve">5.61325216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48271131515503</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287721633911</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040437698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.73040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65676498413086</t>
+    <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.55634927749634</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47267007827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50948858261108</t>
+    <t xml:space="preserve">5.47266960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50948810577393</t>
   </si>
   <si>
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894821166992</t>
+    <t xml:space="preserve">5.37894773483276</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">4.94381237030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07770013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2182822227478</t>
+    <t xml:space="preserve">5.07769966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21828269958496</t>
   </si>
   <si>
     <t xml:space="preserve">5.15468597412109</t>
@@ -2636,22 +2636,22 @@
     <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02830457687378</t>
+    <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
     <t xml:space="preserve">6.09859561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8082013130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6374945640564</t>
+    <t xml:space="preserve">6.44335651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80820178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63749408721924</t>
   </si>
   <si>
     <t xml:space="preserve">6.58728647232056</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">6.67766094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41323184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418888092041</t>
+    <t xml:space="preserve">6.41323232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418935775757</t>
   </si>
   <si>
     <t xml:space="preserve">6.7814245223999</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">7.10275459289551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36383724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647645950317</t>
+    <t xml:space="preserve">7.36383628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647693634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.12283897399902</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">7.0893669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97556161880493</t>
+    <t xml:space="preserve">6.97556209564209</t>
   </si>
   <si>
     <t xml:space="preserve">7.20986557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05589532852173</t>
+    <t xml:space="preserve">7.14961576461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589437484741</t>
   </si>
   <si>
     <t xml:space="preserve">7.00233888626099</t>
@@ -2711,64 +2711,64 @@
     <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944938659668</t>
+    <t xml:space="preserve">7.10944986343384</t>
   </si>
   <si>
     <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9822564125061</t>
+    <t xml:space="preserve">6.98225593566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.14292144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96886682510376</t>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9688663482666</t>
   </si>
   <si>
     <t xml:space="preserve">6.90192317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11614418029785</t>
+    <t xml:space="preserve">7.11614370346069</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18978261947632</t>
+    <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.03581094741821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622665405273</t>
+    <t xml:space="preserve">6.90861749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631055831909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2500319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32367086410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55128002166748</t>
+    <t xml:space="preserve">7.25003147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
@@ -2777,31 +2777,31 @@
     <t xml:space="preserve">7.41069746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39061403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47094631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56466913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5111141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53789043426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152935028076</t>
+    <t xml:space="preserve">7.3906135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56466960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51111364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53789091110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61152982711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880670547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252714157104</t>
+    <t xml:space="preserve">7.75880575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8525276184082</t>
   </si>
   <si>
     <t xml:space="preserve">8.07344341278076</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1805534362793</t>
+    <t xml:space="preserve">8.18055248260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66254901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89685440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91693592071533</t>
+    <t xml:space="preserve">8.66254997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89685344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.48849487304688</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21402454376221</t>
+    <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
@@ -2843,40 +2843,40 @@
     <t xml:space="preserve">8.45502376556396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724822998047</t>
+    <t xml:space="preserve">8.18724727630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32782936096191</t>
+    <t xml:space="preserve">8.26758003234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3278284072876</t>
   </si>
   <si>
     <t xml:space="preserve">7.81236171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77888917922974</t>
+    <t xml:space="preserve">7.77888965606689</t>
   </si>
   <si>
     <t xml:space="preserve">7.91277694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89938735961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99980449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97049140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68009853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55290412902832</t>
+    <t xml:space="preserve">7.89938831329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99980354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97049236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68009757995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55290508270264</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">10.0282068252563</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85415172576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77381992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365211486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168981552124</t>
+    <t xml:space="preserve">9.85415267944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77381896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039247512817</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">10.4767303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.677562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.6775636672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2942,19 +2942,19 @@
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90528011322021</t>
+    <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55733680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59435176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43888664245605</t>
+    <t xml:space="preserve">9.55733585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59435081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43888759613037</t>
   </si>
   <si>
     <t xml:space="preserve">9.57954502105713</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79423427581787</t>
+    <t xml:space="preserve">9.76462173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79423332214355</t>
   </si>
   <si>
     <t xml:space="preserve">9.83865261077881</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7572193145752</t>
+    <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8534574508667</t>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533399581909</t>
+    <t xml:space="preserve">10.0533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40927600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26121520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14276599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10575103759766</t>
+    <t xml:space="preserve">9.4018726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40927505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26121425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14276504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10575008392334</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34634876251221</t>
+    <t xml:space="preserve">9.34634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">9.37226009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4166784286499</t>
+    <t xml:space="preserve">9.41667938232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.30563163757324</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">9.17978096008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160171508789</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">9.01691436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03912162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15757083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3130350112915</t>
+    <t xml:space="preserve">9.03912258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15757179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31303596496582</t>
   </si>
   <si>
     <t xml:space="preserve">9.35745429992676</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03172016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02431583404541</t>
+    <t xml:space="preserve">9.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99470520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8016357421875</t>
+    <t xml:space="preserve">9.09834766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.994704246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80163669586182</t>
   </si>
   <si>
     <t xml:space="preserve">10.0237283706665</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.668381690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32784175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46109580993652</t>
+    <t xml:space="preserve">9.32784271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46109676361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">9.52772426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885261535645</t>
+    <t xml:space="preserve">8.86885166168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92067527770996</t>
+    <t xml:space="preserve">8.92067432403564</t>
   </si>
   <si>
     <t xml:space="preserve">8.93548011779785</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33078336715698</t>
+    <t xml:space="preserve">4.33078384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51586008071899</t>
+    <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
     <t xml:space="preserve">4.5898904800415</t>
@@ -3167,31 +3167,31 @@
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58248710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31227540969849</t>
+    <t xml:space="preserve">4.69723415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5824875831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.10128927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13090085983276</t>
+    <t xml:space="preserve">4.13090133666992</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1938271522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1679162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17161846160889</t>
+    <t xml:space="preserve">4.19382667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16791677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17161798477173</t>
   </si>
   <si>
     <t xml:space="preserve">4.2456488609314</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12719964981079</t>
+    <t xml:space="preserve">4.12720012664795</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">4.21233510971069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033763885498</t>
+    <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36039590835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15311098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10499048233032</t>
+    <t xml:space="preserve">4.39741086959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36039543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758758544922</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">4.17902088165283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93842244148254</t>
+    <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
@@ -3254,13 +3254,13 @@
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58862829208374</t>
+    <t xml:space="preserve">4.04576683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">4.07537889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206466674805</t>
+    <t xml:space="preserve">4.04206418991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34559011459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27526044845581</t>
+    <t xml:space="preserve">4.34558963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510821342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433258056641</t>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433281898499</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95322823524475</t>
+    <t xml:space="preserve">3.95322799682617</t>
   </si>
   <si>
     <t xml:space="preserve">4.05316925048828</t>
@@ -3308,61 +3308,61 @@
     <t xml:space="preserve">4.01985549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88660049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8643913269043</t>
+    <t xml:space="preserve">3.88660097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86439180374146</t>
   </si>
   <si>
     <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73483777046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50164222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53310561180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716490745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52014994621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48313450813293</t>
+    <t xml:space="preserve">3.73483824729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50164246559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53310513496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52015018463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48313474655151</t>
   </si>
   <si>
     <t xml:space="preserve">3.51459765434265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57382154464722</t>
+    <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
     <t xml:space="preserve">3.6200909614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61638951301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70152425765991</t>
+    <t xml:space="preserve">3.61638975143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.33137226104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358119010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1092803478241</t>
+    <t xml:space="preserve">3.35358095169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10928058624268</t>
   </si>
   <si>
     <t xml:space="preserve">3.24623703956604</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10187768936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.10187745094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00748872756958</t>
+    <t xml:space="preserve">3.007488489151</t>
   </si>
   <si>
     <t xml:space="preserve">2.98342895507812</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503872871399</t>
+    <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014433860779</t>
+    <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059125900269</t>
+    <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
     <t xml:space="preserve">2.82426309585571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83721876144409</t>
+    <t xml:space="preserve">2.83721852302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.763188123703</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">2.60032105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297690391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56515622138977</t>
+    <t xml:space="preserve">2.49297666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44855856895447</t>
+    <t xml:space="preserve">2.44855833053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.47446918487549</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">2.27273607254028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2579300403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34861731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41339373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34676647186279</t>
+    <t xml:space="preserve">2.25792980194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34861707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4133939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34676671028137</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790042877197</t>
@@ -3527,25 +3527,25 @@
     <t xml:space="preserve">2.18760085105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29679608345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28569149971008</t>
+    <t xml:space="preserve">2.29679584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2856912612915</t>
   </si>
   <si>
     <t xml:space="preserve">2.30234813690186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35416960716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3412139415741</t>
+    <t xml:space="preserve">2.35416984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.25422859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26718401908875</t>
+    <t xml:space="preserve">2.26718378067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.28754210472107</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607895851135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276544570923</t>
+    <t xml:space="preserve">2.25607919692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
@@ -3575,10 +3575,10 @@
     <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29124355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24867630004883</t>
+    <t xml:space="preserve">2.2912437915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
     <t xml:space="preserve">2.21351170539856</t>
@@ -3596,28 +3596,28 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13763022422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14688420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0839581489563</t>
+    <t xml:space="preserve">2.08765959739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13763046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14688444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08395838737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.10246586799622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0710027217865</t>
+    <t xml:space="preserve">2.07100296020508</t>
   </si>
   <si>
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434632301331</t>
+    <t xml:space="preserve">2.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
@@ -3626,37 +3626,37 @@
     <t xml:space="preserve">2.11912274360657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12652587890625</t>
+    <t xml:space="preserve">2.12652564048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.07285380363464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01362919807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95810639858246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186707019806</t>
+    <t xml:space="preserve">2.01362943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95810651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132343769073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638429641724</t>
+    <t xml:space="preserve">1.90132355690002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638417720795</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91036558151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077318668365</t>
+    <t xml:space="preserve">1.91036570072174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077330589294</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953665733337</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679887771606</t>
+    <t xml:space="preserve">1.86679899692535</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8955694437027</t>
+    <t xml:space="preserve">1.89556932449341</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79199552536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8585786819458</t>
+    <t xml:space="preserve">1.79199540615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85857880115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">1.95311069488525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95886468887329</t>
+    <t xml:space="preserve">1.958864569664</t>
   </si>
   <si>
     <t xml:space="preserve">2.00078773498535</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">1.98023724555969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03942227363586</t>
+    <t xml:space="preserve">2.03942251205444</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559084892273</t>
+    <t xml:space="preserve">2.07559108734131</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">2.07970118522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00489735603333</t>
+    <t xml:space="preserve">2.0048975944519</t>
   </si>
   <si>
     <t xml:space="preserve">1.99749958515167</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204921722412</t>
+    <t xml:space="preserve">2.2420494556427</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">2.14135241508484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573740005493</t>
+    <t xml:space="preserve">2.15573763847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">2.28520512580872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34480142593384</t>
+    <t xml:space="preserve">2.34480118751526</t>
   </si>
   <si>
     <t xml:space="preserve">2.2728750705719</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30781030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34685635566711</t>
+    <t xml:space="preserve">2.30781054496765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34685659408569</t>
   </si>
   <si>
     <t xml:space="preserve">2.35096621513367</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821448326111</t>
+    <t xml:space="preserve">2.24821424484253</t>
   </si>
   <si>
     <t xml:space="preserve">2.25848960876465</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546227455139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21944403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24615931510925</t>
+    <t xml:space="preserve">2.14546251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21944379806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24615955352783</t>
   </si>
   <si>
     <t xml:space="preserve">2.26670980453491</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">2.25437951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30986571311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3550763130188</t>
+    <t xml:space="preserve">2.30986547470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35507655143738</t>
   </si>
   <si>
     <t xml:space="preserve">2.41056251525879</t>
@@ -3842,34 +3842,34 @@
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619550704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52770018577576</t>
+    <t xml:space="preserve">2.54619526863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
     <t xml:space="preserve">2.55236029624939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5379753112793</t>
+    <t xml:space="preserve">2.53797507286072</t>
   </si>
   <si>
     <t xml:space="preserve">2.54003024101257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45988345146179</t>
+    <t xml:space="preserve">2.45988368988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153468132019</t>
+    <t xml:space="preserve">2.52153491973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51125979423523</t>
+    <t xml:space="preserve">2.51125955581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674427986145</t>
+    <t xml:space="preserve">2.63250708580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66744256019592</t>
   </si>
   <si>
     <t xml:space="preserve">2.67155265808105</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">2.7414243221283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70443344116211</t>
+    <t xml:space="preserve">2.70443320274353</t>
   </si>
   <si>
     <t xml:space="preserve">2.72498393058777</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869009017944</t>
+    <t xml:space="preserve">2.78868985176086</t>
   </si>
   <si>
     <t xml:space="preserve">2.77019476890564</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60784649848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6263415813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648837089539</t>
+    <t xml:space="preserve">2.6078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62634181976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648860931396</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524084091187</t>
+    <t xml:space="preserve">2.58524107933044</t>
   </si>
   <si>
     <t xml:space="preserve">2.58935141563416</t>
@@ -4010,10 +4010,10 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048810958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97158885002136</t>
+    <t xml:space="preserve">2.93048787117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
     <t xml:space="preserve">2.91404747962952</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035953521729</t>
+    <t xml:space="preserve">3.00035929679871</t>
   </si>
   <si>
     <t xml:space="preserve">2.99419403076172</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773566246033</t>
+    <t xml:space="preserve">2.82773590087891</t>
   </si>
   <si>
     <t xml:space="preserve">2.74553418159485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61606669425964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68388319015503</t>
+    <t xml:space="preserve">2.61606645584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68388295173645</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">2.84212112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7722499370575</t>
+    <t xml:space="preserve">2.77224969863892</t>
   </si>
   <si>
     <t xml:space="preserve">2.78457975387573</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89555239677429</t>
+    <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
     <t xml:space="preserve">3.10927653312683</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">2.9633686542511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93665289878845</t>
+    <t xml:space="preserve">2.93665313720703</t>
   </si>
   <si>
     <t xml:space="preserve">2.89966225624084</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034132003784</t>
+    <t xml:space="preserve">2.85034108161926</t>
   </si>
   <si>
     <t xml:space="preserve">2.86883687973022</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">2.9818639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01268935203552</t>
+    <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
     <t xml:space="preserve">2.94281816482544</t>
@@ -5598,6 +5598,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.04400014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05999994277954</t>
   </si>
 </sst>
 </file>
@@ -70962,7 +70965,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6915162037</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>424065</v>
@@ -70983,6 +70986,32 @@
         <v>1861</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6912037037</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>956590</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>4.05800008773804</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>4.22599983215332</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="1866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="1865">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356557846069</t>
+    <t xml:space="preserve">12.2356548309326</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.195689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7028007507324</t>
+    <t xml:space="preserve">12.1956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027997970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.5895690917969</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">11.076696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302526473999</t>
+    <t xml:space="preserve">11.136643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302536010742</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770582199097</t>
@@ -80,31 +80,31 @@
     <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3906478881836</t>
+    <t xml:space="preserve">10.2507753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7370042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
     <t xml:space="preserve">10.4239521026611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5438432693481</t>
+    <t xml:space="preserve">10.5438442230225</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2707567214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4838981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.297399520874</t>
+    <t xml:space="preserve">10.2707557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4838972091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2973985671997</t>
   </si>
   <si>
     <t xml:space="preserve">10.1042394638062</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">10.8702163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.717022895813</t>
+    <t xml:space="preserve">10.7170219421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.77786731719971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9110803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54474258422852</t>
+    <t xml:space="preserve">9.91107940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54474353790283</t>
   </si>
   <si>
     <t xml:space="preserve">9.77120590209961</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">10.4639148712158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6171102523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4172916412354</t>
+    <t xml:space="preserve">10.6171112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4172925949097</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703075408936</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436595916748</t>
+    <t xml:space="preserve">9.96436500549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9434852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.436372756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3431253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6495141983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898406982422</t>
+    <t xml:space="preserve">10.7236824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9434843063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363737106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3431243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6495151519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898397445679</t>
   </si>
   <si>
     <t xml:space="preserve">12.0624771118164</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">11.7627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289934158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4754390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422269821167</t>
+    <t xml:space="preserve">12.2289943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.475438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554586410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422260284424</t>
   </si>
   <si>
     <t xml:space="preserve">12.4621171951294</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019897460938</t>
+    <t xml:space="preserve">12.6019916534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823682785034</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">11.496319770813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0633773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561765670776</t>
+    <t xml:space="preserve">11.0633783340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.656177520752</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559059143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689571380615</t>
+    <t xml:space="preserve">12.2689580917358</t>
   </si>
   <si>
     <t xml:space="preserve">12.8217945098877</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350242614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1015424728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281833648682</t>
+    <t xml:space="preserve">12.9350252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101541519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281843185425</t>
   </si>
   <si>
     <t xml:space="preserve">13.2480764389038</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">13.1947917938232</t>
   </si>
   <si>
-    <t xml:space="preserve">13.181468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614894866943</t>
+    <t xml:space="preserve">13.1814699172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614875793457</t>
   </si>
   <si>
     <t xml:space="preserve">13.361307144165</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">13.2347555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3946113586426</t>
+    <t xml:space="preserve">13.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">12.981650352478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6885805130005</t>
+    <t xml:space="preserve">12.6885786056519</t>
   </si>
   <si>
     <t xml:space="preserve">12.5620288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8817386627197</t>
+    <t xml:space="preserve">12.881739616394</t>
   </si>
   <si>
     <t xml:space="preserve">12.8617572784424</t>
@@ -287,52 +287,52 @@
     <t xml:space="preserve">12.8884000778198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0482559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.375527381897</t>
+    <t xml:space="preserve">13.0482549667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
     <t xml:space="preserve">12.4221515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3488855361938</t>
+    <t xml:space="preserve">12.3488874435425</t>
   </si>
   <si>
     <t xml:space="preserve">12.7218837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7685089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344060897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159883499146</t>
+    <t xml:space="preserve">12.7685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159873962402</t>
   </si>
   <si>
     <t xml:space="preserve">13.6230983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5226812362671</t>
+    <t xml:space="preserve">13.5226831436157</t>
   </si>
   <si>
     <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4222660064697</t>
+    <t xml:space="preserve">13.4222650527954</t>
   </si>
   <si>
     <t xml:space="preserve">13.3620157241821</t>
@@ -341,31 +341,31 @@
     <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0741586685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9938249588013</t>
+    <t xml:space="preserve">13.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.194655418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.659104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833864212036</t>
+    <t xml:space="preserve">13.2749891281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6591033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833854675293</t>
   </si>
   <si>
     <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620553970337</t>
+    <t xml:space="preserve">11.7620544433594</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218894958496</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">13.1411008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8850889205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487064361572</t>
+    <t xml:space="preserve">10.8850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487054824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8382291793823</t>
+    <t xml:space="preserve">10.8382301330566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4834251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177295684814</t>
+    <t xml:space="preserve">10.7177286148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0482912063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4432582855225</t>
+    <t xml:space="preserve">10.0482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193933486938</t>
+    <t xml:space="preserve">11.1193943023682</t>
   </si>
   <si>
     <t xml:space="preserve">11.474196434021</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">11.0189771652222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.811450958252</t>
+    <t xml:space="preserve">11.0122842788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783950805664</t>
+    <t xml:space="preserve">10.8783941268921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1754837036133</t>
+    <t xml:space="preserve">10.175482749939</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762474060059</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">8.93032455444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313205718994</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479583740234</t>
+    <t xml:space="preserve">9.20479488372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.37215423583984</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.23826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31860065460205</t>
+    <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13115787506104</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6332368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51273822784424</t>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51273918151855</t>
   </si>
   <si>
     <t xml:space="preserve">9.43909931182861</t>
@@ -533,19 +533,19 @@
     <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78720855712891</t>
+    <t xml:space="preserve">9.78720760345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.87423610687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6734037399292</t>
+    <t xml:space="preserve">9.67340469360352</t>
   </si>
   <si>
     <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17132472991943</t>
+    <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.07090854644775</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31190586090088</t>
+    <t xml:space="preserve">9.3119068145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.17801761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3654613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38554573059082</t>
+    <t xml:space="preserve">9.35207366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36546039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3855447769165</t>
   </si>
   <si>
     <t xml:space="preserve">9.24496269226074</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">8.70941066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72279834747314</t>
+    <t xml:space="preserve">8.72279930114746</t>
   </si>
   <si>
     <t xml:space="preserve">8.87007617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76965999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74957752227783</t>
+    <t xml:space="preserve">8.7696590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304958343506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78974342346191</t>
+    <t xml:space="preserve">8.78974437713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.71610546112061</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.66924285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33452415466309</t>
+    <t xml:space="preserve">8.3345251083374</t>
   </si>
   <si>
     <t xml:space="preserve">8.20063591003418</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83913803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6316123008728</t>
+    <t xml:space="preserve">7.83913898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63161277770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.62491893768311</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541664123535</t>
+    <t xml:space="preserve">7.74541759490967</t>
   </si>
   <si>
     <t xml:space="preserve">7.7119460105896</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">7.48433637619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64500093460083</t>
+    <t xml:space="preserve">7.64500188827515</t>
   </si>
   <si>
     <t xml:space="preserve">7.65169620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68516635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9596381187439</t>
+    <t xml:space="preserve">7.68516731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963716506958</t>
   </si>
   <si>
     <t xml:space="preserve">8.12699794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38138580322266</t>
+    <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.9236307144165</t>
@@ -677,43 +677,43 @@
     <t xml:space="preserve">9.09768581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1168575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9294157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8691654205322</t>
+    <t xml:space="preserve">11.9963598251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1168584823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8691644668579</t>
   </si>
   <si>
     <t xml:space="preserve">12.0499143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8615627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833080291748</t>
+    <t xml:space="preserve">14.8615608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833061218262</t>
   </si>
   <si>
     <t xml:space="preserve">13.7971525192261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6967363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7569847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975687026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908720016479</t>
+    <t xml:space="preserve">13.6967344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975667953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908739089966</t>
   </si>
   <si>
     <t xml:space="preserve">13.9578170776367</t>
@@ -749,67 +749,67 @@
     <t xml:space="preserve">14.1251783370972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8172340393066</t>
+    <t xml:space="preserve">13.8172359466553</t>
   </si>
   <si>
     <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557371139526</t>
+    <t xml:space="preserve">13.4557390213013</t>
   </si>
   <si>
     <t xml:space="preserve">13.2415180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544895172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549066543579</t>
+    <t xml:space="preserve">13.1544904708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549047470093</t>
   </si>
   <si>
     <t xml:space="preserve">13.2080450057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9268789291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528257369995</t>
+    <t xml:space="preserve">12.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.8264646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9737405776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067983627319</t>
+    <t xml:space="preserve">12.9737415313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067974090576</t>
   </si>
   <si>
     <t xml:space="preserve">13.1611843109131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0540752410889</t>
+    <t xml:space="preserve">13.0540742874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.9134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2147397994995</t>
+    <t xml:space="preserve">13.2147388458252</t>
   </si>
   <si>
     <t xml:space="preserve">13.1879625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3419342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812686920166</t>
+    <t xml:space="preserve">13.3419351577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181266784668</t>
   </si>
   <si>
     <t xml:space="preserve">13.033989906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.859935760498</t>
+    <t xml:space="preserve">12.8599348068237</t>
   </si>
   <si>
     <t xml:space="preserve">12.9871301651001</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">13.0473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0206031799316</t>
+    <t xml:space="preserve">13.0206022262573</t>
   </si>
   <si>
     <t xml:space="preserve">12.9201860427856</t>
@@ -830,22 +830,22 @@
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754053115845</t>
+    <t xml:space="preserve">13.3754034042358</t>
   </si>
   <si>
     <t xml:space="preserve">13.4758195877075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3486280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214345932007</t>
+    <t xml:space="preserve">13.3486289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214336395264</t>
   </si>
   <si>
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406847000122</t>
+    <t xml:space="preserve">13.0406837463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666305541992</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197689056396</t>
+    <t xml:space="preserve">12.9001035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197708129883</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858825683594</t>
@@ -887,19 +887,19 @@
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708292007446</t>
+    <t xml:space="preserve">12.2708301544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.67502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1771078109741</t>
+    <t xml:space="preserve">11.6750288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
     <t xml:space="preserve">12.1436357498169</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">12.7862987518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8800182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9469623565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448843002319</t>
+    <t xml:space="preserve">12.8800210952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9469633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
     <t xml:space="preserve">12.1637201309204</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6189403533936</t>
+    <t xml:space="preserve">12.558690071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1034698486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0900802612305</t>
+    <t xml:space="preserve">12.1971921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1034708023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0900812149048</t>
   </si>
   <si>
     <t xml:space="preserve">12.0633029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5519952774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6724939346313</t>
+    <t xml:space="preserve">12.5519943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6724948883057</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176898956299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8089170455933</t>
+    <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.0030546188354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813074111938</t>
+    <t xml:space="preserve">11.5813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">11.6147785186768</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">11.5076694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6549453735352</t>
+    <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
     <t xml:space="preserve">11.5880002975464</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.661639213562</t>
+    <t xml:space="preserve">11.6616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">11.634861946106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7018060684204</t>
+    <t xml:space="preserve">11.7687501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7018051147461</t>
   </si>
   <si>
     <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3804750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7043409347534</t>
+    <t xml:space="preserve">11.3804759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2265043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7980613708496</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">11.1461706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0658378601074</t>
+    <t xml:space="preserve">11.0658388137817</t>
   </si>
   <si>
     <t xml:space="preserve">11.1327810287476</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">11.1528654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0993099212646</t>
+    <t xml:space="preserve">11.099310874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.1997261047363</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1126985549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4206409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5411405563354</t>
+    <t xml:space="preserve">11.112699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4206399917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5411415100098</t>
   </si>
   <si>
     <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198095321655</t>
+    <t xml:space="preserve">11.2198104858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
+    <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
     <t xml:space="preserve">11.4608087539673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541139602661</t>
+    <t xml:space="preserve">11.4541149139404</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336133956909</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1595602035522</t>
+    <t xml:space="preserve">11.1595592498779</t>
   </si>
   <si>
     <t xml:space="preserve">11.0524492263794</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897037506104</t>
+    <t xml:space="preserve">10.3897047042847</t>
   </si>
   <si>
     <t xml:space="preserve">10.3093719482422</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">10.1620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156496047974</t>
+    <t xml:space="preserve">10.2156505584717</t>
   </si>
   <si>
     <t xml:space="preserve">10.3361492156982</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68679237365723</t>
+    <t xml:space="preserve">9.68679332733154</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74034690856934</t>
+    <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
     <t xml:space="preserve">9.75373554229736</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5235929489136</t>
+    <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">10.7110347747803</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708688735962</t>
+    <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641750335693</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">10.188871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.275899887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1286220550537</t>
+    <t xml:space="preserve">10.2758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.128623008728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
+    <t xml:space="preserve">10.2357339859009</t>
   </si>
   <si>
     <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102033615112</t>
+    <t xml:space="preserve">10.5102024078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.316065788269</t>
@@ -1217,22 +1217,22 @@
     <t xml:space="preserve">10.2089567184448</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52612686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62654304504395</t>
+    <t xml:space="preserve">9.65331935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52612590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62654209136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959823608398</t>
+    <t xml:space="preserve">9.8474588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436744689941</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">10.82483959198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725336074829</t>
+    <t xml:space="preserve">10.9654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
     <t xml:space="preserve">10.998893737793</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">11.0926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796436309814</t>
+    <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9185609817505</t>
+    <t xml:space="preserve">10.9185619354248</t>
   </si>
   <si>
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051733016968</t>
+    <t xml:space="preserve">10.9051723480225</t>
   </si>
   <si>
     <t xml:space="preserve">10.8917837142944</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277708053589</t>
+    <t xml:space="preserve">10.7277717590332</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633417129517</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871877670288</t>
+    <t xml:space="preserve">10.5871868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3696212768555</t>
+    <t xml:space="preserve">10.2658586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3696203231812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135507583618</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6240072250366</t>
+    <t xml:space="preserve">10.533634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
     <t xml:space="preserve">10.4097871780396</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">11.172947883606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9821586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261070251465</t>
+    <t xml:space="preserve">10.982159614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269403457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261060714722</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394956588745</t>
+    <t xml:space="preserve">10.3394966125488</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629264831543</t>
@@ -1382,25 +1382,25 @@
     <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94452571868896</t>
+    <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349016189575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9788103103638</t>
+    <t xml:space="preserve">10.0951490402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9788093566895</t>
   </si>
   <si>
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762962341309</t>
+    <t xml:space="preserve">11.0357122421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620752334595</t>
+    <t xml:space="preserve">10.9620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">11.0223245620728</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.082573890686</t>
+    <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">10.952033996582</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352970123291</t>
+    <t xml:space="preserve">10.9352960586548</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">9.74369525909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28847503662109</t>
+    <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
     <t xml:space="preserve">9.34537792205811</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">9.6700553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72695922851562</t>
+    <t xml:space="preserve">9.72695827484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633590698242</t>
+    <t xml:space="preserve">9.57633495330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.48596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637619018555</t>
+    <t xml:space="preserve">9.58637714385986</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
@@ -1493,37 +1493,37 @@
     <t xml:space="preserve">9.57298755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56964111328125</t>
+    <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
     <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4792652130127</t>
+    <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319564819336</t>
+    <t xml:space="preserve">9.62319660186768</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83660411834717</t>
+    <t xml:space="preserve">8.83660316467285</t>
   </si>
   <si>
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932723999023</t>
+    <t xml:space="preserve">8.68932819366455</t>
   </si>
   <si>
     <t xml:space="preserve">8.72949409484863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89350700378418</t>
+    <t xml:space="preserve">8.89350605010986</t>
   </si>
   <si>
     <t xml:space="preserve">9.14119911193848</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">9.13785266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45583534240723</t>
+    <t xml:space="preserve">9.45583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28178119659424</t>
+    <t xml:space="preserve">9.28178215026855</t>
   </si>
   <si>
     <t xml:space="preserve">9.61315441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46922588348389</t>
+    <t xml:space="preserve">9.7169189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37550354003906</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">9.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31525421142578</t>
+    <t xml:space="preserve">9.31525325775146</t>
   </si>
   <si>
     <t xml:space="preserve">9.26504516601562</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02070045471191</t>
+    <t xml:space="preserve">9.02070140838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.85334014892578</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86003398895264</t>
+    <t xml:space="preserve">8.86003494262695</t>
   </si>
   <si>
     <t xml:space="preserve">8.92028427124023</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78639602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77635383605957</t>
+    <t xml:space="preserve">8.78639507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71944999694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77635478973389</t>
   </si>
   <si>
     <t xml:space="preserve">9.16462993621826</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20814418792725</t>
+    <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
     <t xml:space="preserve">9.22822570800781</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">8.94706058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0006160736084</t>
+    <t xml:space="preserve">9.00061702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12780952453613</t>
+    <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03408908843994</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8499927520752</t>
+    <t xml:space="preserve">8.84999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30855941772461</t>
+    <t xml:space="preserve">9.29517078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30855846405029</t>
   </si>
   <si>
     <t xml:space="preserve">9.50604438781738</t>
@@ -1721,31 +1721,31 @@
     <t xml:space="preserve">9.12111663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11107349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.294358253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3110933303833</t>
+    <t xml:space="preserve">9.1110725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31109428405762</t>
   </si>
   <si>
     <t xml:space="preserve">8.34456539154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32448387145996</t>
+    <t xml:space="preserve">8.32448291778564</t>
   </si>
   <si>
     <t xml:space="preserve">8.24749755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48514938354492</t>
+    <t xml:space="preserve">8.48514842987061</t>
   </si>
   <si>
     <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93367290496826</t>
+    <t xml:space="preserve">8.93367385864258</t>
   </si>
   <si>
     <t xml:space="preserve">9.19810104370117</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">9.23492050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70271587371826</t>
+    <t xml:space="preserve">8.70271682739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.25753879547119</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">8.5018835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75627040863037</t>
+    <t xml:space="preserve">8.75627136230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.82321548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84329891204834</t>
+    <t xml:space="preserve">8.84329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">8.74622917175293</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">9.84411144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.522780418396</t>
+    <t xml:space="preserve">9.52277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60646057128906</t>
+    <t xml:space="preserve">9.60645961761475</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456886291504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41566944122314</t>
+    <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
     <t xml:space="preserve">9.35876655578613</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275806427002</t>
+    <t xml:space="preserve">8.7127571105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10438060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27843379974365</t>
+    <t xml:space="preserve">9.10437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.52947425842285</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">9.24830913543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47257137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55625152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42571067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15124034881592</t>
+    <t xml:space="preserve">9.47257041931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55625247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4257116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15124130249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14789390563965</t>
+    <t xml:space="preserve">9.14789295196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.43240547180176</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">9.33533573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24161529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454555511475</t>
+    <t xml:space="preserve">9.24161434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">9.50939083099365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73700141906738</t>
+    <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
     <t xml:space="preserve">9.79724979400635</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62989139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38889026641846</t>
+    <t xml:space="preserve">9.62989044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
     <t xml:space="preserve">9.45248889923096</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">8.76631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62573051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.77300643920898</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">9.02404594421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40562725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63993072509766</t>
+    <t xml:space="preserve">9.4056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60311222076416</t>
+    <t xml:space="preserve">9.60311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">9.35542011260986</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94371509552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99057483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87342357635498</t>
+    <t xml:space="preserve">8.94371318817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9805326461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99057579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87342262268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068061828613</t>
+    <t xml:space="preserve">9.81063938140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.30521106719971</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">9.08764457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04413032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09099006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288272857666</t>
+    <t xml:space="preserve">9.0441312789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09099102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88346576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
@@ -2069,28 +2069,28 @@
     <t xml:space="preserve">8.88681125640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0039644241333</t>
+    <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06086540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15458869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97383880615234</t>
+    <t xml:space="preserve">9.060866355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1545877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97383785247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.11776828765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0809497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96714401245117</t>
+    <t xml:space="preserve">9.08094882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040798187256</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92698001861572</t>
+    <t xml:space="preserve">8.99726867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82990837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64246654510498</t>
+    <t xml:space="preserve">8.829909324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64246559143066</t>
   </si>
   <si>
     <t xml:space="preserve">8.40146827697754</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410701751709</t>
+    <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
@@ -2144,19 +2144,19 @@
     <t xml:space="preserve">8.03327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624853134155</t>
+    <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
     <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93286085128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02323436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96633243560791</t>
+    <t xml:space="preserve">7.93286037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96633148193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997039794922</t>
@@ -2165,16 +2165,16 @@
     <t xml:space="preserve">7.9429030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6717791557312</t>
+    <t xml:space="preserve">7.78558254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
     <t xml:space="preserve">7.12953233718872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22325372695923</t>
+    <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
     <t xml:space="preserve">7.54793167114258</t>
@@ -2189,28 +2189,28 @@
     <t xml:space="preserve">6.87514543533325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72786855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256633758545</t>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">6.15884494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55802249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57978010177612</t>
+    <t xml:space="preserve">5.55802297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.45091247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58566236495972</t>
+    <t xml:space="preserve">4.58566188812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.96556901931763</t>
@@ -2219,31 +2219,31 @@
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05929040908813</t>
+    <t xml:space="preserve">5.05928993225098</t>
   </si>
   <si>
     <t xml:space="preserve">5.27183723449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69023752212524</t>
+    <t xml:space="preserve">5.6902379989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98311710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05842876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23917818069458</t>
+    <t xml:space="preserve">5.98311758041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05842924118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47515535354614</t>
+    <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.49356508255005</t>
@@ -2252,22 +2252,22 @@
     <t xml:space="preserve">6.36637163162231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6174111366272</t>
+    <t xml:space="preserve">6.61741161346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.53038501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64753580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720304489136</t>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720399856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4266209602356</t>
+    <t xml:space="preserve">6.42662048339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.3596773147583</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00487375259399</t>
+    <t xml:space="preserve">6.00487470626831</t>
   </si>
   <si>
     <t xml:space="preserve">6.20235919952393</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156854629517</t>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156759262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.89776372909546</t>
@@ -2327,19 +2327,19 @@
     <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82747268676758</t>
+    <t xml:space="preserve">5.82747220993042</t>
   </si>
   <si>
     <t xml:space="preserve">5.68354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6601128578186</t>
+    <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
     <t xml:space="preserve">5.08439445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87017345428467</t>
+    <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
     <t xml:space="preserve">4.75302219390869</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">4.91368722915649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774185180664</t>
+    <t xml:space="preserve">5.08774137496948</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
@@ -2357,25 +2357,25 @@
     <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34212923049927</t>
+    <t xml:space="preserve">5.34212875366211</t>
   </si>
   <si>
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22162914276123</t>
+    <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74379205703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89106893539429</t>
+    <t xml:space="preserve">5.74379253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044561386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
     <t xml:space="preserve">5.94127750396729</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19819927215576</t>
+    <t xml:space="preserve">5.19819974899292</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861545562744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28522634506226</t>
+    <t xml:space="preserve">5.28522682189941</t>
   </si>
   <si>
     <t xml:space="preserve">5.30196237564087</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">5.23167085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886478424072</t>
+    <t xml:space="preserve">5.35886430740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.32204580307007</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">5.28187942504883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2283239364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04422807693481</t>
+    <t xml:space="preserve">5.22832345962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04422760009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.97059011459351</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
+    <t xml:space="preserve">5.11786699295044</t>
   </si>
   <si>
     <t xml:space="preserve">5.12121391296387</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">4.96389532089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41576719284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38898944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48940515518188</t>
+    <t xml:space="preserve">5.41576766967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38898992538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48940467834473</t>
   </si>
   <si>
     <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32874011993408</t>
+    <t xml:space="preserve">5.32874059677124</t>
   </si>
   <si>
     <t xml:space="preserve">5.57643270492554</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">6.15215063095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244215011597</t>
+    <t xml:space="preserve">6.27934503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244167327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880418777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524774551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441680908203</t>
+    <t xml:space="preserve">5.89441633224487</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375082015991</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61325168609619</t>
+    <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
     <t xml:space="preserve">5.4860577583313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48271131515503</t>
+    <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287721633911</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">5.73040437698364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55634927749634</t>
+    <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262788772583</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258665084839</t>
+    <t xml:space="preserve">5.45258617401123</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894821166992</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372894287109</t>
+    <t xml:space="preserve">4.92372941970825</t>
   </si>
   <si>
     <t xml:space="preserve">4.95385360717773</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21828269958496</t>
+    <t xml:space="preserve">5.2182822227478</t>
   </si>
   <si>
     <t xml:space="preserve">5.15468597412109</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09859561920166</t>
+    <t xml:space="preserve">6.09859609603882</t>
   </si>
   <si>
     <t xml:space="preserve">6.44335746765137</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63749504089355</t>
+    <t xml:space="preserve">6.6374945640564</t>
   </si>
   <si>
     <t xml:space="preserve">6.58728647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72117519378662</t>
+    <t xml:space="preserve">6.72117471694946</t>
   </si>
   <si>
     <t xml:space="preserve">6.67766141891479</t>
@@ -2669,37 +2669,37 @@
     <t xml:space="preserve">6.41323232650757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76134061813354</t>
+    <t xml:space="preserve">6.64418935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76134157180786</t>
   </si>
   <si>
     <t xml:space="preserve">7.10275506973267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936548233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961624145508</t>
+    <t xml:space="preserve">7.36383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647741317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936738967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961576461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.05589389801025</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">7.00233936309814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86175632476807</t>
+    <t xml:space="preserve">6.86175727844238</t>
   </si>
   <si>
     <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944986343384</t>
+    <t xml:space="preserve">7.10944938659668</t>
   </si>
   <si>
     <t xml:space="preserve">7.07597732543945</t>
@@ -2726,43 +2726,43 @@
     <t xml:space="preserve">7.14292144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200708389282</t>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200613021851</t>
   </si>
   <si>
     <t xml:space="preserve">6.96886730194092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90192365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11614513397217</t>
+    <t xml:space="preserve">6.90192270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.189781665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861701965332</t>
+    <t xml:space="preserve">7.18978261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581190109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861797332764</t>
   </si>
   <si>
     <t xml:space="preserve">7.08267164230347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13622617721558</t>
+    <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25003147125244</t>
+    <t xml:space="preserve">7.25003099441528</t>
   </si>
   <si>
     <t xml:space="preserve">7.27011585235596</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41069746017456</t>
+    <t xml:space="preserve">7.41069650650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39061403274536</t>
@@ -2792,28 +2792,28 @@
     <t xml:space="preserve">7.51111268997192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53789234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152839660645</t>
+    <t xml:space="preserve">7.53789138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6115288734436</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7588062286377</t>
+    <t xml:space="preserve">7.75880575180054</t>
   </si>
   <si>
     <t xml:space="preserve">7.85252714157104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1805534362793</t>
+    <t xml:space="preserve">8.07344436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18055438995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">8.91693592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849487304688</t>
+    <t xml:space="preserve">8.48849391937256</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485691070557</t>
+    <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724822998047</t>
+    <t xml:space="preserve">8.18724727630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
+    <t xml:space="preserve">8.26758098602295</t>
   </si>
   <si>
     <t xml:space="preserve">8.32782936096191</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">9.68009853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290508270264</t>
+    <t xml:space="preserve">9.55290412902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473476409912</t>
+    <t xml:space="preserve">9.9947338104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">10.0081224441528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.028205871582</t>
+    <t xml:space="preserve">10.0282068252563</t>
   </si>
   <si>
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365306854248</t>
+    <t xml:space="preserve">9.7738208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365211486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.5168972015381</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">10.476731300354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.677562713623</t>
+    <t xml:space="preserve">10.6775636672974</t>
   </si>
   <si>
     <t xml:space="preserve">10.6440916061401</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">10.038535118103</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84605598449707</t>
+    <t xml:space="preserve">9.84605503082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346567153931</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">10.1865949630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0755500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93489074707031</t>
+    <t xml:space="preserve">10.0755491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93489170074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.94969749450684</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">9.89787673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98671245574951</t>
+    <t xml:space="preserve">9.97931003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98671340942383</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047431945801</t>
+    <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80904006958008</t>
+    <t xml:space="preserve">9.80903911590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.85345840454102</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">9.40187168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524322509766</t>
+    <t xml:space="preserve">9.40927505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575008392334</t>
+    <t xml:space="preserve">9.10575103759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37225914001465</t>
+    <t xml:space="preserve">9.37226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.4166784286499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30563259124756</t>
+    <t xml:space="preserve">9.30563163757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.17237854003906</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199108123779</t>
+    <t xml:space="preserve">9.20199012756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31303596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35745525360107</t>
+    <t xml:space="preserve">9.3130350112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35745429992676</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016746520996</t>
+    <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.03171920776367</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">9.02431583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98730087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09834671020508</t>
+    <t xml:space="preserve">8.98730182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09834766387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">10.0237283706665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95710182189941</t>
+    <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.66838264465332</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">9.60915756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32784175872803</t>
+    <t xml:space="preserve">9.32784271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.46109580993652</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75040435791016</t>
+    <t xml:space="preserve">8.86885166168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24564838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24934959411621</t>
+    <t xml:space="preserve">4.2456488609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24935007095337</t>
   </si>
   <si>
     <t xml:space="preserve">4.20493173599243</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687046051025</t>
+    <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328698158264</t>
+    <t xml:space="preserve">4.04576635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328650474548</t>
   </si>
   <si>
     <t xml:space="preserve">3.58862781524658</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86069011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07537889480591</t>
+    <t xml:space="preserve">3.86069059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.04206418991089</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">3.90510845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96433281898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654246330261</t>
+    <t xml:space="preserve">3.96433234214783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">4.01985549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88660049438477</t>
+    <t xml:space="preserve">3.88660097122192</t>
   </si>
   <si>
     <t xml:space="preserve">3.8643913269043</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50164198875427</t>
+    <t xml:space="preserve">3.50164246559143</t>
   </si>
   <si>
     <t xml:space="preserve">3.53310513496399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55716466903687</t>
+    <t xml:space="preserve">3.55716514587402</t>
   </si>
   <si>
     <t xml:space="preserve">3.52014994621277</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459717750549</t>
+    <t xml:space="preserve">3.51459765434265</t>
   </si>
   <si>
     <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62009072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638927459717</t>
+    <t xml:space="preserve">3.6200909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358142852783</t>
+    <t xml:space="preserve">3.35358119010925</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2018187046051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26474452018738</t>
+    <t xml:space="preserve">3.14999747276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20181846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
     <t xml:space="preserve">3.10187745094299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">3.00748872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98342871665955</t>
+    <t xml:space="preserve">2.98342895507812</t>
   </si>
   <si>
     <t xml:space="preserve">2.93345808982849</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8649799823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86683082580566</t>
+    <t xml:space="preserve">2.86497974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503896713257</t>
@@ -3437,22 +3437,22 @@
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981514930725</t>
+    <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82426333427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83721852302551</t>
+    <t xml:space="preserve">2.82426309585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83721828460693</t>
   </si>
   <si>
     <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772395133972</t>
+    <t xml:space="preserve">2.6077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">2.52999210357666</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">2.60032105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297690391541</t>
+    <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
     <t xml:space="preserve">2.56515645980835</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57811164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888751983643</t>
+    <t xml:space="preserve">2.57811188697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.44855833053589</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">2.47817063331604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45596146583557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48927545547485</t>
+    <t xml:space="preserve">2.45596170425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48927521705627</t>
   </si>
   <si>
     <t xml:space="preserve">2.52629041671753</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18760108947754</t>
+    <t xml:space="preserve">2.18760085105896</t>
   </si>
   <si>
     <t xml:space="preserve">2.29679584503174</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">2.28569149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30234789848328</t>
+    <t xml:space="preserve">2.30234813690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35416960716248</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">2.26718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28754186630249</t>
+    <t xml:space="preserve">2.28754210472107</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18204855918884</t>
+    <t xml:space="preserve">2.18204879760742</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15798902511597</t>
+    <t xml:space="preserve">2.15798878669739</t>
   </si>
   <si>
     <t xml:space="preserve">2.14873504638672</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
+    <t xml:space="preserve">2.08765959739685</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688444137573</t>
+    <t xml:space="preserve">2.14688420295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912298202515</t>
+    <t xml:space="preserve">2.11912274360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652564048767</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810627937317</t>
+    <t xml:space="preserve">1.95810651779175</t>
   </si>
   <si>
     <t xml:space="preserve">1.86186683177948</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132367610931</t>
+    <t xml:space="preserve">1.90132343769073</t>
   </si>
   <si>
     <t xml:space="preserve">1.83638429641724</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.770623087883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556234836578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79199540615082</t>
+    <t xml:space="preserve">1.77062296867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79199552536011</t>
   </si>
   <si>
     <t xml:space="preserve">1.8585786819458</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311045646667</t>
+    <t xml:space="preserve">1.95311069488525</t>
   </si>
   <si>
     <t xml:space="preserve">1.95886468887329</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">2.00078773498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03695631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98023700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03942203521729</t>
+    <t xml:space="preserve">2.03695607185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98023724555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03942227363586</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">2.07970118522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0048975944519</t>
+    <t xml:space="preserve">2.00489735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.99749958515167</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204897880554</t>
+    <t xml:space="preserve">2.24204921722412</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135217666626</t>
+    <t xml:space="preserve">2.14135241508484</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573740005493</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">2.28520512580872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34480118751526</t>
+    <t xml:space="preserve">2.34480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">2.2728750705719</t>
@@ -3785,16 +3785,16 @@
     <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30781054496765</t>
+    <t xml:space="preserve">2.30781030654907</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685635566711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35096645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3427460193634</t>
+    <t xml:space="preserve">2.35096621513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34274625778198</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">2.14546227455139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21944379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24615955352783</t>
+    <t xml:space="preserve">2.21944403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24615931510925</t>
   </si>
   <si>
     <t xml:space="preserve">2.26670980453491</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">2.25437951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30986547470093</t>
+    <t xml:space="preserve">2.30986571311951</t>
   </si>
   <si>
     <t xml:space="preserve">2.3550763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41056227684021</t>
+    <t xml:space="preserve">2.41056251525879</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52769994735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55236053466797</t>
+    <t xml:space="preserve">2.52770018577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55236029624939</t>
   </si>
   <si>
     <t xml:space="preserve">2.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54003000259399</t>
+    <t xml:space="preserve">2.54003024101257</t>
   </si>
   <si>
     <t xml:space="preserve">2.45988345146179</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51125955581665</t>
+    <t xml:space="preserve">2.51125979423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5585253238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55647015571594</t>
+    <t xml:space="preserve">2.55852556228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55647039413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786423683167</t>
+    <t xml:space="preserve">2.75786447525024</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087383270264</t>
+    <t xml:space="preserve">2.72087359428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74142408370972</t>
+    <t xml:space="preserve">2.7414243221283</t>
   </si>
   <si>
     <t xml:space="preserve">2.70443344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72498369216919</t>
+    <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">2.78869009017944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77019453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703886032104</t>
+    <t xml:space="preserve">2.77019476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703909873962</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428689002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59757161140442</t>
+    <t xml:space="preserve">2.62428712844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59757137298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057915687561</t>
@@ -3995,10 +3995,10 @@
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524107933044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58935117721558</t>
+    <t xml:space="preserve">2.58524084091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58935141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97158861160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9140477180481</t>
+    <t xml:space="preserve">2.97158885002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91404747962952</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">3.00035953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99419379234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99830436706543</t>
+    <t xml:space="preserve">2.99419403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99830412864685</t>
   </si>
   <si>
     <t xml:space="preserve">2.89760732650757</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.82773566246033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74553442001343</t>
+    <t xml:space="preserve">2.74553418159485</t>
   </si>
   <si>
     <t xml:space="preserve">2.61606669425964</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896545410156</t>
+    <t xml:space="preserve">2.79896521568298</t>
   </si>
   <si>
     <t xml:space="preserve">2.7907452583313</t>
@@ -4079,16 +4079,16 @@
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93459796905518</t>
+    <t xml:space="preserve">2.9345977306366</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77224969863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78457999229431</t>
+    <t xml:space="preserve">2.7722499370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78457975387573</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10927629470825</t>
+    <t xml:space="preserve">2.82979083061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89555239677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10927653312683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">2.9633686542511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93665313720703</t>
+    <t xml:space="preserve">2.93665289878845</t>
   </si>
   <si>
     <t xml:space="preserve">2.89966225624084</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82568073272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92226791381836</t>
+    <t xml:space="preserve">2.82568097114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92226767539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.88733220100403</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995559692383</t>
+    <t xml:space="preserve">3.05995535850525</t>
   </si>
   <si>
     <t xml:space="preserve">2.9818639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0126895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94281792640686</t>
+    <t xml:space="preserve">3.01268935203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">2.92432260513306</t>
@@ -5607,9 +5607,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.99799990653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90199995040894</t>
   </si>
 </sst>
 </file>
@@ -71052,25 +71049,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6918055556</v>
+        <v>45968.6911921296</v>
       </c>
       <c r="B2505" t="n">
-        <v>652923</v>
+        <v>442507</v>
       </c>
       <c r="C2505" t="n">
-        <v>4.01800012588501</v>
+        <v>3.97000002861023</v>
       </c>
       <c r="D2505" t="n">
-        <v>3.90199995040894</v>
+        <v>3.85800004005432</v>
       </c>
       <c r="E2505" t="n">
-        <v>4.01000022888184</v>
+        <v>3.90400004386902</v>
       </c>
       <c r="F2505" t="n">
-        <v>3.90199995040894</v>
+        <v>3.94600009918213</v>
       </c>
       <c r="G2505" t="s">
-        <v>1865</v>
+        <v>1810</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="1865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1867">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027997970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895690917969</t>
+    <t xml:space="preserve">12.1956882476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7028007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895700454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.4097309112549</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">10.9101800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.076696395874</t>
+    <t xml:space="preserve">11.0766983032227</t>
   </si>
   <si>
     <t xml:space="preserve">11.136643409729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770582199097</t>
+    <t xml:space="preserve">10.8302526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770572662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.3107204437256</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507753372192</t>
+    <t xml:space="preserve">10.2507734298706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7370042800903</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4239521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438442230225</t>
+    <t xml:space="preserve">10.4239511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574348449707</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">10.4838972091675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2973985671997</t>
+    <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
     <t xml:space="preserve">10.1042394638062</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">10.7170219421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77786731719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91107940673828</t>
+    <t xml:space="preserve">9.77786636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
     <t xml:space="preserve">9.54474353790283</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">10.2174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4639148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6171112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4172925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703075408936</t>
+    <t xml:space="preserve">10.4639167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.617112159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4172916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7703065872192</t>
   </si>
   <si>
     <t xml:space="preserve">10.9301624298096</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236824035645</t>
+    <t xml:space="preserve">10.7236814498901</t>
   </si>
   <si>
     <t xml:space="preserve">10.9434843063354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4363737106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3431243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6495151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898397445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0624771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627468109131</t>
+    <t xml:space="preserve">11.4363746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3431253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6495161056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.062479019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627458572388</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289943695068</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">12.475438117981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4554586410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422260284424</t>
+    <t xml:space="preserve">12.4554567337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422250747681</t>
   </si>
   <si>
     <t xml:space="preserve">12.4621171951294</t>
@@ -197,82 +197,82 @@
     <t xml:space="preserve">12.6019916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6961402893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5695877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0757961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9159421920776</t>
+    <t xml:space="preserve">12.1823692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.696138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5695896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0757970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9159412384033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1890296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.496319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0633783340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.656177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9559059143066</t>
+    <t xml:space="preserve">11.4963207244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0633764266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.955906867981</t>
   </si>
   <si>
     <t xml:space="preserve">12.2689580917358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8217945098877</t>
+    <t xml:space="preserve">12.8217926025391</t>
   </si>
   <si>
     <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947917938232</t>
+    <t xml:space="preserve">12.9350242614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1015424728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947908401489</t>
   </si>
   <si>
     <t xml:space="preserve">13.1814699172974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1614875793457</t>
+    <t xml:space="preserve">13.1614894866943</t>
   </si>
   <si>
     <t xml:space="preserve">13.361307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2347555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946132659912</t>
+    <t xml:space="preserve">13.2347564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946123123169</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.981650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6885786056519</t>
+    <t xml:space="preserve">12.9816484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6885795593262</t>
   </si>
   <si>
     <t xml:space="preserve">12.5620288848877</t>
@@ -284,22 +284,22 @@
     <t xml:space="preserve">12.8617572784424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8884000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482549667358</t>
+    <t xml:space="preserve">12.8884010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482568740845</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488874435425</t>
+    <t xml:space="preserve">12.3755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488864898682</t>
   </si>
   <si>
     <t xml:space="preserve">12.7218837738037</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887929916382</t>
+    <t xml:space="preserve">13.134407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159873962402</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">13.5226831436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5561542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620157241821</t>
+    <t xml:space="preserve">13.5561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.422266960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620147705078</t>
   </si>
   <si>
     <t xml:space="preserve">13.3553228378296</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156108856201</t>
+    <t xml:space="preserve">13.2749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1946544647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.659104347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833864212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156118392944</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620544433594</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">11.7218894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0766935348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524095535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850898742676</t>
+    <t xml:space="preserve">12.0766925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850889205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.1487054824829</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599744796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1260890960693</t>
+    <t xml:space="preserve">11.2599754333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126088142395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122842788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8114500045776</t>
+    <t xml:space="preserve">11.0122833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.811450958252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783941268921</t>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0616779327393</t>
+    <t xml:space="preserve">10.0616788864136</t>
   </si>
   <si>
     <t xml:space="preserve">10.175482749939</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06421375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93032455444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67593765258789</t>
+    <t xml:space="preserve">9.0642147064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93032550811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67593860626221</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313205718994</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">9.20479488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37215423583984</t>
+    <t xml:space="preserve">9.37215518951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33868312835693</t>
+    <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.23826789855957</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37884998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19140720367432</t>
+    <t xml:space="preserve">9.13115692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37885093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63323783874512</t>
+    <t xml:space="preserve">9.6332368850708</t>
   </si>
   <si>
     <t xml:space="preserve">9.79390335083008</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">9.55959796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43909931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265575408936</t>
+    <t xml:space="preserve">9.51273822784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">9.53951549530029</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">9.82737445831299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76043128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78720760345459</t>
+    <t xml:space="preserve">9.76043033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78720855712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.87423610687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67340469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760238647461</t>
+    <t xml:space="preserve">9.6734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760334014893</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">9.07090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3119068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207366943359</t>
+    <t xml:space="preserve">9.08429718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31190586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3855447769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24496269226074</t>
+    <t xml:space="preserve">9.38554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24496364593506</t>
   </si>
   <si>
     <t xml:space="preserve">9.03743553161621</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">8.87007617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7696590423584</t>
+    <t xml:space="preserve">8.76966094970703</t>
   </si>
   <si>
     <t xml:space="preserve">8.74957656860352</t>
@@ -593,43 +593,43 @@
     <t xml:space="preserve">8.78304958343506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78974437713623</t>
+    <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.71610546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66924285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3345251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20063591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
+    <t xml:space="preserve">8.66924381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2006368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10022163391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.1203031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79227781295776</t>
+    <t xml:space="preserve">7.79227924346924</t>
   </si>
   <si>
     <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83913898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63161277770996</t>
+    <t xml:space="preserve">7.83913850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63161182403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.62491893768311</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7119460105896</t>
+    <t xml:space="preserve">7.74541664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71194648742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.69186162948608</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">7.48433637619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64500188827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95963716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12699794769287</t>
+    <t xml:space="preserve">7.64500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.651695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516683578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.38138484954834</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21148872375488</t>
+    <t xml:space="preserve">9.2114896774292</t>
   </si>
   <si>
     <t xml:space="preserve">9.09768581390381</t>
@@ -686,76 +686,76 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499143600464</t>
+    <t xml:space="preserve">11.8691654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499134063721</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615608215332</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2833061218262</t>
+    <t xml:space="preserve">15.2833070755005</t>
   </si>
   <si>
     <t xml:space="preserve">13.7971525192261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6967344284058</t>
+    <t xml:space="preserve">13.6967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569856643677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975667953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908739089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180683135986</t>
+    <t xml:space="preserve">13.8975677490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235136032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180692672729</t>
   </si>
   <si>
     <t xml:space="preserve">14.0582332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9712076187134</t>
+    <t xml:space="preserve">13.9712057113647</t>
   </si>
   <si>
     <t xml:space="preserve">14.0917053222656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3126201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2858428955078</t>
+    <t xml:space="preserve">14.3126211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2858438491821</t>
   </si>
   <si>
     <t xml:space="preserve">14.1385669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251783370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8172359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557390213013</t>
+    <t xml:space="preserve">14.1251764297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817234992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101259231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.455738067627</t>
   </si>
   <si>
     <t xml:space="preserve">13.2415180206299</t>
@@ -764,22 +764,22 @@
     <t xml:space="preserve">13.1544904708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2549047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2080450057983</t>
+    <t xml:space="preserve">13.2549066543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.208044052124</t>
   </si>
   <si>
     <t xml:space="preserve">12.9268798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7528247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737415313721</t>
+    <t xml:space="preserve">12.7528257369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067974090576</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">13.2147388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1879625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419351577759</t>
+    <t xml:space="preserve">13.1879634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419332504272</t>
   </si>
   <si>
     <t xml:space="preserve">13.181266784668</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">13.033989906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8599348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0473794937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0206022262573</t>
+    <t xml:space="preserve">12.859935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.007212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0473785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0206031799316</t>
   </si>
   <si>
     <t xml:space="preserve">12.9201860427856</t>
@@ -830,73 +830,73 @@
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758195877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3486289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214336395264</t>
+    <t xml:space="preserve">13.3754053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3486280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214326858521</t>
   </si>
   <si>
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406837463379</t>
+    <t xml:space="preserve">13.0406856536865</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.933575630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8398532867432</t>
+    <t xml:space="preserve">12.8867130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9335746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8398523330688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9001035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9536581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3109951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3310785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4047183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2708301544189</t>
+    <t xml:space="preserve">12.9536590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.819769859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858835220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.310996055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3310794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4047174453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2708292007446</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6750288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624696731567</t>
+    <t xml:space="preserve">11.67502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624706268311</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771087646484</t>
@@ -914,31 +914,31 @@
     <t xml:space="preserve">12.9469633102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448833465576</t>
+    <t xml:space="preserve">12.5653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448852539062</t>
   </si>
   <si>
     <t xml:space="preserve">12.1637201309204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3043012619019</t>
+    <t xml:space="preserve">12.3043003082275</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558690071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649686813354</t>
+    <t xml:space="preserve">12.5586891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649667739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574405670166</t>
+    <t xml:space="preserve">12.2574396133423</t>
   </si>
   <si>
     <t xml:space="preserve">12.2842178344727</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1034708023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0900812149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0633029937744</t>
+    <t xml:space="preserve">12.197190284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1034698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0900802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0633039474487</t>
   </si>
   <si>
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6724948883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3176898956299</t>
+    <t xml:space="preserve">12.672492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3176889419556</t>
   </si>
   <si>
     <t xml:space="preserve">11.8089160919189</t>
@@ -980,52 +980,52 @@
     <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076694488525</t>
+    <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880002975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7084999084473</t>
+    <t xml:space="preserve">11.5879993438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7085008621216</t>
   </si>
   <si>
     <t xml:space="preserve">11.6817226409912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942789077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5210552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.634861946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7687501907349</t>
+    <t xml:space="preserve">11.4942798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5210571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6348609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7687492370605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7018051147461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4474191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3804759979248</t>
+    <t xml:space="preserve">11.4474182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.2265043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.777979850769</t>
+    <t xml:space="preserve">10.7779788970947</t>
   </si>
   <si>
     <t xml:space="preserve">10.7043399810791</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9453392028809</t>
+    <t xml:space="preserve">10.9453401565552</t>
   </si>
   <si>
     <t xml:space="preserve">11.1394758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1930322647095</t>
+    <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
     <t xml:space="preserve">11.1461706161499</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">11.0658388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1327810287476</t>
+    <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591440200806</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">11.1528654098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.099310874939</t>
+    <t xml:space="preserve">11.0993099212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.1997261047363</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4206399917603</t>
+    <t xml:space="preserve">11.1126985549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4206390380859</t>
   </si>
   <si>
     <t xml:space="preserve">11.5411415100098</t>
@@ -1079,34 +1079,34 @@
     <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3001413345337</t>
+    <t xml:space="preserve">11.2198095321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.300142288208</t>
   </si>
   <si>
     <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4608087539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3336133956909</t>
+    <t xml:space="preserve">11.4608097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541139602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336143493652</t>
   </si>
   <si>
     <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1595592498779</t>
+    <t xml:space="preserve">11.1595602035522</t>
   </si>
   <si>
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721155166626</t>
+    <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302858352661</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">10.1620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156505584717</t>
+    <t xml:space="preserve">10.2156496047974</t>
   </si>
   <si>
     <t xml:space="preserve">10.3361492156982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4901208877563</t>
+    <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">10.3428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3562316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84076309204102</t>
+    <t xml:space="preserve">10.3562326431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8407621383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68679332733154</t>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026443481445</t>
+    <t xml:space="preserve">9.72026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704170227051</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70018100738525</t>
+    <t xml:space="preserve">9.75373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70018196105957</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">10.7110347747803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6507863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6708679199219</t>
+    <t xml:space="preserve">10.650785446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6708688735962</t>
   </si>
   <si>
     <t xml:space="preserve">10.6641750335693</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.188871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2758989334106</t>
+    <t xml:space="preserve">10.1888723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2223443984985</t>
+    <t xml:space="preserve">10.2223453521729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2357339859009</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102024078369</t>
+    <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089567184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65331935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52612590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62654209136963</t>
+    <t xml:space="preserve">10.2089557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52612686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8474588394165</t>
+    <t xml:space="preserve">9.84745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436744689941</t>
+    <t xml:space="preserve">10.5436754226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5972309112549</t>
+    <t xml:space="preserve">10.5972299575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.8583116531372</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">10.7311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.82483959198</t>
+    <t xml:space="preserve">10.8248405456543</t>
   </si>
   <si>
     <t xml:space="preserve">10.9654216766357</t>
@@ -1268,52 +1268,52 @@
     <t xml:space="preserve">10.998893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926160812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1796426773071</t>
+    <t xml:space="preserve">11.0926151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1796436309814</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0859212875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9185619354248</t>
+    <t xml:space="preserve">11.0859203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9185609817505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051723480225</t>
+    <t xml:space="preserve">10.9051733016968</t>
   </si>
   <si>
     <t xml:space="preserve">10.8917837142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7512016296387</t>
+    <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633417129517</t>
+    <t xml:space="preserve">10.7277708053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.463342666626</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871868133545</t>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2658586502075</t>
+    <t xml:space="preserve">10.2658576965332</t>
   </si>
   <si>
     <t xml:space="preserve">10.3696203231812</t>
@@ -1322,82 +1322,82 @@
     <t xml:space="preserve">10.5135507583618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6206607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8616590499878</t>
+    <t xml:space="preserve">10.6206617355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.6407442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106185913086</t>
+    <t xml:space="preserve">10.6106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">10.5503692626953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5771474838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.533634185791</t>
+    <t xml:space="preserve">10.5771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6240081787109</t>
+    <t xml:space="preserve">10.6240072250366</t>
   </si>
   <si>
     <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.172947883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982159614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269403457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261060714722</t>
+    <t xml:space="preserve">11.1729497909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9821586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261070251465</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394966125488</t>
+    <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1520528793335</t>
+    <t xml:space="preserve">10.1520538330078</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821775436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94452667236328</t>
+    <t xml:space="preserve">10.1821784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94452571868896</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349016189575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951490402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9788093566895</t>
+    <t xml:space="preserve">10.0951499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9788112640381</t>
   </si>
   <si>
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357122421265</t>
+    <t xml:space="preserve">11.0357141494751</t>
   </si>
   <si>
     <t xml:space="preserve">11.1762952804565</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620761871338</t>
+    <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.0223245620728</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">10.9553804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256719589233</t>
+    <t xml:space="preserve">11.025671005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.0825748443604</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">10.952033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0290184020996</t>
+    <t xml:space="preserve">11.0290193557739</t>
   </si>
   <si>
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2867546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.313530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9352960586548</t>
+    <t xml:space="preserve">11.28675365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3135299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9352970123291</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729677200317</t>
+    <t xml:space="preserve">10.3729686737061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.245774269104</t>
+    <t xml:space="preserve">10.2457752227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74369525909424</t>
+    <t xml:space="preserve">9.74369621276855</t>
   </si>
   <si>
     <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6700553894043</t>
+    <t xml:space="preserve">9.34537887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67005634307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.72695827484131</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">9.48596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637714385986</t>
+    <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5428638458252</t>
+    <t xml:space="preserve">9.54286289215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298755645752</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50269603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47926616668701</t>
+    <t xml:space="preserve">9.5026969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4792652130127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319660186768</t>
+    <t xml:space="preserve">9.62319469451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932819366455</t>
+    <t xml:space="preserve">8.68932723999023</t>
   </si>
   <si>
     <t xml:space="preserve">8.72949409484863</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22488021850586</t>
+    <t xml:space="preserve">9.30186462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22487926483154</t>
   </si>
   <si>
     <t xml:space="preserve">9.28512859344482</t>
@@ -1541,28 +1541,28 @@
     <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45583629608154</t>
+    <t xml:space="preserve">9.13785171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28178215026855</t>
+    <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
     <t xml:space="preserve">9.61315441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7169189453125</t>
+    <t xml:space="preserve">9.71691703796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550354003906</t>
+    <t xml:space="preserve">9.37550258636475</t>
   </si>
   <si>
     <t xml:space="preserve">9.54621028900146</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73284149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02070140838623</t>
+    <t xml:space="preserve">8.7328405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
     <t xml:space="preserve">8.85334014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86338138580322</t>
+    <t xml:space="preserve">8.86338043212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003494262695</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88011741638184</t>
+    <t xml:space="preserve">8.88011837005615</t>
   </si>
   <si>
     <t xml:space="preserve">8.82656288146973</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29770565032959</t>
+    <t xml:space="preserve">8.29770469665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.2742748260498</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2508430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64581489562988</t>
+    <t xml:space="preserve">8.25084400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64581394195557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795402526855</t>
@@ -1631,25 +1631,25 @@
     <t xml:space="preserve">8.47175979614258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53870296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71944999694824</t>
+    <t xml:space="preserve">8.53870391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71945190429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635478973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16462993621826</t>
+    <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
     <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00731086730957</t>
+    <t xml:space="preserve">9.00730991363525</t>
   </si>
   <si>
     <t xml:space="preserve">9.01065826416016</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94706058502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00061702728271</t>
+    <t xml:space="preserve">8.94706249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735210418701</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66589641571045</t>
+    <t xml:space="preserve">8.66589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">8.47510623931885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30105209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62907886505127</t>
+    <t xml:space="preserve">8.30105113983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62907791137695</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90689468383789</t>
+    <t xml:space="preserve">8.90689563751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.29517078399658</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">9.30855846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50604438781738</t>
+    <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.46587657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1110725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29435729980469</t>
+    <t xml:space="preserve">9.12111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
     <t xml:space="preserve">8.31109428405762</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">8.34456539154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32448291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749755859375</t>
+    <t xml:space="preserve">8.32448387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749565124512</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514842987061</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93367385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">8.93367290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19810009002686</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">8.70271682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25753879547119</t>
+    <t xml:space="preserve">8.25753784179688</t>
   </si>
   <si>
     <t xml:space="preserve">8.56548118591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5018835067749</t>
+    <t xml:space="preserve">8.50188446044922</t>
   </si>
   <si>
     <t xml:space="preserve">8.75627136230469</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236232757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169776916504</t>
+    <t xml:space="preserve">9.42236423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169872283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.29851722717285</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">9.91105556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84411144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52277946472168</t>
+    <t xml:space="preserve">9.8441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.522780418396</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7127571105957</t>
+    <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10437965393066</t>
+    <t xml:space="preserve">9.10438060760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843284606934</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">9.52947425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51943302154541</t>
+    <t xml:space="preserve">9.51943206787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.42905807495117</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24830913543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47257041931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55625247955322</t>
+    <t xml:space="preserve">9.2483081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47257137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.4257116317749</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">9.15124130249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128158569336</t>
+    <t xml:space="preserve">9.16128253936768</t>
   </si>
   <si>
     <t xml:space="preserve">9.14789295196533</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533573150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24161434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.33533668518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24161529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79724979400635</t>
+    <t xml:space="preserve">9.79725074768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.9210958480835</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62572956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953628540039</t>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62573146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953533172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.77300643920898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75961875915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02404594421387</t>
+    <t xml:space="preserve">8.75961780548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02404689788818</t>
   </si>
   <si>
     <t xml:space="preserve">9.4056282043457</t>
@@ -1967,22 +1967,22 @@
     <t xml:space="preserve">9.94787406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76712608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66670989990234</t>
+    <t xml:space="preserve">9.76712417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
     <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60311126708984</t>
+    <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20144844055176</t>
+    <t xml:space="preserve">9.20144939422607</t>
   </si>
   <si>
     <t xml:space="preserve">9.10103321075439</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">8.99057579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342262268066</t>
+    <t xml:space="preserve">8.87342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
@@ -2012,100 +2012,100 @@
     <t xml:space="preserve">8.67928600311279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86084651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82402801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81063938140869</t>
+    <t xml:space="preserve">10.0415964126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82402896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81063842773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30521106719971</t>
+    <t xml:space="preserve">9.30521202087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.15793514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16797542572021</t>
+    <t xml:space="preserve">9.16797637939453</t>
   </si>
   <si>
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0441312789917</t>
+    <t xml:space="preserve">9.08764362335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04413032531738</t>
   </si>
   <si>
     <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88346576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79308986663818</t>
+    <t xml:space="preserve">8.88346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288368225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7930908203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681125640869</t>
+    <t xml:space="preserve">8.84664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681221008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05417156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.060866355896</t>
+    <t xml:space="preserve">9.05417060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06086540222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
+    <t xml:space="preserve">8.97383880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094787597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95040798187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90019989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94036674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99726867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92697906494141</t>
+    <t xml:space="preserve">8.95040893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90020084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94036769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99726963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92697811126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64246559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40146827697754</t>
+    <t xml:space="preserve">8.64246654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40146732330322</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410797119141</t>
+    <t xml:space="preserve">8.23410701751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98976230621338</t>
+    <t xml:space="preserve">7.98976373672485</t>
   </si>
   <si>
     <t xml:space="preserve">8.06005382537842</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94624900817871</t>
+    <t xml:space="preserve">8.03327655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94624948501587</t>
   </si>
   <si>
     <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93286037445068</t>
+    <t xml:space="preserve">7.93285989761353</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323532104492</t>
@@ -2162,52 +2162,52 @@
     <t xml:space="preserve">8.03997039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9429030418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558254241943</t>
+    <t xml:space="preserve">7.94290161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12953233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22325468063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793167114258</t>
+    <t xml:space="preserve">7.1295313835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22325420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793214797974</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786951065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15884494781494</t>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15884447097778</t>
   </si>
   <si>
     <t xml:space="preserve">5.55802297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45091247558594</t>
+    <t xml:space="preserve">5.57978010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05928993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6902379989624</t>
+    <t xml:space="preserve">5.05929040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693183898926</t>
@@ -2243,61 +2243,61 @@
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47515487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038501739502</t>
+    <t xml:space="preserve">6.47515535354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49356460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53038454055786</t>
   </si>
   <si>
     <t xml:space="preserve">6.647536277771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56720399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662048339844</t>
+    <t xml:space="preserve">6.56720352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266209602356</t>
   </si>
   <si>
     <t xml:space="preserve">6.3596773147583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09190130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03834676742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1789288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85759735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00487470626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20235919952393</t>
+    <t xml:space="preserve">6.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03834629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85759687423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00487422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20235872268677</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628820419312</t>
+    <t xml:space="preserve">6.32620429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628868103027</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01826286315918</t>
+    <t xml:space="preserve">6.01826238632202</t>
   </si>
   <si>
     <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01156759262085</t>
+    <t xml:space="preserve">6.01156806945801</t>
   </si>
   <si>
     <t xml:space="preserve">5.89776372909546</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87433290481567</t>
+    <t xml:space="preserve">6.05508184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87433338165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747220993042</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08439445495605</t>
+    <t xml:space="preserve">5.0843939781189</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75302219390869</t>
+    <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
     <t xml:space="preserve">4.91368722915649</t>
@@ -2378,34 +2378,34 @@
     <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94127750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82077836990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60655736923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29526805877686</t>
+    <t xml:space="preserve">5.94127702713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82077789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60655784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29526853561401</t>
   </si>
   <si>
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19819974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29861545562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28522682189941</t>
+    <t xml:space="preserve">5.1981987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29861497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
     <t xml:space="preserve">5.30196237564087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.238365650177</t>
+    <t xml:space="preserve">5.23836517333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.33208751678467</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">5.27853202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23167085647583</t>
+    <t xml:space="preserve">5.23167133331299</t>
   </si>
   <si>
     <t xml:space="preserve">5.35886430740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32204580307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32539319992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28187942504883</t>
+    <t xml:space="preserve">5.32204532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3253927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
     <t xml:space="preserve">5.22832345962524</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">4.97059011459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02079772949219</t>
+    <t xml:space="preserve">4.94046545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02079820632935</t>
   </si>
   <si>
     <t xml:space="preserve">5.08104705810547</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790775299072</t>
+    <t xml:space="preserve">5.12790822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
@@ -2468,25 +2468,25 @@
     <t xml:space="preserve">5.05092239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98063135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10447835922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0375337600708</t>
+    <t xml:space="preserve">4.98063182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03753328323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.96389532089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41576766967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38898992538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48940467834473</t>
+    <t xml:space="preserve">5.41576719284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38898944854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48940563201904</t>
   </si>
   <si>
     <t xml:space="preserve">5.36890649795532</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961277008057</t>
+    <t xml:space="preserve">5.53961324691772</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568424224854</t>
+    <t xml:space="preserve">5.39568376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221170425415</t>
@@ -2516,31 +2516,31 @@
     <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3454761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3053092956543</t>
+    <t xml:space="preserve">5.34547567367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30530977249146</t>
   </si>
   <si>
     <t xml:space="preserve">5.27518463134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09108877182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60320997238159</t>
+    <t xml:space="preserve">5.09108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60321044921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537336349487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215063095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934503555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244167327881</t>
+    <t xml:space="preserve">6.15215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27934455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244262695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">6.1488037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09524774551392</t>
+    <t xml:space="preserve">6.09524869918823</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441633224487</t>
+    <t xml:space="preserve">5.89441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375082015991</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4860577583313</t>
+    <t xml:space="preserve">5.48605823516846</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271083831787</t>
@@ -2579,31 +2579,31 @@
     <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040437698364</t>
+    <t xml:space="preserve">5.7304048538208</t>
   </si>
   <si>
     <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65676546096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5563497543335</t>
+    <t xml:space="preserve">5.70362615585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65676498413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55634927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47266960144043</t>
+    <t xml:space="preserve">5.47267007827759</t>
   </si>
   <si>
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258617401123</t>
+    <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894821166992</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372941970825</t>
+    <t xml:space="preserve">4.92372894287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.95385360717773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88021564483643</t>
+    <t xml:space="preserve">4.88021516799927</t>
   </si>
   <si>
     <t xml:space="preserve">4.94381237030029</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02830410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80820178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6374945640564</t>
+    <t xml:space="preserve">6.02830457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0985951423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44335651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8082013130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63749504089355</t>
   </si>
   <si>
     <t xml:space="preserve">6.58728647232056</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">6.67766141891479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41323232650757</t>
+    <t xml:space="preserve">6.41323184967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.64418935775757</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">6.76134157180786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647741317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936738967896</t>
+    <t xml:space="preserve">7.10275459289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283849716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936595916748</t>
   </si>
   <si>
     <t xml:space="preserve">6.97556114196777</t>
@@ -2699,16 +2699,16 @@
     <t xml:space="preserve">7.20986557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14961576461792</t>
+    <t xml:space="preserve">7.14961671829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.05589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175727844238</t>
+    <t xml:space="preserve">7.0023398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175680160522</t>
   </si>
   <si>
     <t xml:space="preserve">7.0692834854126</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98225593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14292144775391</t>
+    <t xml:space="preserve">6.9822564125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14292192459106</t>
   </si>
   <si>
     <t xml:space="preserve">7.09606170654297</t>
@@ -2741,37 +2741,37 @@
     <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01572799682617</t>
+    <t xml:space="preserve">7.01572751998901</t>
   </si>
   <si>
     <t xml:space="preserve">7.18978261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581190109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267164230347</t>
+    <t xml:space="preserve">7.03581094741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267211914062</t>
   </si>
   <si>
     <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15631008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25003099441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011585235596</t>
+    <t xml:space="preserve">7.15631055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25003242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011489868164</t>
   </si>
   <si>
     <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55127954483032</t>
+    <t xml:space="preserve">7.55128002166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
@@ -2783,22 +2783,22 @@
     <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47094631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56466865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51111268997192</t>
+    <t xml:space="preserve">7.47094774246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56466913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5111141204834</t>
   </si>
   <si>
     <t xml:space="preserve">7.53789138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6115288734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61822414398193</t>
+    <t xml:space="preserve">7.61152839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61822319030762</t>
   </si>
   <si>
     <t xml:space="preserve">7.75880575180054</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">7.85252714157104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07344436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18055438995361</t>
+    <t xml:space="preserve">8.07344341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1805534362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">8.91693592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849391937256</t>
+    <t xml:space="preserve">8.48849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21402549743652</t>
+    <t xml:space="preserve">8.21402454376221</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45502281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.45502376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
@@ -2861,34 +2861,34 @@
     <t xml:space="preserve">7.81236171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77888870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938879013062</t>
+    <t xml:space="preserve">7.77888965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277599334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938831329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049236297607</t>
+    <t xml:space="preserve">8.97049140930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290412902832</t>
+    <t xml:space="preserve">9.55290508270264</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9947338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96126270294189</t>
+    <t xml:space="preserve">9.99473476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96126365661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.94118022918701</t>
@@ -2900,31 +2900,31 @@
     <t xml:space="preserve">10.0282068252563</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85415267944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7738208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365211486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168972015381</t>
+    <t xml:space="preserve">9.85415172576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77381896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168981552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039247512817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.476731300354</t>
+    <t xml:space="preserve">10.4767303466797</t>
   </si>
   <si>
     <t xml:space="preserve">10.6775636672974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440916061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.038535118103</t>
+    <t xml:space="preserve">10.6440906524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0385360717773</t>
   </si>
   <si>
     <t xml:space="preserve">9.84605503082275</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">10.0755491256714</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93489170074463</t>
+    <t xml:space="preserve">9.93489265441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.94969749450684</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462173461914</t>
+    <t xml:space="preserve">9.76462078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">9.97931003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98671340942383</t>
+    <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047336578369</t>
+    <t xml:space="preserve">9.89047241210938</t>
   </si>
   <si>
     <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80903911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.80904006958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7720251083374</t>
+    <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0533409118652</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54993343353271</t>
+    <t xml:space="preserve">9.6017541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5499324798584</t>
   </si>
   <si>
     <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187168121338</t>
+    <t xml:space="preserve">9.4018726348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524417877197</t>
+    <t xml:space="preserve">9.33524513244629</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575103759766</t>
+    <t xml:space="preserve">9.10574913024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34634971618652</t>
+    <t xml:space="preserve">9.34634876251221</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11315250396729</t>
+    <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3130350112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35745429992676</t>
+    <t xml:space="preserve">9.31303691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35745525360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
@@ -3095,31 +3095,31 @@
     <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03171920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02431583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98730182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09834766387939</t>
+    <t xml:space="preserve">9.03172016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02431678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98730278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09834671020508</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80163669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0237283706665</t>
+    <t xml:space="preserve">9.8016357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0237293243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.66838359832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3131,22 +3131,22 @@
     <t xml:space="preserve">9.46109580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43148422241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52772331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86885166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75040340423584</t>
+    <t xml:space="preserve">9.43148326873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52772426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86885261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75040245056152</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93548011779785</t>
+    <t xml:space="preserve">8.93547916412354</t>
   </si>
   <si>
     <t xml:space="preserve">8.80962753295898</t>
@@ -3161,28 +3161,28 @@
     <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51585960388184</t>
+    <t xml:space="preserve">4.51586008071899</t>
   </si>
   <si>
     <t xml:space="preserve">4.58989000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62690544128418</t>
+    <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5824875831604</t>
+    <t xml:space="preserve">4.58248710632324</t>
   </si>
   <si>
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128879547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090133666992</t>
+    <t xml:space="preserve">4.10128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090181350708</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2456488609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24935007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20493173599243</t>
+    <t xml:space="preserve">4.24564838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24934959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20493125915527</t>
   </si>
   <si>
     <t xml:space="preserve">4.12719964981079</t>
@@ -3227,19 +3227,19 @@
     <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741134643555</t>
+    <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.36039590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758758544922</t>
+    <t xml:space="preserve">4.15311098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10499048233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758710861206</t>
   </si>
   <si>
     <t xml:space="preserve">4.17902135848999</t>
@@ -3248,34 +3248,34 @@
     <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06057214736938</t>
+    <t xml:space="preserve">4.06057262420654</t>
   </si>
   <si>
     <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87549614906311</t>
+    <t xml:space="preserve">3.87549662590027</t>
   </si>
   <si>
     <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58862781524658</t>
+    <t xml:space="preserve">3.85328698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862805366516</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86069059371948</t>
+    <t xml:space="preserve">3.8606903553009</t>
   </si>
   <si>
     <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206418991089</t>
+    <t xml:space="preserve">4.04206466674805</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94952654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433234214783</t>
+    <t xml:space="preserve">3.9495267868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9051079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433305740356</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95322823524475</t>
+    <t xml:space="preserve">3.95322847366333</t>
   </si>
   <si>
     <t xml:space="preserve">4.05316925048828</t>
@@ -3311,28 +3311,28 @@
     <t xml:space="preserve">4.01985549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88660097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8643913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036092758179</t>
+    <t xml:space="preserve">3.88660073280334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86439156532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036140441895</t>
   </si>
   <si>
     <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50164246559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53310513496399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52014994621277</t>
+    <t xml:space="preserve">3.50164198875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53310537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716490745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52015018463135</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313450813293</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6200909614563</t>
+    <t xml:space="preserve">3.62009072303772</t>
   </si>
   <si>
     <t xml:space="preserve">3.61638975143433</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42391037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33137226104736</t>
+    <t xml:space="preserve">3.42391014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33137178421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">3.14999747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20181846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2647442817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10187745094299</t>
+    <t xml:space="preserve">3.2018187046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26474452018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10187768936157</t>
   </si>
   <si>
     <t xml:space="preserve">3.01304125785828</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">2.88718914985657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05005621910095</t>
+    <t xml:space="preserve">3.05005598068237</t>
   </si>
   <si>
     <t xml:space="preserve">3.00748872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93345808982849</t>
+    <t xml:space="preserve">2.98342871665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93345832824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86497974395752</t>
+    <t xml:space="preserve">2.8649799823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503896713257</t>
+    <t xml:space="preserve">2.76503872871399</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">2.86868143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92420434951782</t>
+    <t xml:space="preserve">2.9242045879364</t>
   </si>
   <si>
     <t xml:space="preserve">2.90014433860779</t>
@@ -3437,28 +3437,28 @@
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059102058411</t>
+    <t xml:space="preserve">2.82981562614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059125900269</t>
   </si>
   <si>
     <t xml:space="preserve">2.82426309585571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83721828460693</t>
+    <t xml:space="preserve">2.83721852302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6077241897583</t>
+    <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.52999210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49852919578552</t>
+    <t xml:space="preserve">2.49852895736694</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515645980835</t>
+    <t xml:space="preserve">2.56515622138977</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">2.47817063331604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45596170425415</t>
+    <t xml:space="preserve">2.45596146583557</t>
   </si>
   <si>
     <t xml:space="preserve">2.48927521705627</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">2.2727358341217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25792980194092</t>
+    <t xml:space="preserve">2.2579300403595</t>
   </si>
   <si>
     <t xml:space="preserve">2.34861731529236</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18760085105896</t>
+    <t xml:space="preserve">2.18760061264038</t>
   </si>
   <si>
     <t xml:space="preserve">2.29679584503174</t>
@@ -3557,49 +3557,49 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458691596985</t>
+    <t xml:space="preserve">2.27458667755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607895851135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276568412781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24312376976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18204879760742</t>
+    <t xml:space="preserve">2.25607919692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24312400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18204855918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2912437915802</t>
+    <t xml:space="preserve">2.29124355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21351170539856</t>
+    <t xml:space="preserve">2.21351146697998</t>
   </si>
   <si>
     <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15798878669739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14873504638672</t>
+    <t xml:space="preserve">2.15798902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14873480796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765959739685</t>
+    <t xml:space="preserve">2.08765983581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">2.08395838737488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10246586799622</t>
+    <t xml:space="preserve">2.10246562957764</t>
   </si>
   <si>
     <t xml:space="preserve">2.07100296020508</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434632301331</t>
+    <t xml:space="preserve">2.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
@@ -3635,40 +3635,40 @@
     <t xml:space="preserve">2.07285380363464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01362943649292</t>
+    <t xml:space="preserve">2.01362919807434</t>
   </si>
   <si>
     <t xml:space="preserve">1.95810651779175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86186683177948</t>
+    <t xml:space="preserve">1.86186671257019</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132343769073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638429641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255311012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91036558151245</t>
+    <t xml:space="preserve">1.90132355690002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638441562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255299091339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91036581993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84953665733337</t>
+    <t xml:space="preserve">1.84953641891479</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70814979076385</t>
+    <t xml:space="preserve">1.70814990997314</t>
   </si>
   <si>
     <t xml:space="preserve">1.86679887771606</t>
@@ -3677,19 +3677,19 @@
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8955694437027</t>
+    <t xml:space="preserve">1.89556956291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720624446869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78541910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76158058643341</t>
+    <t xml:space="preserve">1.8372061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78541922569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7615807056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.77062296867371</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79199552536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90625560283661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95311069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95886468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078773498535</t>
+    <t xml:space="preserve">1.79199540615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85857856273651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90625584125519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95311057567596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95886480808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078725814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.03695607185364</t>
@@ -3728,22 +3728,22 @@
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559084892273</t>
+    <t xml:space="preserve">2.07559132575989</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07970118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00489735603333</t>
+    <t xml:space="preserve">2.07970094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0048975944519</t>
   </si>
   <si>
     <t xml:space="preserve">1.99749958515167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11258172988892</t>
+    <t xml:space="preserve">2.11258149147034</t>
   </si>
   <si>
     <t xml:space="preserve">2.09203147888184</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204921722412</t>
+    <t xml:space="preserve">2.2420494556427</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135241508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573740005493</t>
+    <t xml:space="preserve">2.14135217666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573763847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">2.19889330863953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28520512580872</t>
+    <t xml:space="preserve">2.28520488739014</t>
   </si>
   <si>
     <t xml:space="preserve">2.34480142593384</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">2.34685635566711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35096621513367</t>
+    <t xml:space="preserve">2.35096645355225</t>
   </si>
   <si>
     <t xml:space="preserve">2.34274625778198</t>
@@ -3818,7 +3818,7 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546227455139</t>
+    <t xml:space="preserve">2.14546251296997</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944403648376</t>
@@ -3848,10 +3848,10 @@
     <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52770018577576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55236029624939</t>
+    <t xml:space="preserve">2.5276997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55236053466797</t>
   </si>
   <si>
     <t xml:space="preserve">2.5379753112793</t>
@@ -3860,25 +3860,25 @@
     <t xml:space="preserve">2.54003024101257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45988345146179</t>
+    <t xml:space="preserve">2.45988368988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153468132019</t>
+    <t xml:space="preserve">2.52153491973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51125979423523</t>
+    <t xml:space="preserve">2.51125955581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48454427719116</t>
+    <t xml:space="preserve">2.48454403877258</t>
   </si>
   <si>
     <t xml:space="preserve">2.45577335357666</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920462608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55852556228638</t>
+    <t xml:space="preserve">2.50920438766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5585253238678</t>
   </si>
   <si>
     <t xml:space="preserve">2.55647039413452</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786447525024</t>
+    <t xml:space="preserve">2.75786471366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
@@ -3917,31 +3917,31 @@
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674427986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67155265808105</t>
+    <t xml:space="preserve">2.63250708580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66744256019592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67155289649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.68799304962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68182802200317</t>
+    <t xml:space="preserve">2.68182778358459</t>
   </si>
   <si>
     <t xml:space="preserve">2.7414243221283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70443344116211</t>
+    <t xml:space="preserve">2.70443320274353</t>
   </si>
   <si>
     <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70854353904724</t>
+    <t xml:space="preserve">2.70854377746582</t>
   </si>
   <si>
     <t xml:space="preserve">2.7784149646759</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">2.71881866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78663516044617</t>
+    <t xml:space="preserve">2.78663539886475</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869009017944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77019476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703909873962</t>
+    <t xml:space="preserve">2.77019453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
@@ -3971,43 +3971,43 @@
     <t xml:space="preserve">2.60784649848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6263415813446</t>
+    <t xml:space="preserve">2.62634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63867211341858</t>
+    <t xml:space="preserve">2.63867235183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428712844849</t>
+    <t xml:space="preserve">2.62428689002991</t>
   </si>
   <si>
     <t xml:space="preserve">2.59757137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6057915687561</t>
+    <t xml:space="preserve">2.60579133033752</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524084091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58935141563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57907605171204</t>
+    <t xml:space="preserve">2.58524131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58935117721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57907581329346</t>
   </si>
   <si>
     <t xml:space="preserve">2.69621324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79485511779785</t>
+    <t xml:space="preserve">2.79485535621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.86678171157837</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97158885002136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91404747962952</t>
+    <t xml:space="preserve">2.97158861160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9140477180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">2.98597383499146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95925831794739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035953521729</t>
+    <t xml:space="preserve">2.95925855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035929679871</t>
   </si>
   <si>
     <t xml:space="preserve">2.99419403076172</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553418159485</t>
+    <t xml:space="preserve">2.82773590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553394317627</t>
   </si>
   <si>
     <t xml:space="preserve">2.61606669425964</t>
@@ -4058,37 +4058,37 @@
     <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6982684135437</t>
+    <t xml:space="preserve">2.69826817512512</t>
   </si>
   <si>
     <t xml:space="preserve">2.70237827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66538786888123</t>
+    <t xml:space="preserve">2.66538763046265</t>
   </si>
   <si>
     <t xml:space="preserve">2.79896521568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7907452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99213933944702</t>
+    <t xml:space="preserve">2.79074501991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99213910102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9345977306366</t>
+    <t xml:space="preserve">2.93459796905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7722499370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78457975387573</t>
+    <t xml:space="preserve">2.77224969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78457999229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89555239677429</t>
+    <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
     <t xml:space="preserve">3.10927653312683</t>
@@ -4109,16 +4109,16 @@
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582728385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9633686542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93665289878845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89966225624084</t>
+    <t xml:space="preserve">2.90582752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96336841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93665313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89966201782227</t>
   </si>
   <si>
     <t xml:space="preserve">2.85856151580811</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86883687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82568097114563</t>
+    <t xml:space="preserve">2.86883664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82568073272705</t>
   </si>
   <si>
     <t xml:space="preserve">2.92226767539978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88733220100403</t>
+    <t xml:space="preserve">2.88733196258545</t>
   </si>
   <si>
     <t xml:space="preserve">2.8893871307373</t>
@@ -4148,16 +4148,16 @@
     <t xml:space="preserve">3.02296471595764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06612062454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05995535850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9818639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01268935203552</t>
+    <t xml:space="preserve">3.06612038612366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05995559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98186421394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
     <t xml:space="preserve">2.94281816482544</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">2.90442943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92211246490479</t>
+    <t xml:space="preserve">2.92211222648621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98621320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04147243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1033627986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136608123779</t>
+    <t xml:space="preserve">3.04147267341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136584281921</t>
   </si>
   <si>
     <t xml:space="preserve">3.11883544921875</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">3.07241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09452152252197</t>
+    <t xml:space="preserve">3.09452128410339</t>
   </si>
   <si>
     <t xml:space="preserve">3.07020735740662</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.97958207130432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97074055671692</t>
+    <t xml:space="preserve">2.97074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.91548109054565</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.93316435813904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92874336242676</t>
+    <t xml:space="preserve">2.92874360084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.90221905708313</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">2.90000867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87790513038635</t>
+    <t xml:space="preserve">2.87790489196777</t>
   </si>
   <si>
     <t xml:space="preserve">2.86464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83369755744934</t>
+    <t xml:space="preserve">2.83369731903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.81822490692139</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">2.69002318382263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60160851478577</t>
+    <t xml:space="preserve">2.60160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.66791939735413</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">2.68560242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62813305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6502366065979</t>
+    <t xml:space="preserve">2.62813282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65023636817932</t>
   </si>
   <si>
     <t xml:space="preserve">2.60381865501404</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.5551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47340655326843</t>
+    <t xml:space="preserve">2.47340679168701</t>
   </si>
   <si>
     <t xml:space="preserve">2.44909262657166</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">2.47119641304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47782754898071</t>
+    <t xml:space="preserve">2.47782731056213</t>
   </si>
   <si>
     <t xml:space="preserve">2.46014451980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624221801758</t>
+    <t xml:space="preserve">2.56624245643616</t>
   </si>
   <si>
     <t xml:space="preserve">2.55961132049561</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.54855942726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50877285003662</t>
+    <t xml:space="preserve">2.50877261161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.53087639808655</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">2.32531189918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24529623985291</t>
+    <t xml:space="preserve">2.24529647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.19932055473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15422892570496</t>
+    <t xml:space="preserve">2.15422916412354</t>
   </si>
   <si>
     <t xml:space="preserve">2.14715576171875</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">2.17633247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29746103286743</t>
+    <t xml:space="preserve">2.29746127128601</t>
   </si>
   <si>
     <t xml:space="preserve">2.38720226287842</t>
@@ -4367,40 +4367,40 @@
     <t xml:space="preserve">2.33813214302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51894021034241</t>
+    <t xml:space="preserve">2.51894044876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46854400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42345213890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51319360733032</t>
+    <t xml:space="preserve">2.42345237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51319336891174</t>
   </si>
   <si>
     <t xml:space="preserve">2.57287359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52026653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55076956748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53794980049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54723334312439</t>
+    <t xml:space="preserve">2.52026677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56712651252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53794956207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54723310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.70461177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78109073638916</t>
+    <t xml:space="preserve">2.78109049797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.75854468345642</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">2.79302644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75633430480957</t>
+    <t xml:space="preserve">2.75633454322815</t>
   </si>
   <si>
     <t xml:space="preserve">2.77357530593872</t>
@@ -4436,13 +4436,13 @@
     <t xml:space="preserve">2.91327095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84253883361816</t>
+    <t xml:space="preserve">2.84253907203674</t>
   </si>
   <si>
     <t xml:space="preserve">2.93935322761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94112133979797</t>
+    <t xml:space="preserve">2.94112157821655</t>
   </si>
   <si>
     <t xml:space="preserve">2.92343854904175</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">2.94554233551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785954475403</t>
+    <t xml:space="preserve">2.92785930633545</t>
   </si>
   <si>
     <t xml:space="preserve">2.93537449836731</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">2.89249348640442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88851451873779</t>
+    <t xml:space="preserve">2.88851475715637</t>
   </si>
   <si>
     <t xml:space="preserve">2.93006944656372</t>
@@ -4475,25 +4475,25 @@
     <t xml:space="preserve">2.88011527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92741727828979</t>
+    <t xml:space="preserve">2.92741751670837</t>
   </si>
   <si>
     <t xml:space="preserve">3.02378964424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03926229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03086280822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96189880371094</t>
+    <t xml:space="preserve">3.03926205635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03086256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96189904212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.93493247032166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89824032783508</t>
+    <t xml:space="preserve">2.89824056625366</t>
   </si>
   <si>
     <t xml:space="preserve">2.91724944114685</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">2.9106183052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9176914691925</t>
+    <t xml:space="preserve">2.91769170761108</t>
   </si>
   <si>
     <t xml:space="preserve">2.9256489276886</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">2.98444485664368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02246332168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00168585777283</t>
+    <t xml:space="preserve">3.02246308326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00168561935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.95438385009766</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">2.73865151405334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67101407051086</t>
+    <t xml:space="preserve">2.67101383209229</t>
   </si>
   <si>
     <t xml:space="preserve">2.68737077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66084623336792</t>
+    <t xml:space="preserve">2.6608464717865</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869686126709</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.64537382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72052621841431</t>
+    <t xml:space="preserve">2.72052645683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70947456359863</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">2.62327003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58701992034912</t>
+    <t xml:space="preserve">2.5870201587677</t>
   </si>
   <si>
     <t xml:space="preserve">2.60426068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57729411125183</t>
+    <t xml:space="preserve">2.57729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">2.58171510696411</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">2.58083081245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59497737884521</t>
+    <t xml:space="preserve">2.59497714042664</t>
   </si>
   <si>
     <t xml:space="preserve">2.65288901329041</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">2.69488620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69223380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64139485359192</t>
+    <t xml:space="preserve">2.69223356246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6413950920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480954170227</t>
@@ -4622,19 +4622,19 @@
     <t xml:space="preserve">2.70549583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71168494224548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67985534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85049629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342336654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9318380355835</t>
+    <t xml:space="preserve">2.7116847038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67985558509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85049605369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342312812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93183779716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.91946005821228</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">2.94952082633972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878894805908</t>
+    <t xml:space="preserve">2.87878918647766</t>
   </si>
   <si>
     <t xml:space="preserve">3.13872885704041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">3.30671715736389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42519307136536</t>
+    <t xml:space="preserve">3.42519330978394</t>
   </si>
   <si>
     <t xml:space="preserve">3.41988825798035</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">3.34561967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33500981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43933939933777</t>
+    <t xml:space="preserve">3.33501005172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43933963775635</t>
   </si>
   <si>
     <t xml:space="preserve">3.36507105827332</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">3.29787564277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30848574638367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32793688774109</t>
+    <t xml:space="preserve">3.30848550796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32793664932251</t>
   </si>
   <si>
     <t xml:space="preserve">3.41458320617676</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">3.41104674339294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49592518806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57019352912903</t>
+    <t xml:space="preserve">3.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57019376754761</t>
   </si>
   <si>
     <t xml:space="preserve">3.57372999191284</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">3.50123000144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50653481483459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52598595619202</t>
+    <t xml:space="preserve">3.50653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5259861946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616945266724</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">3.61793756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59848666191101</t>
+    <t xml:space="preserve">3.59848642349243</t>
   </si>
   <si>
     <t xml:space="preserve">3.63031578063965</t>
@@ -4748,28 +4748,28 @@
     <t xml:space="preserve">3.7045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77708435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84074282646179</t>
+    <t xml:space="preserve">3.77708411216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82129192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">3.84781646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85488963127136</t>
+    <t xml:space="preserve">3.85488939285278</t>
   </si>
   <si>
     <t xml:space="preserve">3.87610912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232815742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85842609405518</t>
+    <t xml:space="preserve">3.75232839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8584258556366</t>
   </si>
   <si>
     <t xml:space="preserve">3.65860843658447</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">3.46409559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57903504371643</t>
+    <t xml:space="preserve">3.57903480529785</t>
   </si>
   <si>
     <t xml:space="preserve">3.52775454521179</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">3.4941565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52952265739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62324261665344</t>
+    <t xml:space="preserve">3.52952289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62324237823486</t>
   </si>
   <si>
     <t xml:space="preserve">3.61440086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68690133094788</t>
+    <t xml:space="preserve">3.6869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">3.65684032440186</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">3.6957426071167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74525499343872</t>
+    <t xml:space="preserve">3.7452552318573</t>
   </si>
   <si>
     <t xml:space="preserve">3.75056004524231</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">3.80714583396912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05824375152588</t>
+    <t xml:space="preserve">4.20501279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05824422836304</t>
   </si>
   <si>
     <t xml:space="preserve">4.09184122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12013387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1678786277771</t>
+    <t xml:space="preserve">4.1201343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16787815093994</t>
   </si>
   <si>
     <t xml:space="preserve">4.07592678070068</t>
@@ -5607,6 +5607,12 @@
   </si>
   <si>
     <t xml:space="preserve">3.99799990653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97000002861023</t>
   </si>
 </sst>
 </file>
@@ -71049,27 +71055,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911921296</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>407668</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>3.96600008010864</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>3.99799990653992</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>652923</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>4.01800012588501</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>3.90199995040894</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>3.90199995040894</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>442507</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>3.97000002861023</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>3.85800004005432</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>3.90400004386902</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>3.94600009918213</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1810</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6910300926</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>290631</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>4.0019998550415</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>3.95799994468689</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>3.9760000705719</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="1868">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356548309326</t>
+    <t xml:space="preserve">12.2356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956911087036</t>
+    <t xml:space="preserve">12.195689201355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5895700454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101781845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.076696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302516937256</t>
+    <t xml:space="preserve">11.5895690917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101800918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0766973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.136643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302536010742</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770582199097</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7370042800903</t>
+    <t xml:space="preserve">10.737003326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438442230225</t>
+    <t xml:space="preserve">10.4239521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2707557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4838962554932</t>
+    <t xml:space="preserve">10.2707567214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4838981628418</t>
   </si>
   <si>
     <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1042394638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8702173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77786636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91107940673828</t>
+    <t xml:space="preserve">10.1042385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7170219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77786731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
     <t xml:space="preserve">9.54474353790283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77120590209961</t>
+    <t xml:space="preserve">9.77120685577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6171112060547</t>
+    <t xml:space="preserve">10.6171102523804</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9434843063354</t>
+    <t xml:space="preserve">10.7236814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9434833526611</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363737106323</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">11.3431253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6495161056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898387908936</t>
+    <t xml:space="preserve">11.6495141983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">12.0624780654907</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">11.7627477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289953231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4754371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554576873779</t>
+    <t xml:space="preserve">12.2289943695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4754390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554567337036</t>
   </si>
   <si>
     <t xml:space="preserve">12.3422269821167</t>
@@ -191,25 +191,25 @@
     <t xml:space="preserve">12.4621171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5553665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6961402893066</t>
+    <t xml:space="preserve">12.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6961393356323</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695867538452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.075798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9159412384033</t>
+    <t xml:space="preserve">12.0757970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9159421920776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1890287399292</t>
@@ -221,91 +221,91 @@
     <t xml:space="preserve">11.0633764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6561756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9559078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2689571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217945098877</t>
+    <t xml:space="preserve">11.6561765670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.955906867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2689580917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217926025391</t>
   </si>
   <si>
     <t xml:space="preserve">12.9217042922974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1015424728394</t>
+    <t xml:space="preserve">12.9350261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1015434265137</t>
   </si>
   <si>
     <t xml:space="preserve">13.1281833648682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2480773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947917938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1814708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882196426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.981650352478</t>
+    <t xml:space="preserve">13.2480764389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947889328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.16148853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.361307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882205963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9816484451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.6885795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620279312134</t>
+    <t xml:space="preserve">12.5620269775391</t>
   </si>
   <si>
     <t xml:space="preserve">12.881739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8617563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884010314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7218837738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685089111328</t>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482549667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.375527381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7218828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685098648071</t>
   </si>
   <si>
     <t xml:space="preserve">12.9150419235229</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1344079971313</t>
+    <t xml:space="preserve">13.1344060897827</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5159883499146</t>
+    <t xml:space="preserve">13.5159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">13.6230983734131</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">13.5226812362671</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5561542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620166778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553218841553</t>
+    <t xml:space="preserve">13.5561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.355320930481</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.993824005127</t>
+    <t xml:space="preserve">12.9938249588013</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6591033935547</t>
+    <t xml:space="preserve">13.2749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194655418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6591053009033</t>
   </si>
   <si>
     <t xml:space="preserve">12.0833864212036</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620553970337</t>
+    <t xml:space="preserve">11.762056350708</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0766916275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524105072021</t>
+    <t xml:space="preserve">12.0766935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524095535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4515781402588</t>
+    <t xml:space="preserve">12.4515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">13.1410999298096</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">10.8850898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1487054824829</t>
+    <t xml:space="preserve">10.1487064361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834260940552</t>
+    <t xml:space="preserve">10.4834251403809</t>
   </si>
   <si>
     <t xml:space="preserve">10.7177295684814</t>
@@ -407,43 +407,43 @@
     <t xml:space="preserve">10.2290382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4164810180664</t>
+    <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
     <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4432601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7445058822632</t>
+    <t xml:space="preserve">10.4432592391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
     <t xml:space="preserve">11.1193933486938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.474196434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0189762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0122842788696</t>
+    <t xml:space="preserve">11.4741954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1260890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0189771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0122833251953</t>
   </si>
   <si>
     <t xml:space="preserve">10.811450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9252557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8783941268921</t>
+    <t xml:space="preserve">10.9252548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">9.06421375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93032550811768</t>
+    <t xml:space="preserve">8.93032455444336</t>
   </si>
   <si>
     <t xml:space="preserve">8.67593860626221</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37215614318848</t>
+    <t xml:space="preserve">9.20479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37215518951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23826885223389</t>
+    <t xml:space="preserve">9.23826789855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.31860065460205</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6332368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959796905518</t>
+    <t xml:space="preserve">9.23157405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959892272949</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43910026550293</t>
+    <t xml:space="preserve">9.43909931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.56629371643066</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">9.8273754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76043033599854</t>
+    <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
     <t xml:space="preserve">9.78720855712891</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">9.87423515319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67340278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760334014893</t>
+    <t xml:space="preserve">9.6734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">9.31190586090088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17801761627197</t>
+    <t xml:space="preserve">9.17801856994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.35207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3654613494873</t>
+    <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.3855447769165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24496269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03743553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007617950439</t>
+    <t xml:space="preserve">9.24496173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03743648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72279930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007522583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.76965999603271</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">8.78304862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78974437713623</t>
+    <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.71610546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66924381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3345251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2006368637085</t>
+    <t xml:space="preserve">8.66924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20063591003418</t>
   </si>
   <si>
     <t xml:space="preserve">8.10022068023682</t>
@@ -614,163 +614,163 @@
     <t xml:space="preserve">8.12030410766602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79227828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82575035095215</t>
+    <t xml:space="preserve">7.79227781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583330154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63161182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491750717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74541759490967</t>
+    <t xml:space="preserve">7.86591672897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6316123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508531570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74541664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.71194553375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69186115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6450023651123</t>
+    <t xml:space="preserve">7.69186210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500093460083</t>
   </si>
   <si>
     <t xml:space="preserve">7.65169620513916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68516778945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9596381187439</t>
+    <t xml:space="preserve">7.68516731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963716506958</t>
   </si>
   <si>
     <t xml:space="preserve">8.12699794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38138484954834</t>
+    <t xml:space="preserve">8.38138580322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.92363166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21149063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963579177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1168594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8691654205322</t>
+    <t xml:space="preserve">9.2114896774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1168575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9294157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8691663742065</t>
   </si>
   <si>
     <t xml:space="preserve">12.0499153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8615617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7569847106934</t>
+    <t xml:space="preserve">14.8615627288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569856643677</t>
   </si>
   <si>
     <t xml:space="preserve">13.8975687026978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908720016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.957818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904567718506</t>
+    <t xml:space="preserve">13.7235126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908739089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.6004800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582342147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3126211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2858419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1385669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101249694824</t>
+    <t xml:space="preserve">14.0180673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3126201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2858428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1385679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
     <t xml:space="preserve">13.4557390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2415161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544904708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268808364868</t>
+    <t xml:space="preserve">13.2415180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2080450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268798828125</t>
   </si>
   <si>
     <t xml:space="preserve">12.7528257369995</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611852645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9134931564331</t>
+    <t xml:space="preserve">12.9067983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611843109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0540752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9134912490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.2147397994995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1879634857178</t>
+    <t xml:space="preserve">13.1879625320435</t>
   </si>
   <si>
     <t xml:space="preserve">13.3419332504272</t>
@@ -806,76 +806,76 @@
     <t xml:space="preserve">13.1812677383423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.033989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.859935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.007212638855</t>
+    <t xml:space="preserve">13.0339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8599367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072135925293</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0206022262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.920184135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8934087753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3754034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758214950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3486270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406847000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8666315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8867139816284</t>
+    <t xml:space="preserve">13.0206031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3754043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3486280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406856536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8867130279541</t>
   </si>
   <si>
     <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532419204712</t>
+    <t xml:space="preserve">12.8398542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532409667969</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197689056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6858825683594</t>
+    <t xml:space="preserve">12.6858816146851</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3109951019287</t>
+    <t xml:space="preserve">12.310996055603</t>
   </si>
   <si>
     <t xml:space="preserve">12.3310794830322</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708311080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1570243835449</t>
+    <t xml:space="preserve">12.2708292007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1570253372192</t>
   </si>
   <si>
     <t xml:space="preserve">11.67502784729</t>
@@ -896,52 +896,52 @@
     <t xml:space="preserve">11.8624706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1771087646484</t>
+    <t xml:space="preserve">12.1771078109741</t>
   </si>
   <si>
     <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862977981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.946964263916</t>
+    <t xml:space="preserve">12.7862987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800191879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9469633102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4448843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637182235718</t>
+    <t xml:space="preserve">12.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637201309204</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043012619019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5586881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6189384460449</t>
+    <t xml:space="preserve">12.3913288116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.558687210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.284218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4181060791016</t>
+    <t xml:space="preserve">12.2842168807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4181070327759</t>
   </si>
   <si>
     <t xml:space="preserve">12.1971912384033</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0633039474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519933700562</t>
+    <t xml:space="preserve">12.0633029937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.6724939346313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8089151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813055038452</t>
+    <t xml:space="preserve">12.3176898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8089160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">11.6147785186768</t>
@@ -983,40 +983,40 @@
     <t xml:space="preserve">11.6549453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880012512207</t>
+    <t xml:space="preserve">11.5880002975464</t>
   </si>
   <si>
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5210571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151937484741</t>
+    <t xml:space="preserve">11.6817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5210552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
     <t xml:space="preserve">11.661639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.634861946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7687501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7018070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4474191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3804759979248</t>
+    <t xml:space="preserve">11.6348609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.2265043258667</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">10.7779788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7043409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7980613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9453401565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1394758224487</t>
+    <t xml:space="preserve">10.7043399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7980623245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9453392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.139476776123</t>
   </si>
   <si>
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461706161499</t>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591449737549</t>
+    <t xml:space="preserve">11.0591440200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.1528654098511</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112699508667</t>
+    <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206409454346</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
+    <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
     <t xml:space="preserve">11.460807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3336143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3536958694458</t>
+    <t xml:space="preserve">11.4541139602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
     <t xml:space="preserve">11.1595602035522</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721155166626</t>
+    <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897047042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1620950698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2156496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3361482620239</t>
+    <t xml:space="preserve">10.3897037506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1620941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2156505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3361492156982</t>
   </si>
   <si>
     <t xml:space="preserve">10.490119934082</t>
@@ -1130,28 +1130,28 @@
     <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3428440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3562326431274</t>
+    <t xml:space="preserve">10.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3562316894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80059814453125</t>
+    <t xml:space="preserve">9.80059719085693</t>
   </si>
   <si>
     <t xml:space="preserve">9.80729007720947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68679332733154</t>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026538848877</t>
+    <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704265594482</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70018196105957</t>
+    <t xml:space="preserve">9.75373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650785446167</t>
+    <t xml:space="preserve">10.7110357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507863998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3763151168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759008407593</t>
+    <t xml:space="preserve">10.376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1888723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">10.1286220550537</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
+    <t xml:space="preserve">10.2357320785522</t>
   </si>
   <si>
     <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160648345947</t>
+    <t xml:space="preserve">10.5102033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
     <t xml:space="preserve">10.2089557647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65332126617432</t>
+    <t xml:space="preserve">9.6533203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.52612590789795</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83406829833984</t>
+    <t xml:space="preserve">9.83406925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.84745788574219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2959833145142</t>
+    <t xml:space="preserve">10.2959823608398</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436754226685</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">10.5972299575806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8583106994629</t>
+    <t xml:space="preserve">10.8583116531372</t>
   </si>
   <si>
     <t xml:space="preserve">10.9855051040649</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">10.7311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8248405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9988956451416</t>
+    <t xml:space="preserve">10.82483959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9988946914673</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926160812378</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8917837142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7512016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0390605926514</t>
+    <t xml:space="preserve">10.9051742553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8917827606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7512006759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0390596389771</t>
   </si>
   <si>
     <t xml:space="preserve">10.7277708053589</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">10.4633417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658576965332</t>
+    <t xml:space="preserve">10.1554002761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871877670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.289288520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658567428589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3696212768555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135498046875</t>
+    <t xml:space="preserve">10.5135507583618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6206607818604</t>
@@ -1325,31 +1325,31 @@
     <t xml:space="preserve">10.8616590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6407451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5503692626953</t>
+    <t xml:space="preserve">10.6407442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
+    <t xml:space="preserve">10.533634185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6240072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4097881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1729497909546</t>
+    <t xml:space="preserve">10.6240081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4097871780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.172947883606</t>
   </si>
   <si>
     <t xml:space="preserve">10.9821586608887</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">10.5269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261079788208</t>
+    <t xml:space="preserve">10.3261070251465</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.36292552948</t>
+    <t xml:space="preserve">10.3629274368286</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
@@ -1376,34 +1376,34 @@
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821784973145</t>
+    <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0349016189575</t>
+    <t xml:space="preserve">10.0349006652832</t>
   </si>
   <si>
     <t xml:space="preserve">10.0951499938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0357141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762962341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8717002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.868353843689</t>
+    <t xml:space="preserve">10.9788103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1060037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0357131958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762952804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8717012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8683528900146</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620752334595</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">10.9553804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025671005249</t>
+    <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
     <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.952033996582</t>
+    <t xml:space="preserve">10.9520330429077</t>
   </si>
   <si>
     <t xml:space="preserve">11.0290193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0758790969849</t>
+    <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">11.28675365448</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2457752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0683736801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74369430541992</t>
+    <t xml:space="preserve">10.245774269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0683727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74369525909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67005634307861</t>
+    <t xml:space="preserve">9.34537887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6700553894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.72695827484131</t>
@@ -1472,16 +1472,16 @@
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48596000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58637619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6165018081665</t>
+    <t xml:space="preserve">9.57633590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58637523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">9.54286289215088</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">9.56964111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5026969909668</t>
+    <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.47926616668701</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319469451904</t>
+    <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949409484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350700378418</t>
+    <t xml:space="preserve">8.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350605010986</t>
   </si>
   <si>
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186367034912</t>
+    <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.22487926483154</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45583629608154</t>
+    <t xml:space="preserve">9.13785171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
@@ -1553,31 +1553,31 @@
     <t xml:space="preserve">9.6131534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691703796387</t>
+    <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550258636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54621028900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31525325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015865325928</t>
+    <t xml:space="preserve">9.37550354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54621124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31525421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26504611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88011741638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82656192779541</t>
+    <t xml:space="preserve">8.92028427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88011837005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29770469665527</t>
+    <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.2742748260498</t>
@@ -1613,25 +1613,25 @@
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25084400177002</t>
+    <t xml:space="preserve">8.2508430480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35795497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47845458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47175884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5387020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639602661133</t>
+    <t xml:space="preserve">8.35795402526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47845363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47175788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639507293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.71945190429688</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">8.77635383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16462898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00731182098389</t>
+    <t xml:space="preserve">9.16462993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1345043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00731086730957</t>
   </si>
   <si>
     <t xml:space="preserve">9.01065826416016</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0006160736084</t>
+    <t xml:space="preserve">9.00061702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735305786133</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">9.12780952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408813476562</t>
+    <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
     <t xml:space="preserve">8.66589736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8499927520752</t>
+    <t xml:space="preserve">8.59560585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84999370574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7529239654541</t>
+    <t xml:space="preserve">8.62907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75292301177979</t>
   </si>
   <si>
     <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29517078399658</t>
+    <t xml:space="preserve">9.29516887664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855941772461</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111663818359</t>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111568450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107444763184</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">8.3110933303833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34456634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32448387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514842987061</t>
+    <t xml:space="preserve">8.34456539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32448291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514938354492</t>
   </si>
   <si>
     <t xml:space="preserve">8.49184322357178</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">9.19810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">8.70271587371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25753974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5654821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75627040863037</t>
+    <t xml:space="preserve">8.25753879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56548023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5018835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627136230469</t>
   </si>
   <si>
     <t xml:space="preserve">8.82321548461914</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236423492432</t>
+    <t xml:space="preserve">9.42236328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.26169776916504</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">9.44914054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91105461120605</t>
+    <t xml:space="preserve">9.91105556488037</t>
   </si>
   <si>
     <t xml:space="preserve">9.8441104888916</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">9.45918273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4424467086792</t>
+    <t xml:space="preserve">9.44244575500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60646057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95456886291504</t>
+    <t xml:space="preserve">9.60645961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95456790924072</t>
   </si>
   <si>
     <t xml:space="preserve">9.41566848754883</t>
@@ -1829,19 +1829,19 @@
     <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8098258972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10437870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27843284606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943206787109</t>
+    <t xml:space="preserve">8.80982685089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27843379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.42905902862549</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24830913543701</t>
+    <t xml:space="preserve">9.24831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42570972442627</t>
+    <t xml:space="preserve">9.55625057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42571067810059</t>
   </si>
   <si>
     <t xml:space="preserve">9.15124034881592</t>
@@ -1868,43 +1868,43 @@
     <t xml:space="preserve">9.16128253936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14789295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240547180176</t>
+    <t xml:space="preserve">9.14789390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240451812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533668518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24161434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.33533573150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24161529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73030662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69013977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73699951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92109489440918</t>
+    <t xml:space="preserve">9.73030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69014072418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50939083099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73700046539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79725074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9210958480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.90770721435547</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">9.62989044189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45248794555664</t>
+    <t xml:space="preserve">9.38889122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45248889923096</t>
   </si>
   <si>
     <t xml:space="preserve">9.25500392913818</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77300643920898</t>
+    <t xml:space="preserve">8.7730073928833</t>
   </si>
   <si>
     <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02404689788818</t>
+    <t xml:space="preserve">9.02404594421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.4056282043457</t>
@@ -1958,25 +1958,25 @@
     <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70687580108643</t>
+    <t xml:space="preserve">9.70687675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.94787406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76712512969971</t>
+    <t xml:space="preserve">9.76712608337402</t>
   </si>
   <si>
     <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53282165527344</t>
+    <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
     <t xml:space="preserve">9.60311317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35541915893555</t>
+    <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
     <t xml:space="preserve">9.20144844055176</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02739429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9437141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053359985352</t>
+    <t xml:space="preserve">9.02739524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94371509552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9805326461792</t>
   </si>
   <si>
     <t xml:space="preserve">8.99057483673096</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">8.68263339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67928600311279</t>
+    <t xml:space="preserve">8.67928504943848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86084651947021</t>
+    <t xml:space="preserve">9.86084747314453</t>
   </si>
   <si>
     <t xml:space="preserve">9.82402801513672</t>
@@ -2024,19 +2024,19 @@
     <t xml:space="preserve">9.82068061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30521202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15793609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16797542572021</t>
+    <t xml:space="preserve">9.30521106719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15793514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16797637939453</t>
   </si>
   <si>
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764362335205</t>
+    <t xml:space="preserve">9.08764457702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">8.79308986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250778198242</t>
+    <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681125640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00396347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05417060852051</t>
+    <t xml:space="preserve">8.87677001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681221008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0039644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
     <t xml:space="preserve">9.060866355896</t>
@@ -2078,28 +2078,28 @@
     <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96714496612549</t>
+    <t xml:space="preserve">8.97383880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0809497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714401245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020084381104</t>
+    <t xml:space="preserve">8.90019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99727058410645</t>
+    <t xml:space="preserve">8.99726867675781</t>
   </si>
   <si>
     <t xml:space="preserve">8.92697906494141</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">8.64246559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40146827697754</t>
+    <t xml:space="preserve">8.40146923065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
@@ -2123,28 +2123,28 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410892486572</t>
+    <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9897632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06005477905273</t>
+    <t xml:space="preserve">7.98976230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327560424805</t>
+    <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
     <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95629119873047</t>
+    <t xml:space="preserve">7.95629024505615</t>
   </si>
   <si>
     <t xml:space="preserve">7.93286037445068</t>
@@ -2153,37 +2153,37 @@
     <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96633148193359</t>
+    <t xml:space="preserve">7.96633243560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558301925659</t>
+    <t xml:space="preserve">7.94290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558254241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12953233718872</t>
+    <t xml:space="preserve">7.12953281402588</t>
   </si>
   <si>
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793214797974</t>
+    <t xml:space="preserve">7.54793167114258</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300439834595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07263088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514638900757</t>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514543533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.72786951065063</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">6.57222461700439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25256729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1588454246521</t>
+    <t xml:space="preserve">6.25256681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15884494781494</t>
   </si>
   <si>
     <t xml:space="preserve">5.55802297592163</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45091247558594</t>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05928993225098</t>
+    <t xml:space="preserve">5.05929040908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27183771133423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6902379989624</t>
+    <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693231582642</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">5.98311758041382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05842971801758</t>
+    <t xml:space="preserve">6.05842876434326</t>
   </si>
   <si>
     <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29440641403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47515535354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49356460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753675460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720399856567</t>
+    <t xml:space="preserve">6.29440689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47515487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49356508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637163162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6174111366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53038501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64753532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720304489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4266209602356</t>
+    <t xml:space="preserve">6.42662048339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.35967683792114</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834581375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85759687423706</t>
+    <t xml:space="preserve">6.03834676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
     <t xml:space="preserve">6.00487422943115</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620525360107</t>
+    <t xml:space="preserve">6.32620477676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.34628820419312</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20905303955078</t>
+    <t xml:space="preserve">6.20905351638794</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826286315918</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">6.08520698547363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01156806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813772201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05508184432983</t>
+    <t xml:space="preserve">6.01156854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05508232116699</t>
   </si>
   <si>
     <t xml:space="preserve">5.87433290481567</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0843939781189</t>
+    <t xml:space="preserve">5.08439445495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2348,25 +2348,25 @@
     <t xml:space="preserve">5.08774185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17142200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18815755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34212875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15803241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22163009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37225294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74379301071167</t>
+    <t xml:space="preserve">5.17142152786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.188157081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34212923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15803289413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22162961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37225341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74379205703735</t>
   </si>
   <si>
     <t xml:space="preserve">5.74044513702393</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94127750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82077789306641</t>
+    <t xml:space="preserve">5.94127798080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82077836990356</t>
   </si>
   <si>
     <t xml:space="preserve">5.60655736923218</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2082405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1981987953186</t>
+    <t xml:space="preserve">5.20824098587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861497879028</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30196237564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23836517333984</t>
+    <t xml:space="preserve">5.30196189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.238365650177</t>
   </si>
   <si>
     <t xml:space="preserve">5.33208703994751</t>
@@ -2417,13 +2417,13 @@
     <t xml:space="preserve">5.35886478424072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32204532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3253927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28187942504883</t>
+    <t xml:space="preserve">5.32204580307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32539319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
     <t xml:space="preserve">5.2283239364624</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104753494263</t>
+    <t xml:space="preserve">5.08104705810547</t>
   </si>
   <si>
     <t xml:space="preserve">5.13125514984131</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12121391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98063182830811</t>
+    <t xml:space="preserve">5.11786603927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12121343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
     <t xml:space="preserve">5.10447788238525</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">4.96389579772949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41576719284058</t>
+    <t xml:space="preserve">5.41576671600342</t>
   </si>
   <si>
     <t xml:space="preserve">5.38898944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48940563201904</t>
+    <t xml:space="preserve">5.48940515518188</t>
   </si>
   <si>
     <t xml:space="preserve">5.36890649795532</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568471908569</t>
+    <t xml:space="preserve">5.39568424224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221218109131</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34547662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30530977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27518463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60321044921875</t>
+    <t xml:space="preserve">5.3454761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3053092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27518510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09108877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60320997238159</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537288665771</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">6.15215063095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1956639289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1488037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524774551392</t>
+    <t xml:space="preserve">6.2793436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19566440582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14880466461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524822235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441680908203</t>
+    <t xml:space="preserve">5.89441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375082015991</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4860577583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48271131515503</t>
+    <t xml:space="preserve">5.48605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287721633911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65341854095459</t>
+    <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
     <t xml:space="preserve">5.73040390014648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5563497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46262788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47267007827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50948810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45258665084839</t>
+    <t xml:space="preserve">5.55634927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46262741088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47266960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50948858261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45258712768555</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894773483276</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">4.95385360717773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88021516799927</t>
+    <t xml:space="preserve">4.88021564483643</t>
   </si>
   <si>
     <t xml:space="preserve">4.94381237030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07769966125488</t>
+    <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
     <t xml:space="preserve">5.21828269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55300235748291</t>
+    <t xml:space="preserve">5.15468549728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55300188064575</t>
   </si>
   <si>
     <t xml:space="preserve">5.8609447479248</t>
@@ -2642,58 +2642,58 @@
     <t xml:space="preserve">6.09859561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398174285889</t>
+    <t xml:space="preserve">6.44335651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
     <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63749408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58728647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72117376327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766094207764</t>
+    <t xml:space="preserve">6.63749504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58728694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72117471694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766046524048</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323232650757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
+    <t xml:space="preserve">6.64418983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142499923706</t>
   </si>
   <si>
     <t xml:space="preserve">6.76134061813354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275506973267</t>
+    <t xml:space="preserve">7.10275459289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19647693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0893669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986557006836</t>
+    <t xml:space="preserve">7.19647598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283849716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986652374268</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961624145508</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">7.05589437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00233840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0692834854126</t>
+    <t xml:space="preserve">7.0023398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06928396224976</t>
   </si>
   <si>
     <t xml:space="preserve">7.10944986343384</t>
@@ -2720,103 +2720,103 @@
     <t xml:space="preserve">6.98225593566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14292097091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606170654297</t>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606122970581</t>
   </si>
   <si>
     <t xml:space="preserve">6.92200660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9688663482666</t>
+    <t xml:space="preserve">6.96886730194092</t>
   </si>
   <si>
     <t xml:space="preserve">6.90192365646362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11614370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01572751998901</t>
+    <t xml:space="preserve">7.11614465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01572799682617</t>
   </si>
   <si>
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622713088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15631055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2500319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55128002166748</t>
+    <t xml:space="preserve">7.03581142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622665405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25003147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32367086410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4106969833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3906135559082</t>
+    <t xml:space="preserve">7.41069746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56466960906982</t>
+    <t xml:space="preserve">7.56466770172119</t>
   </si>
   <si>
     <t xml:space="preserve">7.51111364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53789043426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152935028076</t>
+    <t xml:space="preserve">7.53789138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61152982711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8525276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18055248260498</t>
+    <t xml:space="preserve">7.7588062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1805534362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66254997253418</t>
+    <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.89685344696045</t>
@@ -2831,16 +2831,16 @@
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21402549743652</t>
+    <t xml:space="preserve">8.41485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21402454376221</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45502376556396</t>
+    <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
     <t xml:space="preserve">8.18724727630615</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32782936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236219406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277742385864</t>
+    <t xml:space="preserve">8.26758098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3278284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
   </si>
   <si>
     <t xml:space="preserve">7.89938831329346</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">7.99980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049140930176</t>
+    <t xml:space="preserve">8.97049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009757995605</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96126365661621</t>
+    <t xml:space="preserve">9.99473571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96126270294189</t>
   </si>
   <si>
     <t xml:space="preserve">9.9411792755127</t>
@@ -2894,64 +2894,64 @@
     <t xml:space="preserve">10.0081233978271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0282068252563</t>
+    <t xml:space="preserve">10.028205871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381896972656</t>
+    <t xml:space="preserve">9.7738208770752</t>
   </si>
   <si>
     <t xml:space="preserve">9.73365306854248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039247512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6775636672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.5168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476731300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.677562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84605503082275</t>
+    <t xml:space="preserve">9.84605598449707</t>
   </si>
   <si>
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.186595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0755491256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93489170074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94969844818115</t>
+    <t xml:space="preserve">10.1865949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0755500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93489074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63877105712891</t>
+    <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59435081481934</t>
+    <t xml:space="preserve">9.59435176849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.43888759613037</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
+    <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83865261077881</t>
+    <t xml:space="preserve">9.83865165710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97931098937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98671340942383</t>
+    <t xml:space="preserve">9.97930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047336578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7572193145752</t>
+    <t xml:space="preserve">9.89047431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
+    <t xml:space="preserve">9.7720251083374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0533409118652</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4018726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40927505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26121520996094</t>
+    <t xml:space="preserve">9.40187168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40927410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26121425628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575103759766</t>
+    <t xml:space="preserve">9.10575008392334</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
@@ -3044,31 +3044,31 @@
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37226009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41667938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30563163757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17237758636475</t>
+    <t xml:space="preserve">9.37225914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4166784286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30563259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17237854003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17978096008301</t>
+    <t xml:space="preserve">9.20199108123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23160171508789</t>
+    <t xml:space="preserve">9.23160266876221</t>
   </si>
   <si>
     <t xml:space="preserve">9.01691436767578</t>
@@ -3077,28 +3077,28 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.31303596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35745334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26861667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15016841888428</t>
+    <t xml:space="preserve">9.35745525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26861763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15016746520996</t>
   </si>
   <si>
     <t xml:space="preserve">9.03171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02431678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98730278015137</t>
+    <t xml:space="preserve">9.02431583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98730087280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.09834671020508</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">10.0237283706665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95709991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.668381690979</t>
+    <t xml:space="preserve">9.95710182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772426605225</t>
+    <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885261535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75040340423584</t>
+    <t xml:space="preserve">8.75040435791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33078336715698</t>
+    <t xml:space="preserve">4.33078384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5898904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62690591812134</t>
+    <t xml:space="preserve">4.58989000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62690544128418</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128927230835</t>
+    <t xml:space="preserve">4.10128879547119</t>
   </si>
   <si>
     <t xml:space="preserve">4.13090133666992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27155876159668</t>
+    <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.1938271522522</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24564933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24935007095337</t>
+    <t xml:space="preserve">4.24564838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24934959411621</t>
   </si>
   <si>
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12720012664795</t>
+    <t xml:space="preserve">4.12719964981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
@@ -3212,19 +3212,19 @@
     <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233510971069</t>
+    <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
     <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41962051391602</t>
+    <t xml:space="preserve">4.41962003707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741086959839</t>
+    <t xml:space="preserve">4.39741134643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.36039590835571</t>
@@ -3233,37 +3233,37 @@
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499048233032</t>
+    <t xml:space="preserve">4.10499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17902088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93842244148254</t>
+    <t xml:space="preserve">4.17902135848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687141418457</t>
+    <t xml:space="preserve">4.05687046051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328674316406</t>
+    <t xml:space="preserve">4.04576683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51644802093506</t>
+    <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
     <t xml:space="preserve">3.86069011688232</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.07537889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206466674805</t>
+    <t xml:space="preserve">4.04206418991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510869026184</t>
+    <t xml:space="preserve">3.90510845184326</t>
   </si>
   <si>
     <t xml:space="preserve">3.96433281898499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98654174804688</t>
+    <t xml:space="preserve">3.98654246330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05316877365112</t>
+    <t xml:space="preserve">4.05316925048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.01615428924561</t>
@@ -3308,43 +3308,43 @@
     <t xml:space="preserve">4.01985549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88660097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86439156532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036116600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73483777046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50164246559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53310537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52015018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48313474655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51459765434265</t>
+    <t xml:space="preserve">3.88660049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8643913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036092758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73483824729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50164198875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53310513496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716466903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52014994621277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48313450813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51459717750549</t>
   </si>
   <si>
     <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62009119987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
+    <t xml:space="preserve">3.62009072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638927459717</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358095169067</t>
+    <t xml:space="preserve">3.35358142852783</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999747276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20181822776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2647442817688</t>
+    <t xml:space="preserve">3.14999771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2018187046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26474452018738</t>
   </si>
   <si>
     <t xml:space="preserve">3.10187745094299</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.007488489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">3.00748872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98342871665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3407,22 +3407,22 @@
     <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81130790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86497974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86683058738708</t>
+    <t xml:space="preserve">2.81130766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8649799823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86683082580566</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90569686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86868166923523</t>
+    <t xml:space="preserve">2.90569663047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86868143081665</t>
   </si>
   <si>
     <t xml:space="preserve">2.92420434951782</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981538772583</t>
+    <t xml:space="preserve">2.82981514930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059102058411</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999186515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49852895736694</t>
+    <t xml:space="preserve">2.52999210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49852919578552</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56515622138977</t>
+    <t xml:space="preserve">2.49297690391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57811188697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888728141785</t>
+    <t xml:space="preserve">2.57811164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888751983643</t>
   </si>
   <si>
     <t xml:space="preserve">2.44855833053589</t>
@@ -3485,22 +3485,22 @@
     <t xml:space="preserve">2.46706604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47817087173462</t>
+    <t xml:space="preserve">2.47817063331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.45596146583557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4892749786377</t>
+    <t xml:space="preserve">2.48927545547485</t>
   </si>
   <si>
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742461204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27273607254028</t>
+    <t xml:space="preserve">2.48742437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2727358341217</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34676647186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30790042877197</t>
+    <t xml:space="preserve">2.34676671028137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30790066719055</t>
   </si>
   <si>
     <t xml:space="preserve">2.19685482978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13577938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18760085105896</t>
+    <t xml:space="preserve">2.13577961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18760108947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.29679584503174</t>
@@ -3533,22 +3533,22 @@
     <t xml:space="preserve">2.28569149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30234813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35416984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34121441841125</t>
+    <t xml:space="preserve">2.30234789848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35416960716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.25422859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26718354225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28754210472107</t>
+    <t xml:space="preserve">2.26718378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28754186630249</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607919692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276544570923</t>
+    <t xml:space="preserve">2.25607895851135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18204879760742</t>
+    <t xml:space="preserve">2.18204855918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
@@ -3587,10 +3587,10 @@
     <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15798854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14873480796814</t>
+    <t xml:space="preserve">2.15798902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14873504638672</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688420295715</t>
+    <t xml:space="preserve">2.14688444137573</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434608459473</t>
+    <t xml:space="preserve">2.05434632301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912274360657</t>
+    <t xml:space="preserve">2.11912298202515</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652564048767</t>
@@ -3638,25 +3638,25 @@
     <t xml:space="preserve">1.95810627937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86186695098877</t>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132355690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638417720795</t>
+    <t xml:space="preserve">1.90132367610931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91036570072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077330589294</t>
+    <t xml:space="preserve">1.91036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953665733337</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679899692535</t>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556932449341</t>
+    <t xml:space="preserve">1.8955694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77062296867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556222915649</t>
+    <t xml:space="preserve">1.770623087883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556234836578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85857880115509</t>
+    <t xml:space="preserve">1.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.958864569664</t>
+    <t xml:space="preserve">1.95311045646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95886468887329</t>
   </si>
   <si>
     <t xml:space="preserve">2.00078773498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03695607185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98023724555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03942251205444</t>
+    <t xml:space="preserve">2.03695631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03942203521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559084892273</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2420494556427</t>
+    <t xml:space="preserve">2.24204897880554</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135241508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573763847351</t>
+    <t xml:space="preserve">2.14135217666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573740005493</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">2.30781054496765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34685659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35096621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34274625778198</t>
+    <t xml:space="preserve">2.34685635566711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35096645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3427460193634</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821424484253</t>
+    <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
     <t xml:space="preserve">2.25848960876465</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546251296997</t>
+    <t xml:space="preserve">2.14546227455139</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944379806519</t>
@@ -3833,37 +3833,37 @@
     <t xml:space="preserve">2.30986547470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35507655143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41056251525879</t>
+    <t xml:space="preserve">2.3550763130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41056227684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619526863098</t>
+    <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
     <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55236029624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53797507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54003024101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45988368988037</t>
+    <t xml:space="preserve">2.55236053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5379753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54003000259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45988345146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153491973877</t>
+    <t xml:space="preserve">2.52153468132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55852556228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55647039413452</t>
+    <t xml:space="preserve">2.5585253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55647015571594</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786447525024</t>
+    <t xml:space="preserve">2.75786423683167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087359428406</t>
+    <t xml:space="preserve">2.72087383270264</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250708580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66744256019592</t>
+    <t xml:space="preserve">2.63250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674427986145</t>
   </si>
   <si>
     <t xml:space="preserve">2.67155265808105</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7414243221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70443320274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72498393058777</t>
+    <t xml:space="preserve">2.74142408370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70443344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72498369216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3953,25 +3953,25 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78868985176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77019476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703909873962</t>
+    <t xml:space="preserve">2.78869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77019453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62634181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648860931396</t>
+    <t xml:space="preserve">2.60784649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6263415813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428712844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59757137298584</t>
+    <t xml:space="preserve">2.62428689002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59757161140442</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057915687561</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">2.58524107933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58935141563416</t>
+    <t xml:space="preserve">2.58935117721558</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048787117004</t>
+    <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
     <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91404747962952</t>
+    <t xml:space="preserve">2.9140477180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035929679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99419403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99830412864685</t>
+    <t xml:space="preserve">3.00035953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99419379234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99830436706543</t>
   </si>
   <si>
     <t xml:space="preserve">2.89760732650757</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553418159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61606645584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68388295173645</t>
+    <t xml:space="preserve">2.82773566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61606669425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896521568298</t>
+    <t xml:space="preserve">2.79896545410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.7907452583313</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9345977306366</t>
+    <t xml:space="preserve">2.93459796905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">2.77224969863892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78457975387573</t>
+    <t xml:space="preserve">2.78457999229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979083061218</t>
+    <t xml:space="preserve">2.82979106903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10927653312683</t>
+    <t xml:space="preserve">3.10927629470825</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034108161926</t>
+    <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
     <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82568097114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92226767539978</t>
+    <t xml:space="preserve">2.82568073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92226791381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.88733220100403</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995535850525</t>
+    <t xml:space="preserve">3.05995559692383</t>
   </si>
   <si>
     <t xml:space="preserve">2.9818639755249</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94281816482544</t>
+    <t xml:space="preserve">2.94281792640686</t>
   </si>
   <si>
     <t xml:space="preserve">2.92432260513306</t>
@@ -5613,6 +5613,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.00600004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03000020980835</t>
   </si>
 </sst>
 </file>
@@ -71159,7 +71162,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6909722222</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>309838</v>
@@ -71180,6 +71183,32 @@
         <v>1866</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911342593</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>460638</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>4.08199977874756</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>4.00600004196167</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="1868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="1869">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356557846069</t>
+    <t xml:space="preserve">12.2356548309326</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.195689201355</t>
+    <t xml:space="preserve">12.1956911087036</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101800918579</t>
+    <t xml:space="preserve">11.4097299575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101791381836</t>
   </si>
   <si>
     <t xml:space="preserve">11.0766973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.136643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770582199097</t>
+    <t xml:space="preserve">11.1366424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.677059173584</t>
   </si>
   <si>
     <t xml:space="preserve">10.3107204437256</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3906488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239521026611</t>
+    <t xml:space="preserve">10.7370042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3906478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239511489868</t>
   </si>
   <si>
     <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2574348449707</t>
+    <t xml:space="preserve">10.257435798645</t>
   </si>
   <si>
     <t xml:space="preserve">10.2707567214966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4838981628418</t>
+    <t xml:space="preserve">10.4838962554932</t>
   </si>
   <si>
     <t xml:space="preserve">10.297399520874</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">9.54474353790283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77120685577393</t>
+    <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6171102523804</t>
+    <t xml:space="preserve">10.6171112060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">9.96436500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4905586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7236814498901</t>
+    <t xml:space="preserve">10.4905595779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7236824035645</t>
   </si>
   <si>
     <t xml:space="preserve">10.9434833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4363737106323</t>
+    <t xml:space="preserve">11.4363746643066</t>
   </si>
   <si>
     <t xml:space="preserve">11.3431253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6495141983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0624780654907</t>
+    <t xml:space="preserve">11.6495151519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0624771118164</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289943695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4754390716553</t>
+    <t xml:space="preserve">12.2289953231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4754362106323</t>
   </si>
   <si>
     <t xml:space="preserve">12.4554567337036</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">12.3422269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4621171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823692321777</t>
+    <t xml:space="preserve">12.4621162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.555365562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823711395264</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961393356323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695867538452</t>
+    <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9159421920776</t>
+    <t xml:space="preserve">11.9159412384033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1890287399292</t>
@@ -221,130 +221,130 @@
     <t xml:space="preserve">11.0633764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6561765670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.955906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2689580917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217042922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9350261688232</t>
+    <t xml:space="preserve">11.6561756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2689571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.921703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9350252151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.1015434265137</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1281833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947889328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.16148853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.361307144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347574234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946132659912</t>
+    <t xml:space="preserve">13.1281843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1814708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3613080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347536087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946104049683</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9816484451294</t>
+    <t xml:space="preserve">12.981650352478</t>
   </si>
   <si>
     <t xml:space="preserve">12.6885795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.881739616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617572784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482549667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.375527381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7218828201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685098648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214345932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344060897827</t>
+    <t xml:space="preserve">12.5620279312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482568740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.721884727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344079971313</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5159893035889</t>
+    <t xml:space="preserve">13.5159883499146</t>
   </si>
   <si>
     <t xml:space="preserve">13.6230983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5226812362671</t>
+    <t xml:space="preserve">13.5226821899414</t>
   </si>
   <si>
     <t xml:space="preserve">13.5561532974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4222640991211</t>
+    <t xml:space="preserve">13.4222650527954</t>
   </si>
   <si>
     <t xml:space="preserve">13.3620147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.355320930481</t>
+    <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9938249588013</t>
+    <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">13.2749900817871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.194655418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6591053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833864212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.762056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7218894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766935348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524095535278</t>
+    <t xml:space="preserve">13.1946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.659104347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7218885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524085998535</t>
   </si>
   <si>
     <t xml:space="preserve">12.6925764083862</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">12.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1410999298096</t>
+    <t xml:space="preserve">13.1411018371582</t>
   </si>
   <si>
     <t xml:space="preserve">10.8850898742676</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834251403809</t>
+    <t xml:space="preserve">10.4834260940552</t>
   </si>
   <si>
     <t xml:space="preserve">10.7177295684814</t>
@@ -410,31 +410,31 @@
     <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0482902526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4432592391968</t>
+    <t xml:space="preserve">10.0482912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4432582855225</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4741954803467</t>
+    <t xml:space="preserve">11.1193943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
     <t xml:space="preserve">11.2599744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260890960693</t>
+    <t xml:space="preserve">11.126088142395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122833251953</t>
+    <t xml:space="preserve">11.0122842788696</t>
   </si>
   <si>
     <t xml:space="preserve">10.811450958252</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">10.9252548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7645902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0616788864136</t>
+    <t xml:space="preserve">10.8783941268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.764591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
     <t xml:space="preserve">10.1754837036133</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">8.67593860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80313110351562</t>
+    <t xml:space="preserve">8.80313205718994</t>
   </si>
   <si>
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37215518951416</t>
+    <t xml:space="preserve">9.20479488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37215423583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">9.37884998321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19140720367432</t>
+    <t xml:space="preserve">9.19140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63323783874512</t>
+    <t xml:space="preserve">9.6332368850708</t>
   </si>
   <si>
     <t xml:space="preserve">9.79390335083008</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">9.51273822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43909931182861</t>
+    <t xml:space="preserve">9.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.56629371643066</t>
@@ -527,34 +527,34 @@
     <t xml:space="preserve">9.53951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8273754119873</t>
+    <t xml:space="preserve">9.82737445831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78720855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87423515319824</t>
+    <t xml:space="preserve">9.78720760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87423610687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.6734037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07760238647461</t>
+    <t xml:space="preserve">9.07760334014893</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07090759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31190586090088</t>
+    <t xml:space="preserve">9.07090854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08429718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3119068145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.17801856994629</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3855447769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24496173858643</t>
+    <t xml:space="preserve">9.38554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24496269226074</t>
   </si>
   <si>
     <t xml:space="preserve">9.03743648529053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70940971374512</t>
+    <t xml:space="preserve">8.70941066741943</t>
   </si>
   <si>
     <t xml:space="preserve">8.72279930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87007522583008</t>
+    <t xml:space="preserve">8.87007617950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957752227783</t>
+    <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304862976074</t>
@@ -596,46 +596,46 @@
     <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71610546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66924285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20063591003418</t>
+    <t xml:space="preserve">8.71610450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66924381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2006368637085</t>
   </si>
   <si>
     <t xml:space="preserve">8.10022068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227781295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83913898468018</t>
+    <t xml:space="preserve">8.1203031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83913850784302</t>
   </si>
   <si>
     <t xml:space="preserve">7.86591672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6316123008728</t>
+    <t xml:space="preserve">7.84583330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63161277770996</t>
   </si>
   <si>
     <t xml:space="preserve">7.62491798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66508531570435</t>
+    <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
     <t xml:space="preserve">7.74541664123535</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">7.71194553375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69186210632324</t>
+    <t xml:space="preserve">7.69186162948608</t>
   </si>
   <si>
     <t xml:space="preserve">7.48433542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64500093460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95963716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12699794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38138580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92363166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2114896774292</t>
+    <t xml:space="preserve">7.64500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.651695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516683578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9596381187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12699699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38138484954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9236307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21149063110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.09768486022949</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">11.9294157028198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499153137207</t>
+    <t xml:space="preserve">11.8691654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499143600464</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2833099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971525192261</t>
+    <t xml:space="preserve">15.2833089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971515655518</t>
   </si>
   <si>
     <t xml:space="preserve">13.6967353820801</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">13.8975687026978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7235126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908739089966</t>
+    <t xml:space="preserve">13.7235145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908720016479</t>
   </si>
   <si>
     <t xml:space="preserve">13.9578189849854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7904596328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004800796509</t>
+    <t xml:space="preserve">13.7904577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004791259766</t>
   </si>
   <si>
     <t xml:space="preserve">14.0180673599243</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">14.0582332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9712085723877</t>
+    <t xml:space="preserve">13.9712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">14.0917043685913</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3126201629639</t>
+    <t xml:space="preserve">14.3126211166382</t>
   </si>
   <si>
     <t xml:space="preserve">14.2858428955078</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">14.1385679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251783370972</t>
+    <t xml:space="preserve">14.1251764297485</t>
   </si>
   <si>
     <t xml:space="preserve">13.8172340393066</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557390213013</t>
+    <t xml:space="preserve">13.4557371139526</t>
   </si>
   <si>
     <t xml:space="preserve">13.2415180206299</t>
@@ -770,70 +770,70 @@
     <t xml:space="preserve">13.2080450057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9268798828125</t>
+    <t xml:space="preserve">12.9268789291382</t>
   </si>
   <si>
     <t xml:space="preserve">12.7528257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8264646530151</t>
+    <t xml:space="preserve">12.8264656066895</t>
   </si>
   <si>
     <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067983627319</t>
+    <t xml:space="preserve">12.9067974090576</t>
   </si>
   <si>
     <t xml:space="preserve">13.1611843109131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0540752410889</t>
+    <t xml:space="preserve">13.0540733337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.9134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879625320435</t>
+    <t xml:space="preserve">13.2147417068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879615783691</t>
   </si>
   <si>
     <t xml:space="preserve">13.3419332504272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339889526367</t>
+    <t xml:space="preserve">13.181266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339908599854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8599367141724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9871301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0473794937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0206031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9201850891113</t>
+    <t xml:space="preserve">12.9871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.007212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0473785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0206022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758186340332</t>
+    <t xml:space="preserve">13.3754062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">13.3486280441284</t>
@@ -848,43 +848,43 @@
     <t xml:space="preserve">12.8666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867130279541</t>
+    <t xml:space="preserve">12.8867139816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8398542404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197689056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858816146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.310996055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3310794830322</t>
+    <t xml:space="preserve">12.8398532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.819769859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3109970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3310785293579</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708292007446</t>
+    <t xml:space="preserve">12.2708301544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570253372192</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862987518311</t>
+    <t xml:space="preserve">12.7862997055054</t>
   </si>
   <si>
     <t xml:space="preserve">12.8800191879272</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4448833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637201309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3043012619019</t>
+    <t xml:space="preserve">12.4448852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637182235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3043003082275</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913288116455</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574405670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4181070327759</t>
+    <t xml:space="preserve">12.2574396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2842178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
     <t xml:space="preserve">12.1971912384033</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0633029937744</t>
+    <t xml:space="preserve">12.0633039474487</t>
   </si>
   <si>
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6724939346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3176898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8089160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030536651611</t>
+    <t xml:space="preserve">12.672492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3176889419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8089170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030546188354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813064575195</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076694488525</t>
+    <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549453735352</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817235946655</t>
+    <t xml:space="preserve">11.6817226409912</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5210552215576</t>
+    <t xml:space="preserve">11.5210561752319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151947021484</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">11.7018060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4474201202393</t>
+    <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2265043258667</t>
+    <t xml:space="preserve">11.2265033721924</t>
   </si>
   <si>
     <t xml:space="preserve">10.7779788970947</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7980623245239</t>
+    <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
     <t xml:space="preserve">10.9453392028809</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0658388137817</t>
+    <t xml:space="preserve">11.1461706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0658378601074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528654098511</t>
+    <t xml:space="preserve">11.0591430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528644561768</t>
   </si>
   <si>
     <t xml:space="preserve">11.0993099212646</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1126985549927</t>
+    <t xml:space="preserve">11.112699508667</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5411405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5679187774658</t>
+    <t xml:space="preserve">11.5411396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5679178237915</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005575180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541139602661</t>
+    <t xml:space="preserve">11.4005584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4608087539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541149139404</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336133956909</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1595602035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0524492263794</t>
+    <t xml:space="preserve">11.1595592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0524482727051</t>
   </si>
   <si>
     <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5302858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3897037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093709945679</t>
+    <t xml:space="preserve">10.5302867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3897047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093719482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.1620941162109</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">10.2156505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3361492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.490119934082</t>
+    <t xml:space="preserve">10.3361482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4901208877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">10.3562316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076309204102</t>
+    <t xml:space="preserve">9.84076404571533</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80729007720947</t>
+    <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.68679237365723</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74704265594482</t>
+    <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6507863998413</t>
+    <t xml:space="preserve">10.7110347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650785446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.664174079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.376314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1888723373413</t>
+    <t xml:space="preserve">10.6641750335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3763151168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188871383667</t>
   </si>
   <si>
     <t xml:space="preserve">10.275899887085</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">10.1286220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2223443984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357320785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570640563965</t>
+    <t xml:space="preserve">10.2223453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570650100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5102033615112</t>
@@ -1217,22 +1217,22 @@
     <t xml:space="preserve">9.6533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52612590789795</t>
+    <t xml:space="preserve">9.52612686157227</t>
   </si>
   <si>
     <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83406925201416</t>
+    <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
     <t xml:space="preserve">9.84745788574219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2959823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436754226685</t>
+    <t xml:space="preserve">10.2959814071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">10.9855051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9587278366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7311182022095</t>
+    <t xml:space="preserve">10.9587268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7311191558838</t>
   </si>
   <si>
     <t xml:space="preserve">10.82483959198</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">10.9988946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926160812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1796426773071</t>
+    <t xml:space="preserve">11.0926151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1796436309814</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051742553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8917827606201</t>
+    <t xml:space="preserve">10.9051733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8917837142944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0390596389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7277708053589</t>
+    <t xml:space="preserve">11.0390605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7277717590332</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633417129517</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.289288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3696212768555</t>
+    <t xml:space="preserve">10.2892875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3696203231812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135507583618</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.533634185791</t>
+    <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6240081787109</t>
+    <t xml:space="preserve">10.6240072250366</t>
   </si>
   <si>
     <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.172947883606</t>
+    <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
     <t xml:space="preserve">10.9821586608887</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3629274368286</t>
+    <t xml:space="preserve">10.3394966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0349006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0951499938965</t>
+    <t xml:space="preserve">9.94452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0349016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.9788103103638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1060037612915</t>
+    <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0357131958008</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8717012405396</t>
+    <t xml:space="preserve">10.8717002868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.8683528900146</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">10.9553804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0256719589233</t>
+    <t xml:space="preserve">11.025671005249</t>
   </si>
   <si>
     <t xml:space="preserve">11.0825748443604</t>
@@ -1430,40 +1430,40 @@
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.28675365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.313530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9352970123291</t>
+    <t xml:space="preserve">11.2867546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3135299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9352960586548</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729677200317</t>
+    <t xml:space="preserve">10.3729686737061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.245774269104</t>
+    <t xml:space="preserve">10.2457752227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74369525909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847599029541</t>
+    <t xml:space="preserve">9.74369621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847503662109</t>
   </si>
   <si>
     <t xml:space="preserve">9.34537887573242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6700553894043</t>
+    <t xml:space="preserve">9.67005634307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.72695827484131</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">9.48596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637523651123</t>
+    <t xml:space="preserve">9.58637714385986</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">9.54286289215088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57298851013184</t>
+    <t xml:space="preserve">9.57298755645752</t>
   </si>
   <si>
     <t xml:space="preserve">9.56964111328125</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47926616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49600219726562</t>
+    <t xml:space="preserve">9.4792652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49600124359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.62319564819336</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949314117432</t>
+    <t xml:space="preserve">8.68932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949409484863</t>
   </si>
   <si>
     <t xml:space="preserve">8.89350605010986</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487926483154</t>
+    <t xml:space="preserve">9.22487831115723</t>
   </si>
   <si>
     <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2148380279541</t>
+    <t xml:space="preserve">9.21483707427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.13785171508789</t>
@@ -1550,34 +1550,34 @@
     <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6131534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71691799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46922492980957</t>
+    <t xml:space="preserve">9.61315441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71691703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46922588348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54621124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31525421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26504611968994</t>
+    <t xml:space="preserve">9.54621028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31525325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.73284149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80647945404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015960693359</t>
+    <t xml:space="preserve">8.80647754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86003398895264</t>
+    <t xml:space="preserve">8.86003494262695</t>
   </si>
   <si>
     <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88011837005615</t>
+    <t xml:space="preserve">8.88011741638184</t>
   </si>
   <si>
     <t xml:space="preserve">8.82656288146973</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2742748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24080276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2508430480957</t>
+    <t xml:space="preserve">8.27427387237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24080371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25084400177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639507293701</t>
+    <t xml:space="preserve">8.47175884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639602661133</t>
   </si>
   <si>
     <t xml:space="preserve">8.71945190429688</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00061702728271</t>
+    <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12780952453613</t>
+    <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66589736938477</t>
+    <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">8.47510623931885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30105209350586</t>
+    <t xml:space="preserve">8.30105113983154</t>
   </si>
   <si>
     <t xml:space="preserve">8.62907886505127</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516887664795</t>
+    <t xml:space="preserve">9.29517078399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855941772461</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111568450928</t>
+    <t xml:space="preserve">9.46587753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107444763184</t>
@@ -1745,49 +1745,49 @@
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810199737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23492050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25753879547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56548023223877</t>
+    <t xml:space="preserve">9.19810009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23491954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70271682739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56548118591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.5018835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75627136230469</t>
+    <t xml:space="preserve">8.75627040863037</t>
   </si>
   <si>
     <t xml:space="preserve">8.82321548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84329891204834</t>
+    <t xml:space="preserve">8.84329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">8.74622917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18471240997314</t>
+    <t xml:space="preserve">9.18471336364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.42236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26169776916504</t>
+    <t xml:space="preserve">9.26169872283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44914054870605</t>
+    <t xml:space="preserve">9.44914150238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.91105556488037</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">9.522780418396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45918273925781</t>
+    <t xml:space="preserve">9.45918369293213</t>
   </si>
   <si>
     <t xml:space="preserve">9.44244575500488</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456790924072</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27174091339111</t>
+    <t xml:space="preserve">9.2717399597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275806427002</t>
+    <t xml:space="preserve">8.71275901794434</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
@@ -1838,25 +1838,25 @@
     <t xml:space="preserve">9.27843379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947425842285</t>
+    <t xml:space="preserve">9.52947330474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42905902862549</t>
+    <t xml:space="preserve">9.42905807495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24831008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47257137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55625057220459</t>
+    <t xml:space="preserve">9.24830913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47257041931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.42571067810059</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">9.16128253936768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240451812744</t>
+    <t xml:space="preserve">9.14789295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240547180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.39223861694336</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454555511475</t>
+    <t xml:space="preserve">9.14454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69014072418213</t>
+    <t xml:space="preserve">9.69013977050781</t>
   </si>
   <si>
     <t xml:space="preserve">9.50939083099365</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79725074768066</t>
+    <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.9210958480835</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">9.90770721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92779159545898</t>
+    <t xml:space="preserve">9.92779064178467</t>
   </si>
   <si>
     <t xml:space="preserve">9.77716636657715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7102222442627</t>
+    <t xml:space="preserve">9.71022319793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.62989044189453</t>
@@ -1925,40 +1925,40 @@
     <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296615600586</t>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296520233154</t>
   </si>
   <si>
     <t xml:space="preserve">8.76631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62573051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7730073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961780548096</t>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953533172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77300643920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961971282959</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404594421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4056282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63993167877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70687675476074</t>
+    <t xml:space="preserve">9.40562725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63993072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70687580108643</t>
   </si>
   <si>
     <t xml:space="preserve">9.94787406921387</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53282070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60311317443848</t>
+    <t xml:space="preserve">9.53282165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20144844055176</t>
+    <t xml:space="preserve">9.20144939422607</t>
   </si>
   <si>
     <t xml:space="preserve">9.10103321075439</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">9.02739524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94371509552002</t>
+    <t xml:space="preserve">8.9437141418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.9805326461792</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">8.99057483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342357635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90354824066162</t>
+    <t xml:space="preserve">8.87342262268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90354919433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.68263339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67928504943848</t>
+    <t xml:space="preserve">8.67928600311279</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86084747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82402801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81063842773438</t>
+    <t xml:space="preserve">9.86084651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8240270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81063938140869</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068061828613</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764457702637</t>
+    <t xml:space="preserve">9.08764362335205</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">8.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288272857666</t>
+    <t xml:space="preserve">8.74288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677001953125</t>
+    <t xml:space="preserve">8.84664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677097320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681221008301</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.060866355896</t>
+    <t xml:space="preserve">9.06086540222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0809497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96714401245117</t>
+    <t xml:space="preserve">9.11776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726867675781</t>
+    <t xml:space="preserve">8.99726963043213</t>
   </si>
   <si>
     <t xml:space="preserve">8.92697906494141</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64246559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40146923065186</t>
+    <t xml:space="preserve">8.64246654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40146827697754</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
@@ -2123,85 +2123,85 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98976230621338</t>
+    <t xml:space="preserve">8.23410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98976278305054</t>
   </si>
   <si>
     <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01654052734375</t>
+    <t xml:space="preserve">8.01653957366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95629024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93286037445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02323436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96633243560791</t>
+    <t xml:space="preserve">7.94624948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95629119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93286085128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96633148193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558254241943</t>
+    <t xml:space="preserve">7.94290161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12953281402588</t>
+    <t xml:space="preserve">7.12953233718872</t>
   </si>
   <si>
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793167114258</t>
+    <t xml:space="preserve">7.54793214797974</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300439834595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07263040542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786951065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222461700439</t>
+    <t xml:space="preserve">7.07262992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222366333008</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256681442261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15884494781494</t>
+    <t xml:space="preserve">6.15884447097778</t>
   </si>
   <si>
     <t xml:space="preserve">5.55802297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57978010177612</t>
+    <t xml:space="preserve">5.57977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.4509129524231</t>
@@ -2213,19 +2213,19 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800109863281</t>
+    <t xml:space="preserve">4.74800062179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.05929040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27183771133423</t>
+    <t xml:space="preserve">5.27183723449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693231582642</t>
+    <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311758041382</t>
@@ -2237,46 +2237,46 @@
     <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29440689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47515487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6174111366272</t>
+    <t xml:space="preserve">6.2944073677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47515535354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49356460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741161346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.53038501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64753532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35967683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09190130233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03834676742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892837524414</t>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3596773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03834629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892789840698</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620477676392</t>
+    <t xml:space="preserve">6.32620429992676</t>
   </si>
   <si>
     <t xml:space="preserve">6.34628820419312</t>
@@ -2300,40 +2300,40 @@
     <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20905351638794</t>
+    <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156854629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813819885254</t>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433290481567</t>
+    <t xml:space="preserve">5.87433338165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68354272842407</t>
+    <t xml:space="preserve">5.68354320526123</t>
   </si>
   <si>
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08439445495605</t>
+    <t xml:space="preserve">5.0843939781189</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91368770599365</t>
+    <t xml:space="preserve">4.91368722915649</t>
   </si>
   <si>
     <t xml:space="preserve">5.08774185180664</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.188157081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34212923049927</t>
+    <t xml:space="preserve">5.18815755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34212875366211</t>
   </si>
   <si>
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22162961959839</t>
+    <t xml:space="preserve">5.22162914276123</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74379205703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89106941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94127798080444</t>
+    <t xml:space="preserve">5.74379253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044561386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89106893539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94127750396729</t>
   </si>
   <si>
     <t xml:space="preserve">5.82077836990356</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19819927215576</t>
+    <t xml:space="preserve">5.1981987953186</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861497879028</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30196189880371</t>
+    <t xml:space="preserve">5.30196237564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.238365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33208703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27853202819824</t>
+    <t xml:space="preserve">5.33208751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2785325050354</t>
   </si>
   <si>
     <t xml:space="preserve">5.23167085647583</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">5.35886478424072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32204580307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32539319992065</t>
+    <t xml:space="preserve">5.32204532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3253927230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">5.04422807693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97058963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94046497344971</t>
+    <t xml:space="preserve">4.97059011459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94046545028687</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786603927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12121343612671</t>
+    <t xml:space="preserve">5.11786651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12121391296387</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092239379883</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">5.0375337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96389579772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41576671600342</t>
+    <t xml:space="preserve">4.96389532089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41576719284058</t>
   </si>
   <si>
     <t xml:space="preserve">5.38898944854736</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32874011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57643270492554</t>
+    <t xml:space="preserve">5.32874059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57643222808838</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961324691772</t>
@@ -2501,16 +2501,16 @@
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568424224854</t>
+    <t xml:space="preserve">5.39568376541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221218109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38229513168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36555910110474</t>
+    <t xml:space="preserve">5.38229560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36555957794189</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
@@ -2525,34 +2525,34 @@
     <t xml:space="preserve">5.09108877182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60320997238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12537288665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15215063095093</t>
+    <t xml:space="preserve">5.60321044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12537336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15215015411377</t>
   </si>
   <si>
     <t xml:space="preserve">6.2793436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22244167327881</t>
+    <t xml:space="preserve">6.22244262695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524869918823</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441728591919</t>
+    <t xml:space="preserve">5.89441680908203</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375082015991</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61325216293335</t>
+    <t xml:space="preserve">5.61325168609619</t>
   </si>
   <si>
     <t xml:space="preserve">5.48605823516846</t>
@@ -2576,19 +2576,19 @@
     <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027875900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65676546096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55634927749634</t>
+    <t xml:space="preserve">5.73040437698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70362615585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65676498413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262741088867</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37894773483276</t>
+    <t xml:space="preserve">5.45258665084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37894821166992</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21828269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55300188064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8609447479248</t>
+    <t xml:space="preserve">5.2182822227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55300235748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86094427108765</t>
   </si>
   <si>
     <t xml:space="preserve">6.02830410003662</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">6.09859561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80820178985596</t>
+    <t xml:space="preserve">6.44335699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8082013130188</t>
   </si>
   <si>
     <t xml:space="preserve">6.63749504089355</t>
@@ -2660,28 +2660,28 @@
     <t xml:space="preserve">6.72117471694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67766046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41323232650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78142499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76134061813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10275459289551</t>
+    <t xml:space="preserve">6.67766141891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41323280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7613410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10275506973267</t>
   </si>
   <si>
     <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19647598266602</t>
+    <t xml:space="preserve">7.19647693634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.12283849716187</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">6.97556114196777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20986652374268</t>
+    <t xml:space="preserve">7.20986557006836</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961624145508</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">7.0023398399353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86175632476807</t>
+    <t xml:space="preserve">6.86175727844238</t>
   </si>
   <si>
     <t xml:space="preserve">7.06928396224976</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98225593566895</t>
+    <t xml:space="preserve">6.9822564125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.14292144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606122970581</t>
+    <t xml:space="preserve">7.09606075286865</t>
   </si>
   <si>
     <t xml:space="preserve">6.92200660705566</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">6.90192365646362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11614465713501</t>
+    <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572799682617</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581142425537</t>
+    <t xml:space="preserve">7.03581047058105</t>
   </si>
   <si>
     <t xml:space="preserve">6.90861701965332</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">7.13622665405273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15631008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25003147125244</t>
+    <t xml:space="preserve">7.15631055831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2500319480896</t>
   </si>
   <si>
     <t xml:space="preserve">7.27011489868164</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">7.32367086410522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55127954483032</t>
+    <t xml:space="preserve">7.55128002166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41069746017456</t>
+    <t xml:space="preserve">7.41069650650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56466770172119</t>
+    <t xml:space="preserve">7.47094631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56466817855835</t>
   </si>
   <si>
     <t xml:space="preserve">7.51111364364624</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">7.53789138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61152982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61822414398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7588062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113647460938</t>
+    <t xml:space="preserve">7.61152935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61822319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75880670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252714157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.1805534362793</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">8.89685344696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91693687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48849582672119</t>
+    <t xml:space="preserve">8.91693592071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48849487304688</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">8.41485691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21402454376221</t>
+    <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45502281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.45502376556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">8.26758098602295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3278284072876</t>
+    <t xml:space="preserve">8.32782936096191</t>
   </si>
   <si>
     <t xml:space="preserve">7.81236171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77888870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277694702148</t>
+    <t xml:space="preserve">7.77888965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277742385864</t>
   </si>
   <si>
     <t xml:space="preserve">7.89938831329346</t>
@@ -2870,25 +2870,25 @@
     <t xml:space="preserve">7.99980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049236297607</t>
+    <t xml:space="preserve">8.97049140930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290508270264</t>
+    <t xml:space="preserve">9.55290412902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473571777344</t>
+    <t xml:space="preserve">9.99473476409912</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9411792755127</t>
+    <t xml:space="preserve">9.94118022918701</t>
   </si>
   <si>
     <t xml:space="preserve">10.0081233978271</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">10.028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85415267944336</t>
+    <t xml:space="preserve">9.85415172576904</t>
   </si>
   <si>
     <t xml:space="preserve">9.7738208770752</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039237976074</t>
+    <t xml:space="preserve">10.6039247512817</t>
   </si>
   <si>
     <t xml:space="preserve">10.476731300354</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">10.677562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440916061401</t>
+    <t xml:space="preserve">10.6440906524658</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1865949630737</t>
+    <t xml:space="preserve">10.186595916748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755500793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93489074707031</t>
+    <t xml:space="preserve">9.93489170074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9052791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63877010345459</t>
+    <t xml:space="preserve">9.90528011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63876914978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047431945801</t>
+    <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.75721836090088</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.7720251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533409118652</t>
+    <t xml:space="preserve">10.0533399581909</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">9.60175514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54993343353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52032089233398</t>
+    <t xml:space="preserve">9.5499324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52031993865967</t>
   </si>
   <si>
     <t xml:space="preserve">9.40187168121338</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">9.40927410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524322509766</t>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575008392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99655532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34634971618652</t>
+    <t xml:space="preserve">9.10574913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99655437469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34634876251221</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37225914001465</t>
+    <t xml:space="preserve">9.37226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.4166784286499</t>
@@ -3059,31 +3059,31 @@
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199108123779</t>
+    <t xml:space="preserve">9.20199012756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.11315441131592</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01691436767578</t>
+    <t xml:space="preserve">9.01691341400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757179260254</t>
+    <t xml:space="preserve">9.15757083892822</t>
   </si>
   <si>
     <t xml:space="preserve">9.31303596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35745525360107</t>
+    <t xml:space="preserve">9.35745429992676</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">9.03171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02431583404541</t>
+    <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
     <t xml:space="preserve">8.98730087280273</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">9.95710182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.668381690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">9.32784175872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46109580993652</t>
+    <t xml:space="preserve">9.46109676361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772331237793</t>
+    <t xml:space="preserve">9.52772235870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885261535645</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.75040435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92067432403564</t>
+    <t xml:space="preserve">8.92067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.93548011779785</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261257171631</t>
+    <t xml:space="preserve">8.77261352539062</t>
   </si>
   <si>
     <t xml:space="preserve">4.33078384399414</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">4.58989000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62690544128418</t>
+    <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">4.10128879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13090133666992</t>
+    <t xml:space="preserve">4.13090085983276</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">4.16791677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24564838409424</t>
+    <t xml:space="preserve">4.17161798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2456488609314</t>
   </si>
   <si>
     <t xml:space="preserve">4.24934959411621</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033716201782</t>
+    <t xml:space="preserve">4.46033668518066</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35669469833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39741134643555</t>
+    <t xml:space="preserve">4.35669422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.36039590835571</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758758544922</t>
+    <t xml:space="preserve">4.10499143600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758710861206</t>
   </si>
   <si>
     <t xml:space="preserve">4.17902135848999</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687046051025</t>
+    <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58862781524658</t>
+    <t xml:space="preserve">3.58862805366516</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.86069011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07537889480591</t>
+    <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.04206418991089</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433281898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654246330261</t>
+    <t xml:space="preserve">3.9051079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">3.88660049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8643913269043</t>
+    <t xml:space="preserve">3.86439180374146</t>
   </si>
   <si>
     <t xml:space="preserve">3.79036092758179</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50164198875427</t>
+    <t xml:space="preserve">3.50164222717285</t>
   </si>
   <si>
     <t xml:space="preserve">3.53310513496399</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">3.55716466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52014994621277</t>
+    <t xml:space="preserve">3.52014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313450813293</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">3.51459717750549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5738217830658</t>
+    <t xml:space="preserve">3.57382154464722</t>
   </si>
   <si>
     <t xml:space="preserve">3.62009072303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61638927459717</t>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42391037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33137226104736</t>
+    <t xml:space="preserve">3.42391014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33137202262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999771118164</t>
+    <t xml:space="preserve">3.14999747276306</t>
   </si>
   <si>
     <t xml:space="preserve">3.2018187046051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26474452018738</t>
+    <t xml:space="preserve">3.26474475860596</t>
   </si>
   <si>
     <t xml:space="preserve">3.10187745094299</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88718914985657</t>
+    <t xml:space="preserve">2.88718891143799</t>
   </si>
   <si>
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00748872756958</t>
+    <t xml:space="preserve">3.007488489151</t>
   </si>
   <si>
     <t xml:space="preserve">2.98342871665955</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">2.8649799823761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503896713257</t>
+    <t xml:space="preserve">2.86683058738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503872871399</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014433860779</t>
+    <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981514930725</t>
+    <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059102058411</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999210357666</t>
+    <t xml:space="preserve">2.52999186515808</t>
   </si>
   <si>
     <t xml:space="preserve">2.49852919578552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60032105445862</t>
+    <t xml:space="preserve">2.60032081604004</t>
   </si>
   <si>
     <t xml:space="preserve">2.49297690391541</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6151270866394</t>
+    <t xml:space="preserve">2.61512732505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.57811164855957</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2727358341217</t>
+    <t xml:space="preserve">2.27273607254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4133939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34676671028137</t>
+    <t xml:space="preserve">2.41339421272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34676647186279</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790066719055</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">2.28569149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30234789848328</t>
+    <t xml:space="preserve">2.30234813690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35416960716248</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25422859191895</t>
+    <t xml:space="preserve">2.25422835350037</t>
   </si>
   <si>
     <t xml:space="preserve">2.26718378067017</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607895851135</t>
+    <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
     <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24312376976013</t>
+    <t xml:space="preserve">2.24312400817871</t>
   </si>
   <si>
     <t xml:space="preserve">2.18204855918884</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">2.21351170539856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1302273273468</t>
+    <t xml:space="preserve">2.13022756576538</t>
   </si>
   <si>
     <t xml:space="preserve">2.15798902511597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14873504638672</t>
+    <t xml:space="preserve">2.14873480796814</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912298202515</t>
+    <t xml:space="preserve">2.11912274360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652564048767</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132367610931</t>
+    <t xml:space="preserve">1.90132355690002</t>
   </si>
   <si>
     <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255311012268</t>
+    <t xml:space="preserve">1.87255322933197</t>
   </si>
   <si>
     <t xml:space="preserve">1.91036558151245</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84953665733337</t>
+    <t xml:space="preserve">1.84953653812408</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
@@ -3668,25 +3668,25 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679887771606</t>
+    <t xml:space="preserve">1.86679875850677</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8955694437027</t>
+    <t xml:space="preserve">1.89556956291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720624446869</t>
+    <t xml:space="preserve">1.8372061252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.78541910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76158058643341</t>
+    <t xml:space="preserve">1.7615807056427</t>
   </si>
   <si>
     <t xml:space="preserve">1.770623087883</t>
@@ -3698,34 +3698,34 @@
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8585786819458</t>
+    <t xml:space="preserve">1.85857880115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311045646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95886468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03695631027222</t>
+    <t xml:space="preserve">1.95311057567596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.958864569664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078749656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03695607185364</t>
   </si>
   <si>
     <t xml:space="preserve">1.98023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03942203521729</t>
+    <t xml:space="preserve">2.03942227363586</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559084892273</t>
+    <t xml:space="preserve">2.07559108734131</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204897880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23382902145386</t>
+    <t xml:space="preserve">2.24204921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23382925987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.14135217666626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573740005493</t>
+    <t xml:space="preserve">2.15573763847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">2.2728750705719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904009819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30781054496765</t>
+    <t xml:space="preserve">2.27904033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30781030654907</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685635566711</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">2.35096645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3427460193634</t>
+    <t xml:space="preserve">2.34274625778198</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25848960876465</t>
+    <t xml:space="preserve">2.25848937034607</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3812,10 +3812,10 @@
     <t xml:space="preserve">2.22766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1619029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14546227455139</t>
+    <t xml:space="preserve">2.16190266609192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14546251296997</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944379806519</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">2.3550763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41056227684021</t>
+    <t xml:space="preserve">2.41056251525879</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52769994735718</t>
+    <t xml:space="preserve">2.5276997089386</t>
   </si>
   <si>
     <t xml:space="preserve">2.55236053466797</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">2.54003000259399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45988345146179</t>
+    <t xml:space="preserve">2.45988368988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153468132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54208517074585</t>
+    <t xml:space="preserve">2.52153491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54208493232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.51125955581665</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920462608337</t>
+    <t xml:space="preserve">2.50920438766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.5585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55647015571594</t>
+    <t xml:space="preserve">2.55647039413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3902,25 +3902,25 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786423683167</t>
+    <t xml:space="preserve">2.75786447525024</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087383270264</t>
+    <t xml:space="preserve">2.72087359428406</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6674427986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67155265808105</t>
+    <t xml:space="preserve">2.63250708580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66744256019592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67155289649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.68799304962158</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">2.70443344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72498369216919</t>
+    <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">2.60784649848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6263415813446</t>
+    <t xml:space="preserve">2.62634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">2.70648837089539</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">2.62428689002991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59757161140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6057915687561</t>
+    <t xml:space="preserve">2.59757137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60579133033752</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">2.69621324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79485511779785</t>
+    <t xml:space="preserve">2.79485535621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.86678171157837</t>
@@ -4031,28 +4031,28 @@
     <t xml:space="preserve">3.00035953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99419379234314</t>
+    <t xml:space="preserve">2.99419403076172</t>
   </si>
   <si>
     <t xml:space="preserve">2.99830436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89760732650757</t>
+    <t xml:space="preserve">2.89760756492615</t>
   </si>
   <si>
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773566246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553442001343</t>
+    <t xml:space="preserve">2.82773590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553418159485</t>
   </si>
   <si>
     <t xml:space="preserve">2.61606669425964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68388319015503</t>
+    <t xml:space="preserve">2.68388295173645</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4064,13 +4064,13 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896545410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7907452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99213933944702</t>
+    <t xml:space="preserve">2.79896521568298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79074501991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99213910102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.99008417129517</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582728385925</t>
+    <t xml:space="preserve">2.90582752227783</t>
   </si>
   <si>
     <t xml:space="preserve">2.9633686542511</t>
@@ -4124,16 +4124,16 @@
     <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86883687973022</t>
+    <t xml:space="preserve">2.86883664131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.82568073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92226791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88733220100403</t>
+    <t xml:space="preserve">2.92226767539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88733196258545</t>
   </si>
   <si>
     <t xml:space="preserve">2.8893871307373</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">3.05995559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9818639755249</t>
+    <t xml:space="preserve">2.98186421394348</t>
   </si>
   <si>
     <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94281792640686</t>
+    <t xml:space="preserve">2.94281816482544</t>
   </si>
   <si>
     <t xml:space="preserve">2.92432260513306</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">2.90442943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92211246490479</t>
+    <t xml:space="preserve">2.92211222648621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98621320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04147243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1033627986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136608123779</t>
+    <t xml:space="preserve">3.04147267341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136584281921</t>
   </si>
   <si>
     <t xml:space="preserve">3.11883544921875</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">3.07241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09452152252197</t>
+    <t xml:space="preserve">3.09452128410339</t>
   </si>
   <si>
     <t xml:space="preserve">3.07020735740662</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.97958207130432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97074055671692</t>
+    <t xml:space="preserve">2.97074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.91548109054565</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">2.93316435813904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92874336242676</t>
+    <t xml:space="preserve">2.92874360084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.90221905708313</t>
@@ -4235,13 +4235,13 @@
     <t xml:space="preserve">2.90000867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87790513038635</t>
+    <t xml:space="preserve">2.87790489196777</t>
   </si>
   <si>
     <t xml:space="preserve">2.86464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83369755744934</t>
+    <t xml:space="preserve">2.83369731903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.81822490692139</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">2.69002318382263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60160851478577</t>
+    <t xml:space="preserve">2.60160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.66791939735413</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">2.68560242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62813305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6502366065979</t>
+    <t xml:space="preserve">2.62813282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65023636817932</t>
   </si>
   <si>
     <t xml:space="preserve">2.60381865501404</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">2.5551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47340655326843</t>
+    <t xml:space="preserve">2.47340679168701</t>
   </si>
   <si>
     <t xml:space="preserve">2.44909262657166</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">2.47119641304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47782754898071</t>
+    <t xml:space="preserve">2.47782731056213</t>
   </si>
   <si>
     <t xml:space="preserve">2.46014451980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624221801758</t>
+    <t xml:space="preserve">2.56624245643616</t>
   </si>
   <si>
     <t xml:space="preserve">2.55961132049561</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">2.54855942726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50877285003662</t>
+    <t xml:space="preserve">2.50877261161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.53087639808655</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">2.32531189918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24529623985291</t>
+    <t xml:space="preserve">2.24529647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.19932055473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15422892570496</t>
+    <t xml:space="preserve">2.15422916412354</t>
   </si>
   <si>
     <t xml:space="preserve">2.14715576171875</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">2.17633247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29746103286743</t>
+    <t xml:space="preserve">2.29746127128601</t>
   </si>
   <si>
     <t xml:space="preserve">2.38720226287842</t>
@@ -4364,40 +4364,40 @@
     <t xml:space="preserve">2.33813214302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51894021034241</t>
+    <t xml:space="preserve">2.51894044876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46854400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42345213890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51319360733032</t>
+    <t xml:space="preserve">2.42345237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51319336891174</t>
   </si>
   <si>
     <t xml:space="preserve">2.57287359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52026653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55076956748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53794980049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54723334312439</t>
+    <t xml:space="preserve">2.52026677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56712651252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53794956207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54723310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.70461177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78109073638916</t>
+    <t xml:space="preserve">2.78109049797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.75854468345642</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">2.79302644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75633430480957</t>
+    <t xml:space="preserve">2.75633454322815</t>
   </si>
   <si>
     <t xml:space="preserve">2.77357530593872</t>
@@ -4433,13 +4433,13 @@
     <t xml:space="preserve">2.91327095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84253883361816</t>
+    <t xml:space="preserve">2.84253907203674</t>
   </si>
   <si>
     <t xml:space="preserve">2.93935322761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94112133979797</t>
+    <t xml:space="preserve">2.94112157821655</t>
   </si>
   <si>
     <t xml:space="preserve">2.92343854904175</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">2.94554233551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785954475403</t>
+    <t xml:space="preserve">2.92785930633545</t>
   </si>
   <si>
     <t xml:space="preserve">2.93537449836731</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">2.89249348640442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88851451873779</t>
+    <t xml:space="preserve">2.88851475715637</t>
   </si>
   <si>
     <t xml:space="preserve">2.93006944656372</t>
@@ -4472,25 +4472,25 @@
     <t xml:space="preserve">2.88011527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92741727828979</t>
+    <t xml:space="preserve">2.92741751670837</t>
   </si>
   <si>
     <t xml:space="preserve">3.02378964424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03926229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03086280822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96189880371094</t>
+    <t xml:space="preserve">3.03926205635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03086256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96189904212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.93493247032166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89824032783508</t>
+    <t xml:space="preserve">2.89824056625366</t>
   </si>
   <si>
     <t xml:space="preserve">2.91724944114685</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">2.9106183052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9176914691925</t>
+    <t xml:space="preserve">2.91769170761108</t>
   </si>
   <si>
     <t xml:space="preserve">2.9256489276886</t>
@@ -4511,10 +4511,10 @@
     <t xml:space="preserve">2.98444485664368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02246332168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00168585777283</t>
+    <t xml:space="preserve">3.02246308326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00168561935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.95438385009766</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">2.73865151405334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67101407051086</t>
+    <t xml:space="preserve">2.67101383209229</t>
   </si>
   <si>
     <t xml:space="preserve">2.68737077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66084623336792</t>
+    <t xml:space="preserve">2.6608464717865</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869686126709</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">2.64537382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72052621841431</t>
+    <t xml:space="preserve">2.72052645683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70947456359863</t>
@@ -4571,13 +4571,13 @@
     <t xml:space="preserve">2.62327003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58701992034912</t>
+    <t xml:space="preserve">2.5870201587677</t>
   </si>
   <si>
     <t xml:space="preserve">2.60426068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57729411125183</t>
+    <t xml:space="preserve">2.57729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">2.58171510696411</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">2.58083081245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59497737884521</t>
+    <t xml:space="preserve">2.59497714042664</t>
   </si>
   <si>
     <t xml:space="preserve">2.65288901329041</t>
@@ -4601,10 +4601,10 @@
     <t xml:space="preserve">2.69488620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69223380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64139485359192</t>
+    <t xml:space="preserve">2.69223356246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6413950920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480954170227</t>
@@ -4619,19 +4619,19 @@
     <t xml:space="preserve">2.70549583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71168494224548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67985534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85049629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342336654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9318380355835</t>
+    <t xml:space="preserve">2.7116847038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67985558509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85049605369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342312812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93183779716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.91946005821228</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">2.94952082633972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878894805908</t>
+    <t xml:space="preserve">2.87878918647766</t>
   </si>
   <si>
     <t xml:space="preserve">3.13872885704041</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">3.30671715736389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42519307136536</t>
+    <t xml:space="preserve">3.42519330978394</t>
   </si>
   <si>
     <t xml:space="preserve">3.41988825798035</t>
@@ -4676,10 +4676,10 @@
     <t xml:space="preserve">3.34561967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33500981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43933939933777</t>
+    <t xml:space="preserve">3.33501005172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43933963775635</t>
   </si>
   <si>
     <t xml:space="preserve">3.36507105827332</t>
@@ -4691,10 +4691,10 @@
     <t xml:space="preserve">3.29787564277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30848574638367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32793688774109</t>
+    <t xml:space="preserve">3.30848550796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32793664932251</t>
   </si>
   <si>
     <t xml:space="preserve">3.41458320617676</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">3.41104674339294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49592518806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57019352912903</t>
+    <t xml:space="preserve">3.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57019376754761</t>
   </si>
   <si>
     <t xml:space="preserve">3.57372999191284</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">3.50123000144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50653481483459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52598595619202</t>
+    <t xml:space="preserve">3.50653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5259861946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616945266724</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">3.61793756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59848666191101</t>
+    <t xml:space="preserve">3.59848642349243</t>
   </si>
   <si>
     <t xml:space="preserve">3.63031578063965</t>
@@ -4745,28 +4745,28 @@
     <t xml:space="preserve">3.7045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77708435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84074282646179</t>
+    <t xml:space="preserve">3.77708411216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82129192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">3.84781646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85488963127136</t>
+    <t xml:space="preserve">3.85488939285278</t>
   </si>
   <si>
     <t xml:space="preserve">3.87610912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232815742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85842609405518</t>
+    <t xml:space="preserve">3.75232839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8584258556366</t>
   </si>
   <si>
     <t xml:space="preserve">3.65860843658447</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.46409559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57903504371643</t>
+    <t xml:space="preserve">3.57903480529785</t>
   </si>
   <si>
     <t xml:space="preserve">3.52775454521179</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">3.4941565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52952265739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62324261665344</t>
+    <t xml:space="preserve">3.52952289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62324237823486</t>
   </si>
   <si>
     <t xml:space="preserve">3.61440086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68690133094788</t>
+    <t xml:space="preserve">3.6869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">3.65684032440186</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">3.6957426071167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74525499343872</t>
+    <t xml:space="preserve">3.7452552318573</t>
   </si>
   <si>
     <t xml:space="preserve">3.75056004524231</t>
@@ -4823,19 +4823,19 @@
     <t xml:space="preserve">3.80714583396912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05824375152588</t>
+    <t xml:space="preserve">4.20501279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05824422836304</t>
   </si>
   <si>
     <t xml:space="preserve">4.09184122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12013387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1678786277771</t>
+    <t xml:space="preserve">4.1201343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16787815093994</t>
   </si>
   <si>
     <t xml:space="preserve">4.07592678070068</t>
@@ -5616,6 +5616,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.03000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05000019073486</t>
   </si>
 </sst>
 </file>
@@ -71188,7 +71191,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911342593</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>460638</v>
@@ -71209,6 +71212,32 @@
         <v>1867</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6910185185</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>232368</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>4.07000017166138</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>4.06599998474121</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356538772583</t>
+    <t xml:space="preserve">12.2356548309326</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">12.1956901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028007507324</t>
+    <t xml:space="preserve">11.7027997970581</t>
   </si>
   <si>
     <t xml:space="preserve">11.5895690917969</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">11.4097309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9101791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0766973495483</t>
+    <t xml:space="preserve">10.9101800918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076696395874</t>
   </si>
   <si>
     <t xml:space="preserve">11.136643409729</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">10.3107204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2907390594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65797328948975</t>
+    <t xml:space="preserve">10.2907381057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.2507753372192</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">10.3906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4239511489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438432693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2574338912964</t>
+    <t xml:space="preserve">10.4239521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
     <t xml:space="preserve">10.2707557678223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4838962554932</t>
+    <t xml:space="preserve">10.4838972091675</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973985671997</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">10.1042394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8702173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7170209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77786540985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91108131408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54474258422852</t>
+    <t xml:space="preserve">10.8702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7170219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77786731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91107940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54474353790283</t>
   </si>
   <si>
     <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2174701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639158248901</t>
+    <t xml:space="preserve">10.2174711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639148712158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.417290687561</t>
+    <t xml:space="preserve">10.4172925949097</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703075408936</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436405181885</t>
+    <t xml:space="preserve">9.96436500549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
@@ -167,79 +167,79 @@
     <t xml:space="preserve">11.6495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0624780654907</t>
+    <t xml:space="preserve">11.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0624771118164</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289934158325</t>
+    <t xml:space="preserve">12.2289943695068</t>
   </si>
   <si>
     <t xml:space="preserve">12.475438117981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4554576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422269821167</t>
+    <t xml:space="preserve">12.4554586410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422260284424</t>
   </si>
   <si>
     <t xml:space="preserve">12.4621171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5553684234619</t>
+    <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823701858521</t>
+    <t xml:space="preserve">12.1823682785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695867538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0757970809937</t>
+    <t xml:space="preserve">11.5695877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0757961273193</t>
   </si>
   <si>
     <t xml:space="preserve">11.9159421920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1890306472778</t>
+    <t xml:space="preserve">12.1890296936035</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0633764266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561756134033</t>
+    <t xml:space="preserve">11.0633783340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.656177520752</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559059143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217042922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9350233078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1015405654907</t>
+    <t xml:space="preserve">12.2689580917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.921703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9350252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101541519165</t>
   </si>
   <si>
     <t xml:space="preserve">13.1281843185425</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">13.2480764389038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1947908401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614894866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613080978394</t>
+    <t xml:space="preserve">13.1947917938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1814699172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.361307144165</t>
   </si>
   <si>
     <t xml:space="preserve">13.2347555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3946104049683</t>
+    <t xml:space="preserve">13.3946132659912</t>
   </si>
   <si>
     <t xml:space="preserve">13.0882205963135</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">12.6885786056519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620269775391</t>
+    <t xml:space="preserve">12.5620288848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.881739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8617563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884010314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482568740845</t>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482549667358</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
@@ -296,40 +296,40 @@
     <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221525192261</t>
+    <t xml:space="preserve">12.4221515655518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488874435425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.721884727478</t>
+    <t xml:space="preserve">12.7218837738037</t>
   </si>
   <si>
     <t xml:space="preserve">12.7685079574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9150419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344060897827</t>
+    <t xml:space="preserve">12.9150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344079971313</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5159883499146</t>
+    <t xml:space="preserve">13.5159873962402</t>
   </si>
   <si>
     <t xml:space="preserve">13.6230983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5226821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561532974243</t>
+    <t xml:space="preserve">13.5226831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.4222650527954</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">13.3620157241821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3553218841553</t>
+    <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9938249588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017663955688</t>
+    <t xml:space="preserve">12.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
     <t xml:space="preserve">13.2749891281128</t>
@@ -356,52 +356,52 @@
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6591053009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833864212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156099319458</t>
+    <t xml:space="preserve">12.6591033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620544433594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.721887588501</t>
+    <t xml:space="preserve">11.7218894958496</t>
   </si>
   <si>
     <t xml:space="preserve">12.0766935348511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6524105072021</t>
+    <t xml:space="preserve">12.6524095535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4515800476074</t>
+    <t xml:space="preserve">12.4515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">13.1411008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8850908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487064361572</t>
+    <t xml:space="preserve">10.8850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487054824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8382291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4834260940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177305221558</t>
+    <t xml:space="preserve">10.8382301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177286148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4432601928711</t>
+    <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4741954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126088142395</t>
+    <t xml:space="preserve">11.1193943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.474196434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1260890960693</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.811450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.925256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8783950805664</t>
+    <t xml:space="preserve">11.0122842788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8114500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9252557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8783941268921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
@@ -452,19 +452,19 @@
     <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1754837036133</t>
+    <t xml:space="preserve">10.175482749939</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06421279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93032550811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">9.06421375274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93032455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313205718994</t>
@@ -473,55 +473,55 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37215614318848</t>
+    <t xml:space="preserve">9.20479488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37215423583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33868408203125</t>
+    <t xml:space="preserve">9.33868312835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.23826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31860065460205</t>
+    <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13115787506104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37885093688965</t>
+    <t xml:space="preserve">9.37884998321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6332368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51273822784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43910026550293</t>
+    <t xml:space="preserve">9.23157405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43909931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.56629276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.49265575408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.53951549530029</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">9.78720760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87423515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6734037399292</t>
+    <t xml:space="preserve">9.87423610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67340469360352</t>
   </si>
   <si>
     <t xml:space="preserve">9.07760238647461</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">9.07090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08429718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31190586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36546230316162</t>
+    <t xml:space="preserve">9.08429622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.3855447769165</t>
@@ -581,85 +581,85 @@
     <t xml:space="preserve">8.72279930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87007713317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76965999603271</t>
+    <t xml:space="preserve">8.87007617950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7696590423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78304862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78974342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71610450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66924381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2006368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1002197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12030410766602</t>
+    <t xml:space="preserve">8.78304958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78974437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71610546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3345251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20063591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1203031539917</t>
   </si>
   <si>
     <t xml:space="preserve">7.79227781295776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82575035095215</t>
+    <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583330154419</t>
+    <t xml:space="preserve">7.86591577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.63161277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62491846084595</t>
+    <t xml:space="preserve">7.62491893768311</t>
   </si>
   <si>
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194553375244</t>
+    <t xml:space="preserve">7.74541759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7119460105896</t>
   </si>
   <si>
     <t xml:space="preserve">7.69186162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48433542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169668197632</t>
+    <t xml:space="preserve">7.48433637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500188827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169620513916</t>
   </si>
   <si>
     <t xml:space="preserve">7.68516731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95963764190674</t>
+    <t xml:space="preserve">7.95963716506958</t>
   </si>
   <si>
     <t xml:space="preserve">8.12699794769287</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768676757812</t>
+    <t xml:space="preserve">9.21148872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768581390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.9963598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1168594360352</t>
+    <t xml:space="preserve">12.1168584823608</t>
   </si>
   <si>
     <t xml:space="preserve">11.9294147491455</t>
@@ -692,55 +692,55 @@
     <t xml:space="preserve">12.0499143600464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8615617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833089828491</t>
+    <t xml:space="preserve">14.8615608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833061218262</t>
   </si>
   <si>
     <t xml:space="preserve">13.7971525192261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6967363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7569847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235136032104</t>
+    <t xml:space="preserve">13.6967344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975667953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235145568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.8908739089966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.957818031311</t>
+    <t xml:space="preserve">13.9578170776367</t>
   </si>
   <si>
     <t xml:space="preserve">13.7904577255249</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6004800796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180673599243</t>
+    <t xml:space="preserve">14.6004781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180683135986</t>
   </si>
   <si>
     <t xml:space="preserve">14.0582332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9712066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3126211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2858438491821</t>
+    <t xml:space="preserve">13.9712076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3126201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2858428955078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1385669708252</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">14.1251783370972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557371139526</t>
+    <t xml:space="preserve">13.8172359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557390213013</t>
   </si>
   <si>
     <t xml:space="preserve">13.2415180206299</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">13.2549047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.208044052124</t>
+    <t xml:space="preserve">13.2080450057983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9268798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7528257369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737405776978</t>
+    <t xml:space="preserve">12.7528247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737415313721</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067974090576</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">13.1611843109131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9134931564331</t>
+    <t xml:space="preserve">13.0540742874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9134912490845</t>
   </si>
   <si>
     <t xml:space="preserve">13.2147388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1879615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599376678467</t>
+    <t xml:space="preserve">13.1879625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419351577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8599348068237</t>
   </si>
   <si>
     <t xml:space="preserve">12.9871301651001</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">13.0206022262573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9201850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8934087753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3754024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3486270904541</t>
+    <t xml:space="preserve">12.9201860427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3754034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758195877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3486289978027</t>
   </si>
   <si>
     <t xml:space="preserve">13.2214336395264</t>
@@ -845,28 +845,28 @@
     <t xml:space="preserve">13.1745729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406847000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8666315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8867139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8398542404175</t>
+    <t xml:space="preserve">13.0406837463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8666305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8867149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.933575630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
     <t xml:space="preserve">12.9001035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9536590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532428741455</t>
+    <t xml:space="preserve">12.9536581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532409667969</t>
   </si>
   <si>
     <t xml:space="preserve">12.8197708129883</t>
@@ -875,40 +875,40 @@
     <t xml:space="preserve">12.6858825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386056900024</t>
+    <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
     <t xml:space="preserve">12.3109951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3310804367065</t>
+    <t xml:space="preserve">12.3310785293579</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708292007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1570253372192</t>
+    <t xml:space="preserve">12.2708301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
     <t xml:space="preserve">11.6750288009644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8624715805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1771078109741</t>
+    <t xml:space="preserve">11.8624696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
     <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862997055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800191879272</t>
+    <t xml:space="preserve">12.7862987518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800210952759</t>
   </si>
   <si>
     <t xml:space="preserve">12.9469633102417</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4448843002319</t>
+    <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
     <t xml:space="preserve">12.1637201309204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3043003082275</t>
+    <t xml:space="preserve">12.3043012619019</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
+    <t xml:space="preserve">12.558690071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649686813354</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189393997192</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.284218788147</t>
+    <t xml:space="preserve">12.2842178344727</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.197190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1034688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0900802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0633039474487</t>
+    <t xml:space="preserve">12.1971921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1034708023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0900812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0633029937744</t>
   </si>
   <si>
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6724939346313</t>
+    <t xml:space="preserve">12.6724948883057</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176898956299</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030527114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813055038452</t>
+    <t xml:space="preserve">12.0030546188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076684951782</t>
+    <t xml:space="preserve">11.5076694488525</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549444198608</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5210561752319</t>
+    <t xml:space="preserve">11.5210552215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6348609924316</t>
+    <t xml:space="preserve">11.6616401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.634861946106</t>
   </si>
   <si>
     <t xml:space="preserve">11.7687501907349</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3804750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2265033721924</t>
+    <t xml:space="preserve">11.3804759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">10.777979850769</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">10.9453392028809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.139476776123</t>
+    <t xml:space="preserve">11.1394758224487</t>
   </si>
   <si>
     <t xml:space="preserve">11.1930322647095</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">11.0658388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1327819824219</t>
+    <t xml:space="preserve">11.1327810287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591440200806</t>
@@ -1070,28 +1070,28 @@
     <t xml:space="preserve">11.112699508667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4206409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5411396026611</t>
+    <t xml:space="preserve">11.4206399917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5411415100098</t>
   </si>
   <si>
     <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198095321655</t>
+    <t xml:space="preserve">11.2198104858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541130065918</t>
+    <t xml:space="preserve">11.4005575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4608087539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541149139404</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336133956909</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">11.1595592498779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5302867889404</t>
+    <t xml:space="preserve">11.0524492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.3897047042847</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3093709945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1620950698853</t>
+    <t xml:space="preserve">10.3093719482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.2156505584717</t>
@@ -1127,37 +1127,37 @@
     <t xml:space="preserve">10.3361492156982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490119934082</t>
+    <t xml:space="preserve">10.4901208877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3428440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3562326431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84076404571533</t>
+    <t xml:space="preserve">10.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3562316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80729007720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68679141998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71356964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72026538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74704265594482</t>
+    <t xml:space="preserve">9.80729103088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68679332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7135705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72026443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
@@ -1169,28 +1169,28 @@
     <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5235929489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7110357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650785446167</t>
+    <t xml:space="preserve">10.5235919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7110347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507863998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708688735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.664174079895</t>
+    <t xml:space="preserve">10.6708679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6641750335693</t>
   </si>
   <si>
     <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1888723373413</t>
+    <t xml:space="preserve">10.188871383667</t>
   </si>
   <si>
     <t xml:space="preserve">10.2758989334106</t>
@@ -1202,46 +1202,46 @@
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
+    <t xml:space="preserve">10.2357339859009</t>
   </si>
   <si>
     <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102033615112</t>
+    <t xml:space="preserve">10.5102024078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52612686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62654304504395</t>
+    <t xml:space="preserve">10.2089567184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65331935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52612590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62654209136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7712841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5972299575806</t>
+    <t xml:space="preserve">9.8474588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5436744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7712850570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5972309112549</t>
   </si>
   <si>
     <t xml:space="preserve">10.8583116531372</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">10.9855051040649</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9587287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7311191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8248405456543</t>
+    <t xml:space="preserve">10.9587278366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7311182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82483959198</t>
   </si>
   <si>
     <t xml:space="preserve">10.9654216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9988946914673</t>
+    <t xml:space="preserve">11.0725326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.998893737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796436309814</t>
+    <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9185609817505</t>
+    <t xml:space="preserve">10.9185619354248</t>
   </si>
   <si>
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051742553711</t>
+    <t xml:space="preserve">10.9051723480225</t>
   </si>
   <si>
     <t xml:space="preserve">10.8917837142944</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277708053589</t>
+    <t xml:space="preserve">10.7277717590332</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633417129517</t>
@@ -1307,40 +1307,40 @@
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.5871868133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3696193695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.620659828186</t>
+    <t xml:space="preserve">10.2658586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3696203231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135507583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
     <t xml:space="preserve">10.8616590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6407432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5503702163696</t>
+    <t xml:space="preserve">10.6407442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5503692626953</t>
   </si>
   <si>
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
+    <t xml:space="preserve">10.533634185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
@@ -1352,22 +1352,22 @@
     <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1729488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9821586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269384384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261070251465</t>
+    <t xml:space="preserve">11.172947883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.982159614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269403457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261060714722</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394956588745</t>
+    <t xml:space="preserve">10.3394966125488</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629264831543</t>
@@ -1376,31 +1376,31 @@
     <t xml:space="preserve">10.1520528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.202260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821765899658</t>
+    <t xml:space="preserve">10.2022609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0349006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0951509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9788112640381</t>
+    <t xml:space="preserve">10.0349016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0951490402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9788093566895</t>
   </si>
   <si>
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762962341309</t>
+    <t xml:space="preserve">11.0357122421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620752334595</t>
+    <t xml:space="preserve">10.9620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">11.0223245620728</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.082573890686</t>
+    <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">10.952033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0290193557739</t>
+    <t xml:space="preserve">11.0290184020996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.28675365448</t>
+    <t xml:space="preserve">11.2867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.9352960586548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5068550109863</t>
+    <t xml:space="preserve">10.5068559646606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729677200317</t>
@@ -1454,22 +1454,22 @@
     <t xml:space="preserve">10.245774269104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683736801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74369430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34537887573242</t>
+    <t xml:space="preserve">10.0683727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74369525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34537792205811</t>
   </si>
   <si>
     <t xml:space="preserve">9.6700553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72695732116699</t>
+    <t xml:space="preserve">9.72695827484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">9.57633495330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58637619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6165018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54286289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57298851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56964111328125</t>
+    <t xml:space="preserve">9.48596000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58637714385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5428638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57298755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
     <t xml:space="preserve">9.50269603729248</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60980701446533</t>
+    <t xml:space="preserve">9.62319660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60980606079102</t>
   </si>
   <si>
     <t xml:space="preserve">8.83660316467285</t>
@@ -1517,52 +1517,52 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14120006561279</t>
+    <t xml:space="preserve">8.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949409484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350605010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
     <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21483707427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13785171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45583438873291</t>
+    <t xml:space="preserve">9.22488021850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512859344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2148380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13785266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28178119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6131534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71691799163818</t>
+    <t xml:space="preserve">9.28178215026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61315441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7169189453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550258636475</t>
+    <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.54621028900146</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">9.31525325775146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26504611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647945404053</t>
+    <t xml:space="preserve">9.26504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647850036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02070045471191</t>
+    <t xml:space="preserve">9.02070140838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.85334014892578</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86003398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92028331756592</t>
+    <t xml:space="preserve">8.86003494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.88011741638184</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27427387237549</t>
+    <t xml:space="preserve">8.2742748260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25084400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64581394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35795497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47845458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47176074981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945095062256</t>
+    <t xml:space="preserve">8.2508430480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64581489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35795402526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47845363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71944999694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635478973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16462898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">9.16462993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00731086730957</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94706153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0006160736084</t>
+    <t xml:space="preserve">8.94706058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00061702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735210418701</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
+    <t xml:space="preserve">8.62907886505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516983032227</t>
+    <t xml:space="preserve">9.29517078399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855846405029</t>
@@ -1715,28 +1715,28 @@
     <t xml:space="preserve">9.50604438781738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11107444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.294358253479</t>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1110725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29435729980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.31109428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34456634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32448387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749565124512</t>
+    <t xml:space="preserve">8.34456539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32448291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749755859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514842987061</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93367195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19810199737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2349214553833</t>
+    <t xml:space="preserve">8.93367385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19810104370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23492050170898</t>
   </si>
   <si>
     <t xml:space="preserve">8.70271682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25753974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5654821395874</t>
+    <t xml:space="preserve">8.25753879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56548118591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.5018835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75627040863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82321453094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84329891204834</t>
+    <t xml:space="preserve">8.75627136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82321548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">8.74622917175293</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29851818084717</t>
+    <t xml:space="preserve">9.42236232757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169776916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.44914150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91105461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8441104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.522780418396</t>
+    <t xml:space="preserve">9.91105556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84411144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">9.4424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41901588439941</t>
+    <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.60645961761475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95456790924072</t>
+    <t xml:space="preserve">9.95456886291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.41566848754883</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27174091339111</t>
+    <t xml:space="preserve">9.2717399597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8098258972168</t>
+    <t xml:space="preserve">8.7127571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27843379974365</t>
+    <t xml:space="preserve">9.27843284606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.52947425842285</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">9.42905807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3621129989624</t>
+    <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">9.24830913543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47257137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55625152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42571067810059</t>
+    <t xml:space="preserve">9.47257041931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55625247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4257116317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.15124130249023</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">9.43240547180176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39223957061768</t>
+    <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
     <t xml:space="preserve">9.33533573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24161529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454555511475</t>
+    <t xml:space="preserve">9.24161434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73030662536621</t>
+    <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.69013977050781</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79725074768066</t>
+    <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90770816802979</t>
+    <t xml:space="preserve">9.90770721435547</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">9.77716636657715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71022319793701</t>
+    <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.62989044189453</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">9.25500297546387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62573051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
+    <t xml:space="preserve">8.76296520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.77300643920898</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70687484741211</t>
+    <t xml:space="preserve">9.70687580108643</t>
   </si>
   <si>
     <t xml:space="preserve">9.94787406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76712512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66670894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60311222076416</t>
+    <t xml:space="preserve">9.76712608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66670989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53282070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">9.35542011260986</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">9.20144844055176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10103225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02739334106445</t>
+    <t xml:space="preserve">9.10103321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.94371318817139</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">8.90354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68263339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67928504943848</t>
+    <t xml:space="preserve">8.68263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67928600311279</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063842773438</t>
+    <t xml:space="preserve">9.81063938140869</t>
   </si>
   <si>
     <t xml:space="preserve">9.82067966461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30521202087402</t>
+    <t xml:space="preserve">9.30521106719971</t>
   </si>
   <si>
     <t xml:space="preserve">9.15793514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17467021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08764362335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04413032531738</t>
+    <t xml:space="preserve">9.16797542572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08764457702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0441312789917</t>
   </si>
   <si>
     <t xml:space="preserve">9.09099102020264</t>
@@ -2051,25 +2051,25 @@
     <t xml:space="preserve">8.88346576690674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288272857666</t>
+    <t xml:space="preserve">8.74288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677001953125</t>
+    <t xml:space="preserve">8.65250873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677097320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681125640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0039644241333</t>
+    <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.05417156219482</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383880615234</t>
+    <t xml:space="preserve">8.97383785247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.11776828765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08094787597656</t>
+    <t xml:space="preserve">9.08094882965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95040893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020084381104</t>
+    <t xml:space="preserve">8.95040798187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82990837097168</t>
+    <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
     <t xml:space="preserve">8.64246559143066</t>
@@ -2123,25 +2123,25 @@
     <t xml:space="preserve">8.33787155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28431701660156</t>
+    <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98976373672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0600528717041</t>
+    <t xml:space="preserve">8.15377616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98976230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327655792236</t>
+    <t xml:space="preserve">8.03327560424805</t>
   </si>
   <si>
     <t xml:space="preserve">7.94624900817871</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93286085128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02323436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96633195877075</t>
+    <t xml:space="preserve">7.93286037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96633148193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997039794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67177867889404</t>
+    <t xml:space="preserve">7.9429030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
     <t xml:space="preserve">7.12953233718872</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793214797974</t>
+    <t xml:space="preserve">7.54793167114258</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07263040542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222366333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256681442261</t>
+    <t xml:space="preserve">7.07262992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514543533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">6.15884494781494</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05929088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69023752212524</t>
+    <t xml:space="preserve">5.05928993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6902379989624</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693183898926</t>
@@ -2234,58 +2234,58 @@
     <t xml:space="preserve">5.98311758041382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05842971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23917818069458</t>
+    <t xml:space="preserve">6.05842924118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47515535354614</t>
+    <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.49356508255005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36637210845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35967683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0919017791748</t>
+    <t xml:space="preserve">6.36637163162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53038501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3596773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
     <t xml:space="preserve">6.03834676742554</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17892837524414</t>
+    <t xml:space="preserve">6.1789288520813</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00487375259399</t>
+    <t xml:space="preserve">6.00487470626831</t>
   </si>
   <si>
     <t xml:space="preserve">6.20235919952393</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620525360107</t>
+    <t xml:space="preserve">6.32620477676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28603935241699</t>
+    <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
     <t xml:space="preserve">6.20905303955078</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776420593262</t>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776372909546</t>
   </si>
   <si>
     <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05508184432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87433242797852</t>
+    <t xml:space="preserve">6.05508232116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747220993042</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">4.91368722915649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17142200469971</t>
+    <t xml:space="preserve">5.08774137496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
     <t xml:space="preserve">5.18815755844116</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22163009643555</t>
+    <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">5.74379253387451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74044513702393</t>
+    <t xml:space="preserve">5.74044561386108</t>
   </si>
   <si>
     <t xml:space="preserve">5.89106941223145</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">5.94127750396729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82077741622925</t>
+    <t xml:space="preserve">5.82077836990356</t>
   </si>
   <si>
     <t xml:space="preserve">5.60655736923218</t>
@@ -2393,22 +2393,22 @@
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1981987953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29861497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28522634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23836517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33208703994751</t>
+    <t xml:space="preserve">5.19819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29861545562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28522682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.238365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33208751678467</t>
   </si>
   <si>
     <t xml:space="preserve">5.27853202819824</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">5.23167085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886526107788</t>
+    <t xml:space="preserve">5.35886430740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.32204580307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3253927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28187894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2283239364624</t>
+    <t xml:space="preserve">5.32539319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28187942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22832345962524</t>
   </si>
   <si>
     <t xml:space="preserve">5.04422760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97058963775635</t>
+    <t xml:space="preserve">4.97059011459351</t>
   </si>
   <si>
     <t xml:space="preserve">4.94046497344971</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104753494263</t>
+    <t xml:space="preserve">5.08104705810547</t>
   </si>
   <si>
     <t xml:space="preserve">5.13125514984131</t>
@@ -2453,25 +2453,25 @@
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790822982788</t>
+    <t xml:space="preserve">5.12790775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12121438980103</t>
+    <t xml:space="preserve">5.11786699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12121391296387</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98063182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1044774055481</t>
+    <t xml:space="preserve">4.98063135147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10447835922241</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
@@ -2486,103 +2486,103 @@
     <t xml:space="preserve">5.38898992538452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48940563201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32874011993408</t>
+    <t xml:space="preserve">5.48940467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36890649795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32874059677124</t>
   </si>
   <si>
     <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961324691772</t>
+    <t xml:space="preserve">5.53961277008057</t>
   </si>
   <si>
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568471908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36221218109131</t>
+    <t xml:space="preserve">5.39568424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36221170425415</t>
   </si>
   <si>
     <t xml:space="preserve">5.38229513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36555957794189</t>
+    <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30530977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27518510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09108829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60321044921875</t>
+    <t xml:space="preserve">5.3053092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27518463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09108877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60320997238159</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537336349487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244215011597</t>
+    <t xml:space="preserve">6.15215063095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27934503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244167327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70697259902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89441680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375034332275</t>
+    <t xml:space="preserve">6.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524774551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7069730758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89441633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48605823516846</t>
+    <t xml:space="preserve">5.61325216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4860577583313</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65341758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.52287721633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65341806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040437698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46262836456299</t>
+    <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.47266960144043</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37894773483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10113000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92372894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95385408401489</t>
+    <t xml:space="preserve">5.45258617401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37894821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10113048553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92372941970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95385360717773</t>
   </si>
   <si>
     <t xml:space="preserve">4.88021564483643</t>
@@ -2627,28 +2627,28 @@
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21828269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468549728394</t>
+    <t xml:space="preserve">5.2182822227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468597412109</t>
   </si>
   <si>
     <t xml:space="preserve">5.55300235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86094379425049</t>
+    <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
     <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0985951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44335699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398078918457</t>
+    <t xml:space="preserve">6.09859609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44335746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
     <t xml:space="preserve">6.80820178985596</t>
@@ -2660,55 +2660,55 @@
     <t xml:space="preserve">6.58728647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7211742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41323280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78142356872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7613410949707</t>
+    <t xml:space="preserve">6.72117471694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766141891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41323232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76134157180786</t>
   </si>
   <si>
     <t xml:space="preserve">7.10275506973267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936643600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556161880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2098650932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05589485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00233888626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175680160522</t>
+    <t xml:space="preserve">7.36383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647741317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936738967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961576461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00233936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175727844238</t>
   </si>
   <si>
     <t xml:space="preserve">7.0692834854126</t>
@@ -2717,85 +2717,85 @@
     <t xml:space="preserve">7.10944938659668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07597780227661</t>
+    <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
     <t xml:space="preserve">6.98225593566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14292192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200660705566</t>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200613021851</t>
   </si>
   <si>
     <t xml:space="preserve">6.96886730194092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90192317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11614370346069</t>
+    <t xml:space="preserve">6.90192270278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11614418029785</t>
   </si>
   <si>
     <t xml:space="preserve">7.01572799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18978118896484</t>
+    <t xml:space="preserve">7.18978261947632</t>
   </si>
   <si>
     <t xml:space="preserve">7.03581190109253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15631055831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2500319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32367038726807</t>
+    <t xml:space="preserve">6.90861797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267164230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622713088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15631008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25003099441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
     <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4776406288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4106969833374</t>
+    <t xml:space="preserve">7.47764158248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41069650650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47094678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56466817855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51111364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53789186477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152982711792</t>
+    <t xml:space="preserve">7.47094631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56466865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51111268997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53789138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6115288734436</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">7.75880575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8525276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1805534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37469005584717</t>
+    <t xml:space="preserve">7.85252714157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18055438995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37469100952148</t>
   </si>
   <si>
     <t xml:space="preserve">8.66254901885986</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">8.91693592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849582672119</t>
+    <t xml:space="preserve">8.48849391937256</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485691070557</t>
+    <t xml:space="preserve">8.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2846,40 +2846,40 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20732975006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26758003234863</t>
+    <t xml:space="preserve">8.18724727630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20733070373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26758098602295</t>
   </si>
   <si>
     <t xml:space="preserve">8.32782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8123607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8993878364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99980354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97049140930176</t>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938879013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99980449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290508270264</t>
+    <t xml:space="preserve">9.55290412902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">9.9947338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96126365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9411792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0081233978271</t>
+    <t xml:space="preserve">9.96126270294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94118022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0081224441528</t>
   </si>
   <si>
     <t xml:space="preserve">10.0282068252563</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365306854248</t>
+    <t xml:space="preserve">9.7738208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365211486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.677562713623</t>
+    <t xml:space="preserve">10.6039247512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.476731300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6775636672974</t>
   </si>
   <si>
     <t xml:space="preserve">10.6440916061401</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.186595916748</t>
+    <t xml:space="preserve">10.1865949630737</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755491256714</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">9.93489170074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94969654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90528011322021</t>
+    <t xml:space="preserve">9.94969749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.63877010345459</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
+    <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">9.97931003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98671245574951</t>
+    <t xml:space="preserve">9.98671340942383</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7572193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80904102325439</t>
+    <t xml:space="preserve">9.75721836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80903911590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.85345840454102</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0533399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72020244598389</t>
+    <t xml:space="preserve">9.7720251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0533409118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
     <t xml:space="preserve">9.60175514221191</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">9.40187168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524513244629</t>
+    <t xml:space="preserve">9.40927505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575008392334</t>
+    <t xml:space="preserve">9.10575103759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.99655532836914</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">9.30563163757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17237758636475</t>
+    <t xml:space="preserve">9.17237854003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199108123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17978096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1131534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23160171508789</t>
+    <t xml:space="preserve">9.20199012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17978000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11315250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23160266876221</t>
   </si>
   <si>
     <t xml:space="preserve">9.01691436767578</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.3130350112915</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99470520019531</t>
+    <t xml:space="preserve">9.09834766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.994704246521</t>
   </si>
   <si>
     <t xml:space="preserve">9.80163669586182</t>
@@ -3122,25 +3122,25 @@
     <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60915660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32784175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46109676361084</t>
+    <t xml:space="preserve">9.60915756225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32784271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772426605225</t>
+    <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75040435791016</t>
+    <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33078336715698</t>
+    <t xml:space="preserve">8.77261257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33078384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5898904800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62690591812134</t>
+    <t xml:space="preserve">4.58989000320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62690544128418</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090085983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.271559715271</t>
+    <t xml:space="preserve">4.10128879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090133666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.1938271522522</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">4.16791677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17161798477173</t>
+    <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.2456488609314</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21233510971069</t>
+    <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
     <t xml:space="preserve">4.46033716201782</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">4.36039590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15311098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10499048233032</t>
+    <t xml:space="preserve">4.15311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758758544922</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">4.17902135848999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93842196464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06057262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05687046051025</t>
+    <t xml:space="preserve">3.93842220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06057214736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85328722000122</t>
+    <t xml:space="preserve">3.85328650474548</t>
   </si>
   <si>
     <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51644802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86069011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07537889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04206514358521</t>
+    <t xml:space="preserve">3.51644825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86069059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07537841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04206418991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">4.34558963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27526044845581</t>
+    <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510821342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433258056641</t>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433234214783</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985502243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660049438477</t>
+    <t xml:space="preserve">4.01985549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660097122192</t>
   </si>
   <si>
     <t xml:space="preserve">3.8643913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79036045074463</t>
+    <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
     <t xml:space="preserve">3.73483824729919</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">3.53310513496399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55716490745544</t>
+    <t xml:space="preserve">3.55716514587402</t>
   </si>
   <si>
     <t xml:space="preserve">3.52014994621277</t>
@@ -3338,25 +3338,25 @@
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459741592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57382154464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62009072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70152425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42391014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33137178421021</t>
+    <t xml:space="preserve">3.51459765434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5738217830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6200909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70152449607849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42391037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33137226104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">3.35358119010925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1092803478241</t>
+    <t xml:space="preserve">3.10928058624268</t>
   </si>
   <si>
     <t xml:space="preserve">3.24623703956604</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10187792778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.10187745094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8649799823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86683034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503872871399</t>
+    <t xml:space="preserve">2.86497974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86683058738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059125900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82426333427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83721876144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76318788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772395133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52999186515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49852895736694</t>
+    <t xml:space="preserve">2.77059102058411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82426309585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83721828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.763188123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6077241897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52999210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49852919578552</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56515622138977</t>
+    <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742413520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27273607254028</t>
+    <t xml:space="preserve">2.48742437362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2727358341217</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
@@ -3512,25 +3512,25 @@
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41339373588562</t>
+    <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676671028137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790042877197</t>
+    <t xml:space="preserve">2.30790066719055</t>
   </si>
   <si>
     <t xml:space="preserve">2.19685482978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1357798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18760108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29679608345032</t>
+    <t xml:space="preserve">2.13577961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18760085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29679584503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.28569149971008</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">2.35416960716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3412139415741</t>
+    <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
     <t xml:space="preserve">2.25422859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26718401908875</t>
+    <t xml:space="preserve">2.26718378067017</t>
   </si>
   <si>
     <t xml:space="preserve">2.28754210472107</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">2.25607895851135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276520729065</t>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">2.2912437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24867630004883</t>
+    <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
     <t xml:space="preserve">2.21351170539856</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">2.15798878669739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14873480796814</t>
+    <t xml:space="preserve">2.14873504638672</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13763022422791</t>
+    <t xml:space="preserve">2.08765959739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
     <t xml:space="preserve">2.14688420295715</t>
@@ -3626,19 +3626,19 @@
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912250518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652587890625</t>
+    <t xml:space="preserve">2.11912274360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652564048767</t>
   </si>
   <si>
     <t xml:space="preserve">2.07285380363464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01362919807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95810639858246</t>
+    <t xml:space="preserve">2.01362943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95810651779175</t>
   </si>
   <si>
     <t xml:space="preserve">1.86186683177948</t>
@@ -71304,7 +71304,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6910300926</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>237319</v>
@@ -71325,6 +71325,32 @@
         <v>1866</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910185185</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>209351</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>3.93600010871887</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>3.94600009918213</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1808</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1874">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.195689201355</t>
+    <t xml:space="preserve">12.1956901550293</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101800918579</t>
+    <t xml:space="preserve">11.4097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101810455322</t>
   </si>
   <si>
     <t xml:space="preserve">11.0766973495483</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">11.136643409729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8302536010742</t>
+    <t xml:space="preserve">10.8302526473999</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770582199097</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">9.65797424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507753372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7370042800903</t>
+    <t xml:space="preserve">10.2507743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.737003326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.3906488418579</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1042394638062</t>
+    <t xml:space="preserve">10.1042385101318</t>
   </si>
   <si>
     <t xml:space="preserve">10.8702163696289</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">10.7170219421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77786636352539</t>
+    <t xml:space="preserve">9.77786731719971</t>
   </si>
   <si>
     <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54474353790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120590209961</t>
+    <t xml:space="preserve">9.54474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120494842529</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4639158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6171112060547</t>
+    <t xml:space="preserve">10.4639148712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6171102523804</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">9.96436595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4905586242676</t>
+    <t xml:space="preserve">10.4905576705933</t>
   </si>
   <si>
     <t xml:space="preserve">10.7236824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9434843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363737106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3431253433228</t>
+    <t xml:space="preserve">10.9434833526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.436372756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3431243896484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6495151519775</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">11.2898387908936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0624780654907</t>
+    <t xml:space="preserve">12.0624771118164</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627468109131</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">12.4621181488037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.555365562439</t>
+    <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.696138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5695896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0757970809937</t>
+    <t xml:space="preserve">12.1823701858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6961393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5695877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0757989883423</t>
   </si>
   <si>
     <t xml:space="preserve">11.9159421920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1890296936035</t>
+    <t xml:space="preserve">12.1890287399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">11.0633764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6561756134033</t>
+    <t xml:space="preserve">11.656174659729</t>
   </si>
   <si>
     <t xml:space="preserve">11.955906867981</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">12.2689580917358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217023849487</t>
+    <t xml:space="preserve">12.8217935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
     <t xml:space="preserve">12.9350252151489</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">13.2480773925781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1947898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1814699172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.16148853302</t>
+    <t xml:space="preserve">13.1947908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1814708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614875793457</t>
   </si>
   <si>
     <t xml:space="preserve">13.3613080978394</t>
@@ -266,82 +266,82 @@
     <t xml:space="preserve">13.3946123123169</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0882196426392</t>
+    <t xml:space="preserve">13.0882186889648</t>
   </si>
   <si>
     <t xml:space="preserve">12.9816493988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6885814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5620288848877</t>
+    <t xml:space="preserve">12.6885805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5620279312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.881739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8617572784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884019851685</t>
+    <t xml:space="preserve">12.8617582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
   </si>
   <si>
     <t xml:space="preserve">13.0482568740845</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4088315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221525192261</t>
+    <t xml:space="preserve">12.4088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221534729004</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488874435425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7218837738037</t>
+    <t xml:space="preserve">12.7218828201294</t>
   </si>
   <si>
     <t xml:space="preserve">12.7685098648071</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9150438308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214345932007</t>
+    <t xml:space="preserve">12.9150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214336395264</t>
   </si>
   <si>
     <t xml:space="preserve">13.1344060897827</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3887939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6230983734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561552047729</t>
+    <t xml:space="preserve">13.3887929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159883499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6230974197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.4222660064697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3620157241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0741577148438</t>
+    <t xml:space="preserve">13.3620147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3553228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0741567611694</t>
   </si>
   <si>
     <t xml:space="preserve">12.993824005127</t>
@@ -371,52 +371,52 @@
     <t xml:space="preserve">11.7218894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0766916275024</t>
+    <t xml:space="preserve">12.0766925811768</t>
   </si>
   <si>
     <t xml:space="preserve">12.6524085998535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6925773620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1410989761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487054824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4231767654419</t>
+    <t xml:space="preserve">12.6925764083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4231758117676</t>
   </si>
   <si>
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834260940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177286148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2290372848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4164819717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0482912063599</t>
+    <t xml:space="preserve">10.4834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2290382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4164810180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0482902526855</t>
   </si>
   <si>
     <t xml:space="preserve">10.4432601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7445077896118</t>
+    <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
     <t xml:space="preserve">11.1193933486938</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599763870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1260890960693</t>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126088142395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0122833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8114500045776</t>
+    <t xml:space="preserve">11.0122842788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.811450958252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.764591217041</t>
+    <t xml:space="preserve">10.8783960342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7645902633667</t>
   </si>
   <si>
     <t xml:space="preserve">10.0616779327393</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">10.175482749939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88762378692627</t>
+    <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.06421375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93032646179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80313205718994</t>
+    <t xml:space="preserve">8.93032550811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67593860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">8.93702030181885</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">9.20479488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37215423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25835037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33868312835693</t>
+    <t xml:space="preserve">9.37215614318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.23826789855957</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">9.13115787506104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37885093688965</t>
+    <t xml:space="preserve">9.37884998321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315731048584</t>
+    <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.6332368850708</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">9.79390335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55959892272949</t>
+    <t xml:space="preserve">9.55959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43910026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629276275635</t>
+    <t xml:space="preserve">9.43909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">9.53951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82737445831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76043033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78720951080322</t>
+    <t xml:space="preserve">9.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76043128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78720760345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.87423515319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67340469360352</t>
+    <t xml:space="preserve">9.6734037399292</t>
   </si>
   <si>
     <t xml:space="preserve">9.07760238647461</t>
@@ -548,34 +548,34 @@
     <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07090854644775</t>
+    <t xml:space="preserve">9.07090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31190586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36546039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3855447769165</t>
+    <t xml:space="preserve">9.31190490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3654613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38554573059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.24496269226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03743457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70941066741943</t>
+    <t xml:space="preserve">9.03743553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">8.72280025482178</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">8.7897424697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71610450744629</t>
+    <t xml:space="preserve">8.71610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">8.66924381256104</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20063591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
+    <t xml:space="preserve">8.2006368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002197265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1203031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79227733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83913946151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591672897339</t>
+    <t xml:space="preserve">7.79227876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83913898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591577529907</t>
   </si>
   <si>
     <t xml:space="preserve">7.84583377838135</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541664123535</t>
+    <t xml:space="preserve">7.74541759490967</t>
   </si>
   <si>
     <t xml:space="preserve">7.71194553375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69186067581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169525146484</t>
+    <t xml:space="preserve">7.69186162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169620513916</t>
   </si>
   <si>
     <t xml:space="preserve">7.68516731262207</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">7.9596381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12699794769287</t>
+    <t xml:space="preserve">8.12699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92363166809082</t>
+    <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
     <t xml:space="preserve">9.21149063110352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09768581390381</t>
+    <t xml:space="preserve">9.09768676757812</t>
   </si>
   <si>
     <t xml:space="preserve">11.9963598251343</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691654205322</t>
+    <t xml:space="preserve">11.8691644668579</t>
   </si>
   <si>
     <t xml:space="preserve">12.0499143600464</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">15.2833080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7971525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967353820801</t>
+    <t xml:space="preserve">13.7971534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967344284058</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569847106934</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">13.8908739089966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9578189849854</t>
+    <t xml:space="preserve">13.957818031311</t>
   </si>
   <si>
     <t xml:space="preserve">13.7904586791992</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">14.6004800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180692672729</t>
+    <t xml:space="preserve">14.0180683135986</t>
   </si>
   <si>
     <t xml:space="preserve">14.0582332611084</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">14.1251773834229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8172369003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101249694824</t>
+    <t xml:space="preserve">13.817234992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
   </si>
   <si>
     <t xml:space="preserve">13.455738067627</t>
@@ -761,46 +761,46 @@
     <t xml:space="preserve">13.2415180206299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544895172119</t>
+    <t xml:space="preserve">13.1544885635376</t>
   </si>
   <si>
     <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2080450057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528276443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264656066895</t>
+    <t xml:space="preserve">13.2080459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268808364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264646530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9067974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611843109131</t>
+    <t xml:space="preserve">12.9067983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611852645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.0540742874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9134922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419322967529</t>
+    <t xml:space="preserve">12.9134931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2147388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419332504272</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812686920166</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">12.8599367141724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9871292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.007212638855</t>
+    <t xml:space="preserve">12.9871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072135925293</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
@@ -830,46 +830,46 @@
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754053115845</t>
+    <t xml:space="preserve">13.3754062652588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4758214950562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3486289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406856536865</t>
+    <t xml:space="preserve">13.3486280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406837463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867149353027</t>
+    <t xml:space="preserve">12.8867139816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536600112915</t>
+    <t xml:space="preserve">12.8398523330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.819769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858816146851</t>
+    <t xml:space="preserve">12.8197689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858835220337</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386056900024</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.4047174453735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708292007446</t>
+    <t xml:space="preserve">12.2708301544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
@@ -899,49 +899,49 @@
     <t xml:space="preserve">12.1771087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1436367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800191879272</t>
+    <t xml:space="preserve">12.1436347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862977981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.9469633102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653829574585</t>
+    <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637191772461</t>
+    <t xml:space="preserve">12.1637201309204</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913288116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5586881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6189374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2574396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.284218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4181060791016</t>
+    <t xml:space="preserve">12.3913297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5586891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6189393997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2574405670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2842178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4181070327759</t>
   </si>
   <si>
     <t xml:space="preserve">12.197190284729</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.672492980957</t>
+    <t xml:space="preserve">12.6724920272827</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176898956299</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813055038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6147785186768</t>
+    <t xml:space="preserve">12.0030536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813064575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6147794723511</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6549453735352</t>
+    <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
     <t xml:space="preserve">11.5880002975464</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942798614502</t>
+    <t xml:space="preserve">11.6817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.5210571289062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7151947021484</t>
+    <t xml:space="preserve">11.7151937484741</t>
   </si>
   <si>
     <t xml:space="preserve">11.6616401672363</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3804740905762</t>
+    <t xml:space="preserve">11.7018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4474191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.2265043258667</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">10.777979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7043409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7980623245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9453392028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.139476776123</t>
+    <t xml:space="preserve">10.7043399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7980613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9453401565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1394758224487</t>
   </si>
   <si>
     <t xml:space="preserve">11.1930313110352</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">11.0591449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1528654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0993099212646</t>
+    <t xml:space="preserve">11.1528663635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.099310874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.1997261047363</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112699508667</t>
+    <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206399917603</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">11.5411405563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5679178237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2198085784912</t>
+    <t xml:space="preserve">11.5679187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2198095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4608097076416</t>
+    <t xml:space="preserve">11.4005575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4608087539673</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541139602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336143493652</t>
+    <t xml:space="preserve">11.3336153030396</t>
   </si>
   <si>
     <t xml:space="preserve">11.3536968231201</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5302867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3897047042847</t>
+    <t xml:space="preserve">10.9721174240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5302858352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3897037506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3093719482422</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">10.1620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3361492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901189804077</t>
+    <t xml:space="preserve">10.2156505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3361482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4901208877563</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">10.3428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3562316894531</t>
+    <t xml:space="preserve">10.3562326431274</t>
   </si>
   <si>
     <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80059719085693</t>
+    <t xml:space="preserve">9.80059814453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.80729198455811</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026443481445</t>
+    <t xml:space="preserve">9.72026348114014</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74034786224365</t>
+    <t xml:space="preserve">9.74034690856934</t>
   </si>
   <si>
     <t xml:space="preserve">9.75373649597168</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110347747803</t>
+    <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
     <t xml:space="preserve">10.650785446167</t>
@@ -1178,40 +1178,40 @@
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708688735962</t>
+    <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376314163208</t>
+    <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
     <t xml:space="preserve">10.1888723373413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2759008407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1286220550537</t>
+    <t xml:space="preserve">10.275899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.128623008728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5102033615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3160648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2089548110962</t>
+    <t xml:space="preserve">10.2357339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5102024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.316065788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2089557647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.6533203125</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">10.2959823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436754226685</t>
+    <t xml:space="preserve">10.5436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
@@ -1256,31 +1256,31 @@
     <t xml:space="preserve">10.82483959198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654216766357</t>
+    <t xml:space="preserve">10.9654226303101</t>
   </si>
   <si>
     <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9988946914673</t>
+    <t xml:space="preserve">10.998893737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2465867996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.1796436309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2465877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9118671417236</t>
+    <t xml:space="preserve">10.9118661880493</t>
   </si>
   <si>
     <t xml:space="preserve">10.9051733016968</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633417129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.7277698516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.463342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">10.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3696212768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135498046875</t>
+    <t xml:space="preserve">10.3696203231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135507583618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6407451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5503692626953</t>
+    <t xml:space="preserve">10.8616590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6407442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106185913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
     <t xml:space="preserve">10.5771474838257</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4097881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1729497909546</t>
+    <t xml:space="preserve">10.4097871780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
     <t xml:space="preserve">10.9821586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269393920898</t>
+    <t xml:space="preserve">10.5269403457642</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261079788208</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394966125488</t>
+    <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1520538330078</t>
+    <t xml:space="preserve">10.1520528793335</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821784973145</t>
+    <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
     <t xml:space="preserve">9.94452667236328</t>
@@ -1391,34 +1391,34 @@
     <t xml:space="preserve">10.9788093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1060037612915</t>
+    <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0357141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1762952804565</t>
+    <t xml:space="preserve">11.1762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717012405396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8683547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620752334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9553813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0256719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.082573890686</t>
+    <t xml:space="preserve">10.868353843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0223245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9553804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.025671005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9520330429077</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.28675365448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3135299682617</t>
+    <t xml:space="preserve">11.2867546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
     <t xml:space="preserve">10.9352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5068559646606</t>
+    <t xml:space="preserve">10.506856918335</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729677200317</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">10.2457752227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683736801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74369621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34537887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6700553894043</t>
+    <t xml:space="preserve">10.0683727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74369525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34537792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67005634307861</t>
   </si>
   <si>
     <t xml:space="preserve">9.72695827484131</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5428638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57298755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56963920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50269603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47926616668701</t>
+    <t xml:space="preserve">9.6165018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54286289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57298851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56964015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5026969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47926712036133</t>
   </si>
   <si>
     <t xml:space="preserve">9.49600219726562</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60980701446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83660411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60564613342285</t>
+    <t xml:space="preserve">9.60980606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83660316467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60564804077148</t>
   </si>
   <si>
     <t xml:space="preserve">8.68932723999023</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186462402344</t>
+    <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.22487926483154</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">9.21483707427979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785076141357</t>
+    <t xml:space="preserve">9.13785171508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.45583534240723</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">9.6131534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691799163818</t>
+    <t xml:space="preserve">9.71691703796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54621124267578</t>
+    <t xml:space="preserve">9.37550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54621028900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.31525421142578</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647850036621</t>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647945404053</t>
   </si>
   <si>
     <t xml:space="preserve">8.89015960693359</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85334014892578</t>
+    <t xml:space="preserve">8.85333919525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86003494262695</t>
+    <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
     <t xml:space="preserve">8.92028427124023</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">8.82656288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58891105651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29770565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27427387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24080371856689</t>
+    <t xml:space="preserve">8.58891201019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29770469665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2742748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.25084400177002</t>
@@ -1625,25 +1625,25 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639698028564</t>
+    <t xml:space="preserve">8.47175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639602661133</t>
   </si>
   <si>
     <t xml:space="preserve">8.71945095062256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77635383605957</t>
+    <t xml:space="preserve">8.77635478973389</t>
   </si>
   <si>
     <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00730991363525</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20814228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22822666168213</t>
+    <t xml:space="preserve">9.20814418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00061702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735305786133</t>
+    <t xml:space="preserve">9.0006160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735210418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408813476562</t>
+    <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
     <t xml:space="preserve">8.66589641571045</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">8.8499927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53535556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47510528564453</t>
+    <t xml:space="preserve">8.53535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47510623931885</t>
   </si>
   <si>
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
+    <t xml:space="preserve">8.62907886505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.75292491912842</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">8.90689563751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516983032227</t>
+    <t xml:space="preserve">9.29517078399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50604343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111568450928</t>
+    <t xml:space="preserve">9.50604438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107349395752</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31109428405762</t>
+    <t xml:space="preserve">8.3110933303833</t>
   </si>
   <si>
     <t xml:space="preserve">8.34456539154053</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">8.32448291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24749565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49184226989746</t>
+    <t xml:space="preserve">8.24749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">9.19810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">8.70271587371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25753784179688</t>
+    <t xml:space="preserve">8.25753879547119</t>
   </si>
   <si>
     <t xml:space="preserve">8.56548118591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5018835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75627136230469</t>
+    <t xml:space="preserve">8.50188446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627040863037</t>
   </si>
   <si>
     <t xml:space="preserve">8.82321548461914</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">8.74622917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18471336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42236423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29851818084717</t>
+    <t xml:space="preserve">9.18471240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169776916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.44914054870605</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">9.8441104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52277946472168</t>
+    <t xml:space="preserve">9.522780418396</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456886291504</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35876750946045</t>
+    <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.2717399597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54874420166016</t>
+    <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
     <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8098258972168</t>
+    <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.10438060760498</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">9.27843379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943206787109</t>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.42905807495117</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">9.15124130249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128253936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240547180176</t>
+    <t xml:space="preserve">9.16128349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240642547607</t>
   </si>
   <si>
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533573150635</t>
+    <t xml:space="preserve">9.33533668518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.24161529541016</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25165557861328</t>
+    <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
     <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69013977050781</t>
+    <t xml:space="preserve">9.69014072418213</t>
   </si>
   <si>
     <t xml:space="preserve">9.50939083099365</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9210958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9077091217041</t>
+    <t xml:space="preserve">9.92109680175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90770721435547</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">9.77716732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71022319793701</t>
+    <t xml:space="preserve">9.7102222442627</t>
   </si>
   <si>
     <t xml:space="preserve">9.62989044189453</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">9.45248889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2550048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631355285645</t>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631259918213</t>
   </si>
   <si>
     <t xml:space="preserve">8.62573051452637</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">8.7730073928833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75961875915527</t>
+    <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404689788818</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">9.70687580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94787311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76712512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66670894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60311317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35541915893555</t>
+    <t xml:space="preserve">9.94787406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76712417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66670989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53282070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35542011260986</t>
   </si>
   <si>
     <t xml:space="preserve">9.20144844055176</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">8.99057483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342357635498</t>
+    <t xml:space="preserve">8.87342262268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
@@ -2015,31 +2015,31 @@
     <t xml:space="preserve">9.86084651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8240270614624</t>
+    <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
     <t xml:space="preserve">9.81063842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30521202087402</t>
+    <t xml:space="preserve">9.82067966461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30521106719971</t>
   </si>
   <si>
     <t xml:space="preserve">9.15793514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16797637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17467021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08764457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04413032531738</t>
+    <t xml:space="preserve">9.16797542572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08764362335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0441312789917</t>
   </si>
   <si>
     <t xml:space="preserve">9.09099102020264</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">8.7930908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250873565674</t>
+    <t xml:space="preserve">8.65250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681221008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00396347045898</t>
+    <t xml:space="preserve">8.87677097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396537780762</t>
   </si>
   <si>
     <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.060866355896</t>
+    <t xml:space="preserve">9.06086540222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
+    <t xml:space="preserve">9.11776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0809497833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95040988922119</t>
+    <t xml:space="preserve">8.95040893554688</t>
   </si>
   <si>
     <t xml:space="preserve">8.90020084381104</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">8.99726867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92697811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06756019592285</t>
+    <t xml:space="preserve">8.92697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06756114959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.829909324646</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">8.40146827697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33787155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28431701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98976230621338</t>
+    <t xml:space="preserve">8.33787250518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28431606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9897632598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.06005382537842</t>
@@ -2150,37 +2150,37 @@
     <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02323532104492</t>
+    <t xml:space="preserve">8.02323341369629</t>
   </si>
   <si>
     <t xml:space="preserve">7.96633243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03997135162354</t>
+    <t xml:space="preserve">8.03997039794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.94290113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78558301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12953186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22325420379639</t>
+    <t xml:space="preserve">7.78558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67177820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22325372695923</t>
   </si>
   <si>
     <t xml:space="preserve">7.54793167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16300392150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07263040542603</t>
+    <t xml:space="preserve">7.16300487518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07262992858887</t>
   </si>
   <si>
     <t xml:space="preserve">6.87514638900757</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">6.72786903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57222461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256633758545</t>
+    <t xml:space="preserve">6.57222414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256681442261</t>
   </si>
   <si>
     <t xml:space="preserve">6.15884494781494</t>
@@ -2210,22 +2210,22 @@
     <t xml:space="preserve">4.58566188812256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96556854248047</t>
+    <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05929040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69023704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69693231582642</t>
+    <t xml:space="preserve">5.05928993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69023752212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311710357666</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356460571289</t>
+    <t xml:space="preserve">6.49356508255005</t>
   </si>
   <si>
     <t xml:space="preserve">6.36637163162231</t>
@@ -2252,34 +2252,34 @@
     <t xml:space="preserve">6.6174111366272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753675460815</t>
+    <t xml:space="preserve">6.5303840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
   </si>
   <si>
     <t xml:space="preserve">6.56720304489136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54377365112305</t>
+    <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
     <t xml:space="preserve">6.42662143707275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3596773147583</t>
+    <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
     <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834581375122</t>
+    <t xml:space="preserve">6.03834629058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.17892837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85759735107422</t>
+    <t xml:space="preserve">5.85759687423706</t>
   </si>
   <si>
     <t xml:space="preserve">6.00487422943115</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">6.32620429992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34628868103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28603887557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20905303955078</t>
+    <t xml:space="preserve">6.34628820419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28603839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20905351638794</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520698547363</t>
+    <t xml:space="preserve">6.08520746231079</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156854629517</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433385848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82747268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68354320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6601128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08439493179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87017393112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75302171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91368722915649</t>
+    <t xml:space="preserve">5.87433338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82747220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68354225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66011238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08439445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87017345428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75302219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91368770599365</t>
   </si>
   <si>
     <t xml:space="preserve">5.08774137496948</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.188157081604</t>
+    <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.34212923049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15803241729736</t>
+    <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
     <t xml:space="preserve">5.22163009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37225389480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74379301071167</t>
+    <t xml:space="preserve">5.37225341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74379253387451</t>
   </si>
   <si>
     <t xml:space="preserve">5.74044561386108</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94127750396729</t>
+    <t xml:space="preserve">5.94127702713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.82077789306641</t>
@@ -2387,19 +2387,19 @@
     <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20824098587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19819974899292</t>
+    <t xml:space="preserve">5.2082405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861545562744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28522634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196189880371</t>
+    <t xml:space="preserve">5.2852258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196237564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.23836517333984</t>
@@ -2408,22 +2408,22 @@
     <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27853202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23167085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35886430740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204532623291</t>
+    <t xml:space="preserve">5.2785325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23167133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35886478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204580307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.3253927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28187942504883</t>
+    <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
     <t xml:space="preserve">5.2283239364624</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">4.97059011459351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046545028687</t>
+    <t xml:space="preserve">4.94046497344971</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">5.13125514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11451864242554</t>
+    <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.12790822982788</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
+    <t xml:space="preserve">5.11786699295044</t>
   </si>
   <si>
     <t xml:space="preserve">5.12121391296387</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1044774055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03753423690796</t>
+    <t xml:space="preserve">5.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0375337600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.96389532089233</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32874011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57643270492554</t>
+    <t xml:space="preserve">5.32873964309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961324691772</t>
@@ -2501,61 +2501,61 @@
     <t xml:space="preserve">5.49609994888306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39568424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36221170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38229560852051</t>
+    <t xml:space="preserve">5.39568376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36221218109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38229513168335</t>
   </si>
   <si>
     <t xml:space="preserve">5.36555957794189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34547567367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30530977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27518463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09108924865723</t>
+    <t xml:space="preserve">5.3454761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3053092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27518510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09108877182007</t>
   </si>
   <si>
     <t xml:space="preserve">5.60320997238159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12537336349487</t>
+    <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
     <t xml:space="preserve">6.15215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934408187866</t>
+    <t xml:space="preserve">6.27934455871582</t>
   </si>
   <si>
     <t xml:space="preserve">6.22244167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19566440582275</t>
+    <t xml:space="preserve">6.19566488265991</t>
   </si>
   <si>
     <t xml:space="preserve">6.1488037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09524822235107</t>
+    <t xml:space="preserve">6.09524774551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375034332275</t>
+    <t xml:space="preserve">5.89441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">5.62664079666138</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48605823516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48271083831787</t>
+    <t xml:space="preserve">5.48605871200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48271131515503</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287721633911</t>
@@ -2576,25 +2576,25 @@
     <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7304048538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70362615585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65676498413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5563497543335</t>
+    <t xml:space="preserve">5.73040437698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027875900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70362663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65676546096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55634927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47266960144043</t>
+    <t xml:space="preserve">5.47267007827759</t>
   </si>
   <si>
     <t xml:space="preserve">5.50948858261108</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894821166992</t>
+    <t xml:space="preserve">5.37894773483276</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">4.92372941970825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95385456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88021516799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94381189346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07770013809204</t>
+    <t xml:space="preserve">4.95385360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88021564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94381237030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07769966125488</t>
   </si>
   <si>
     <t xml:space="preserve">5.2182822227478</t>
@@ -2630,58 +2630,58 @@
     <t xml:space="preserve">5.15468597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55300188064575</t>
+    <t xml:space="preserve">5.55300235748291</t>
   </si>
   <si>
     <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02830457687378</t>
+    <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
     <t xml:space="preserve">6.0985951423645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80820226669312</t>
+    <t xml:space="preserve">6.44335699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
     <t xml:space="preserve">6.6374945640564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58728647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72117519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41323280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418935775757</t>
+    <t xml:space="preserve">6.5872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72117471694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766141891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41323232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418888092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.7814245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7613410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10275459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647645950317</t>
+    <t xml:space="preserve">6.76134157180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10275554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647693634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.12283897399902</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">7.08936595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97556161880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986604690552</t>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986557006836</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05589389801025</t>
+    <t xml:space="preserve">7.05589437484741</t>
   </si>
   <si>
     <t xml:space="preserve">7.00233936309814</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944986343384</t>
+    <t xml:space="preserve">7.10944890975952</t>
   </si>
   <si>
     <t xml:space="preserve">7.07597780227661</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">7.14292192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96886682510376</t>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96886777877808</t>
   </si>
   <si>
     <t xml:space="preserve">6.90192317962646</t>
@@ -2738,43 +2738,43 @@
     <t xml:space="preserve">7.11614465713501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01572751998901</t>
+    <t xml:space="preserve">7.01572847366333</t>
   </si>
   <si>
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861845016479</t>
+    <t xml:space="preserve">7.03581190109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861749649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.08267211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13622808456421</t>
+    <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25003242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2701153755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366943359375</t>
+    <t xml:space="preserve">7.25003147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
     <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47764205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4106969833374</t>
+    <t xml:space="preserve">7.47764158248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41069650650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.3906135559082</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">7.56466865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5111141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53789138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152982711792</t>
+    <t xml:space="preserve">7.51111459732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53789091110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6115288734436</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">7.75880575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1805534362793</t>
+    <t xml:space="preserve">7.8525276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18055438995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
@@ -2822,19 +2822,19 @@
     <t xml:space="preserve">8.89685344696045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91693592071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48849582672119</t>
+    <t xml:space="preserve">8.91693687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48849487304688</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21402454376221</t>
+    <t xml:space="preserve">8.41485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
@@ -2846,34 +2846,34 @@
     <t xml:space="preserve">8.18724632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20733165740967</t>
+    <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
     <t xml:space="preserve">8.26758098602295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32783031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277599334717</t>
+    <t xml:space="preserve">8.32782936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277647018433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89938879013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99980449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97049140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68009853363037</t>
+    <t xml:space="preserve">7.99980354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97049236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
     <t xml:space="preserve">9.55290508270264</t>
@@ -2897,28 +2897,28 @@
     <t xml:space="preserve">10.028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85415172576904</t>
+    <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
     <t xml:space="preserve">9.77381992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73365306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039237976074</t>
+    <t xml:space="preserve">9.7336540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039247512817</t>
   </si>
   <si>
     <t xml:space="preserve">10.4767303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.677562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.6775636672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1865949630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0755500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93489265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94969749450684</t>
+    <t xml:space="preserve">10.1865968704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0755491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93489170074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94969654083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63877010345459</t>
+    <t xml:space="preserve">9.63876914978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
+    <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0903558731079</t>
+    <t xml:space="preserve">10.0903549194336</t>
   </si>
   <si>
     <t xml:space="preserve">9.89047241210938</t>
@@ -2990,28 +2990,28 @@
     <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80904006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.80904102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0533409118652</t>
+    <t xml:space="preserve">9.7720251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0533399581909</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5499324798584</t>
+    <t xml:space="preserve">9.6017541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54993343353271</t>
   </si>
   <si>
     <t xml:space="preserve">9.52032089233398</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524513244629</t>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,25 +3035,25 @@
     <t xml:space="preserve">9.10575008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655437469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34634876251221</t>
+    <t xml:space="preserve">8.99655532836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37226009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4166784286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30563163757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17237854003906</t>
+    <t xml:space="preserve">9.37225914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41667938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30563259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17237758636475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2464075088501</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.31303691864014</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03172016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02431774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98730278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09834671020508</t>
+    <t xml:space="preserve">9.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02431678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98730182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09834766387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8016357421875</t>
+    <t xml:space="preserve">9.80163669586182</t>
   </si>
   <si>
     <t xml:space="preserve">10.0237283706665</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">9.46109676361084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43148326873779</t>
+    <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
     <t xml:space="preserve">9.52772331237793</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">8.86885166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75040245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92067527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93547916412354</t>
+    <t xml:space="preserve">8.75040340423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92067432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93548011779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.80962753295898</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51586008071899</t>
+    <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
     <t xml:space="preserve">4.58989000320435</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723463058472</t>
+    <t xml:space="preserve">4.69723415374756</t>
   </si>
   <si>
     <t xml:space="preserve">4.58248710632324</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">4.10128927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13090181350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27155876159668</t>
+    <t xml:space="preserve">4.13090133666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.1938271522522</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">4.16791677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17161846160889</t>
+    <t xml:space="preserve">4.17161798477173</t>
   </si>
   <si>
     <t xml:space="preserve">4.2456488609314</t>
@@ -3209,31 +3209,31 @@
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018468856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21233463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46033763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41962051391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35669469833374</t>
+    <t xml:space="preserve">4.09018516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21233510971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46033716201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41962003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35669422149658</t>
   </si>
   <si>
     <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36039590835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15311098098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10499048233032</t>
+    <t xml:space="preserve">4.36039543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758710861206</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">4.05687093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87549662590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04576587677002</t>
+    <t xml:space="preserve">3.87549614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58862805366516</t>
+    <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8606903553009</t>
+    <t xml:space="preserve">3.86069059371948</t>
   </si>
   <si>
     <t xml:space="preserve">4.07537841796875</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">4.34558963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27526140213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9495267868042</t>
+    <t xml:space="preserve">4.27526092529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
     <t xml:space="preserve">3.90510845184326</t>
@@ -3293,43 +3293,43 @@
     <t xml:space="preserve">3.96433305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98654198646545</t>
+    <t xml:space="preserve">3.98654246330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05316877365112</t>
+    <t xml:space="preserve">4.05316925048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660073280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86439156532288</t>
+    <t xml:space="preserve">4.01985502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8643913269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73483800888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50164222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53310513496399</t>
+    <t xml:space="preserve">3.73483824729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50164246559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53310489654541</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52014994621277</t>
+    <t xml:space="preserve">3.52015018463135</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313426971436</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">3.51459765434265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57382154464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6200909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
+    <t xml:space="preserve">3.5738217830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62009072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.33137178421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358119010925</t>
+    <t xml:space="preserve">3.35358095169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">3.10187745094299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01304125785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92050290107727</t>
+    <t xml:space="preserve">3.0130410194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
     <t xml:space="preserve">2.88718914985657</t>
@@ -3398,22 +3398,22 @@
     <t xml:space="preserve">2.98342871665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8723828792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81130790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8649799823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86683058738708</t>
+    <t xml:space="preserve">2.87238311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81130766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86497974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86683082580566</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503896713257</t>
@@ -3425,19 +3425,19 @@
     <t xml:space="preserve">2.86868143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9242045879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90014433860779</t>
+    <t xml:space="preserve">2.92420434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981562614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059125900269</t>
+    <t xml:space="preserve">2.82981538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
     <t xml:space="preserve">2.82426309585571</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772395133972</t>
+    <t xml:space="preserve">2.6077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">2.52999210357666</t>
@@ -3458,22 +3458,22 @@
     <t xml:space="preserve">2.49852895736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60032105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297690391541</t>
+    <t xml:space="preserve">2.60032081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297666549683</t>
   </si>
   <si>
     <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61512684822083</t>
+    <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
     <t xml:space="preserve">2.57811188697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888751983643</t>
+    <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.44855833053589</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">2.46706604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47817087173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45596146583557</t>
+    <t xml:space="preserve">2.47817063331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">2.48927521705627</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742437362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2727358341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2579300403595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34861731529236</t>
+    <t xml:space="preserve">2.48742413520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27273607254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25792980194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34861707687378</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133939743042</t>
@@ -3518,16 +3518,16 @@
     <t xml:space="preserve">2.30790066719055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19685459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13577938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18760061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29679584503174</t>
+    <t xml:space="preserve">2.19685482978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13577961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18760085105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29679560661316</t>
   </si>
   <si>
     <t xml:space="preserve">2.2856912612915</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">2.30234837532043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35416960716248</t>
+    <t xml:space="preserve">2.35416984558105</t>
   </si>
   <si>
     <t xml:space="preserve">2.34121417999268</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607943534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22276544570923</t>
+    <t xml:space="preserve">2.25607919692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21351146697998</t>
+    <t xml:space="preserve">2.21351170539856</t>
   </si>
   <si>
     <t xml:space="preserve">2.1302273273468</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13763070106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14688420295715</t>
+    <t xml:space="preserve">2.08765959739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13763046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14688444137573</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">2.07285380363464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01362919807434</t>
+    <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
     <t xml:space="preserve">1.95810651779175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86186671257019</t>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
@@ -3647,16 +3647,16 @@
     <t xml:space="preserve">1.90132355690002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83638441562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255299091339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91036581993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077318668365</t>
+    <t xml:space="preserve">1.83638429641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8725528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91036570072174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077330589294</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953641891479</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">1.78377532958984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70814990997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86679887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93338215351105</t>
+    <t xml:space="preserve">1.70814979076385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86679899692535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93338239192963</t>
   </si>
   <si>
     <t xml:space="preserve">1.89556956291199</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">1.78541922569275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7615807056427</t>
+    <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.77062296867371</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79199540615082</t>
+    <t xml:space="preserve">1.79199528694153</t>
   </si>
   <si>
     <t xml:space="preserve">1.85857856273651</t>
@@ -3704,19 +3704,19 @@
     <t xml:space="preserve">1.90625584125519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311057567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95886480808258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078725814819</t>
+    <t xml:space="preserve">1.95311069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.958864569664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078749656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.03695607185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98023724555969</t>
+    <t xml:space="preserve">1.98023700714111</t>
   </si>
   <si>
     <t xml:space="preserve">2.03942227363586</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559132575989</t>
+    <t xml:space="preserve">2.07559108734131</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.99749958515167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11258149147034</t>
+    <t xml:space="preserve">2.11258172988892</t>
   </si>
   <si>
     <t xml:space="preserve">2.09203147888184</t>
@@ -3758,31 +3758,31 @@
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135217666626</t>
+    <t xml:space="preserve">2.14135241508484</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573763847351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14751744270325</t>
+    <t xml:space="preserve">2.14751720428467</t>
   </si>
   <si>
     <t xml:space="preserve">2.19889330863953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28520488739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2728750705719</t>
+    <t xml:space="preserve">2.28520512580872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34480118751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27287483215332</t>
   </si>
   <si>
     <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30781030654907</t>
+    <t xml:space="preserve">2.30781054496765</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685635566711</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821448326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25848960876465</t>
+    <t xml:space="preserve">2.24821424484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25848984718323</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21944403648376</t>
+    <t xml:space="preserve">2.14546227455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21944379806519</t>
   </si>
   <si>
     <t xml:space="preserve">2.24615931510925</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">2.26670980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25437951087952</t>
+    <t xml:space="preserve">2.2543797492981</t>
   </si>
   <si>
     <t xml:space="preserve">2.30986571311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3550763130188</t>
+    <t xml:space="preserve">2.35507655143738</t>
   </si>
   <si>
     <t xml:space="preserve">2.41056251525879</t>
@@ -3842,16 +3842,16 @@
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619550704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5276997089386</t>
+    <t xml:space="preserve">2.54619526863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
     <t xml:space="preserve">2.55236053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5379753112793</t>
+    <t xml:space="preserve">2.53797507286072</t>
   </si>
   <si>
     <t xml:space="preserve">2.54003024101257</t>
@@ -3869,40 +3869,40 @@
     <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51125955581665</t>
+    <t xml:space="preserve">2.51125979423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48454403877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45577335357666</t>
+    <t xml:space="preserve">2.48454427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45577359199524</t>
   </si>
   <si>
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920438766479</t>
+    <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
     <t xml:space="preserve">2.5585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55647039413452</t>
+    <t xml:space="preserve">2.5564706325531</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65716743469238</t>
+    <t xml:space="preserve">2.65716767311096</t>
   </si>
   <si>
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786471366882</t>
+    <t xml:space="preserve">2.75786447525024</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">2.66744256019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67155289649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68799304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68182778358459</t>
+    <t xml:space="preserve">2.67155265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.687992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
     <t xml:space="preserve">2.7414243221283</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70854377746582</t>
+    <t xml:space="preserve">2.70854353904724</t>
   </si>
   <si>
     <t xml:space="preserve">2.7784149646759</t>
@@ -3950,31 +3950,31 @@
     <t xml:space="preserve">2.71881866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78663539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869009017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77019453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703886032104</t>
+    <t xml:space="preserve">2.78663516044617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78868985176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77019476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703909873962</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60784649848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62634181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648837089539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63867235183716</t>
+    <t xml:space="preserve">2.6078462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62634205818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63867211341858</t>
   </si>
   <si>
     <t xml:space="preserve">2.67360782623291</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">2.62428689002991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59757137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60579133033752</t>
+    <t xml:space="preserve">2.59757161140442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6057915687561</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
@@ -4010,22 +4010,22 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048810958862</t>
+    <t xml:space="preserve">2.93048787117004</t>
   </si>
   <si>
     <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9140477180481</t>
+    <t xml:space="preserve">2.91404747962952</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98597383499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95925855636597</t>
+    <t xml:space="preserve">2.98597407341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
     <t xml:space="preserve">3.00035929679871</t>
@@ -4040,22 +4040,22 @@
     <t xml:space="preserve">2.89760732650757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84006595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82773590087891</t>
+    <t xml:space="preserve">2.8400661945343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82773613929749</t>
   </si>
   <si>
     <t xml:space="preserve">2.74553394317627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61606669425964</t>
+    <t xml:space="preserve">2.61606645584106</t>
   </si>
   <si>
     <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69826817512512</t>
+    <t xml:space="preserve">2.6982684135437</t>
   </si>
   <si>
     <t xml:space="preserve">2.70237827301025</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">2.66538763046265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896521568298</t>
+    <t xml:space="preserve">2.79896545410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.79074501991272</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93459796905518</t>
+    <t xml:space="preserve">2.9345977306366</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89555215835571</t>
+    <t xml:space="preserve">2.89555239677429</t>
   </si>
   <si>
     <t xml:space="preserve">3.10927653312683</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582752227783</t>
+    <t xml:space="preserve">2.90582728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.96336841583252</t>
@@ -4115,16 +4115,16 @@
     <t xml:space="preserve">2.93665313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89966201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85856151580811</t>
+    <t xml:space="preserve">2.89966225624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85856127738953</t>
   </si>
   <si>
     <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86883664131165</t>
+    <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.82568073272705</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">2.88733196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8893871307373</t>
+    <t xml:space="preserve">2.88938689231873</t>
   </si>
   <si>
     <t xml:space="preserve">2.91199254989624</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">3.02296471595764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06612038612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05995559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98186421394348</t>
+    <t xml:space="preserve">3.06612062454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05995535850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9818639755249</t>
   </si>
   <si>
     <t xml:space="preserve">3.0126895904541</t>
@@ -4160,66 +4160,69 @@
     <t xml:space="preserve">2.94281816482544</t>
   </si>
   <si>
+    <t xml:space="preserve">2.92432284355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94863700866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92211222648621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98621320724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04147267341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136584281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11883544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1254665851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16746354103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10999393463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07241773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09452128410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07020735740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08125901222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0171582698822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99063396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97958207130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97074031829834</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.92432260513306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94863700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92211222648621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98621320724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04147267341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10336303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136584281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11883544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1254665851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16746354103088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10999393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07241773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09452128410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07020735740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08125901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0171582698822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99063396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97958207130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97074031829834</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.91548109054565</t>
   </si>
   <si>
@@ -5628,6 +5631,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.05200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09800004959106</t>
   </si>
 </sst>
 </file>
@@ -56580,7 +56586,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>1382</v>
+        <v>1402</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -56606,7 +56612,7 @@
         <v>3.29749989509583</v>
       </c>
       <c r="G1948" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -56632,7 +56638,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G1949" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -56658,7 +56664,7 @@
         <v>3.3125</v>
       </c>
       <c r="G1950" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -56684,7 +56690,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1951" t="s">
-        <v>1382</v>
+        <v>1402</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -56736,7 +56742,7 @@
         <v>3.28250002861023</v>
       </c>
       <c r="G1953" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -56762,7 +56768,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1954" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -56788,7 +56794,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1955" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -56814,7 +56820,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1956" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -56840,7 +56846,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1957" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56866,7 +56872,7 @@
         <v>3.1875</v>
       </c>
       <c r="G1958" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56892,7 +56898,7 @@
         <v>3.29250001907349</v>
       </c>
       <c r="G1959" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56918,7 +56924,7 @@
         <v>3.20250010490417</v>
       </c>
       <c r="G1960" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56944,7 +56950,7 @@
         <v>3.12249994277954</v>
       </c>
       <c r="G1961" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56970,7 +56976,7 @@
         <v>3.06750011444092</v>
       </c>
       <c r="G1962" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56996,7 +57002,7 @@
         <v>3.04250001907349</v>
       </c>
       <c r="G1963" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -57022,7 +57028,7 @@
         <v>2.94250011444092</v>
       </c>
       <c r="G1964" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -57048,7 +57054,7 @@
         <v>3.01749992370605</v>
       </c>
       <c r="G1965" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -57074,7 +57080,7 @@
         <v>3.07249999046326</v>
       </c>
       <c r="G1966" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -57100,7 +57106,7 @@
         <v>3.0625</v>
       </c>
       <c r="G1967" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -57126,7 +57132,7 @@
         <v>3.03749990463257</v>
       </c>
       <c r="G1968" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -57152,7 +57158,7 @@
         <v>2.97250008583069</v>
       </c>
       <c r="G1969" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57178,7 +57184,7 @@
         <v>2.99749994277954</v>
       </c>
       <c r="G1970" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57204,7 +57210,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1971" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57230,7 +57236,7 @@
         <v>2.97250008583069</v>
       </c>
       <c r="G1972" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57256,7 +57262,7 @@
         <v>2.97250008583069</v>
       </c>
       <c r="G1973" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57282,7 +57288,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1974" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57308,7 +57314,7 @@
         <v>2.79749989509583</v>
       </c>
       <c r="G1975" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57334,7 +57340,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1976" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57360,7 +57366,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1977" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57386,7 +57392,7 @@
         <v>2.80250000953674</v>
       </c>
       <c r="G1978" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57412,7 +57418,7 @@
         <v>2.78250002861023</v>
       </c>
       <c r="G1979" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57438,7 +57444,7 @@
         <v>2.90249991416931</v>
       </c>
       <c r="G1980" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57464,7 +57470,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1981" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57490,7 +57496,7 @@
         <v>2.8824999332428</v>
       </c>
       <c r="G1982" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57516,7 +57522,7 @@
         <v>2.80250000953674</v>
       </c>
       <c r="G1983" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57542,7 +57548,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G1984" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57568,7 +57574,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1985" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57594,7 +57600,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G1986" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57620,7 +57626,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1987" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57646,7 +57652,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1988" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57672,7 +57678,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G1989" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57698,7 +57704,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57724,7 +57730,7 @@
         <v>2.53949999809265</v>
       </c>
       <c r="G1991" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57750,7 +57756,7 @@
         <v>2.48749995231628</v>
       </c>
       <c r="G1992" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57776,7 +57782,7 @@
         <v>2.43650007247925</v>
       </c>
       <c r="G1993" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57802,7 +57808,7 @@
         <v>2.4284999370575</v>
       </c>
       <c r="G1994" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57828,7 +57834,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1995" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57854,7 +57860,7 @@
         <v>2.4614999294281</v>
       </c>
       <c r="G1996" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57880,7 +57886,7 @@
         <v>2.59850001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57906,7 +57912,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1998" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57932,7 +57938,7 @@
         <v>2.66300010681152</v>
       </c>
       <c r="G1999" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57958,7 +57964,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G2000" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57984,7 +57990,7 @@
         <v>2.64450001716614</v>
       </c>
       <c r="G2001" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -58010,7 +58016,7 @@
         <v>2.84899997711182</v>
       </c>
       <c r="G2002" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -58036,7 +58042,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G2003" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -58062,7 +58068,7 @@
         <v>2.7409999370575</v>
       </c>
       <c r="G2004" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -58088,7 +58094,7 @@
         <v>2.84249997138977</v>
       </c>
       <c r="G2005" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -58114,7 +58120,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2006" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -58140,7 +58146,7 @@
         <v>2.85050010681152</v>
       </c>
       <c r="G2007" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58166,7 +58172,7 @@
         <v>2.90350008010864</v>
       </c>
       <c r="G2008" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58192,7 +58198,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2009" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58218,7 +58224,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G2010" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58244,7 +58250,7 @@
         <v>2.88100004196167</v>
       </c>
       <c r="G2011" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58270,7 +58276,7 @@
         <v>3.05900001525879</v>
       </c>
       <c r="G2012" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58296,7 +58302,7 @@
         <v>3.14549994468689</v>
       </c>
       <c r="G2013" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58322,7 +58328,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2014" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58348,7 +58354,7 @@
         <v>3.16300010681152</v>
       </c>
       <c r="G2015" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58374,7 +58380,7 @@
         <v>3.17950010299683</v>
       </c>
       <c r="G2016" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58400,7 +58406,7 @@
         <v>3.15899991989136</v>
       </c>
       <c r="G2017" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58426,7 +58432,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G2018" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58452,7 +58458,7 @@
         <v>3.13700008392334</v>
       </c>
       <c r="G2019" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58478,7 +58484,7 @@
         <v>3.1324999332428</v>
       </c>
       <c r="G2020" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58504,7 +58510,7 @@
         <v>3.20050001144409</v>
       </c>
       <c r="G2021" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58530,7 +58536,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G2022" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -58556,7 +58562,7 @@
         <v>3.26900005340576</v>
       </c>
       <c r="G2023" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58608,7 +58614,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G2025" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58634,7 +58640,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G2026" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58660,7 +58666,7 @@
         <v>3.32450008392334</v>
       </c>
       <c r="G2027" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58686,7 +58692,7 @@
         <v>3.32649993896484</v>
       </c>
       <c r="G2028" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58712,7 +58718,7 @@
         <v>3.30649995803833</v>
       </c>
       <c r="G2029" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58738,7 +58744,7 @@
         <v>3.31649994850159</v>
       </c>
       <c r="G2030" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58764,7 +58770,7 @@
         <v>3.33150005340576</v>
       </c>
       <c r="G2031" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58790,7 +58796,7 @@
         <v>3.31150007247925</v>
       </c>
       <c r="G2032" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58816,7 +58822,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2033" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58842,7 +58848,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G2034" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58868,7 +58874,7 @@
         <v>3.27150011062622</v>
       </c>
       <c r="G2035" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58894,7 +58900,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2036" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58920,7 +58926,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G2037" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58946,7 +58952,7 @@
         <v>3.2574999332428</v>
       </c>
       <c r="G2038" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58972,7 +58978,7 @@
         <v>3.31100010871887</v>
       </c>
       <c r="G2039" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -59024,7 +59030,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G2041" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59050,7 +59056,7 @@
         <v>3.4375</v>
       </c>
       <c r="G2042" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59076,7 +59082,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G2043" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59102,7 +59108,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2044" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59128,7 +59134,7 @@
         <v>3.31949996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59154,7 +59160,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2046" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59180,7 +59186,7 @@
         <v>3.29949998855591</v>
       </c>
       <c r="G2047" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59206,7 +59212,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G2048" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59232,7 +59238,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59258,7 +59264,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2050" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59284,7 +59290,7 @@
         <v>3.30900001525879</v>
       </c>
       <c r="G2051" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59310,7 +59316,7 @@
         <v>3.34349989891052</v>
       </c>
       <c r="G2052" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59336,7 +59342,7 @@
         <v>3.37549996376038</v>
       </c>
       <c r="G2053" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59362,7 +59368,7 @@
         <v>3.41849994659424</v>
       </c>
       <c r="G2054" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59388,7 +59394,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G2055" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59414,7 +59420,7 @@
         <v>3.34150004386902</v>
       </c>
       <c r="G2056" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59440,7 +59446,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G2057" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59466,7 +59472,7 @@
         <v>3.34299993515015</v>
       </c>
       <c r="G2058" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59492,7 +59498,7 @@
         <v>3.27449989318848</v>
       </c>
       <c r="G2059" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59544,7 +59550,7 @@
         <v>3.25</v>
       </c>
       <c r="G2061" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59570,7 +59576,7 @@
         <v>3.09750008583069</v>
       </c>
       <c r="G2062" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59596,7 +59602,7 @@
         <v>3.02099990844727</v>
       </c>
       <c r="G2063" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59622,7 +59628,7 @@
         <v>3.03949999809265</v>
       </c>
       <c r="G2064" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59648,7 +59654,7 @@
         <v>3.00950002670288</v>
       </c>
       <c r="G2065" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59674,7 +59680,7 @@
         <v>3.04099988937378</v>
       </c>
       <c r="G2066" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59700,7 +59706,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G2067" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59726,7 +59732,7 @@
         <v>3.07699990272522</v>
       </c>
       <c r="G2068" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59752,7 +59758,7 @@
         <v>3.06450009346008</v>
       </c>
       <c r="G2069" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59778,7 +59784,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G2070" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59804,7 +59810,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G2071" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59830,7 +59836,7 @@
         <v>2.97250008583069</v>
       </c>
       <c r="G2072" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59856,7 +59862,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G2073" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59882,7 +59888,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G2074" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59908,7 +59914,7 @@
         <v>2.96700000762939</v>
       </c>
       <c r="G2075" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59934,7 +59940,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G2076" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59960,7 +59966,7 @@
         <v>2.94549989700317</v>
       </c>
       <c r="G2077" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59986,7 +59992,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2078" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -60012,7 +60018,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2079" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -60038,7 +60044,7 @@
         <v>2.95099997520447</v>
       </c>
       <c r="G2080" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -60064,7 +60070,7 @@
         <v>2.91899991035461</v>
       </c>
       <c r="G2081" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -60090,7 +60096,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G2082" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -60116,7 +60122,7 @@
         <v>2.94549989700317</v>
       </c>
       <c r="G2083" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -60142,7 +60148,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G2084" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60168,7 +60174,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G2085" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -60194,7 +60200,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G2086" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60220,7 +60226,7 @@
         <v>3.07699990272522</v>
       </c>
       <c r="G2087" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60246,7 +60252,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2088" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60272,7 +60278,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G2089" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60298,7 +60304,7 @@
         <v>2.92350006103516</v>
       </c>
       <c r="G2090" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60324,7 +60330,7 @@
         <v>3.05699992179871</v>
       </c>
       <c r="G2091" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60350,7 +60356,7 @@
         <v>3.07550001144409</v>
       </c>
       <c r="G2092" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60376,7 +60382,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2093" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60402,7 +60408,7 @@
         <v>3.06699991226196</v>
       </c>
       <c r="G2094" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60428,7 +60434,7 @@
         <v>3.03099989891052</v>
       </c>
       <c r="G2095" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60454,7 +60460,7 @@
         <v>3.07550001144409</v>
       </c>
       <c r="G2096" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60480,7 +60486,7 @@
         <v>3.14549994468689</v>
       </c>
       <c r="G2097" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60506,7 +60512,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G2098" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60532,7 +60538,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G2099" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60558,7 +60564,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2100" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60584,7 +60590,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G2101" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60610,7 +60616,7 @@
         <v>3.30200004577637</v>
       </c>
       <c r="G2102" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60636,7 +60642,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2103" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60662,7 +60668,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G2104" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60688,7 +60694,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G2105" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60714,7 +60720,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G2106" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60740,7 +60746,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G2107" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60766,7 +60772,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G2108" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60792,7 +60798,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G2109" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60818,7 +60824,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G2110" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60844,7 +60850,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G2111" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60870,7 +60876,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G2112" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60896,7 +60902,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G2113" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60922,7 +60928,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G2114" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60948,7 +60954,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G2115" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60974,7 +60980,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G2116" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -61000,7 +61006,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G2117" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -61026,7 +61032,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G2118" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61052,7 +61058,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2119" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -61078,7 +61084,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G2120" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -61104,7 +61110,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G2121" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -61130,7 +61136,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G2122" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -61156,7 +61162,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2123" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61182,7 +61188,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G2124" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61208,7 +61214,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G2125" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61234,7 +61240,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G2126" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61260,7 +61266,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2127" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61286,7 +61292,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G2128" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61312,7 +61318,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G2129" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61338,7 +61344,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G2130" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61364,7 +61370,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G2131" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61390,7 +61396,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G2132" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61416,7 +61422,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2133" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61442,7 +61448,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G2134" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61468,7 +61474,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2135" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61494,7 +61500,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2136" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61520,7 +61526,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G2137" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61546,7 +61552,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2138" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61572,7 +61578,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G2139" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61598,7 +61604,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2140" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61624,7 +61630,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G2141" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61650,7 +61656,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2142" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61676,7 +61682,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G2143" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61702,7 +61708,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G2144" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61728,7 +61734,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G2145" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61754,7 +61760,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G2146" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61780,7 +61786,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2147" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61806,7 +61812,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G2148" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61832,7 +61838,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G2149" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61858,7 +61864,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G2150" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61884,7 +61890,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G2151" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61910,7 +61916,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G2152" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61936,7 +61942,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2153" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61962,7 +61968,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2154" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61988,7 +61994,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2155" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -62014,7 +62020,7 @@
         <v>4.01599979400635</v>
       </c>
       <c r="G2156" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -62040,7 +62046,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2157" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -62066,7 +62072,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -62092,7 +62098,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G2159" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -62118,7 +62124,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G2160" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -62144,7 +62150,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2161" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62170,7 +62176,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2162" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62196,7 +62202,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G2163" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62222,7 +62228,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G2164" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62248,7 +62254,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2165" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62274,7 +62280,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G2166" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62300,7 +62306,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2167" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62326,7 +62332,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G2168" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62352,7 +62358,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G2169" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62378,7 +62384,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G2170" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62404,7 +62410,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G2171" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62430,7 +62436,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G2172" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62456,7 +62462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G2173" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62482,7 +62488,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G2174" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62508,7 +62514,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62534,7 +62540,7 @@
         <v>4.71400022506714</v>
       </c>
       <c r="G2176" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62560,7 +62566,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62586,7 +62592,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G2178" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62612,7 +62618,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2179" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62638,7 +62644,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2180" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62664,7 +62670,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2181" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62690,7 +62696,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G2182" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62716,7 +62722,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2183" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62742,7 +62748,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G2184" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62768,7 +62774,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G2185" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62794,7 +62800,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G2186" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62820,7 +62826,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G2187" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62846,7 +62852,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2188" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62872,7 +62878,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G2189" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62898,7 +62904,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G2190" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62924,7 +62930,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G2191" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62950,7 +62956,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2192" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62976,7 +62982,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2193" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -63002,7 +63008,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G2194" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -63028,7 +63034,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2195" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -63054,7 +63060,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G2196" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -63080,7 +63086,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G2197" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -63106,7 +63112,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G2198" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -63132,7 +63138,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G2199" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63158,7 +63164,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G2200" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63184,7 +63190,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2201" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63210,7 +63216,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G2202" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63236,7 +63242,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2203" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63262,7 +63268,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2204" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63288,7 +63294,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G2205" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63314,7 +63320,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G2206" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63340,7 +63346,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G2207" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63366,7 +63372,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G2208" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63392,7 +63398,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G2209" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63418,7 +63424,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2210" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63444,7 +63450,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2211" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63470,7 +63476,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G2212" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63496,7 +63502,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G2213" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63522,7 +63528,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G2214" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63548,7 +63554,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G2215" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63574,7 +63580,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G2216" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63600,7 +63606,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G2217" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63626,7 +63632,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63652,7 +63658,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2219" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63678,7 +63684,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G2220" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63704,7 +63710,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G2221" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63730,7 +63736,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G2222" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63756,7 +63762,7 @@
         <v>4.5</v>
       </c>
       <c r="G2223" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63782,7 +63788,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G2224" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63808,7 +63814,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G2225" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63834,7 +63840,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2226" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63860,7 +63866,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G2227" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63886,7 +63892,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2228" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63912,7 +63918,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G2229" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63938,7 +63944,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G2230" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63964,7 +63970,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G2231" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63990,7 +63996,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G2232" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -64016,7 +64022,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G2233" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -64042,7 +64048,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G2234" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -64068,7 +64074,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G2235" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -64094,7 +64100,7 @@
         <v>4.22800016403198</v>
       </c>
       <c r="G2236" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -64120,7 +64126,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2237" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64146,7 +64152,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G2238" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64172,7 +64178,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G2239" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64198,7 +64204,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G2240" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64224,7 +64230,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2241" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64250,7 +64256,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G2242" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64276,7 +64282,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2243" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64302,7 +64308,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G2244" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64328,7 +64334,7 @@
         <v>4.25</v>
       </c>
       <c r="G2245" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64354,7 +64360,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G2246" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64380,7 +64386,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G2247" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64406,7 +64412,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2248" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64432,7 +64438,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G2249" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64458,7 +64464,7 @@
         <v>4.24599981307983</v>
       </c>
       <c r="G2250" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64484,7 +64490,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2251" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64510,7 +64516,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G2252" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64536,7 +64542,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2253" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64562,7 +64568,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G2254" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64588,7 +64594,7 @@
         <v>4.14599990844727</v>
       </c>
       <c r="G2255" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64614,7 +64620,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2256" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64640,7 +64646,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G2257" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64666,7 +64672,7 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G2258" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64692,7 +64698,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G2259" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64718,7 +64724,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G2260" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64744,7 +64750,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G2261" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64770,7 +64776,7 @@
         <v>4.02799987792969</v>
       </c>
       <c r="G2262" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64796,7 +64802,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2263" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64822,7 +64828,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2264" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64848,7 +64854,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G2265" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64874,7 +64880,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G2266" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64900,7 +64906,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G2267" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64926,7 +64932,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G2268" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64952,7 +64958,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G2269" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64978,7 +64984,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G2270" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65004,7 +65010,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G2271" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -65030,7 +65036,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2272" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -65056,7 +65062,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G2273" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -65082,7 +65088,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G2274" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -65108,7 +65114,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G2275" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -65134,7 +65140,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2276" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65160,7 +65166,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G2277" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65186,7 +65192,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2278" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65212,7 +65218,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G2279" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65238,7 +65244,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G2280" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65264,7 +65270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2281" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65290,7 +65296,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2282" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65316,7 +65322,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G2283" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65342,7 +65348,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G2284" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65368,7 +65374,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65394,7 +65400,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2286" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65420,7 +65426,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G2287" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65446,7 +65452,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G2288" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65472,7 +65478,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G2289" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65498,7 +65504,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2290" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65524,7 +65530,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G2291" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65550,7 +65556,7 @@
         <v>4.18800020217896</v>
       </c>
       <c r="G2292" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65576,7 +65582,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G2293" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65602,7 +65608,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2294" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65628,7 +65634,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G2295" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65654,7 +65660,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G2296" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65680,7 +65686,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G2297" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65706,7 +65712,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2298" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65732,7 +65738,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G2299" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65758,7 +65764,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2300" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65784,7 +65790,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G2301" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65810,7 +65816,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2302" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65836,7 +65842,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G2303" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65862,7 +65868,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G2304" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65888,7 +65894,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G2305" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65914,7 +65920,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G2306" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65940,7 +65946,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G2307" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65966,7 +65972,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G2308" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65992,7 +65998,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G2309" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -66018,7 +66024,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G2310" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -66044,7 +66050,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G2311" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -66070,7 +66076,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2312" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -66096,7 +66102,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G2313" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -66122,7 +66128,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G2314" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66148,7 +66154,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G2315" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66174,7 +66180,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2316" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66200,7 +66206,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G2317" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66226,7 +66232,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G2318" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66252,7 +66258,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2319" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66278,7 +66284,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G2320" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66304,7 +66310,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G2321" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66330,7 +66336,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2322" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66356,7 +66362,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G2323" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66382,7 +66388,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2324" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66408,7 +66414,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G2325" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66434,7 +66440,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G2326" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66460,7 +66466,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G2327" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66486,7 +66492,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2328" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66512,7 +66518,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G2329" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66538,7 +66544,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2330" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66564,7 +66570,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G2331" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66590,7 +66596,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G2332" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66616,7 +66622,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G2333" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66642,7 +66648,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2334" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66668,7 +66674,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66694,7 +66700,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G2336" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66720,7 +66726,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G2337" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66746,7 +66752,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G2338" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66772,7 +66778,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G2339" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66798,7 +66804,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G2340" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66824,7 +66830,7 @@
         <v>4.65199995040894</v>
       </c>
       <c r="G2341" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66850,7 +66856,7 @@
         <v>4.81799983978271</v>
       </c>
       <c r="G2342" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66876,7 +66882,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G2343" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66902,7 +66908,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G2344" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66928,7 +66934,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G2345" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66954,7 +66960,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2346" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66980,7 +66986,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2347" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67006,7 +67012,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2348" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67032,7 +67038,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G2349" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67058,7 +67064,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G2350" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67084,7 +67090,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G2351" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67110,7 +67116,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G2352" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67136,7 +67142,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G2353" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67162,7 +67168,7 @@
         <v>4.65199995040894</v>
       </c>
       <c r="G2354" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67188,7 +67194,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G2355" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67214,7 +67220,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G2356" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67240,7 +67246,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2357" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67266,7 +67272,7 @@
         <v>4.18599987030029</v>
       </c>
       <c r="G2358" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67292,7 +67298,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G2359" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67318,7 +67324,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G2360" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67344,7 +67350,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2361" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67370,7 +67376,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2362" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67396,7 +67402,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2363" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67422,7 +67428,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2364" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67448,7 +67454,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2365" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67474,7 +67480,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G2366" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67500,7 +67506,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G2367" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67526,7 +67532,7 @@
         <v>4.21199989318848</v>
       </c>
       <c r="G2368" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67552,7 +67558,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2369" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67578,7 +67584,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2370" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67604,7 +67610,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G2371" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67630,7 +67636,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2372" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67656,7 +67662,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G2373" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67682,7 +67688,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G2374" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67708,7 +67714,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G2375" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67734,7 +67740,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G2376" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67760,7 +67766,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G2377" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67786,7 +67792,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G2378" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67812,7 +67818,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G2379" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67838,7 +67844,7 @@
         <v>4.40399980545044</v>
       </c>
       <c r="G2380" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67864,7 +67870,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2381" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67890,7 +67896,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2382" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67916,7 +67922,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G2383" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67942,7 +67948,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2384" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67968,7 +67974,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G2385" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67994,7 +68000,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G2386" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68020,7 +68026,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G2387" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68046,7 +68052,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G2388" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68072,7 +68078,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2389" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68098,7 +68104,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2390" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68124,7 +68130,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G2391" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68150,7 +68156,7 @@
         <v>4.27199983596802</v>
       </c>
       <c r="G2392" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68176,7 +68182,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G2393" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68202,7 +68208,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G2394" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68228,7 +68234,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2395" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68254,7 +68260,7 @@
         <v>4.22200012207031</v>
       </c>
       <c r="G2396" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68280,7 +68286,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G2397" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68306,7 +68312,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G2398" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68332,7 +68338,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G2399" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68358,7 +68364,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2400" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68384,7 +68390,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G2401" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68410,7 +68416,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G2402" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68436,7 +68442,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G2403" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68462,7 +68468,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G2404" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68488,7 +68494,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2405" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68514,7 +68520,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2406" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68540,7 +68546,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G2407" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68566,7 +68572,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G2408" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68592,7 +68598,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G2409" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68618,7 +68624,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G2410" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68644,7 +68650,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2411" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68670,7 +68676,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G2412" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68696,7 +68702,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2413" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68722,7 +68728,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G2414" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68748,7 +68754,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G2415" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68774,7 +68780,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G2416" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68800,7 +68806,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G2417" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68826,7 +68832,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G2418" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68852,7 +68858,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2419" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68878,7 +68884,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G2420" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68904,7 +68910,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G2421" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68930,7 +68936,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G2422" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68956,7 +68962,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G2423" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68982,7 +68988,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G2424" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69008,7 +69014,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2425" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69034,7 +69040,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G2426" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69060,7 +69066,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2427" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69086,7 +69092,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G2428" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69112,7 +69118,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G2429" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69138,7 +69144,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2430" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69164,7 +69170,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2431" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69190,7 +69196,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G2432" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69216,7 +69222,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G2433" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69242,7 +69248,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G2434" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69268,7 +69274,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G2435" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69294,7 +69300,7 @@
         <v>4</v>
       </c>
       <c r="G2436" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69320,7 +69326,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G2437" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69346,7 +69352,7 @@
         <v>4</v>
       </c>
       <c r="G2438" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69372,7 +69378,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G2439" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69398,7 +69404,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G2440" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69424,7 +69430,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G2441" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69450,7 +69456,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G2442" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69476,7 +69482,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69502,7 +69508,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G2444" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69528,7 +69534,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2445" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69554,7 +69560,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G2446" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69580,7 +69586,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2447" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69606,7 +69612,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G2448" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69632,7 +69638,7 @@
         <v>3.99600005149841</v>
       </c>
       <c r="G2449" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69658,7 +69664,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G2450" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69684,7 +69690,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2451" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69710,7 +69716,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G2452" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69736,7 +69742,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G2453" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69762,7 +69768,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69788,7 +69794,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G2455" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69814,7 +69820,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2456" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69840,7 +69846,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G2457" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69866,7 +69872,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2458" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69892,7 +69898,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G2459" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69918,7 +69924,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2460" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69944,7 +69950,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G2461" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69970,7 +69976,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G2462" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69996,7 +70002,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70022,7 +70028,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70048,7 +70054,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G2465" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70074,7 +70080,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2466" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70100,7 +70106,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2467" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70126,7 +70132,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G2468" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70152,7 +70158,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G2469" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70178,7 +70184,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G2470" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70204,7 +70210,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2471" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70230,7 +70236,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G2472" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70256,7 +70262,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G2473" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70282,7 +70288,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G2474" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70308,7 +70314,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G2475" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70334,7 +70340,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G2476" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70360,7 +70366,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G2477" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70386,7 +70392,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G2478" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70412,7 +70418,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G2479" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70438,7 +70444,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2480" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70464,7 +70470,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G2481" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70490,7 +70496,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G2482" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70516,7 +70522,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G2483" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70542,7 +70548,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G2484" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70568,7 +70574,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2485" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70594,7 +70600,7 @@
         <v>4.25400018692017</v>
       </c>
       <c r="G2486" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70620,7 +70626,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2487" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70646,7 +70652,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G2488" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70672,7 +70678,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2489" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70698,7 +70704,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G2490" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70724,7 +70730,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G2491" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70750,7 +70756,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G2492" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70776,7 +70782,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2493" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70802,7 +70808,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G2494" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70828,7 +70834,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G2495" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70854,7 +70860,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2496" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70880,7 +70886,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G2497" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70906,7 +70912,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2498" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70932,7 +70938,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G2499" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70958,7 +70964,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G2500" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70984,7 +70990,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G2501" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71010,7 +71016,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G2502" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71036,7 +71042,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2503" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -71062,7 +71068,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G2504" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -71088,7 +71094,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G2505" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -71114,7 +71120,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G2506" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -71140,7 +71146,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G2507" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71166,7 +71172,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2508" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71192,7 +71198,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G2509" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71218,7 +71224,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2510" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71244,7 +71250,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2511" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71270,7 +71276,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G2512" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71296,7 +71302,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G2513" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71322,7 +71328,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2514" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71348,7 +71354,7 @@
         <v>4</v>
       </c>
       <c r="G2515" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71356,7 +71362,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6912152778</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>829492</v>
@@ -71374,9 +71380,35 @@
         <v>4.05200004577637</v>
       </c>
       <c r="G2516" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6912731481</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>496677</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>4.09800004959106</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>3.97199988365173</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>4.02400016784668</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>4.09800004959106</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356538772583</t>
+    <t xml:space="preserve">12.2356548309326</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956901550293</t>
+    <t xml:space="preserve">12.195689201355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027997970581</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101800918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0766973495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1366443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302526473999</t>
+    <t xml:space="preserve">11.4097290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.076696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.136643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302536010742</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770582199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3107194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2907371520996</t>
+    <t xml:space="preserve">10.3107213973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2907381057739</t>
   </si>
   <si>
     <t xml:space="preserve">9.65797424316406</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">10.7370042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3906497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438432693481</t>
+    <t xml:space="preserve">10.3906488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438442230225</t>
   </si>
   <si>
     <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2707576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4838962554932</t>
+    <t xml:space="preserve">10.2707557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4838972091675</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973985671997</t>
@@ -110,40 +110,40 @@
     <t xml:space="preserve">10.1042394638062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8702154159546</t>
+    <t xml:space="preserve">10.8702163696289</t>
   </si>
   <si>
     <t xml:space="preserve">10.7170209884644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77786636352539</t>
+    <t xml:space="preserve">9.77786540985107</t>
   </si>
   <si>
     <t xml:space="preserve">9.91107940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120590209961</t>
+    <t xml:space="preserve">9.54474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120685577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4639158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6171102523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4172925949097</t>
+    <t xml:space="preserve">10.4639167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6171112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4172916412354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9301633834839</t>
+    <t xml:space="preserve">10.9301643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.96436500549316</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">10.7236824035645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9434833526611</t>
+    <t xml:space="preserve">10.9434852600098</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363737106323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3431253433228</t>
+    <t xml:space="preserve">11.3431243896484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6495151519775</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">11.2898387908936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0624780654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2289934158325</t>
+    <t xml:space="preserve">12.0624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2289943695068</t>
   </si>
   <si>
     <t xml:space="preserve">12.475438117981</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">12.4621171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5553665161133</t>
+    <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019916534424</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">12.1823692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6961393356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5695877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.075798034668</t>
+    <t xml:space="preserve">11.6961402893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5695867538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
     <t xml:space="preserve">11.9159412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1890296936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4963188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0633773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561765670776</t>
+    <t xml:space="preserve">12.1890306472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.496319770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0633764266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561756134033</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559059143066</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">12.2689580917358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8217935562134</t>
+    <t xml:space="preserve">12.8217945098877</t>
   </si>
   <si>
     <t xml:space="preserve">12.921703338623</t>
@@ -239,43 +239,43 @@
     <t xml:space="preserve">12.9350252151489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947908401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1814708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614866256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882205963135</t>
+    <t xml:space="preserve">13.1015405654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947917938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.361307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882196426392</t>
   </si>
   <si>
     <t xml:space="preserve">12.9816493988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5620279312134</t>
+    <t xml:space="preserve">12.6885786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5620288848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.881739616394</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">12.8884000778198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0482559204102</t>
+    <t xml:space="preserve">13.0482549667358</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
@@ -296,64 +296,64 @@
     <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221534729004</t>
+    <t xml:space="preserve">12.4221525192261</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.721884727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150438308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.134407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887948989868</t>
+    <t xml:space="preserve">12.7218837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685098648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159873962402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230974197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226812362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561552047729</t>
+    <t xml:space="preserve">13.6230983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226831436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.4222650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3620166778564</t>
+    <t xml:space="preserve">13.3620147705078</t>
   </si>
   <si>
     <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0741567611694</t>
+    <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
     <t xml:space="preserve">12.9938249588013</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3017683029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2749881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.194655418396</t>
+    <t xml:space="preserve">13.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2749891281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
     <t xml:space="preserve">12.659104347229</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">12.0833854675293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8156108856201</t>
+    <t xml:space="preserve">11.8156099319458</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620544433594</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7218894958496</t>
+    <t xml:space="preserve">11.7218885421753</t>
   </si>
   <si>
     <t xml:space="preserve">12.0766925811768</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">12.6524095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6925754547119</t>
+    <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
     <t xml:space="preserve">12.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1411008834839</t>
+    <t xml:space="preserve">13.1411018371582</t>
   </si>
   <si>
     <t xml:space="preserve">10.8850908279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1487045288086</t>
+    <t xml:space="preserve">10.1487054824829</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834260940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177286148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2290372848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4164819717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0482902526855</t>
+    <t xml:space="preserve">10.4834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2290382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.416482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0482892990112</t>
   </si>
   <si>
     <t xml:space="preserve">10.4432601928711</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">10.811450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9252548217773</t>
+    <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
     <t xml:space="preserve">10.8783941268921</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.175482749939</t>
+    <t xml:space="preserve">10.1754837036133</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762378692627</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">9.20479583740234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37215423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25835037231445</t>
+    <t xml:space="preserve">9.37215614318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.33868312835693</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">9.23157405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63323783874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959987640381</t>
+    <t xml:space="preserve">9.6332368850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390239715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959892272949</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">9.78720760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87423610687256</t>
+    <t xml:space="preserve">9.87423515319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.6734037399292</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">9.07090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31190490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801761627197</t>
+    <t xml:space="preserve">9.08429718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801856994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.35207366943359</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">9.24496269226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03743648529053</t>
+    <t xml:space="preserve">9.03743553161621</t>
   </si>
   <si>
     <t xml:space="preserve">8.70941066741943</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78304958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7897424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71610546112061</t>
+    <t xml:space="preserve">8.74957656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78304862976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78974342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71610450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.66924381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33452415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2006368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
+    <t xml:space="preserve">8.3345251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20063591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002197265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1203031539917</t>
@@ -620,61 +620,61 @@
     <t xml:space="preserve">7.82574939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83913850784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6316123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491798400879</t>
+    <t xml:space="preserve">7.83913898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63161277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491846084595</t>
   </si>
   <si>
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69186162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500093460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9596381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12699890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38138580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9236307144165</t>
+    <t xml:space="preserve">7.74541711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71194553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6918625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6450023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.651695728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12699794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38138484954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92363166809082</t>
   </si>
   <si>
     <t xml:space="preserve">9.2114896774292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09768676757812</t>
+    <t xml:space="preserve">9.09768581390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.9963598251343</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691654205322</t>
+    <t xml:space="preserve">11.8691644668579</t>
   </si>
   <si>
     <t xml:space="preserve">12.0499153137207</t>
@@ -695,49 +695,49 @@
     <t xml:space="preserve">14.8615617752075</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2833080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971515655518</t>
+    <t xml:space="preserve">15.2833070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971525192261</t>
   </si>
   <si>
     <t xml:space="preserve">13.6967344284058</t>
   </si>
   <si>
-    <t xml:space="preserve">13.756986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975687026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235136032104</t>
+    <t xml:space="preserve">13.7569856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975667953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235145568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.8908729553223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9578189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180692672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3126201629639</t>
+    <t xml:space="preserve">13.9578170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180683135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3126192092896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2858438491821</t>
@@ -746,73 +746,73 @@
     <t xml:space="preserve">14.1385669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251792907715</t>
+    <t xml:space="preserve">14.1251783370972</t>
   </si>
   <si>
     <t xml:space="preserve">13.817234992981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.455738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415199279785</t>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415170669556</t>
   </si>
   <si>
     <t xml:space="preserve">13.1544895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2549057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.208044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268817901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737415313721</t>
+    <t xml:space="preserve">13.254903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2080450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268808364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528257369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737405776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.9067974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1611843109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0540742874146</t>
+    <t xml:space="preserve">13.1611833572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0540733337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.9134922027588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879634857178</t>
+    <t xml:space="preserve">13.2147388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879625320435</t>
   </si>
   <si>
     <t xml:space="preserve">13.3419342041016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812677383423</t>
+    <t xml:space="preserve">13.181266784668</t>
   </si>
   <si>
     <t xml:space="preserve">13.0339908599854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.859935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871311187744</t>
+    <t xml:space="preserve">12.8599348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871292114258</t>
   </si>
   <si>
     <t xml:space="preserve">13.0072135925293</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">13.0473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.020601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.92018699646</t>
+    <t xml:space="preserve">13.0206022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934087753296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758195877075</t>
+    <t xml:space="preserve">13.3754034042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">13.3486280441284</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">13.1745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0406856536865</t>
+    <t xml:space="preserve">13.0406847000122</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9335746765137</t>
+    <t xml:space="preserve">12.8867149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.933575630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.8398542404175</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8532428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.819769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858825683594</t>
+    <t xml:space="preserve">12.8532419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858835220337</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386056900024</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">12.3310794830322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4047193527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2708301544189</t>
+    <t xml:space="preserve">12.4047183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2708292007446</t>
   </si>
   <si>
     <t xml:space="preserve">12.1570243835449</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">12.7862987518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8800191879272</t>
+    <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.9469633102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637182235718</t>
+    <t xml:space="preserve">12.5653839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637191772461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043012619019</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586891174316</t>
+    <t xml:space="preserve">12.558690071106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4649686813354</t>
@@ -938,46 +938,46 @@
     <t xml:space="preserve">12.6189384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574415206909</t>
+    <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2842178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4181051254272</t>
+    <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
     <t xml:space="preserve">12.1971921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1034688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0900802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.063304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519933700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6724939346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3176908493042</t>
+    <t xml:space="preserve">12.1034698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0900812149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0633039474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6724948883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3176898956299</t>
   </si>
   <si>
     <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813055038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6147794723511</t>
+    <t xml:space="preserve">12.0030536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813064575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076684951782</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817235946655</t>
+    <t xml:space="preserve">11.6817226409912</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5210561752319</t>
+    <t xml:space="preserve">11.5210552215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6616401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6348628997803</t>
+    <t xml:space="preserve">11.661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6348609924316</t>
   </si>
   <si>
     <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7018051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3804740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.226505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779788970947</t>
+    <t xml:space="preserve">11.7018060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4474191665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3804750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2265033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.777979850769</t>
   </si>
   <si>
     <t xml:space="preserve">10.7043409347534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7980623245239</t>
+    <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
     <t xml:space="preserve">10.9453392028809</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">11.139476776123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1930313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461706161499</t>
+    <t xml:space="preserve">11.1930322647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">11.1327810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0993099212646</t>
+    <t xml:space="preserve">11.0591449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528663635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.099310874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.1997261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9921998977661</t>
+    <t xml:space="preserve">10.9922008514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.112699508667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4206409454346</t>
+    <t xml:space="preserve">11.4206399917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.5411405563354</t>
@@ -1085,31 +1085,31 @@
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4608087539673</t>
+    <t xml:space="preserve">11.4005575180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.460807800293</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541139602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336143493652</t>
+    <t xml:space="preserve">11.3336133956909</t>
   </si>
   <si>
     <t xml:space="preserve">11.3536968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1595592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0524492263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721174240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5302867889404</t>
+    <t xml:space="preserve">11.1595602035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0524501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721155166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.3897047042847</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">10.1620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2156496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3361501693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901189804077</t>
+    <t xml:space="preserve">10.2156505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3361492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625112533569</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71356964111328</t>
+    <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">9.72026538848877</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373649597168</t>
+    <t xml:space="preserve">9.75373554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.70018005371094</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6507863998413</t>
+    <t xml:space="preserve">10.650785446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708669662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.664174079895</t>
+    <t xml:space="preserve">10.6708688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6641750335693</t>
   </si>
   <si>
     <t xml:space="preserve">10.3763151168823</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">10.1888723373413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.275899887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.128623008728</t>
+    <t xml:space="preserve">10.2758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1286220550537</t>
   </si>
   <si>
     <t xml:space="preserve">10.2223443984985</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">10.2357330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5570640563965</t>
+    <t xml:space="preserve">10.5570650100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5102033615112</t>
@@ -1214,31 +1214,31 @@
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65331935882568</t>
+    <t xml:space="preserve">10.2089557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6533203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.52612686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62654209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83406829833984</t>
+    <t xml:space="preserve">9.62654304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83406734466553</t>
   </si>
   <si>
     <t xml:space="preserve">9.84745788574219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2959823608398</t>
+    <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436754226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7712850570679</t>
+    <t xml:space="preserve">10.7712841033936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5972309112549</t>
@@ -1247,37 +1247,37 @@
     <t xml:space="preserve">10.8583126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855051040649</t>
+    <t xml:space="preserve">10.9855060577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587287902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7311182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8248405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9654216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998893737793</t>
+    <t xml:space="preserve">10.7311191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82483959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9654226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725336074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9988946914673</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796426773071</t>
+    <t xml:space="preserve">11.1796436309814</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">10.9051733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8917837142944</t>
+    <t xml:space="preserve">10.8917846679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512016296387</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">11.0390605926514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7277717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4633417129517</t>
+    <t xml:space="preserve">10.7277708053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.463342666626</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">10.620659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6407451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106185913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5503692626953</t>
+    <t xml:space="preserve">10.8616590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6407442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
     <t xml:space="preserve">10.5771474838257</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6139659881592</t>
+    <t xml:space="preserve">10.6139650344849</t>
   </si>
   <si>
     <t xml:space="preserve">10.6240081787109</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1729497909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982159614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269403457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261079788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4030923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3394966125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3629264831543</t>
+    <t xml:space="preserve">11.1729488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9821586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4030933380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3394956588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3629274368286</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94452667236328</t>
+    <t xml:space="preserve">10.1821775436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9445276260376</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349006652832</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">11.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0357131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762962341309</t>
+    <t xml:space="preserve">11.0357141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620742797852</t>
+    <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.0223245620728</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">11.025671005249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.082573890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9520330429077</t>
+    <t xml:space="preserve">11.0825748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9520349502563</t>
   </si>
   <si>
     <t xml:space="preserve">11.0290193557739</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2867546081543</t>
+    <t xml:space="preserve">11.28675365448</t>
   </si>
   <si>
     <t xml:space="preserve">11.3135299682617</t>
@@ -1442,19 +1442,19 @@
     <t xml:space="preserve">10.9352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5068559646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1721353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.245774269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0683727264404</t>
+    <t xml:space="preserve">10.5068550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1721363067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2457752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0683736801147</t>
   </si>
   <si>
     <t xml:space="preserve">9.74369621276855</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67005634307861</t>
+    <t xml:space="preserve">9.34537792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6700553894043</t>
   </si>
   <si>
     <t xml:space="preserve">9.72695827484131</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">9.48596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637714385986</t>
+    <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54286289215088</t>
+    <t xml:space="preserve">9.5428638458252</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298755645752</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50269603729248</t>
+    <t xml:space="preserve">9.5026969909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.47926616668701</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319660186768</t>
+    <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980701446533</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">8.83660411834717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60564613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68932723999023</t>
+    <t xml:space="preserve">8.60564804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68932628631592</t>
   </si>
   <si>
     <t xml:space="preserve">8.72949409484863</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22487831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512763977051</t>
+    <t xml:space="preserve">9.30186557769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22487926483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
     <t xml:space="preserve">9.21483707427979</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39558506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28178215026855</t>
+    <t xml:space="preserve">9.39558601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
     <t xml:space="preserve">9.61315441131592</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">9.46922397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550354003906</t>
+    <t xml:space="preserve">9.37550258636475</t>
   </si>
   <si>
     <t xml:space="preserve">9.54621028900146</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.7328405380249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015960693359</t>
+    <t xml:space="preserve">8.80647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86003398895264</t>
+    <t xml:space="preserve">8.86003494262695</t>
   </si>
   <si>
     <t xml:space="preserve">8.92028331756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88011837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82656288146973</t>
+    <t xml:space="preserve">8.88011741638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82656192779541</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">8.24080276489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25084495544434</t>
+    <t xml:space="preserve">8.25084400177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
@@ -1628,58 +1628,58 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945190429688</t>
+    <t xml:space="preserve">8.47175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71945095062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635478973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16462898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00730991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01065921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01400566101074</t>
+    <t xml:space="preserve">9.16462993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1345043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00731086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01065826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22822666168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94706153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00061702728271</t>
+    <t xml:space="preserve">9.22822570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94706058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12780952453613</t>
+    <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03408908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66589546203613</t>
+    <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">8.84999179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53535556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47510528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30105209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62907791137695</t>
+    <t xml:space="preserve">8.53535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47510623931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30105113983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62907886505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90689659118652</t>
+    <t xml:space="preserve">8.90689563751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.29517078399658</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">9.30855846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50604343414307</t>
+    <t xml:space="preserve">9.50604438781738</t>
   </si>
   <si>
     <t xml:space="preserve">9.46587753295898</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">9.11107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.294358253479</t>
+    <t xml:space="preserve">8.29435729980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.31109523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34456539154053</t>
+    <t xml:space="preserve">8.34456634521484</t>
   </si>
   <si>
     <t xml:space="preserve">8.32448291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24749660491943</t>
+    <t xml:space="preserve">8.24749565124512</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514842987061</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">8.70271587371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25753879547119</t>
+    <t xml:space="preserve">8.25753974914551</t>
   </si>
   <si>
     <t xml:space="preserve">8.56548118591309</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">8.75627136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82321453094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84329891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74622917175293</t>
+    <t xml:space="preserve">8.82321548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84329795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74622821807861</t>
   </si>
   <si>
     <t xml:space="preserve">9.18471240997314</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">9.29851818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44914054870605</t>
+    <t xml:space="preserve">9.44914150238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.91105461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8441104888916</t>
+    <t xml:space="preserve">9.84411144256592</t>
   </si>
   <si>
     <t xml:space="preserve">9.52277946472168</t>
@@ -1805,55 +1805,55 @@
     <t xml:space="preserve">9.45918273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44244575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41901588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.4424467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41901683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60645866394043</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456790924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41566944122314</t>
+    <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
     <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2717399597168</t>
+    <t xml:space="preserve">9.27174091339111</t>
   </si>
   <si>
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80982685089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10438060760498</t>
+    <t xml:space="preserve">8.7127571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8098258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42905902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36211395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2483081817627</t>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42905807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3621129989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24831008911133</t>
   </si>
   <si>
     <t xml:space="preserve">9.47257137298584</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4257116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128253936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240451812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39223957061768</t>
+    <t xml:space="preserve">9.42571067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15124130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240547180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
     <t xml:space="preserve">9.33533573150635</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">9.24161434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25165557861328</t>
+    <t xml:space="preserve">9.14454555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
     <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69013977050781</t>
+    <t xml:space="preserve">9.69014072418213</t>
   </si>
   <si>
     <t xml:space="preserve">9.50939083099365</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9210958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90770721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92779064178467</t>
+    <t xml:space="preserve">9.79725074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92109680175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90770816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92778968811035</t>
   </si>
   <si>
     <t xml:space="preserve">9.77716636657715</t>
@@ -1934,19 +1934,19 @@
     <t xml:space="preserve">9.25500392913818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76296520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62573146820068</t>
+    <t xml:space="preserve">8.76296615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62573051452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.73953533172607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7730073928833</t>
+    <t xml:space="preserve">8.77300643920898</t>
   </si>
   <si>
     <t xml:space="preserve">8.75961875915527</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">9.02404689788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40562725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63993072509766</t>
+    <t xml:space="preserve">9.4056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
@@ -1988,28 +1988,28 @@
     <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02739429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9437141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99057483673096</t>
+    <t xml:space="preserve">9.02739334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94371318817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9805326461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99057579040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.87342262268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90354824066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67928600311279</t>
+    <t xml:space="preserve">8.9035472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68263339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67928504943848</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">9.8608455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8240270614624</t>
+    <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
     <t xml:space="preserve">9.81063842773438</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">9.30521202087402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15793609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16797733306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1746711730957</t>
+    <t xml:space="preserve">9.15793514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16797637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17467021942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.08764457702637</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79308986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65250873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84664630889893</t>
+    <t xml:space="preserve">8.88346576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65250778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.87677001953125</t>
@@ -2072,28 +2072,28 @@
     <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05417060852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06086730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1545877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97383975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9671459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95040893554688</t>
+    <t xml:space="preserve">9.05417156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.060866355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15458869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97383785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714496612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95040798187256</t>
   </si>
   <si>
     <t xml:space="preserve">8.90020084381104</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.829909324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40146732330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33787155151367</t>
+    <t xml:space="preserve">8.82991027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64246559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40146827697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33787250518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.28431701660156</t>
@@ -2129,82 +2129,82 @@
     <t xml:space="preserve">8.23410892486572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15377616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9897632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06005382537842</t>
+    <t xml:space="preserve">8.15377521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98976278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94624996185303</t>
+    <t xml:space="preserve">8.03327560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
     <t xml:space="preserve">7.95629119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.932861328125</t>
+    <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96633148193359</t>
+    <t xml:space="preserve">7.96633100509644</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12953186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2232551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793167114258</t>
+    <t xml:space="preserve">7.94290256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67177867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12953233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22325468063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793214797974</t>
   </si>
   <si>
     <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222461700439</t>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514543533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222414016724</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1588454246521</t>
+    <t xml:space="preserve">6.15884494781494</t>
   </si>
   <si>
     <t xml:space="preserve">5.55802345275879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57977962493896</t>
+    <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.45091247558594</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">5.27183771133423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69023704528809</t>
+    <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
     <t xml:space="preserve">5.69693183898926</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356555938721</t>
+    <t xml:space="preserve">6.49356460571289</t>
   </si>
   <si>
     <t xml:space="preserve">6.36637163162231</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">6.647536277771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56720352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35967779159546</t>
+    <t xml:space="preserve">6.56720399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3596773147583</t>
   </si>
   <si>
     <t xml:space="preserve">6.09190130233765</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">6.03834629058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17892789840698</t>
+    <t xml:space="preserve">6.17892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">6.00487422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20235967636108</t>
+    <t xml:space="preserve">6.20235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926160812378</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">6.32620477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34628772735596</t>
+    <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603935241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20905256271362</t>
+    <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826333999634</t>
@@ -2312,19 +2312,19 @@
     <t xml:space="preserve">6.08520698547363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01156806945801</t>
+    <t xml:space="preserve">6.01156759262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.89776420593262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98813772201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87433338165283</t>
+    <t xml:space="preserve">5.98813724517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05508184432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747220993042</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">5.68354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66011238098145</t>
+    <t xml:space="preserve">5.66011190414429</t>
   </si>
   <si>
     <t xml:space="preserve">5.08439445495605</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75302171707153</t>
+    <t xml:space="preserve">4.75302219390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.91368722915649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774137496948</t>
+    <t xml:space="preserve">5.08774185180664</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">5.37225294113159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74379301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044561386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89106893539429</t>
+    <t xml:space="preserve">5.74379253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
     <t xml:space="preserve">5.94127750396729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82077741622925</t>
+    <t xml:space="preserve">5.82077789306641</t>
   </si>
   <si>
     <t xml:space="preserve">5.60655736923218</t>
@@ -2390,46 +2390,46 @@
     <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20824098587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19819974899292</t>
+    <t xml:space="preserve">5.20824146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861545562744</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28522682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196237564087</t>
+    <t xml:space="preserve">5.28522634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196285247803</t>
   </si>
   <si>
     <t xml:space="preserve">5.23836517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33208703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27853202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23167085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35886430740356</t>
+    <t xml:space="preserve">5.33208751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2785325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23167133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35886478424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.32204532623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32539319992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28187894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22832441329956</t>
+    <t xml:space="preserve">5.3253927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28187942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2283239364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.04422760009766</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">4.97058963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94046545028687</t>
+    <t xml:space="preserve">4.94046497344971</t>
   </si>
   <si>
     <t xml:space="preserve">5.02079772949219</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">5.13125562667847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11451864242554</t>
+    <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
     <t xml:space="preserve">5.12790822982788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12456130981445</t>
+    <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
     <t xml:space="preserve">5.11786651611328</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1044774055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03753423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96389532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41576719284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38898944854736</t>
+    <t xml:space="preserve">5.10447788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0375337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96389484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41576766967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38898992538452</t>
   </si>
   <si>
     <t xml:space="preserve">5.48940515518188</t>
@@ -2492,19 +2492,19 @@
     <t xml:space="preserve">5.36890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32874011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57643270492554</t>
+    <t xml:space="preserve">5.32874059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961324691772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49609994888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39568424224854</t>
+    <t xml:space="preserve">5.49610042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39568471908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.36221218109131</t>
@@ -2513,76 +2513,76 @@
     <t xml:space="preserve">5.38229560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36555910110474</t>
+    <t xml:space="preserve">5.36555957794189</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3053092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27518463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60320997238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12537288665771</t>
+    <t xml:space="preserve">5.30530977249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27518510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09108877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60321044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12537336349487</t>
   </si>
   <si>
     <t xml:space="preserve">6.15215063095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244119644165</t>
+    <t xml:space="preserve">6.27934503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244215011597</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880323410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7069730758667</t>
+    <t xml:space="preserve">6.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70697259902954</t>
   </si>
   <si>
     <t xml:space="preserve">5.89441633224487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73375034332275</t>
+    <t xml:space="preserve">5.7337498664856</t>
   </si>
   <si>
     <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61325263977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48605871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48271083831787</t>
+    <t xml:space="preserve">5.61325168609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4860577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48271131515503</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65341806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040437698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.65341758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46262741088867</t>
+    <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.47266960144043</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894773483276</t>
+    <t xml:space="preserve">5.37894821166992</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">4.92372894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95385360717773</t>
+    <t xml:space="preserve">4.95385408401489</t>
   </si>
   <si>
     <t xml:space="preserve">4.88021516799927</t>
@@ -2636,52 +2636,52 @@
     <t xml:space="preserve">5.55300235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8609447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02830457687378</t>
+    <t xml:space="preserve">5.86094427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
     <t xml:space="preserve">6.09859609603882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335699081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59398174285889</t>
+    <t xml:space="preserve">6.44335746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
     <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63749408721924</t>
+    <t xml:space="preserve">6.6374945640564</t>
   </si>
   <si>
     <t xml:space="preserve">6.5872859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72117471694946</t>
+    <t xml:space="preserve">6.7211742401123</t>
   </si>
   <si>
     <t xml:space="preserve">6.67766141891479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41323232650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76134061813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10275363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383581161499</t>
+    <t xml:space="preserve">6.41323280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76134157180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10275506973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
     <t xml:space="preserve">7.19647741317749</t>
@@ -2690,46 +2690,46 @@
     <t xml:space="preserve">7.12283897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08936643600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556161880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961671829224</t>
+    <t xml:space="preserve">7.08936738967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2098650932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961624145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.05589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175680160522</t>
+    <t xml:space="preserve">7.00233888626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175727844238</t>
   </si>
   <si>
     <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944890975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07597780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98225688934326</t>
+    <t xml:space="preserve">7.10944843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07597684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9822564125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.14292192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200613021851</t>
+    <t xml:space="preserve">7.09606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200565338135</t>
   </si>
   <si>
     <t xml:space="preserve">6.96886682510376</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">7.11614370346069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01572847366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18978214263916</t>
+    <t xml:space="preserve">7.01572751998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18978309631348</t>
   </si>
   <si>
     <t xml:space="preserve">7.03581190109253</t>
@@ -2753,64 +2753,64 @@
     <t xml:space="preserve">6.90861749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08267211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15631008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25003147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366991043091</t>
+    <t xml:space="preserve">7.08267116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622760772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15630960464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2500319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32367038726807</t>
   </si>
   <si>
     <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47764205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41069746017456</t>
+    <t xml:space="preserve">7.47764110565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41069650650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47094678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56466865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51111316680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53789138793945</t>
+    <t xml:space="preserve">7.47094631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56466817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51111268997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53789091110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.61152982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61822319030762</t>
+    <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
     <t xml:space="preserve">7.75880575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113647460938</t>
+    <t xml:space="preserve">7.8525276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.1805534362793</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">8.48849487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73618793487549</t>
+    <t xml:space="preserve">8.7361888885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.41485691070557</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28766441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45502376556396</t>
+    <t xml:space="preserve">8.28766345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
     <t xml:space="preserve">8.18724727630615</t>
@@ -2852,31 +2852,31 @@
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32782936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277599334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938879013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99980449676514</t>
+    <t xml:space="preserve">8.26758098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3278284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8123607635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277647018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8993878364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99980354309082</t>
   </si>
   <si>
     <t xml:space="preserve">8.97049140930176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68009853363037</t>
+    <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
     <t xml:space="preserve">9.55290412902832</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473476409912</t>
+    <t xml:space="preserve">9.9947338104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365306854248</t>
+    <t xml:space="preserve">9.77381992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365211486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.5168981552124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039247512817</t>
+    <t xml:space="preserve">10.6039257049561</t>
   </si>
   <si>
     <t xml:space="preserve">10.4767303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6775636672974</t>
+    <t xml:space="preserve">10.677562713623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6440906524658</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1865949630737</t>
+    <t xml:space="preserve">10.186595916748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755491256714</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9052791595459</t>
+    <t xml:space="preserve">9.90528011322021</t>
   </si>
   <si>
     <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55733489990234</t>
+    <t xml:space="preserve">9.55733680725098</t>
   </si>
   <si>
     <t xml:space="preserve">9.59435176849365</t>
@@ -2963,25 +2963,25 @@
     <t xml:space="preserve">9.57954502105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578411102295</t>
+    <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.76462078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83865165710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89787578582764</t>
+    <t xml:space="preserve">9.79423427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83865261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89787673950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.97931003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98671340942383</t>
+    <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75721836090088</t>
+    <t xml:space="preserve">9.7572193145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.8534574508667</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
@@ -3005,85 +3005,85 @@
     <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72020435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60175609588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5499324798584</t>
+    <t xml:space="preserve">10.0533399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7202033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60175514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54993343353271</t>
   </si>
   <si>
     <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4018726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40927505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524417877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26121425628662</t>
+    <t xml:space="preserve">9.40187168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40927600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524513244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26121520996094</t>
   </si>
   <si>
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575008392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99655437469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34634971618652</t>
+    <t xml:space="preserve">9.10575103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99655532836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34634876251221</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37226104736328</t>
+    <t xml:space="preserve">9.37226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.4166784286499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30563259124756</t>
+    <t xml:space="preserve">9.30563163757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.17237758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24640846252441</t>
+    <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
     <t xml:space="preserve">9.20199012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17978000640869</t>
+    <t xml:space="preserve">9.17978096008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23160266876221</t>
+    <t xml:space="preserve">9.23160171508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.01691436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03912258148193</t>
+    <t xml:space="preserve">9.03912162780762</t>
   </si>
   <si>
     <t xml:space="preserve">9.15757083892822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31303596496582</t>
+    <t xml:space="preserve">9.3130350112915</t>
   </si>
   <si>
     <t xml:space="preserve">9.35745429992676</t>
@@ -3092,43 +3092,43 @@
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03171920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02431774139404</t>
+    <t xml:space="preserve">9.15016841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03172016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02431583404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.994704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80163669586182</t>
+    <t xml:space="preserve">9.09834671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99470520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8016357421875</t>
   </si>
   <si>
     <t xml:space="preserve">10.0237283706665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95709991455078</t>
+    <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60915660858154</t>
+    <t xml:space="preserve">9.60915756225586</t>
   </si>
   <si>
     <t xml:space="preserve">9.32784175872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46109676361084</t>
+    <t xml:space="preserve">9.46109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">9.52772426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885166168213</t>
+    <t xml:space="preserve">8.86885261535645</t>
   </si>
   <si>
     <t xml:space="preserve">8.75040340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92067337036133</t>
+    <t xml:space="preserve">8.92067527770996</t>
   </si>
   <si>
     <t xml:space="preserve">8.93548011779785</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261352539062</t>
+    <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">4.33078336715698</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51585960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58989000320435</t>
+    <t xml:space="preserve">4.51586008071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5898904800415</t>
   </si>
   <si>
     <t xml:space="preserve">4.62690591812134</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">4.69723463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5824875831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3122763633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10128879547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090133666992</t>
+    <t xml:space="preserve">4.58248710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31227540969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090085983276</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">4.1938271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16791677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17161798477173</t>
+    <t xml:space="preserve">4.1679162979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17161846160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.2456488609314</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">4.24935007095337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20493125915527</t>
+    <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
     <t xml:space="preserve">4.12719964981079</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018421173096</t>
+    <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233510971069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033668518066</t>
+    <t xml:space="preserve">4.46033763885498</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
@@ -3236,40 +3236,40 @@
     <t xml:space="preserve">4.15311098098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499095916748</t>
+    <t xml:space="preserve">4.10499048233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17902135848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93842172622681</t>
+    <t xml:space="preserve">4.17902088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93842244148254</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87549662590027</t>
+    <t xml:space="preserve">4.05687093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
     <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85328698158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58862781524658</t>
+    <t xml:space="preserve">3.85328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862829208374</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86068987846375</t>
+    <t xml:space="preserve">3.86069011688232</t>
   </si>
   <si>
     <t xml:space="preserve">4.07537889480591</t>
@@ -3278,28 +3278,28 @@
     <t xml:space="preserve">4.04206466674805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15681219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34558963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27526092529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9495267868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433305740356</t>
+    <t xml:space="preserve">4.15681171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34559011459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27526044845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94952654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90510821342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433258056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95322847366333</t>
+    <t xml:space="preserve">3.95322823524475</t>
   </si>
   <si>
     <t xml:space="preserve">4.05316925048828</t>
@@ -3311,22 +3311,22 @@
     <t xml:space="preserve">4.01985549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88660073280334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86439156532288</t>
+    <t xml:space="preserve">3.88660049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8643913269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73483824729919</t>
+    <t xml:space="preserve">3.73483777046204</t>
   </si>
   <si>
     <t xml:space="preserve">3.50164222717285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53310537338257</t>
+    <t xml:space="preserve">3.53310561180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716490745544</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459717750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5738217830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62009072303772</t>
+    <t xml:space="preserve">3.51459765434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57382154464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6200909614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.61638951301575</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137178421021</t>
+    <t xml:space="preserve">3.33137202262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">3.20181846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26474452018738</t>
+    <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
     <t xml:space="preserve">3.10187768936157</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">3.0130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92050290107727</t>
+    <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
     <t xml:space="preserve">2.88718914985657</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.007488489151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98342871665955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">3.00748872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98342895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8723828792572</t>
+    <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8649799823761</t>
+    <t xml:space="preserve">2.86497974395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">2.76503872871399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90569686889648</t>
+    <t xml:space="preserve">2.90569663047791</t>
   </si>
   <si>
     <t xml:space="preserve">2.86868143081665</t>
@@ -3431,43 +3431,43 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85387563705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82981562614441</t>
+    <t xml:space="preserve">2.90014433860779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85387539863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059125900269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82426333427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83721852302551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76318788528442</t>
+    <t xml:space="preserve">2.82426309585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83721876144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999210357666</t>
+    <t xml:space="preserve">2.52999186515808</t>
   </si>
   <si>
     <t xml:space="preserve">2.49852895736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6003212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56515645980835</t>
+    <t xml:space="preserve">2.60032105445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297690391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56515622138977</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44855809211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47446894645691</t>
+    <t xml:space="preserve">2.44855856895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47446918487549</t>
   </si>
   <si>
     <t xml:space="preserve">2.46706604957581</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">2.45596170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4892749786377</t>
+    <t xml:space="preserve">2.48927521705627</t>
   </si>
   <si>
     <t xml:space="preserve">2.52629041671753</t>
@@ -3503,22 +3503,22 @@
     <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2727358341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25792980194092</t>
+    <t xml:space="preserve">2.27273607254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2579300403595</t>
   </si>
   <si>
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4133939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34676671028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30790066719055</t>
+    <t xml:space="preserve">2.41339373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34676647186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30790042877197</t>
   </si>
   <si>
     <t xml:space="preserve">2.19685482978821</t>
@@ -3542,28 +3542,28 @@
     <t xml:space="preserve">2.35416960716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34121441841125</t>
+    <t xml:space="preserve">2.3412139415741</t>
   </si>
   <si>
     <t xml:space="preserve">2.25422859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26718378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28754186630249</t>
+    <t xml:space="preserve">2.26718401908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28754210472107</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458643913269</t>
+    <t xml:space="preserve">2.27458667755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607943534851</t>
+    <t xml:space="preserve">2.25607895851135</t>
   </si>
   <si>
     <t xml:space="preserve">2.22276544570923</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2912437915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24867606163025</t>
+    <t xml:space="preserve">2.29124355316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">2.21351170539856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13022708892822</t>
+    <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
     <t xml:space="preserve">2.15798878669739</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">2.08765983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13763046264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14688444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08395838737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10246562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07100296020508</t>
+    <t xml:space="preserve">2.13763022422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14688420295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0839581489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10246586799622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0710027217865</t>
   </si>
   <si>
     <t xml:space="preserve">2.07470440864563</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912250518799</t>
+    <t xml:space="preserve">2.11912274360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652587890625</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">2.01362919807434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810627937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186695098877</t>
+    <t xml:space="preserve">1.95810639858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186707019806</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132355690002</t>
+    <t xml:space="preserve">1.90132343769073</t>
   </si>
   <si>
     <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255322933197</t>
+    <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
     <t xml:space="preserve">1.91036558151245</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84953653812408</t>
+    <t xml:space="preserve">1.84953665733337</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
@@ -3671,55 +3671,55 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679875850677</t>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556956291199</t>
+    <t xml:space="preserve">1.8955694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8372061252594</t>
+    <t xml:space="preserve">1.83720624446869</t>
   </si>
   <si>
     <t xml:space="preserve">1.78541910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7615807056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.770623087883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556234836578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79199540615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85857880115509</t>
+    <t xml:space="preserve">1.76158058643341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77062296867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79199552536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311057567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.958864569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078749656677</t>
+    <t xml:space="preserve">1.95311069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95886468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078773498535</t>
   </si>
   <si>
     <t xml:space="preserve">2.03695607185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98023700714111</t>
+    <t xml:space="preserve">1.98023724555969</t>
   </si>
   <si>
     <t xml:space="preserve">2.03942227363586</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559084892273</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">2.07970118522644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0048975944519</t>
+    <t xml:space="preserve">2.00489735603333</t>
   </si>
   <si>
     <t xml:space="preserve">1.99749958515167</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">2.24204921722412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23382925987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14135217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573763847351</t>
+    <t xml:space="preserve">2.23382902145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14135241508484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573740005493</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">2.28520512580872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34480118751526</t>
+    <t xml:space="preserve">2.34480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">2.2728750705719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904033660889</t>
+    <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
     <t xml:space="preserve">2.30781030654907</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">2.34685635566711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35096645355225</t>
+    <t xml:space="preserve">2.35096621513367</t>
   </si>
   <si>
     <t xml:space="preserve">2.34274625778198</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25848937034607</t>
+    <t xml:space="preserve">2.25848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">2.22766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16190266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14546251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21944379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24615955352783</t>
+    <t xml:space="preserve">2.1619029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14546227455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21944403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24615931510925</t>
   </si>
   <si>
     <t xml:space="preserve">2.26670980453491</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">2.25437951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30986547470093</t>
+    <t xml:space="preserve">2.30986571311951</t>
   </si>
   <si>
     <t xml:space="preserve">2.3550763130188</t>
@@ -3848,31 +3848,31 @@
     <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5276997089386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55236053466797</t>
+    <t xml:space="preserve">2.52770018577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55236029624939</t>
   </si>
   <si>
     <t xml:space="preserve">2.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54003000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45988368988037</t>
+    <t xml:space="preserve">2.54003024101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45988345146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54208493232727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51125955581665</t>
+    <t xml:space="preserve">2.52153468132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54208517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51125979423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.43933320045471</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920438766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5585253238678</t>
+    <t xml:space="preserve">2.50920462608337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55852556228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.55647039413452</t>
@@ -3917,13 +3917,13 @@
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250708580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66744256019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67155289649963</t>
+    <t xml:space="preserve">2.63250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674427986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67155265808105</t>
   </si>
   <si>
     <t xml:space="preserve">2.68799304962158</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74142408370972</t>
+    <t xml:space="preserve">2.7414243221283</t>
   </si>
   <si>
     <t xml:space="preserve">2.70443344116211</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">2.78869009017944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77019453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703886032104</t>
+    <t xml:space="preserve">2.77019476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703909873962</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">2.60784649848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62634181976318</t>
+    <t xml:space="preserve">2.6263415813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.70648837089539</t>
@@ -3983,22 +3983,22 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428689002991</t>
+    <t xml:space="preserve">2.62428712844849</t>
   </si>
   <si>
     <t xml:space="preserve">2.59757137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60579133033752</t>
+    <t xml:space="preserve">2.6057915687561</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524107933044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58935117721558</t>
+    <t xml:space="preserve">2.58524084091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58935141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">2.69621324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79485535621643</t>
+    <t xml:space="preserve">2.79485511779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.86678171157837</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97158861160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9140477180481</t>
+    <t xml:space="preserve">2.97158885002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91404747962952</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">2.99419403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99830436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89760756492615</t>
+    <t xml:space="preserve">2.99830412864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89760732650757</t>
   </si>
   <si>
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773590087891</t>
+    <t xml:space="preserve">2.82773566246033</t>
   </si>
   <si>
     <t xml:space="preserve">2.74553418159485</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">2.61606669425964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68388295173645</t>
+    <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4070,25 +4070,25 @@
     <t xml:space="preserve">2.79896521568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79074501991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99213910102844</t>
+    <t xml:space="preserve">2.7907452583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99213933944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93459796905518</t>
+    <t xml:space="preserve">2.9345977306366</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77224969863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78457999229431</t>
+    <t xml:space="preserve">2.7722499370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78457975387573</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4097,25 +4097,25 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89555215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10927629470825</t>
+    <t xml:space="preserve">2.82979083061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89555239677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10927653312683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582752227783</t>
+    <t xml:space="preserve">2.90582728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.9633686542511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93665313720703</t>
+    <t xml:space="preserve">2.93665289878845</t>
   </si>
   <si>
     <t xml:space="preserve">2.89966225624084</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86883664131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82568073272705</t>
+    <t xml:space="preserve">2.86883687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82568097114563</t>
   </si>
   <si>
     <t xml:space="preserve">2.92226767539978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88733196258545</t>
+    <t xml:space="preserve">2.88733220100403</t>
   </si>
   <si>
     <t xml:space="preserve">2.8893871307373</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98186421394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0126895904541</t>
+    <t xml:space="preserve">3.05995535850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9818639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01268935203552</t>
   </si>
   <si>
     <t xml:space="preserve">2.94281816482544</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">2.90442943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92211222648621</t>
+    <t xml:space="preserve">2.92211246490479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98621320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04147267341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10336303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136584281921</t>
+    <t xml:space="preserve">3.04147243499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1033627986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136608123779</t>
   </si>
   <si>
     <t xml:space="preserve">3.11883544921875</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">3.07241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09452128410339</t>
+    <t xml:space="preserve">3.09452152252197</t>
   </si>
   <si>
     <t xml:space="preserve">3.07020735740662</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.97958207130432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97074031829834</t>
+    <t xml:space="preserve">2.97074055671692</t>
   </si>
   <si>
     <t xml:space="preserve">2.91548109054565</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.93316435813904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92874360084534</t>
+    <t xml:space="preserve">2.92874336242676</t>
   </si>
   <si>
     <t xml:space="preserve">2.90221905708313</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">2.90000867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87790489196777</t>
+    <t xml:space="preserve">2.87790513038635</t>
   </si>
   <si>
     <t xml:space="preserve">2.86464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83369731903076</t>
+    <t xml:space="preserve">2.83369755744934</t>
   </si>
   <si>
     <t xml:space="preserve">2.81822490692139</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">2.69002318382263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60160827636719</t>
+    <t xml:space="preserve">2.60160851478577</t>
   </si>
   <si>
     <t xml:space="preserve">2.66791939735413</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">2.68560242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62813282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65023636817932</t>
+    <t xml:space="preserve">2.62813305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6502366065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.60381865501404</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.5551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47340679168701</t>
+    <t xml:space="preserve">2.47340655326843</t>
   </si>
   <si>
     <t xml:space="preserve">2.44909262657166</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">2.47119641304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47782731056213</t>
+    <t xml:space="preserve">2.47782754898071</t>
   </si>
   <si>
     <t xml:space="preserve">2.46014451980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624245643616</t>
+    <t xml:space="preserve">2.56624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">2.55961132049561</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.54855942726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50877261161804</t>
+    <t xml:space="preserve">2.50877285003662</t>
   </si>
   <si>
     <t xml:space="preserve">2.53087639808655</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">2.32531189918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24529647827148</t>
+    <t xml:space="preserve">2.24529623985291</t>
   </si>
   <si>
     <t xml:space="preserve">2.19932055473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15422916412354</t>
+    <t xml:space="preserve">2.15422892570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.14715576171875</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">2.17633247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29746127128601</t>
+    <t xml:space="preserve">2.29746103286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38720226287842</t>
@@ -4367,40 +4367,40 @@
     <t xml:space="preserve">2.33813214302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51894044876099</t>
+    <t xml:space="preserve">2.51894021034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.46854400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42345237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51319336891174</t>
+    <t xml:space="preserve">2.42345213890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51319360733032</t>
   </si>
   <si>
     <t xml:space="preserve">2.57287359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52026677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56712651252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5507698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53794956207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54723310470581</t>
+    <t xml:space="preserve">2.52026653289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56712675094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55076956748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53794980049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54723334312439</t>
   </si>
   <si>
     <t xml:space="preserve">2.70461177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78109049797058</t>
+    <t xml:space="preserve">2.78109073638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.75854468345642</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">2.79302644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75633454322815</t>
+    <t xml:space="preserve">2.75633430480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.77357530593872</t>
@@ -4436,13 +4436,13 @@
     <t xml:space="preserve">2.91327095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84253907203674</t>
+    <t xml:space="preserve">2.84253883361816</t>
   </si>
   <si>
     <t xml:space="preserve">2.93935322761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94112157821655</t>
+    <t xml:space="preserve">2.94112133979797</t>
   </si>
   <si>
     <t xml:space="preserve">2.92343854904175</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">2.94554233551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785930633545</t>
+    <t xml:space="preserve">2.92785954475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.93537449836731</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">2.89249348640442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88851475715637</t>
+    <t xml:space="preserve">2.88851451873779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93006944656372</t>
@@ -4475,25 +4475,25 @@
     <t xml:space="preserve">2.88011527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92741751670837</t>
+    <t xml:space="preserve">2.92741727828979</t>
   </si>
   <si>
     <t xml:space="preserve">3.02378964424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03926205635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03086256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96189904212952</t>
+    <t xml:space="preserve">3.03926229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03086280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96189880371094</t>
   </si>
   <si>
     <t xml:space="preserve">2.93493247032166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89824056625366</t>
+    <t xml:space="preserve">2.89824032783508</t>
   </si>
   <si>
     <t xml:space="preserve">2.91724944114685</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">2.9106183052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91769170761108</t>
+    <t xml:space="preserve">2.9176914691925</t>
   </si>
   <si>
     <t xml:space="preserve">2.9256489276886</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">2.98444485664368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02246308326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00168561935425</t>
+    <t xml:space="preserve">3.02246332168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00168585777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.95438385009766</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">2.73865151405334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67101383209229</t>
+    <t xml:space="preserve">2.67101407051086</t>
   </si>
   <si>
     <t xml:space="preserve">2.68737077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6608464717865</t>
+    <t xml:space="preserve">2.66084623336792</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869686126709</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.64537382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72052645683289</t>
+    <t xml:space="preserve">2.72052621841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70947456359863</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">2.62327003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5870201587677</t>
+    <t xml:space="preserve">2.58701992034912</t>
   </si>
   <si>
     <t xml:space="preserve">2.60426068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57729434967041</t>
+    <t xml:space="preserve">2.57729411125183</t>
   </si>
   <si>
     <t xml:space="preserve">2.58171510696411</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">2.58083081245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59497714042664</t>
+    <t xml:space="preserve">2.59497737884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.65288901329041</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">2.69488620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69223356246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6413950920105</t>
+    <t xml:space="preserve">2.69223380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64139485359192</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480954170227</t>
@@ -4622,19 +4622,19 @@
     <t xml:space="preserve">2.70549583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7116847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67985558509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85049605369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342312812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93183779716492</t>
+    <t xml:space="preserve">2.71168494224548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67985534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85049629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342336654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9318380355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.91946005821228</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">2.94952082633972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878918647766</t>
+    <t xml:space="preserve">2.87878894805908</t>
   </si>
   <si>
     <t xml:space="preserve">3.13872885704041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">3.30671715736389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42519330978394</t>
+    <t xml:space="preserve">3.42519307136536</t>
   </si>
   <si>
     <t xml:space="preserve">3.41988825798035</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">3.34561967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33501005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43933963775635</t>
+    <t xml:space="preserve">3.33500981330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43933939933777</t>
   </si>
   <si>
     <t xml:space="preserve">3.36507105827332</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">3.29787564277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30848550796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32793664932251</t>
+    <t xml:space="preserve">3.30848574638367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32793688774109</t>
   </si>
   <si>
     <t xml:space="preserve">3.41458320617676</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">3.41104674339294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57019376754761</t>
+    <t xml:space="preserve">3.49592518806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57019352912903</t>
   </si>
   <si>
     <t xml:space="preserve">3.57372999191284</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">3.50123000144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5259861946106</t>
+    <t xml:space="preserve">3.50653481483459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52598595619202</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616945266724</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">3.61793756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59848642349243</t>
+    <t xml:space="preserve">3.59848666191101</t>
   </si>
   <si>
     <t xml:space="preserve">3.63031578063965</t>
@@ -4748,28 +4748,28 @@
     <t xml:space="preserve">3.7045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77708411216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82129192352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84074306488037</t>
+    <t xml:space="preserve">3.77708435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84074282646179</t>
   </si>
   <si>
     <t xml:space="preserve">3.84781646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85488939285278</t>
+    <t xml:space="preserve">3.85488963127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87610912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8584258556366</t>
+    <t xml:space="preserve">3.75232815742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85842609405518</t>
   </si>
   <si>
     <t xml:space="preserve">3.65860843658447</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">3.46409559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57903480529785</t>
+    <t xml:space="preserve">3.57903504371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.52775454521179</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">3.4941565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52952289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62324237823486</t>
+    <t xml:space="preserve">3.52952265739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62324261665344</t>
   </si>
   <si>
     <t xml:space="preserve">3.61440086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6869010925293</t>
+    <t xml:space="preserve">3.68690133094788</t>
   </si>
   <si>
     <t xml:space="preserve">3.65684032440186</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">3.6957426071167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7452552318573</t>
+    <t xml:space="preserve">3.74525499343872</t>
   </si>
   <si>
     <t xml:space="preserve">3.75056004524231</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">3.80714583396912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05824422836304</t>
+    <t xml:space="preserve">4.20501232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05824375152588</t>
   </si>
   <si>
     <t xml:space="preserve">4.09184122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1201343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16787815093994</t>
+    <t xml:space="preserve">4.12013387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1678786277771</t>
   </si>
   <si>
     <t xml:space="preserve">4.07592678070068</t>
@@ -71527,7 +71527,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6912615741</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>207072</v>
@@ -71548,6 +71548,32 @@
         <v>1873</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6913078704</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>400096</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>4.07200002670288</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>3.99000000953674</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>4.0460000038147</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1881">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356548309326</t>
+    <t xml:space="preserve">12.2356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956901550293</t>
+    <t xml:space="preserve">12.195689201355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097299575806</t>
+    <t xml:space="preserve">11.4097318649292</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.076696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.136643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302536010742</t>
+    <t xml:space="preserve">11.0766973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1366424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302526473999</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770582199097</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">10.3107204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2907390594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65797328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2507734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7370042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3906488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239511489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438451766968</t>
+    <t xml:space="preserve">10.2907381057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2507743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7370023727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3906478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
     <t xml:space="preserve">10.257435798645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2707557678223</t>
+    <t xml:space="preserve">10.2707567214966</t>
   </si>
   <si>
     <t xml:space="preserve">10.4838972091675</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">10.297399520874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1042404174805</t>
+    <t xml:space="preserve">10.1042394638062</t>
   </si>
   <si>
     <t xml:space="preserve">10.8702163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7170209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77786636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91107940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54474258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120685577393</t>
+    <t xml:space="preserve">10.7170219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77786731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9110803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54474353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4639167785645</t>
+    <t xml:space="preserve">10.4639158248901</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171102523804</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436500549316</t>
+    <t xml:space="preserve">9.96436595916748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9434852600098</t>
+    <t xml:space="preserve">10.7236814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9434843063354</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363737106323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3431243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6495141983032</t>
+    <t xml:space="preserve">11.3431253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0624780654907</t>
+    <t xml:space="preserve">12.0624771118164</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627468109131</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">12.4554576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.342227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4621171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019926071167</t>
+    <t xml:space="preserve">12.3422269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4621162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019897460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823692321777</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9159412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1890306472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.496319770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0633764266968</t>
+    <t xml:space="preserve">11.9159421920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1890296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4963188171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0633773803711</t>
   </si>
   <si>
     <t xml:space="preserve">11.6561756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9559078216553</t>
+    <t xml:space="preserve">11.9559059143066</t>
   </si>
   <si>
     <t xml:space="preserve">12.2689580917358</t>
@@ -236,37 +236,37 @@
     <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1814708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882215499878</t>
+    <t xml:space="preserve">12.9350252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1015434265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.16148853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.361307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347536087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882205963135</t>
   </si>
   <si>
     <t xml:space="preserve">12.981650352478</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">12.6885795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620279312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8817386627197</t>
+    <t xml:space="preserve">12.5620288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8817405700684</t>
   </si>
   <si>
     <t xml:space="preserve">12.8617582321167</t>
@@ -287,58 +287,58 @@
     <t xml:space="preserve">12.8884010314941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0482568740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.375527381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488874435425</t>
+    <t xml:space="preserve">13.0482559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488864898682</t>
   </si>
   <si>
     <t xml:space="preserve">12.7218837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7685079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887948989868</t>
+    <t xml:space="preserve">12.7685089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159873962402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6230974197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226831436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620157241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553218841553</t>
+    <t xml:space="preserve">13.6230983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749891281128</t>
+    <t xml:space="preserve">13.2749900817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156099319458</t>
+    <t xml:space="preserve">12.659104347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620553970337</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">11.7218885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0766916275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524095535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487054824829</t>
+    <t xml:space="preserve">12.0766925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487064361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">10.4834251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177295684814</t>
+    <t xml:space="preserve">10.7177305221558</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0482892990112</t>
+    <t xml:space="preserve">10.0482912063599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7445058822632</t>
+    <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
     <t xml:space="preserve">11.1193933486938</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2599754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0189762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0122833251953</t>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1260890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0189771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0122842788696</t>
   </si>
   <si>
     <t xml:space="preserve">10.811450958252</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">10.9252548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783941268921</t>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">10.0616779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.175482749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88762378692627</t>
+    <t xml:space="preserve">10.1754837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.06421375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93032550811768</t>
+    <t xml:space="preserve">8.93032455444336</t>
   </si>
   <si>
     <t xml:space="preserve">8.67593860626221</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">9.20479583740234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37215518951416</t>
+    <t xml:space="preserve">9.37215423583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33868312835693</t>
+    <t xml:space="preserve">9.33868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.23826789855957</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">9.31860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115787506104</t>
+    <t xml:space="preserve">9.13115882873535</t>
   </si>
   <si>
     <t xml:space="preserve">9.37884998321533</t>
@@ -500,37 +500,37 @@
     <t xml:space="preserve">9.19140720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2315731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6332368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390239715576</t>
+    <t xml:space="preserve">9.23157405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.55959892272949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43909931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.51273822784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265575408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.53951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82737445831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76043033599854</t>
+    <t xml:space="preserve">9.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76043128967285</t>
   </si>
   <si>
     <t xml:space="preserve">9.78720760345459</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">9.87423515319824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67340469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760334014893</t>
+    <t xml:space="preserve">9.6734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08429718017578</t>
+    <t xml:space="preserve">9.07090759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
     <t xml:space="preserve">9.31190586090088</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">9.17801856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35207366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3654613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3855447769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24496269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03743553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70941066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72279834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007617950439</t>
+    <t xml:space="preserve">9.35207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36546039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38554573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24496173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03743648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72279930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007522583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957656860352</t>
+    <t xml:space="preserve">8.74957752227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304862976074</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">8.66924381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3345251083374</t>
+    <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
     <t xml:space="preserve">8.20063591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1002197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1203031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574939727783</t>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12030410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
@@ -626,43 +626,43 @@
     <t xml:space="preserve">7.86591672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84583330154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63161277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491846084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508388519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74541759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69186210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433637619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6450023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.651695728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516778945923</t>
+    <t xml:space="preserve">7.84583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6316123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508436203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74541664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71194553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516731262207</t>
   </si>
   <si>
     <t xml:space="preserve">7.9596381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12699890136719</t>
+    <t xml:space="preserve">8.12699794769287</t>
   </si>
   <si>
     <t xml:space="preserve">8.38138484954834</t>
@@ -671,52 +671,52 @@
     <t xml:space="preserve">8.92363166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2114896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963598251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1168584823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9294147491455</t>
+    <t xml:space="preserve">9.21149063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9963579177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1168575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9294157028198</t>
   </si>
   <si>
     <t xml:space="preserve">11.8691654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0499153137207</t>
+    <t xml:space="preserve">12.0499143600464</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615627288818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2833061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967344284058</t>
+    <t xml:space="preserve">15.2833099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971506118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569856643677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975677490234</t>
+    <t xml:space="preserve">13.8975687026978</t>
   </si>
   <si>
     <t xml:space="preserve">13.7235145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8908729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578161239624</t>
+    <t xml:space="preserve">13.8908720016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
   </si>
   <si>
     <t xml:space="preserve">13.7904577255249</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">14.6004800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582342147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712066650391</t>
+    <t xml:space="preserve">14.0180673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712076187134</t>
   </si>
   <si>
     <t xml:space="preserve">14.0917043685913</t>
@@ -740,52 +740,52 @@
     <t xml:space="preserve">14.3126201629639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2858438491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1385669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251783370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415170669556</t>
+    <t xml:space="preserve">14.2858428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1385679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415180206299</t>
   </si>
   <si>
     <t xml:space="preserve">13.1544895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.254903793335</t>
+    <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.2080450057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9268798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528247833252</t>
+    <t xml:space="preserve">12.9268789291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528257369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.8264646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9737415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611833572388</t>
+    <t xml:space="preserve">12.9737405776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611843109131</t>
   </si>
   <si>
     <t xml:space="preserve">13.0540733337402</t>
@@ -794,43 +794,43 @@
     <t xml:space="preserve">12.9134912490845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2147397994995</t>
+    <t xml:space="preserve">13.2147417068481</t>
   </si>
   <si>
     <t xml:space="preserve">13.1879625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3419342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181266784668</t>
+    <t xml:space="preserve">13.3419332504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812677383423</t>
   </si>
   <si>
     <t xml:space="preserve">13.0339908599854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8599348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072135925293</t>
+    <t xml:space="preserve">12.8599367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871282577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.007212638855</t>
   </si>
   <si>
     <t xml:space="preserve">13.0473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0206022262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9201850891113</t>
+    <t xml:space="preserve">13.0206031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754043579102</t>
+    <t xml:space="preserve">13.3754062652588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4758205413818</t>
@@ -839,46 +839,46 @@
     <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2214336395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1745719909668</t>
+    <t xml:space="preserve">13.2214326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1745738983154</t>
   </si>
   <si>
     <t xml:space="preserve">13.0406856536865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8666305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8867149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.933575630188</t>
+    <t xml:space="preserve">12.8666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8867130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
     <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9001026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536581039429</t>
+    <t xml:space="preserve">12.9001035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536590576172</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532419204712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858835220337</t>
+    <t xml:space="preserve">12.819769859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858825683594</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3109951019287</t>
+    <t xml:space="preserve">12.3109970092773</t>
   </si>
   <si>
     <t xml:space="preserve">12.3310785293579</t>
@@ -887,31 +887,31 @@
     <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2708301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1570243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6750288009644</t>
+    <t xml:space="preserve">12.2708292007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1570253372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.67502784729</t>
   </si>
   <si>
     <t xml:space="preserve">11.8624706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1771087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1436367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800210952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.946964263916</t>
+    <t xml:space="preserve">12.1771078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862997055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800191879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9469633102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.5653839111328</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">12.1637191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3043012619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913288116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.558690071106</t>
+    <t xml:space="preserve">12.3043003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.558687210083</t>
   </si>
   <si>
     <t xml:space="preserve">12.4649686813354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6189384460449</t>
+    <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971921920776</t>
+    <t xml:space="preserve">12.1971912384033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1034698486328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0900812149048</t>
+    <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0633039474487</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">12.5519933700562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6724948883057</t>
+    <t xml:space="preserve">12.6724939346313</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176898956299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8089160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813064575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6147785186768</t>
+    <t xml:space="preserve">11.8089170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813074111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6147775650024</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076694488525</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">11.6549453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880012512207</t>
+    <t xml:space="preserve">11.5880002975464</t>
   </si>
   <si>
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817235946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942798614502</t>
+    <t xml:space="preserve">11.6817226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.5210561752319</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.661639213562</t>
+    <t xml:space="preserve">11.6616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6348609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7687501907349</t>
+    <t xml:space="preserve">11.7687492370605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7018060684204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4474191665649</t>
+    <t xml:space="preserve">11.4474201202393</t>
   </si>
   <si>
     <t xml:space="preserve">11.3804750442505</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">10.7779788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7043409347534</t>
+    <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7980613708496</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461715698242</t>
+    <t xml:space="preserve">11.1461706161499</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">11.1327810287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528663635254</t>
+    <t xml:space="preserve">11.0591440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528654098511</t>
   </si>
   <si>
     <t xml:space="preserve">11.0993099212646</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4206399917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5411405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5679187774658</t>
+    <t xml:space="preserve">11.4206409454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5411396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5679178237915</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">11.4541139602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336143493652</t>
+    <t xml:space="preserve">11.3336133956909</t>
   </si>
   <si>
     <t xml:space="preserve">11.3536968231201</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">11.1595602035522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0524501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721155166626</t>
+    <t xml:space="preserve">11.0524482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897047042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1620950698853</t>
+    <t xml:space="preserve">10.3897037506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.2156505584717</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">10.3361482620239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625112533569</t>
+    <t xml:space="preserve">10.4901208877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3428430557251</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">10.3562316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076309204102</t>
+    <t xml:space="preserve">9.84076404571533</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80729103088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68679332733154</t>
+    <t xml:space="preserve">9.80729007720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74704265594482</t>
+    <t xml:space="preserve">9.72026443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5235910415649</t>
+    <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">10.7110357284546</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6641750335693</t>
+    <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
     <t xml:space="preserve">10.3763151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1888723373413</t>
+    <t xml:space="preserve">10.188871383667</t>
   </si>
   <si>
     <t xml:space="preserve">10.275899887085</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">10.5570650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5102024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.316065788269</t>
+    <t xml:space="preserve">10.5102033615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3160648345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.2089557647705</t>
@@ -1220,49 +1220,49 @@
     <t xml:space="preserve">9.6533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52612686157227</t>
+    <t xml:space="preserve">9.52612590789795</t>
   </si>
   <si>
     <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8474588394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959833145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7712841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5972309112549</t>
+    <t xml:space="preserve">9.83406829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5436744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7712850570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5972299575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.8583116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855060577393</t>
+    <t xml:space="preserve">10.9855051040649</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587278366089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7311191558838</t>
+    <t xml:space="preserve">10.7311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">10.82483959198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725326538086</t>
+    <t xml:space="preserve">10.9654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725336074829</t>
   </si>
   <si>
     <t xml:space="preserve">10.9988946914673</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">11.0926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796436309814</t>
+    <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">10.9051733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8917846679688</t>
+    <t xml:space="preserve">10.8917837142944</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0390596389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7277708053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.463342666626</t>
+    <t xml:space="preserve">11.0390605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7277717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4633417129517</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871887207031</t>
+    <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">10.3696212768555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135498046875</t>
+    <t xml:space="preserve">10.5135507583618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6407442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106195449829</t>
+    <t xml:space="preserve">10.8616590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6407432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106185913086</t>
   </si>
   <si>
     <t xml:space="preserve">10.5503702163696</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6139650344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6240081787109</t>
+    <t xml:space="preserve">10.6139659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6240072250366</t>
   </si>
   <si>
     <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1729488372803</t>
+    <t xml:space="preserve">11.172947883606</t>
   </si>
   <si>
     <t xml:space="preserve">10.9821586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269403457642</t>
+    <t xml:space="preserve">10.5269393920898</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261070251465</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394966125488</t>
+    <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629274368286</t>
@@ -1382,64 +1382,64 @@
     <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0349016189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0951490402222</t>
+    <t xml:space="preserve">9.94452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0349006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.9788103103638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0357141494751</t>
+    <t xml:space="preserve">11.1060037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0357131958008</t>
   </si>
   <si>
     <t xml:space="preserve">11.1762962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8717002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.868353843689</t>
+    <t xml:space="preserve">10.8717012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8683528900146</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0223255157471</t>
+    <t xml:space="preserve">11.0223245620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.9553804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0825748443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.952033996582</t>
+    <t xml:space="preserve">11.0256719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.082573890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9520330429077</t>
   </si>
   <si>
     <t xml:space="preserve">11.0290193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0758790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.28675365448</t>
+    <t xml:space="preserve">11.0758800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352970123291</t>
+    <t xml:space="preserve">10.9352960586548</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">10.2457752227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683736801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74369621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847599029541</t>
+    <t xml:space="preserve">10.0683727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74369525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847503662109</t>
   </si>
   <si>
     <t xml:space="preserve">9.34537792205811</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48596000671387</t>
+    <t xml:space="preserve">9.57633590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48596096038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.58637619018555</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54286289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57298755645752</t>
+    <t xml:space="preserve">9.54286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57298851013184</t>
   </si>
   <si>
     <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5026969909668</t>
+    <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.47926616668701</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62319469451904</t>
+    <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">8.83660411834717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60564804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350700378418</t>
+    <t xml:space="preserve">8.60564708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949409484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350605010986</t>
   </si>
   <si>
     <t xml:space="preserve">9.14119911193848</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487926483154</t>
+    <t xml:space="preserve">9.22487831115723</t>
   </si>
   <si>
     <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2148380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13785076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45583629608154</t>
+    <t xml:space="preserve">9.21483707427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13785171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">9.61315441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691799163818</t>
+    <t xml:space="preserve">9.71691703796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54621028900146</t>
+    <t xml:space="preserve">9.54621124267578</t>
   </si>
   <si>
     <t xml:space="preserve">9.31525325775146</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">9.26504516601562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647945404053</t>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647850036621</t>
   </si>
   <si>
     <t xml:space="preserve">8.89015865325928</t>
@@ -1586,34 +1586,34 @@
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85334014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338138580322</t>
+    <t xml:space="preserve">8.85333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338043212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92028331756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88011837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82656192779541</t>
+    <t xml:space="preserve">8.92028427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88011741638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29770469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27427387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24080276489258</t>
+    <t xml:space="preserve">8.29770565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2742748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24080371856689</t>
   </si>
   <si>
     <t xml:space="preserve">8.25084400177002</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175884246826</t>
+    <t xml:space="preserve">8.47175788879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.53870296478271</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">8.78639602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71945095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77635478973389</t>
+    <t xml:space="preserve">8.71945190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77635383605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.16462993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00731086730957</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01400470733643</t>
+    <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
     <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22822666168213</t>
+    <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.94706153869629</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">9.01735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12781047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03408908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66589546203613</t>
+    <t xml:space="preserve">9.12780952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03408813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84999179840088</t>
+    <t xml:space="preserve">8.84999370574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
@@ -1697,16 +1697,16 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7529239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90689563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951717376709</t>
+    <t xml:space="preserve">8.62907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75292301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90689468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29516983032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855941772461</t>
@@ -1718,31 +1718,31 @@
     <t xml:space="preserve">9.46587753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11107349395752</t>
+    <t xml:space="preserve">9.12111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11107444763184</t>
   </si>
   <si>
     <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31109428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34456634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32448196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49184226989746</t>
+    <t xml:space="preserve">8.3110933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34456539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32448291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.93367290496826</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">9.23492050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70271587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25753974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56548023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
+    <t xml:space="preserve">8.70271682739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25753879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56548118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5018835067749</t>
   </si>
   <si>
     <t xml:space="preserve">8.75627136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82321643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84329795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74622821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18471240997314</t>
+    <t xml:space="preserve">8.82321548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74622917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18471336364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.42236328125</t>
@@ -1790,100 +1790,100 @@
     <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91105461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84411144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52277946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45918273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4424467086792</t>
+    <t xml:space="preserve">9.44914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91105556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.522780418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45918369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44244575500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60645961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95456886291504</t>
+    <t xml:space="preserve">9.60646057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95456790924072</t>
   </si>
   <si>
     <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35876655578613</t>
+    <t xml:space="preserve">9.35876750946045</t>
   </si>
   <si>
     <t xml:space="preserve">9.27174091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54874420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7127571105957</t>
+    <t xml:space="preserve">8.54874515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71275901794434</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10437965393066</t>
+    <t xml:space="preserve">9.10438060760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42905807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3621129989624</t>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42905902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">9.24831008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47257041931152</t>
+    <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4257116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240547180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39223766326904</t>
+    <t xml:space="preserve">9.42571067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1512393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128253936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240451812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
     <t xml:space="preserve">9.33533573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24161434173584</t>
+    <t xml:space="preserve">9.24161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.14454555511475</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">9.79724979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9210958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90770816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92779064178467</t>
+    <t xml:space="preserve">9.92109680175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90770721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92779159545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.77716636657715</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">9.62989044189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38889217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62573051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
+    <t xml:space="preserve">9.38889122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.77300643920898</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">8.75961875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02404689788818</t>
+    <t xml:space="preserve">9.02404594421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.40562725067139</t>
@@ -1976,31 +1976,31 @@
     <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60311222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35541915893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20144939422607</t>
+    <t xml:space="preserve">9.60311317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35542011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20144844055176</t>
   </si>
   <si>
     <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02739429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94371318817139</t>
+    <t xml:space="preserve">9.02739524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9437141418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.9805326461792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99057579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87342262268066</t>
+    <t xml:space="preserve">8.99057483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">9.86084651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82402801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81063842773438</t>
+    <t xml:space="preserve">9.8240270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81063938140869</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068061828613</t>
@@ -2030,52 +2030,52 @@
     <t xml:space="preserve">9.30521106719971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15793609619141</t>
+    <t xml:space="preserve">9.15793514251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.16797637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17467021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08764457702637</t>
+    <t xml:space="preserve">9.1746711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08764362335205</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09099102020264</t>
+    <t xml:space="preserve">9.09099006652832</t>
   </si>
   <si>
     <t xml:space="preserve">8.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65250778198242</t>
+    <t xml:space="preserve">8.74288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79308986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677001953125</t>
+    <t xml:space="preserve">8.87677097320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681221008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00396347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05417251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.060866355896</t>
+    <t xml:space="preserve">9.0039644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05417156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06086540222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.15458869934082</t>
@@ -2084,40 +2084,40 @@
     <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08094787597656</t>
+    <t xml:space="preserve">9.11776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0809497833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95040798187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90020084381104</t>
+    <t xml:space="preserve">8.95040893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92697811126709</t>
+    <t xml:space="preserve">8.99726867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82991027832031</t>
+    <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
     <t xml:space="preserve">8.64246559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40146827697754</t>
+    <t xml:space="preserve">8.40146923065186</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377616882324</t>
+    <t xml:space="preserve">8.23410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377521514893</t>
   </si>
   <si>
     <t xml:space="preserve">7.98976230621338</t>
@@ -2138,76 +2138,76 @@
     <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01654148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03327560424805</t>
+    <t xml:space="preserve">8.01654052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95629119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93286037445068</t>
+    <t xml:space="preserve">7.95629024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93286085128784</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96633148193359</t>
+    <t xml:space="preserve">7.96633243560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
+    <t xml:space="preserve">7.94290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12953233718872</t>
+    <t xml:space="preserve">7.12953281402588</t>
   </si>
   <si>
     <t xml:space="preserve">7.22325468063354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54793214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300487518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07263040542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786951065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256633758545</t>
+    <t xml:space="preserve">7.54793167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300439834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07262945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514638900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256681442261</t>
   </si>
   <si>
     <t xml:space="preserve">6.15884494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55802345275879</t>
+    <t xml:space="preserve">5.55802297592163</t>
   </si>
   <si>
     <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45091199874878</t>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2219,49 +2219,49 @@
     <t xml:space="preserve">4.74800109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05928993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183771133423</t>
+    <t xml:space="preserve">5.05929040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183723449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693231582642</t>
+    <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311758041382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05842924118042</t>
+    <t xml:space="preserve">6.05842876434326</t>
   </si>
   <si>
     <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29440689086914</t>
+    <t xml:space="preserve">6.2944073677063</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356460571289</t>
+    <t xml:space="preserve">6.49356412887573</t>
   </si>
   <si>
     <t xml:space="preserve">6.36637163162231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61741209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753675460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720447540283</t>
+    <t xml:space="preserve">6.6174111366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53038501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720399856567</t>
   </si>
   <si>
     <t xml:space="preserve">6.54377317428589</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834581375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892837524414</t>
+    <t xml:space="preserve">6.03834629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892789840698</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628820419312</t>
+    <t xml:space="preserve">6.32620429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628772735596</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
@@ -2306,37 +2306,37 @@
     <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08520698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813724517822</t>
+    <t xml:space="preserve">6.01826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813772201538</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433338165283</t>
+    <t xml:space="preserve">5.87433290481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68354225158691</t>
+    <t xml:space="preserve">5.68354320526123</t>
   </si>
   <si>
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08439445495605</t>
+    <t xml:space="preserve">5.0843939781189</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91368722915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08774137496948</t>
+    <t xml:space="preserve">4.91368770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08774185180664</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
@@ -2357,46 +2357,46 @@
     <t xml:space="preserve">5.18815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34212827682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15803289413452</t>
+    <t xml:space="preserve">5.34212923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15803241729736</t>
   </si>
   <si>
     <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37225294113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74379301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74044561386108</t>
+    <t xml:space="preserve">5.37225341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74379205703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74044513702393</t>
   </si>
   <si>
     <t xml:space="preserve">5.89106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94127750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82077789306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60655689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2952675819397</t>
+    <t xml:space="preserve">5.94127798080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82077836990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60655736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19819927215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29861545562744</t>
+    <t xml:space="preserve">5.1981987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29861497879028</t>
   </si>
   <si>
     <t xml:space="preserve">5.28522634506226</t>
@@ -2405,37 +2405,37 @@
     <t xml:space="preserve">5.30196237564087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23836517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33208751678467</t>
+    <t xml:space="preserve">5.238365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
     <t xml:space="preserve">5.2785325050354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23167133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35886478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204532623291</t>
+    <t xml:space="preserve">5.23167085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35886526107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204580307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.3253927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28187942504883</t>
+    <t xml:space="preserve">5.28187894821167</t>
   </si>
   <si>
     <t xml:space="preserve">5.2283239364624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04422760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97059011459351</t>
+    <t xml:space="preserve">5.04422807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97058963775635</t>
   </si>
   <si>
     <t xml:space="preserve">4.94046497344971</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104753494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13125562667847</t>
+    <t xml:space="preserve">5.08104705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13125514984131</t>
   </si>
   <si>
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790775299072</t>
+    <t xml:space="preserve">5.12790822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">5.11786651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12121391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092287063599</t>
+    <t xml:space="preserve">5.12121343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092239379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.98063135147095</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">5.0375337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96389532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41576719284058</t>
+    <t xml:space="preserve">4.96389579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41576671600342</t>
   </si>
   <si>
     <t xml:space="preserve">5.38898944854736</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">5.48940515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36890697479248</t>
+    <t xml:space="preserve">5.36890602111816</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5764331817627</t>
+    <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961324691772</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">5.38229513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36555957794189</t>
+    <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30530977249146</t>
+    <t xml:space="preserve">5.3053092956543</t>
   </si>
   <si>
     <t xml:space="preserve">5.27518510818481</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">5.60320997238159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12537336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15215063095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934503555298</t>
+    <t xml:space="preserve">6.12537288665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2793436050415</t>
   </si>
   <si>
     <t xml:space="preserve">6.22244215011597</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19566440582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1488037109375</t>
+    <t xml:space="preserve">6.19566488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14880418777466</t>
   </si>
   <si>
     <t xml:space="preserve">6.09524822235107</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62664079666138</t>
+    <t xml:space="preserve">5.89441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62664031982422</t>
   </si>
   <si>
     <t xml:space="preserve">5.61325216293335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4860577583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48271131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52287769317627</t>
+    <t xml:space="preserve">5.48605823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48271083831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52287721633911</t>
   </si>
   <si>
     <t xml:space="preserve">5.65341806411743</t>
@@ -2600,40 +2600,40 @@
     <t xml:space="preserve">5.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50948810577393</t>
+    <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894821166992</t>
+    <t xml:space="preserve">5.37894773483276</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372941970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95385408401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88021516799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94381189346313</t>
+    <t xml:space="preserve">4.92372894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95385360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88021564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94381237030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2182822227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55300235748291</t>
+    <t xml:space="preserve">5.21828269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468549728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55300188064575</t>
   </si>
   <si>
     <t xml:space="preserve">5.86094427108765</t>
@@ -2642,43 +2642,43 @@
     <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09859609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44335746765137</t>
+    <t xml:space="preserve">6.09859561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44335651397705</t>
   </si>
   <si>
     <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80820178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6374945640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5872859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7211742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67766094207764</t>
+    <t xml:space="preserve">6.8082013130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63749504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58728694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72117471694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67766141891479</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323232650757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76134157180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10275506973267</t>
+    <t xml:space="preserve">6.64418888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7613410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10275459289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.36383628845215</t>
@@ -2687,109 +2687,109 @@
     <t xml:space="preserve">7.19647693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12283897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936738967896</t>
+    <t xml:space="preserve">7.12283849716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936595916748</t>
   </si>
   <si>
     <t xml:space="preserve">6.97556114196777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2098650932312</t>
+    <t xml:space="preserve">7.20986557006836</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05589389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00233888626099</t>
+    <t xml:space="preserve">7.05589437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0023398399353</t>
   </si>
   <si>
     <t xml:space="preserve">6.86175727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0692834854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10944890975952</t>
+    <t xml:space="preserve">7.06928396224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10944986343384</t>
   </si>
   <si>
     <t xml:space="preserve">7.07597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9822564125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14292192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200565338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96886682510376</t>
+    <t xml:space="preserve">6.98225593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606122970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96886730194092</t>
   </si>
   <si>
     <t xml:space="preserve">6.90192365646362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11614370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01572751998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18978309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581190109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861749649048</t>
+    <t xml:space="preserve">7.11614465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01572799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18978214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861701965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.08267116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13622760772705</t>
+    <t xml:space="preserve">7.13622665405273</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2500319480896</t>
+    <t xml:space="preserve">7.25003147125244</t>
   </si>
   <si>
     <t xml:space="preserve">7.27011489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55128002166748</t>
+    <t xml:space="preserve">7.32367086410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41069650650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39061450958252</t>
+    <t xml:space="preserve">7.41069746017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.47094631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56466865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51111268997192</t>
+    <t xml:space="preserve">7.56466770172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.53789138793945</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344436645508</t>
+    <t xml:space="preserve">7.75880718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252714157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.32113552093506</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">8.37469100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66254997253418</t>
+    <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.89685344696045</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849582672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7361888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41485691070557</t>
+    <t xml:space="preserve">8.48849487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73618793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41485786437988</t>
   </si>
   <si>
     <t xml:space="preserve">8.21402549743652</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">8.32782936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81236124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277647018433</t>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
   </si>
   <si>
     <t xml:space="preserve">7.89938831329346</t>
@@ -2879,19 +2879,19 @@
     <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290412902832</t>
+    <t xml:space="preserve">9.55290508270264</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9947338104248</t>
+    <t xml:space="preserve">9.99473571777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94118022918701</t>
+    <t xml:space="preserve">9.9411792755127</t>
   </si>
   <si>
     <t xml:space="preserve">10.0081233978271</t>
@@ -2903,55 +2903,55 @@
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381992340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365211486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168981552124</t>
+    <t xml:space="preserve">9.7738208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039247512817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4767303466797</t>
+    <t xml:space="preserve">10.476731300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.677562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84605503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3346576690674</t>
+    <t xml:space="preserve">9.84605598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
     <t xml:space="preserve">10.186595916748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0755491256714</t>
+    <t xml:space="preserve">10.0755500793457</t>
   </si>
   <si>
     <t xml:space="preserve">9.93489170074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94969844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9052791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63877010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55733680725098</t>
+    <t xml:space="preserve">9.94969749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90528011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63876914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55733585357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.59435176849365</t>
@@ -2966,22 +2966,22 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79423427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83865261077881</t>
+    <t xml:space="preserve">9.76462173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79423332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83865165710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97931003570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98671340942383</t>
+    <t xml:space="preserve">9.97930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.0903558731079</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7572193145752</t>
+    <t xml:space="preserve">9.75721836090088</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
+    <t xml:space="preserve">9.7720251083374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0533399581909</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72020435333252</t>
+    <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
     <t xml:space="preserve">9.60175514221191</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">9.5499324798584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52032089233398</t>
+    <t xml:space="preserve">9.52031993865967</t>
   </si>
   <si>
     <t xml:space="preserve">9.40187168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33524513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26121520996094</t>
+    <t xml:space="preserve">9.40927410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33524417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26121425628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10575103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99655532836914</t>
+    <t xml:space="preserve">9.10574913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99655437469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.34634876251221</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">9.20199012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17978096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.17978000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11315441131592</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01691436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03912162780762</t>
+    <t xml:space="preserve">9.01691341400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
     <t xml:space="preserve">9.15757083892822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3130350112915</t>
+    <t xml:space="preserve">9.31303596496582</t>
   </si>
   <si>
     <t xml:space="preserve">9.35745429992676</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03172016143799</t>
+    <t xml:space="preserve">9.15016746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03171920776367</t>
   </si>
   <si>
     <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98730182647705</t>
+    <t xml:space="preserve">8.98730087280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.09834671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99470520019531</t>
+    <t xml:space="preserve">8.994704246521</t>
   </si>
   <si>
     <t xml:space="preserve">9.80163669586182</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">10.0237283706665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9571008682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.95710182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.668381690979</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">9.32784175872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46109580993652</t>
+    <t xml:space="preserve">9.46109676361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772426605225</t>
+    <t xml:space="preserve">9.52772235870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885261535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75040340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92067432403564</t>
+    <t xml:space="preserve">8.75040435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92067337036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.93548011779785</t>
@@ -3152,19 +3152,19 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33078336715698</t>
+    <t xml:space="preserve">8.77261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33078384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5898904800415</t>
+    <t xml:space="preserve">4.51585960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58989000320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.62690591812134</t>
@@ -3173,40 +3173,40 @@
     <t xml:space="preserve">4.69723463058472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58248710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31227540969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090133666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27155876159668</t>
+    <t xml:space="preserve">4.5824875831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31227588653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10128879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.1938271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1679162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17161846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24564933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24935007095337</t>
+    <t xml:space="preserve">4.16791677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17161798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2456488609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24934959411621</t>
   </si>
   <si>
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12720012664795</t>
+    <t xml:space="preserve">4.12719964981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033716201782</t>
+    <t xml:space="preserve">4.46033668518066</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">4.35669422149658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741134643555</t>
+    <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.36039590835571</t>
@@ -3236,31 +3236,31 @@
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17902088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93842244148254</t>
+    <t xml:space="preserve">4.10499143600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758710861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17902135848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87549638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04576635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328674316406</t>
+    <t xml:space="preserve">4.05687093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87549614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04576683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.58862805366516</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">3.86069011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07537889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04206466674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15681219100952</t>
+    <t xml:space="preserve">4.07537841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04206418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15681171417236</t>
   </si>
   <si>
     <t xml:space="preserve">4.34558963775635</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94952702522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510869026184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433281898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654174804688</t>
+    <t xml:space="preserve">3.94952654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9051079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
@@ -3314,40 +3314,40 @@
     <t xml:space="preserve">3.88660049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86439156532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036116600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73483777046204</t>
+    <t xml:space="preserve">3.86439180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036092758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
     <t xml:space="preserve">3.50164222717285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53310561180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716490745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52014994621277</t>
+    <t xml:space="preserve">3.53310513496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716466903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52014970779419</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459741592407</t>
+    <t xml:space="preserve">3.51459717750549</t>
   </si>
   <si>
     <t xml:space="preserve">3.57382154464722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62009119987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
+    <t xml:space="preserve">3.62009072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137226104736</t>
+    <t xml:space="preserve">3.33137202262878</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358119010925</t>
+    <t xml:space="preserve">3.35358142852783</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20181822776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26474452018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10187768936157</t>
+    <t xml:space="preserve">3.14999747276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2018187046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26474475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10187745094299</t>
   </si>
   <si>
     <t xml:space="preserve">3.0130410194397</t>
@@ -3389,19 +3389,19 @@
     <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88718914985657</t>
+    <t xml:space="preserve">2.88718891143799</t>
   </si>
   <si>
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00748872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">3.007488489151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98342871665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81130790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86497974395752</t>
+    <t xml:space="preserve">2.81130766868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8649799823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014433860779</t>
+    <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">2.77059102058411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82426309585571</t>
+    <t xml:space="preserve">2.82426333427429</t>
   </si>
   <si>
     <t xml:space="preserve">2.83721852302551</t>
@@ -3455,31 +3455,31 @@
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49852895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60032105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56515622138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6151270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57811188697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888728141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44855856895447</t>
+    <t xml:space="preserve">2.52999186515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49852919578552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60032081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297690391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56515645980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61512732505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57811164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44855833053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.47446918487549</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">2.45596146583557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48927521705627</t>
+    <t xml:space="preserve">2.48927545547485</t>
   </si>
   <si>
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742461204529</t>
+    <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
     <t xml:space="preserve">2.27273607254028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2579300403595</t>
+    <t xml:space="preserve">2.25792980194092</t>
   </si>
   <si>
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41339373588562</t>
+    <t xml:space="preserve">2.41339421272278</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676647186279</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">2.19685482978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13577938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18760085105896</t>
+    <t xml:space="preserve">2.13577961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18760108947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.29679584503174</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25422859191895</t>
+    <t xml:space="preserve">2.25422835350037</t>
   </si>
   <si>
     <t xml:space="preserve">2.26718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28754210472107</t>
+    <t xml:space="preserve">2.28754186630249</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
@@ -3566,22 +3566,22 @@
     <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24312376976013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.182049036026</t>
+    <t xml:space="preserve">2.22276568412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24312400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18204855918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29124355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24867630004883</t>
+    <t xml:space="preserve">2.2912437915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
     <t xml:space="preserve">2.21351170539856</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">2.13022756576538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15798854827881</t>
+    <t xml:space="preserve">2.15798902511597</t>
   </si>
   <si>
     <t xml:space="preserve">2.14873480796814</t>
@@ -3605,10 +3605,10 @@
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0839581489563</t>
+    <t xml:space="preserve">2.14688444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08395838737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.10246586799622</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434608459473</t>
+    <t xml:space="preserve">2.05434632301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.95810627937317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86186695098877</t>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
@@ -3650,19 +3650,19 @@
     <t xml:space="preserve">1.90132355690002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83638417720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255311012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91036570072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077330589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84953665733337</t>
+    <t xml:space="preserve">1.83638429641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255322933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077318668365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84953653812408</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
@@ -3671,31 +3671,31 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679899692535</t>
+    <t xml:space="preserve">1.86679875850677</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556932449341</t>
+    <t xml:space="preserve">1.89556956291199</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83720624446869</t>
+    <t xml:space="preserve">1.8372061252594</t>
   </si>
   <si>
     <t xml:space="preserve">1.78541910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76158058643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77062296867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556222915649</t>
+    <t xml:space="preserve">1.7615807056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.770623087883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556234836578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79199540615082</t>
@@ -3707,22 +3707,22 @@
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311069488525</t>
+    <t xml:space="preserve">1.95311057567596</t>
   </si>
   <si>
     <t xml:space="preserve">1.958864569664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00078773498535</t>
+    <t xml:space="preserve">2.00078749656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.03695607185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98023724555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03942251205444</t>
+    <t xml:space="preserve">1.98023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03942227363586</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2420494556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23382902145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14135241508484</t>
+    <t xml:space="preserve">2.24204921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23382925987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14135217666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.15573763847351</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">2.2728750705719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904009819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30781054496765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34685659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35096621513367</t>
+    <t xml:space="preserve">2.27904033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30781030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34685635566711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35096645355225</t>
   </si>
   <si>
     <t xml:space="preserve">2.34274625778198</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821424484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25848960876465</t>
+    <t xml:space="preserve">2.24821448326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25848937034607</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">2.22766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1619029045105</t>
+    <t xml:space="preserve">2.16190266609192</t>
   </si>
   <si>
     <t xml:space="preserve">2.14546251296997</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">2.30986547470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35507655143738</t>
+    <t xml:space="preserve">2.3550763130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.41056251525879</t>
@@ -3845,19 +3845,19 @@
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619526863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52769994735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55236029624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53797507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54003024101257</t>
+    <t xml:space="preserve">2.54619550704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5276997089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55236053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5379753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54003000259399</t>
   </si>
   <si>
     <t xml:space="preserve">2.45988368988037</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">2.52153491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54208517074585</t>
+    <t xml:space="preserve">2.54208493232727</t>
   </si>
   <si>
     <t xml:space="preserve">2.51125955581665</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920462608337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55852556228638</t>
+    <t xml:space="preserve">2.50920438766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5585253238678</t>
   </si>
   <si>
     <t xml:space="preserve">2.55647039413452</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.66744256019592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67155265808105</t>
+    <t xml:space="preserve">2.67155289649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.68799304962158</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7414243221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70443320274353</t>
+    <t xml:space="preserve">2.74142408370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70443344116211</t>
   </si>
   <si>
     <t xml:space="preserve">2.72498393058777</t>
@@ -3956,25 +3956,25 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78868985176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77019476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703909873962</t>
+    <t xml:space="preserve">2.78869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77019453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6078462600708</t>
+    <t xml:space="preserve">2.60784649848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.62634181976318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70648860931396</t>
+    <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428712844849</t>
+    <t xml:space="preserve">2.62428689002991</t>
   </si>
   <si>
     <t xml:space="preserve">2.59757137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6057915687561</t>
+    <t xml:space="preserve">2.60579133033752</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">2.58524107933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58935141563416</t>
+    <t xml:space="preserve">2.58935117721558</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">2.69621324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79485511779785</t>
+    <t xml:space="preserve">2.79485535621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048787117004</t>
+    <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
     <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91404747962952</t>
+    <t xml:space="preserve">2.9140477180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035929679871</t>
+    <t xml:space="preserve">3.00035953521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.99419403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99830412864685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89760732650757</t>
+    <t xml:space="preserve">2.99830436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89760756492615</t>
   </si>
   <si>
     <t xml:space="preserve">2.84006595611572</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">2.74553418159485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61606645584106</t>
+    <t xml:space="preserve">2.61606669425964</t>
   </si>
   <si>
     <t xml:space="preserve">2.68388295173645</t>
@@ -4070,16 +4070,16 @@
     <t xml:space="preserve">2.79896521568298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7907452583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99213933944702</t>
+    <t xml:space="preserve">2.79074501991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99213910102844</t>
   </si>
   <si>
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9345977306366</t>
+    <t xml:space="preserve">2.93459796905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">2.77224969863892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78457975387573</t>
+    <t xml:space="preserve">2.78457999229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4097,19 +4097,19 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979083061218</t>
+    <t xml:space="preserve">2.82979106903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10927653312683</t>
+    <t xml:space="preserve">3.10927629470825</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582728385925</t>
+    <t xml:space="preserve">2.90582752227783</t>
   </si>
   <si>
     <t xml:space="preserve">2.9633686542511</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034108161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86883687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82568097114563</t>
+    <t xml:space="preserve">2.85034132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86883664131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82568073272705</t>
   </si>
   <si>
     <t xml:space="preserve">2.92226767539978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88733220100403</t>
+    <t xml:space="preserve">2.88733196258545</t>
   </si>
   <si>
     <t xml:space="preserve">2.8893871307373</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995535850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9818639755249</t>
+    <t xml:space="preserve">3.05995559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98186421394348</t>
   </si>
   <si>
     <t xml:space="preserve">3.0126895904541</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">2.90442943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92211246490479</t>
+    <t xml:space="preserve">2.92211222648621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98621320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04147243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1033627986908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136608123779</t>
+    <t xml:space="preserve">3.04147267341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136584281921</t>
   </si>
   <si>
     <t xml:space="preserve">3.11883544921875</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">3.07241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09452152252197</t>
+    <t xml:space="preserve">3.09452128410339</t>
   </si>
   <si>
     <t xml:space="preserve">3.07020735740662</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.97958207130432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97074055671692</t>
+    <t xml:space="preserve">2.97074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.91548109054565</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.93316435813904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92874336242676</t>
+    <t xml:space="preserve">2.92874360084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.90221905708313</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">2.90000867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87790513038635</t>
+    <t xml:space="preserve">2.87790489196777</t>
   </si>
   <si>
     <t xml:space="preserve">2.86464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83369755744934</t>
+    <t xml:space="preserve">2.83369731903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.81822490692139</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">2.69002318382263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60160851478577</t>
+    <t xml:space="preserve">2.60160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">2.66791939735413</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">2.68560242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62813305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6502366065979</t>
+    <t xml:space="preserve">2.62813282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65023636817932</t>
   </si>
   <si>
     <t xml:space="preserve">2.60381865501404</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.5551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47340655326843</t>
+    <t xml:space="preserve">2.47340679168701</t>
   </si>
   <si>
     <t xml:space="preserve">2.44909262657166</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">2.47119641304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47782754898071</t>
+    <t xml:space="preserve">2.47782731056213</t>
   </si>
   <si>
     <t xml:space="preserve">2.46014451980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624221801758</t>
+    <t xml:space="preserve">2.56624245643616</t>
   </si>
   <si>
     <t xml:space="preserve">2.55961132049561</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.54855942726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50877285003662</t>
+    <t xml:space="preserve">2.50877261161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.53087639808655</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">2.32531189918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24529623985291</t>
+    <t xml:space="preserve">2.24529647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.19932055473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15422892570496</t>
+    <t xml:space="preserve">2.15422916412354</t>
   </si>
   <si>
     <t xml:space="preserve">2.14715576171875</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">2.17633247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29746103286743</t>
+    <t xml:space="preserve">2.29746127128601</t>
   </si>
   <si>
     <t xml:space="preserve">2.38720226287842</t>
@@ -4367,40 +4367,40 @@
     <t xml:space="preserve">2.33813214302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51894021034241</t>
+    <t xml:space="preserve">2.51894044876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46854400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42345213890076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51319360733032</t>
+    <t xml:space="preserve">2.42345237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51319336891174</t>
   </si>
   <si>
     <t xml:space="preserve">2.57287359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52026653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56712675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55076956748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53794980049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54723334312439</t>
+    <t xml:space="preserve">2.52026677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56712651252747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5507698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53794956207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54723310470581</t>
   </si>
   <si>
     <t xml:space="preserve">2.70461177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78109073638916</t>
+    <t xml:space="preserve">2.78109049797058</t>
   </si>
   <si>
     <t xml:space="preserve">2.75854468345642</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">2.79302644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75633430480957</t>
+    <t xml:space="preserve">2.75633454322815</t>
   </si>
   <si>
     <t xml:space="preserve">2.77357530593872</t>
@@ -4436,13 +4436,13 @@
     <t xml:space="preserve">2.91327095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84253883361816</t>
+    <t xml:space="preserve">2.84253907203674</t>
   </si>
   <si>
     <t xml:space="preserve">2.93935322761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94112133979797</t>
+    <t xml:space="preserve">2.94112157821655</t>
   </si>
   <si>
     <t xml:space="preserve">2.92343854904175</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">2.94554233551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785954475403</t>
+    <t xml:space="preserve">2.92785930633545</t>
   </si>
   <si>
     <t xml:space="preserve">2.93537449836731</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">2.89249348640442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88851451873779</t>
+    <t xml:space="preserve">2.88851475715637</t>
   </si>
   <si>
     <t xml:space="preserve">2.93006944656372</t>
@@ -4475,25 +4475,25 @@
     <t xml:space="preserve">2.88011527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92741727828979</t>
+    <t xml:space="preserve">2.92741751670837</t>
   </si>
   <si>
     <t xml:space="preserve">3.02378964424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03926229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03086280822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96189880371094</t>
+    <t xml:space="preserve">3.03926205635071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03086256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96189904212952</t>
   </si>
   <si>
     <t xml:space="preserve">2.93493247032166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89824032783508</t>
+    <t xml:space="preserve">2.89824056625366</t>
   </si>
   <si>
     <t xml:space="preserve">2.91724944114685</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">2.9106183052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9176914691925</t>
+    <t xml:space="preserve">2.91769170761108</t>
   </si>
   <si>
     <t xml:space="preserve">2.9256489276886</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">2.98444485664368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02246332168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00168585777283</t>
+    <t xml:space="preserve">3.02246308326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00168561935425</t>
   </si>
   <si>
     <t xml:space="preserve">2.95438385009766</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">2.73865151405334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67101407051086</t>
+    <t xml:space="preserve">2.67101383209229</t>
   </si>
   <si>
     <t xml:space="preserve">2.68737077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66084623336792</t>
+    <t xml:space="preserve">2.6608464717865</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869686126709</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.64537382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72052621841431</t>
+    <t xml:space="preserve">2.72052645683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70947456359863</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">2.62327003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58701992034912</t>
+    <t xml:space="preserve">2.5870201587677</t>
   </si>
   <si>
     <t xml:space="preserve">2.60426068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57729411125183</t>
+    <t xml:space="preserve">2.57729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">2.58171510696411</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">2.58083081245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59497737884521</t>
+    <t xml:space="preserve">2.59497714042664</t>
   </si>
   <si>
     <t xml:space="preserve">2.65288901329041</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">2.69488620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69223380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64139485359192</t>
+    <t xml:space="preserve">2.69223356246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6413950920105</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480954170227</t>
@@ -4622,19 +4622,19 @@
     <t xml:space="preserve">2.70549583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71168494224548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67985534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85049629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342336654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9318380355835</t>
+    <t xml:space="preserve">2.7116847038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67985558509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85049605369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342312812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93183779716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.91946005821228</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">2.94952082633972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878894805908</t>
+    <t xml:space="preserve">2.87878918647766</t>
   </si>
   <si>
     <t xml:space="preserve">3.13872885704041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">3.30671715736389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42519307136536</t>
+    <t xml:space="preserve">3.42519330978394</t>
   </si>
   <si>
     <t xml:space="preserve">3.41988825798035</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">3.34561967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33500981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43933939933777</t>
+    <t xml:space="preserve">3.33501005172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43933963775635</t>
   </si>
   <si>
     <t xml:space="preserve">3.36507105827332</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">3.29787564277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30848574638367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32793688774109</t>
+    <t xml:space="preserve">3.30848550796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32793664932251</t>
   </si>
   <si>
     <t xml:space="preserve">3.41458320617676</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">3.41104674339294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49592518806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57019352912903</t>
+    <t xml:space="preserve">3.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57019376754761</t>
   </si>
   <si>
     <t xml:space="preserve">3.57372999191284</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">3.50123000144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50653481483459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52598595619202</t>
+    <t xml:space="preserve">3.50653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5259861946106</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616945266724</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">3.61793756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59848666191101</t>
+    <t xml:space="preserve">3.59848642349243</t>
   </si>
   <si>
     <t xml:space="preserve">3.63031578063965</t>
@@ -4748,28 +4748,28 @@
     <t xml:space="preserve">3.7045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77708435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84074282646179</t>
+    <t xml:space="preserve">3.77708411216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82129192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84074306488037</t>
   </si>
   <si>
     <t xml:space="preserve">3.84781646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85488963127136</t>
+    <t xml:space="preserve">3.85488939285278</t>
   </si>
   <si>
     <t xml:space="preserve">3.87610912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232815742493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85842609405518</t>
+    <t xml:space="preserve">3.75232839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8584258556366</t>
   </si>
   <si>
     <t xml:space="preserve">3.65860843658447</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">3.46409559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57903504371643</t>
+    <t xml:space="preserve">3.57903480529785</t>
   </si>
   <si>
     <t xml:space="preserve">3.52775454521179</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">3.4941565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52952265739441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62324261665344</t>
+    <t xml:space="preserve">3.52952289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62324237823486</t>
   </si>
   <si>
     <t xml:space="preserve">3.61440086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68690133094788</t>
+    <t xml:space="preserve">3.6869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">3.65684032440186</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">3.6957426071167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74525499343872</t>
+    <t xml:space="preserve">3.7452552318573</t>
   </si>
   <si>
     <t xml:space="preserve">3.75056004524231</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">3.80714583396912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05824375152588</t>
+    <t xml:space="preserve">4.20501279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05824422836304</t>
   </si>
   <si>
     <t xml:space="preserve">4.09184122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12013387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1678786277771</t>
+    <t xml:space="preserve">4.1201343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16787815093994</t>
   </si>
   <si>
     <t xml:space="preserve">4.07592678070068</t>
@@ -5652,6 +5652,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.97399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92199993133545</t>
   </si>
 </sst>
 </file>
@@ -71666,7 +71669,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6912731481</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>256989</v>
@@ -71687,6 +71690,32 @@
         <v>1879</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6912384259</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>283676</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>4.0019998550415</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>3.91400003433228</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>4.0019998550415</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>3.92199993133545</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1880</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="1881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="1882">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">11.5895690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4097318649292</t>
+    <t xml:space="preserve">11.4097309112549</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101800918579</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">11.1366424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8302526473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3107204437256</t>
+    <t xml:space="preserve">10.8302536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3107194900513</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907381057739</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7370023727417</t>
+    <t xml:space="preserve">10.737003326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.3906478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4239521026611</t>
+    <t xml:space="preserve">10.4239530563354</t>
   </si>
   <si>
     <t xml:space="preserve">10.5438432693481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257435798645</t>
+    <t xml:space="preserve">10.2574348449707</t>
   </si>
   <si>
     <t xml:space="preserve">10.2707567214966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4838972091675</t>
+    <t xml:space="preserve">10.4838981628418</t>
   </si>
   <si>
     <t xml:space="preserve">10.297399520874</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">9.77786731719971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9110803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54474353790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77120590209961</t>
+    <t xml:space="preserve">9.91107940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77120685577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174711227417</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436595916748</t>
+    <t xml:space="preserve">9.96436500549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4905586242676</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">10.9434843063354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4363737106323</t>
+    <t xml:space="preserve">11.436372756958</t>
   </si>
   <si>
     <t xml:space="preserve">11.3431253433228</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">11.6495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898397445679</t>
+    <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">12.0624771118164</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">12.2289943695068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.475438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554576873779</t>
+    <t xml:space="preserve">12.4754390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554586410522</t>
   </si>
   <si>
     <t xml:space="preserve">12.3422269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4621162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5553665161133</t>
+    <t xml:space="preserve">12.4621171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019897460938</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">12.1890296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0633773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6561756134033</t>
+    <t xml:space="preserve">11.496319770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0633764266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6561765670776</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559059143066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689580917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217935562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.921703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9350252151489</t>
+    <t xml:space="preserve">12.2689571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9350242614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.1015434265137</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">13.1947908401489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.181468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.16148853302</t>
+    <t xml:space="preserve">13.1814708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1614904403687</t>
   </si>
   <si>
     <t xml:space="preserve">13.361307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2347536087036</t>
+    <t xml:space="preserve">13.2347555160522</t>
   </si>
   <si>
     <t xml:space="preserve">13.3946113586426</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">12.5620288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8817405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8884010314941</t>
+    <t xml:space="preserve">12.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8884000778198</t>
   </si>
   <si>
     <t xml:space="preserve">13.0482559204102</t>
@@ -293,555 +293,555 @@
     <t xml:space="preserve">12.4088306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755283355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221525192261</t>
+    <t xml:space="preserve">12.375527381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221515655518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7218837738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150428771973</t>
+    <t xml:space="preserve">12.7218828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6230983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5226812362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5561532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4222640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.355320930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9938249588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194655418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6591053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833864212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.762056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7218894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524095535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925764083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4231758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8382291793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4834251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2290382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4164819717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4432592391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7445068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1193933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4741954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599744796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1260890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0189771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0122833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.811450958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9252548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8783950805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7645902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0616788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1754837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88762474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06421375274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93032455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67593860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93702030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37215518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23826789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31860065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13115787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37884998321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19140720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23157405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51273822784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43909931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265575408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53951549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76043128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78720855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87423515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17132377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07090759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08429622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31190586090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36546039581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3855447769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24496173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03743648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72279930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87007522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76965999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74957752227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78304862976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78974342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71610546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33452415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20063591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10022068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12030410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83913898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591672897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6316123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508531570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74541664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71194553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95963716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12699794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38138580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92363166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2114896774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09768486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.99635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1168575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9294157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8691663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615627288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975687026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908739089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904596328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3126201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2858428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1385679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2080450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528257369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8264646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737405776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1611843109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0540752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9134912490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2147397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419332504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8599367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0473794937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0206031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9201850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3754043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6230983734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5226821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5561532974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4222640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553228378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0741577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2749900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.659104347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515790939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4231758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8382291793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4834251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177305221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2290382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4164819717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0482912063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4432592391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7445068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1193933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.474196434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599744796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1260890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0189771652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0122842788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.811450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9252548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8783950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7645902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0616779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1754837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88762474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06421375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93032455444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67593860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80313110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93702030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37215423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25835132598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23826789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31860065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13115882873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37884998321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19140720367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23157405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63323783874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51273822784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43910026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265575408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53951549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8273754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76043128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78720760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87423515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6734037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17132377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07090759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31190586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36546039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38554573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24496173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03743648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72279930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87007522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76965999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74957752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78304862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78974342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71610450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66924381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33452415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20063591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227781295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83913898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6316123008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491798400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508436203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74541664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71194553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69186162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500093460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9596381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12699794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38138484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92363166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21149063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09768486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9963579177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1168575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9294157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8691654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971506118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7569856643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975687026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908720016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004800796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180673599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712076187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3126201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2858428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1385679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8172340393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544895172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2080450057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268789291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528257369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8264646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737405776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1611843109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9134912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2147417068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599367141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871282577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.007212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0473794937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0206031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9201860427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8934097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3754062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3486280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2214326858521</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.1745738983154</t>
   </si>
   <si>
@@ -857,31 +857,31 @@
     <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001035690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.819769859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858825683594</t>
+    <t xml:space="preserve">12.8398542404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001026153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858816146851</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3109970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3310785293579</t>
+    <t xml:space="preserve">12.310996055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3310794830322</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862997055054</t>
+    <t xml:space="preserve">12.7862987518311</t>
   </si>
   <si>
     <t xml:space="preserve">12.8800191879272</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">12.5653839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4448843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3043003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3913297653198</t>
+    <t xml:space="preserve">12.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637201309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3043012619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.558687210083</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2842178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4181060791016</t>
+    <t xml:space="preserve">12.2842168807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4181070327759</t>
   </si>
   <si>
     <t xml:space="preserve">12.1971912384033</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0633039474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519933700562</t>
+    <t xml:space="preserve">12.0633029937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519943237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.6724939346313</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">12.3176898956299</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8089170455933</t>
+    <t xml:space="preserve">11.8089160919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.0030536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813074111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6147775650024</t>
+    <t xml:space="preserve">11.5813064575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076694488525</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817226409912</t>
+    <t xml:space="preserve">11.6817235946655</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5210561752319</t>
+    <t xml:space="preserve">11.5210552215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6616401672363</t>
+    <t xml:space="preserve">11.661639213562</t>
   </si>
   <si>
     <t xml:space="preserve">11.6348609924316</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7980613708496</t>
+    <t xml:space="preserve">10.7980623245239</t>
   </si>
   <si>
     <t xml:space="preserve">10.9453392028809</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1461706161499</t>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1327810287476</t>
+    <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591440200806</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">11.4206409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5411396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5679178237915</t>
+    <t xml:space="preserve">11.5411405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">11.3001413345337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4005584716797</t>
+    <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
     <t xml:space="preserve">11.460807800293</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">11.1595602035522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0524482727051</t>
+    <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
     <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5302867889404</t>
+    <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.3897037506104</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">10.2156505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3361482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901208877563</t>
+    <t xml:space="preserve">10.3361492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">10.3562316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076404571533</t>
+    <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">9.72026443481445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74704170227051</t>
+    <t xml:space="preserve">9.74704265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650785446167</t>
+    <t xml:space="preserve">10.6507863998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700374603271</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3763151168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188871383667</t>
+    <t xml:space="preserve">10.376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1888723373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.275899887085</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570650100708</t>
+    <t xml:space="preserve">10.2357320785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570640563965</t>
   </si>
   <si>
     <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3160648345947</t>
+    <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
     <t xml:space="preserve">10.2089557647705</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83406829833984</t>
+    <t xml:space="preserve">9.83406925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.84745788574219</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">10.2959823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436744689941</t>
+    <t xml:space="preserve">10.5436754226685</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
@@ -1286,19 +1286,19 @@
     <t xml:space="preserve">10.9118671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8917837142944</t>
+    <t xml:space="preserve">10.9051742553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8917827606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0390605926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7277717590332</t>
+    <t xml:space="preserve">11.0390596389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7277708053589</t>
   </si>
   <si>
     <t xml:space="preserve">10.4633417129517</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">10.5871877670288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658576965332</t>
+    <t xml:space="preserve">10.289288520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658567428589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3696212768555</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">10.8616590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6407432556152</t>
+    <t xml:space="preserve">10.6407442092896</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106185913086</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
+    <t xml:space="preserve">10.533634185791</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6240072250366</t>
+    <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
     <t xml:space="preserve">10.4097871780396</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94452571868896</t>
+    <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951509475708</t>
+    <t xml:space="preserve">10.0951499938965</t>
   </si>
   <si>
     <t xml:space="preserve">10.9788103103638</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">11.0357131958008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1762962341309</t>
+    <t xml:space="preserve">11.1762952804565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717012405396</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.082573890686</t>
+    <t xml:space="preserve">11.0825748443604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9520330429077</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2867546081543</t>
+    <t xml:space="preserve">11.28675365448</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352960586548</t>
+    <t xml:space="preserve">10.9352970123291</t>
   </si>
   <si>
     <t xml:space="preserve">10.5068559646606</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2457752227783</t>
+    <t xml:space="preserve">10.245774269104</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683727264404</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">9.74369525909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28847503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34537792205811</t>
+    <t xml:space="preserve">9.28847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.6700553894043</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">9.48596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637619018555</t>
+    <t xml:space="preserve">9.58637523651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54286193847656</t>
+    <t xml:space="preserve">9.54286289215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.57298851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56964015960693</t>
+    <t xml:space="preserve">9.56964111328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.50269603729248</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949409484863</t>
+    <t xml:space="preserve">8.68932819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949314117432</t>
   </si>
   <si>
     <t xml:space="preserve">8.89350605010986</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">9.30186557769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22487831115723</t>
+    <t xml:space="preserve">9.22487926483154</t>
   </si>
   <si>
     <t xml:space="preserve">9.28512859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21483707427979</t>
+    <t xml:space="preserve">9.2148380279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.13785171508789</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61315441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71691703796387</t>
+    <t xml:space="preserve">9.6131534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922492980957</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">9.54621124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31525325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26504516601562</t>
+    <t xml:space="preserve">9.31525421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26504611968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.73284149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80647850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89015865325928</t>
+    <t xml:space="preserve">8.80647945404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86003494262695</t>
+    <t xml:space="preserve">8.85334014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
     <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88011741638184</t>
+    <t xml:space="preserve">8.88011837005615</t>
   </si>
   <si>
     <t xml:space="preserve">8.82656288146973</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">8.2742748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25084400177002</t>
+    <t xml:space="preserve">8.24080276489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2508430480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.64581394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35795497894287</t>
+    <t xml:space="preserve">8.35795402526855</t>
   </si>
   <si>
     <t xml:space="preserve">8.47845363616943</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78639602661133</t>
+    <t xml:space="preserve">8.78639507293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.71945190429688</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0006160736084</t>
+    <t xml:space="preserve">9.00061702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735305786133</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">9.12780952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66589641571045</t>
+    <t xml:space="preserve">9.03408908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">8.53535652160645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47510719299316</t>
+    <t xml:space="preserve">8.47510623931885</t>
   </si>
   <si>
     <t xml:space="preserve">8.30105209350586</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516983032227</t>
+    <t xml:space="preserve">9.29516887664795</t>
   </si>
   <si>
     <t xml:space="preserve">9.30855941772461</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">9.50604343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46587753295898</t>
+    <t xml:space="preserve">9.46587657928467</t>
   </si>
   <si>
     <t xml:space="preserve">9.12111568450928</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">9.19810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70271682739258</t>
+    <t xml:space="preserve">8.70271587371826</t>
   </si>
   <si>
     <t xml:space="preserve">8.25753879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56548118591309</t>
+    <t xml:space="preserve">8.56548023223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.5018835067749</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">8.74622917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18471336364746</t>
+    <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
     <t xml:space="preserve">9.42236328125</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44914150238037</t>
+    <t xml:space="preserve">9.44914054870605</t>
   </si>
   <si>
     <t xml:space="preserve">9.91105556488037</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">9.522780418396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45918369293213</t>
+    <t xml:space="preserve">9.45918273925781</t>
   </si>
   <si>
     <t xml:space="preserve">9.44244575500488</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60646057128906</t>
+    <t xml:space="preserve">9.60645961761475</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456790924072</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35876750946045</t>
+    <t xml:space="preserve">9.35876655578613</t>
   </si>
   <si>
     <t xml:space="preserve">9.27174091339111</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71275901794434</t>
+    <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.80982685089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10438060760498</t>
+    <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843379974365</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">9.52947425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51943206787109</t>
+    <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.42905902862549</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625152587891</t>
+    <t xml:space="preserve">9.55625057220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.42571067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1512393951416</t>
+    <t xml:space="preserve">9.15124034881592</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128253936768</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">9.33533573150635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24161624908447</t>
+    <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
     <t xml:space="preserve">9.14454555511475</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">9.73030567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69013977050781</t>
+    <t xml:space="preserve">9.69014072418213</t>
   </si>
   <si>
     <t xml:space="preserve">9.50939083099365</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">9.73700046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92109680175781</t>
+    <t xml:space="preserve">9.79725074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9210958480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.90770721435547</t>
@@ -1928,40 +1928,40 @@
     <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
+    <t xml:space="preserve">9.45248889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.76631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62572956085205</t>
+    <t xml:space="preserve">8.62573051452637</t>
   </si>
   <si>
     <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77300643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961875915527</t>
+    <t xml:space="preserve">8.7730073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404594421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40562725067139</t>
+    <t xml:space="preserve">9.4056282043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70687580108643</t>
+    <t xml:space="preserve">9.70687675476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.94787406921387</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">9.02739524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9437141418457</t>
+    <t xml:space="preserve">8.94371509552002</t>
   </si>
   <si>
     <t xml:space="preserve">8.9805326461792</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">10.0415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86084651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8240270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81063938140869</t>
+    <t xml:space="preserve">9.86084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82402801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81063842773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068061828613</t>
@@ -2039,19 +2039,19 @@
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764362335205</t>
+    <t xml:space="preserve">9.08764457702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09099006652832</t>
+    <t xml:space="preserve">9.09099102020264</t>
   </si>
   <si>
     <t xml:space="preserve">8.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288177490234</t>
+    <t xml:space="preserve">8.74288272857666</t>
   </si>
   <si>
     <t xml:space="preserve">8.79308986663818</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677097320557</t>
+    <t xml:space="preserve">8.87677001953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681221008301</t>
@@ -2075,22 +2075,22 @@
     <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06086540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15458869934082</t>
+    <t xml:space="preserve">9.060866355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
     <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11776828765869</t>
+    <t xml:space="preserve">9.11776924133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.0809497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96714496612549</t>
+    <t xml:space="preserve">8.96714401245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377521514893</t>
+    <t xml:space="preserve">8.23410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377616882324</t>
   </si>
   <si>
     <t xml:space="preserve">7.98976230621338</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327751159668</t>
+    <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
     <t xml:space="preserve">7.94624900817871</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">7.95629024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93286085128784</t>
+    <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">7.94290208816528</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78558349609375</t>
+    <t xml:space="preserve">7.78558254241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.67177820205688</t>
@@ -2183,16 +2183,16 @@
     <t xml:space="preserve">7.16300439834595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07262945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514638900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222366333008</t>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514543533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222461700439</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256681442261</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">5.05929040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27183723449707</t>
+    <t xml:space="preserve">5.27183771133423</t>
   </si>
   <si>
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693183898926</t>
+    <t xml:space="preserve">5.69693231582642</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311758041382</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">6.23917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2944073677063</t>
+    <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49356412887573</t>
+    <t xml:space="preserve">6.49356508255005</t>
   </si>
   <si>
     <t xml:space="preserve">6.36637163162231</t>
@@ -2258,28 +2258,28 @@
     <t xml:space="preserve">6.53038501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.647536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720399856567</t>
+    <t xml:space="preserve">6.64753532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720304489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4266209602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3596773147583</t>
+    <t xml:space="preserve">6.42662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
     <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892789840698</t>
+    <t xml:space="preserve">6.03834676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
@@ -2294,31 +2294,31 @@
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628772735596</t>
+    <t xml:space="preserve">6.32620477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20905303955078</t>
+    <t xml:space="preserve">6.20905351638794</t>
   </si>
   <si>
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520746231079</t>
+    <t xml:space="preserve">6.08520698547363</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156854629517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89776372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813772201538</t>
+    <t xml:space="preserve">5.89776420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813819885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508232116699</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">5.82747268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68354320526123</t>
+    <t xml:space="preserve">5.68354272842407</t>
   </si>
   <si>
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0843939781189</t>
+    <t xml:space="preserve">5.08439445495605</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18815755844116</t>
+    <t xml:space="preserve">5.188157081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.34212923049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15803241729736</t>
+    <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
     <t xml:space="preserve">5.22162961959839</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1981987953186</t>
+    <t xml:space="preserve">5.19819927215576</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861497879028</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">5.28522634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30196237564087</t>
+    <t xml:space="preserve">5.30196189880371</t>
   </si>
   <si>
     <t xml:space="preserve">5.238365650177</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2785325050354</t>
+    <t xml:space="preserve">5.27853202819824</t>
   </si>
   <si>
     <t xml:space="preserve">5.23167085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886526107788</t>
+    <t xml:space="preserve">5.35886478424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.32204580307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3253927230835</t>
+    <t xml:space="preserve">5.32539319992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786651611328</t>
+    <t xml:space="preserve">5.11786603927612</t>
   </si>
   <si>
     <t xml:space="preserve">5.12121343612671</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">5.48940515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36890602111816</t>
+    <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215015411377</t>
+    <t xml:space="preserve">6.15215063095093</t>
   </si>
   <si>
     <t xml:space="preserve">6.2793436050415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22244215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19566488265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14880418777466</t>
+    <t xml:space="preserve">6.22244167327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19566440582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14880466461182</t>
   </si>
   <si>
     <t xml:space="preserve">6.09524822235107</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">5.73040390014648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70027923583984</t>
+    <t xml:space="preserve">5.70027875900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.70362663269043</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258665084839</t>
+    <t xml:space="preserve">5.45258712768555</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894773483276</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">5.55300188064575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86094427108765</t>
+    <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
     <t xml:space="preserve">6.02830410003662</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8082013130188</t>
+    <t xml:space="preserve">6.80820178985596</t>
   </si>
   <si>
     <t xml:space="preserve">6.63749504089355</t>
@@ -2663,19 +2663,19 @@
     <t xml:space="preserve">6.72117471694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67766141891479</t>
+    <t xml:space="preserve">6.67766046524048</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323232650757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78142404556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7613410949707</t>
+    <t xml:space="preserve">6.64418983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76134061813354</t>
   </si>
   <si>
     <t xml:space="preserve">7.10275459289551</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19647693634033</t>
+    <t xml:space="preserve">7.19647598266602</t>
   </si>
   <si>
     <t xml:space="preserve">7.12283849716187</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">6.97556114196777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20986557006836</t>
+    <t xml:space="preserve">7.20986652374268</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961624145508</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">7.0023398399353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86175727844238</t>
+    <t xml:space="preserve">6.86175632476807</t>
   </si>
   <si>
     <t xml:space="preserve">7.06928396224976</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581047058105</t>
+    <t xml:space="preserve">7.03581142425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.90861701965332</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">7.39061403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47094631195068</t>
+    <t xml:space="preserve">7.470947265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.56466770172119</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75880718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252714157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113552093506</t>
+    <t xml:space="preserve">7.7588062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113647460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.1805534362793</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48849487304688</t>
+    <t xml:space="preserve">8.48849582672119</t>
   </si>
   <si>
     <t xml:space="preserve">8.73618793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41485786437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21402549743652</t>
+    <t xml:space="preserve">8.41485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21402454376221</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724822998047</t>
+    <t xml:space="preserve">8.18724727630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">8.26758098602295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32782936096191</t>
+    <t xml:space="preserve">8.3278284072876</t>
   </si>
   <si>
     <t xml:space="preserve">7.81236171722412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77888965606689</t>
+    <t xml:space="preserve">7.77888870239258</t>
   </si>
   <si>
     <t xml:space="preserve">7.91277694702148</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">7.99980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049140930176</t>
+    <t xml:space="preserve">8.97049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009757995605</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">10.5168972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039247512817</t>
+    <t xml:space="preserve">10.6039237976074</t>
   </si>
   <si>
     <t xml:space="preserve">10.476731300354</t>
@@ -2933,22 +2933,22 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.186595916748</t>
+    <t xml:space="preserve">10.1865949630737</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755500793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93489170074463</t>
+    <t xml:space="preserve">9.93489074707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90528011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63876914978027</t>
+    <t xml:space="preserve">9.9052791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63877010345459</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047336578369</t>
+    <t xml:space="preserve">9.89047431945801</t>
   </si>
   <si>
     <t xml:space="preserve">9.75721836090088</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">9.7720251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533399581909</t>
+    <t xml:space="preserve">10.0533409118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">9.60175514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5499324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52031993865967</t>
+    <t xml:space="preserve">9.54993343353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
     <t xml:space="preserve">9.40187168121338</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">9.40927410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524417877197</t>
+    <t xml:space="preserve">9.33524322509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10574913024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99655437469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34634876251221</t>
+    <t xml:space="preserve">9.10575008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99655532836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37226009368896</t>
+    <t xml:space="preserve">9.37225914001465</t>
   </si>
   <si>
     <t xml:space="preserve">9.4166784286499</t>
@@ -3062,31 +3062,31 @@
     <t xml:space="preserve">9.2464075088501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20199012756348</t>
+    <t xml:space="preserve">9.20199108123779</t>
   </si>
   <si>
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11315441131592</t>
+    <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01691341400146</t>
+    <t xml:space="preserve">9.01691436767578</t>
   </si>
   <si>
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.31303596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35745429992676</t>
+    <t xml:space="preserve">9.35745525360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">9.03171920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02431678771973</t>
+    <t xml:space="preserve">9.02431583404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98730087280273</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">9.95710182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.668381690979</t>
+    <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">9.32784175872803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46109676361084</t>
+    <t xml:space="preserve">9.46109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">9.43148422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772235870361</t>
+    <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885261535645</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">8.75040435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92067337036133</t>
+    <t xml:space="preserve">8.92067432403564</t>
   </si>
   <si>
     <t xml:space="preserve">8.93548011779785</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261352539062</t>
+    <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">4.33078384399414</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">4.58989000320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62690591812134</t>
+    <t xml:space="preserve">4.62690544128418</t>
   </si>
   <si>
     <t xml:space="preserve">4.69723463058472</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">4.10128879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13090085983276</t>
+    <t xml:space="preserve">4.13090133666992</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">4.16791677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17161798477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2456488609314</t>
+    <t xml:space="preserve">4.17161846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24564838409424</t>
   </si>
   <si>
     <t xml:space="preserve">4.24934959411621</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033668518066</t>
+    <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35669422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39741086959839</t>
+    <t xml:space="preserve">4.35669469833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39741134643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.36039590835571</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758710861206</t>
+    <t xml:space="preserve">4.10499095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.17902135848999</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687093734741</t>
+    <t xml:space="preserve">4.05687046051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58862805366516</t>
+    <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">3.86069011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07537841796875</t>
+    <t xml:space="preserve">4.07537889480591</t>
   </si>
   <si>
     <t xml:space="preserve">4.04206418991089</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9051079750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654198646545</t>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433281898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654246330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.95322823524475</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">3.88660049438477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86439180374146</t>
+    <t xml:space="preserve">3.8643913269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.79036092758179</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50164222717285</t>
+    <t xml:space="preserve">3.50164198875427</t>
   </si>
   <si>
     <t xml:space="preserve">3.53310513496399</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">3.55716466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52014970779419</t>
+    <t xml:space="preserve">3.52014994621277</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313450813293</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">3.51459717750549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57382154464722</t>
+    <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
     <t xml:space="preserve">3.62009072303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61638975143433</t>
+    <t xml:space="preserve">3.61638927459717</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42391014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.42391037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33137226104736</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">3.24623703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14999747276306</t>
+    <t xml:space="preserve">3.14999771118164</t>
   </si>
   <si>
     <t xml:space="preserve">3.2018187046051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26474475860596</t>
+    <t xml:space="preserve">3.26474452018738</t>
   </si>
   <si>
     <t xml:space="preserve">3.10187745094299</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88718891143799</t>
+    <t xml:space="preserve">2.88718914985657</t>
   </si>
   <si>
     <t xml:space="preserve">3.05005621910095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.007488489151</t>
+    <t xml:space="preserve">3.00748872756958</t>
   </si>
   <si>
     <t xml:space="preserve">2.98342871665955</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">2.8649799823761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683058738708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503872871399</t>
+    <t xml:space="preserve">2.86683082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503896713257</t>
   </si>
   <si>
     <t xml:space="preserve">2.90569663047791</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014457702637</t>
+    <t xml:space="preserve">2.90014433860779</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981538772583</t>
+    <t xml:space="preserve">2.82981514930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059102058411</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999186515808</t>
+    <t xml:space="preserve">2.52999210357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.49852919578552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60032081604004</t>
+    <t xml:space="preserve">2.60032105445862</t>
   </si>
   <si>
     <t xml:space="preserve">2.49297690391541</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61512732505798</t>
+    <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
     <t xml:space="preserve">2.57811164855957</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27273607254028</t>
+    <t xml:space="preserve">2.2727358341217</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41339421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34676647186279</t>
+    <t xml:space="preserve">2.4133939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34676671028137</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790066719055</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">2.28569149971008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30234813690186</t>
+    <t xml:space="preserve">2.30234789848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.35416960716248</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25422835350037</t>
+    <t xml:space="preserve">2.25422859191895</t>
   </si>
   <si>
     <t xml:space="preserve">2.26718378067017</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">2.22461628913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25607919692993</t>
+    <t xml:space="preserve">2.25607895851135</t>
   </si>
   <si>
     <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24312400817871</t>
+    <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
     <t xml:space="preserve">2.18204855918884</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">2.21351170539856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13022756576538</t>
+    <t xml:space="preserve">2.1302273273468</t>
   </si>
   <si>
     <t xml:space="preserve">2.15798902511597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14873480796814</t>
+    <t xml:space="preserve">2.14873504638672</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912274360657</t>
+    <t xml:space="preserve">2.11912298202515</t>
   </si>
   <si>
     <t xml:space="preserve">2.12652564048767</t>
@@ -3647,13 +3647,13 @@
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132355690002</t>
+    <t xml:space="preserve">1.90132367610931</t>
   </si>
   <si>
     <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87255322933197</t>
+    <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
     <t xml:space="preserve">1.91036558151245</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84953653812408</t>
+    <t xml:space="preserve">1.84953665733337</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
@@ -3671,25 +3671,25 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679875850677</t>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556956291199</t>
+    <t xml:space="preserve">1.8955694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8372061252594</t>
+    <t xml:space="preserve">1.83720624446869</t>
   </si>
   <si>
     <t xml:space="preserve">1.78541910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7615807056427</t>
+    <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.770623087883</t>
@@ -3701,34 +3701,34 @@
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85857880115509</t>
+    <t xml:space="preserve">1.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311057567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.958864569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078749656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03695607185364</t>
+    <t xml:space="preserve">1.95311045646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95886468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03695631027222</t>
   </si>
   <si>
     <t xml:space="preserve">1.98023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03942227363586</t>
+    <t xml:space="preserve">2.03942203521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559084892273</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23382925987244</t>
+    <t xml:space="preserve">2.24204897880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
     <t xml:space="preserve">2.14135217666626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15573763847351</t>
+    <t xml:space="preserve">2.15573740005493</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">2.2728750705719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904033660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30781030654907</t>
+    <t xml:space="preserve">2.27904009819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30781054496765</t>
   </si>
   <si>
     <t xml:space="preserve">2.34685635566711</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">2.35096645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34274625778198</t>
+    <t xml:space="preserve">2.3427460193634</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25848937034607</t>
+    <t xml:space="preserve">2.25848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">2.22766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16190266609192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14546251296997</t>
+    <t xml:space="preserve">2.1619029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14546227455139</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944379806519</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">2.3550763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41056251525879</t>
+    <t xml:space="preserve">2.41056227684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5276997089386</t>
+    <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
     <t xml:space="preserve">2.55236053466797</t>
@@ -3860,16 +3860,16 @@
     <t xml:space="preserve">2.54003000259399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45988368988037</t>
+    <t xml:space="preserve">2.45988345146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54208493232727</t>
+    <t xml:space="preserve">2.52153468132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
     <t xml:space="preserve">2.51125955581665</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">2.44755339622498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50920438766479</t>
+    <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
     <t xml:space="preserve">2.5585253238678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55647039413452</t>
+    <t xml:space="preserve">2.55647015571594</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3905,25 +3905,25 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786447525024</t>
+    <t xml:space="preserve">2.75786423683167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087359428406</t>
+    <t xml:space="preserve">2.72087383270264</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250708580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66744256019592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67155289649963</t>
+    <t xml:space="preserve">2.63250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674427986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67155265808105</t>
   </si>
   <si>
     <t xml:space="preserve">2.68799304962158</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">2.70443344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72498393058777</t>
+    <t xml:space="preserve">2.72498369216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">2.60784649848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62634181976318</t>
+    <t xml:space="preserve">2.6263415813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.70648837089539</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">2.62428689002991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59757137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60579133033752</t>
+    <t xml:space="preserve">2.59757161140442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6057915687561</t>
   </si>
   <si>
     <t xml:space="preserve">2.62017679214478</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">2.69621324539185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79485535621643</t>
+    <t xml:space="preserve">2.79485511779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.86678171157837</t>
@@ -4034,28 +4034,28 @@
     <t xml:space="preserve">3.00035953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99419403076172</t>
+    <t xml:space="preserve">2.99419379234314</t>
   </si>
   <si>
     <t xml:space="preserve">2.99830436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89760756492615</t>
+    <t xml:space="preserve">2.89760732650757</t>
   </si>
   <si>
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553418159485</t>
+    <t xml:space="preserve">2.82773566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553442001343</t>
   </si>
   <si>
     <t xml:space="preserve">2.61606669425964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68388295173645</t>
+    <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4067,13 +4067,13 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896521568298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79074501991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99213910102844</t>
+    <t xml:space="preserve">2.79896545410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7907452583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99213933944702</t>
   </si>
   <si>
     <t xml:space="preserve">2.99008417129517</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">3.03324007987976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90582752227783</t>
+    <t xml:space="preserve">2.90582728385925</t>
   </si>
   <si>
     <t xml:space="preserve">2.9633686542511</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86883664131165</t>
+    <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.82568073272705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92226767539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88733196258545</t>
+    <t xml:space="preserve">2.92226791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88733220100403</t>
   </si>
   <si>
     <t xml:space="preserve">2.8893871307373</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">3.05995559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98186421394348</t>
+    <t xml:space="preserve">2.9818639755249</t>
   </si>
   <si>
     <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94281816482544</t>
+    <t xml:space="preserve">2.94281792640686</t>
   </si>
   <si>
     <t xml:space="preserve">2.92432260513306</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">2.90442943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92211222648621</t>
+    <t xml:space="preserve">2.92211246490479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98621320724487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04147267341614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10336303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06136584281921</t>
+    <t xml:space="preserve">3.04147243499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1033627986908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06136608123779</t>
   </si>
   <si>
     <t xml:space="preserve">3.11883544921875</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">3.07241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09452128410339</t>
+    <t xml:space="preserve">3.09452152252197</t>
   </si>
   <si>
     <t xml:space="preserve">3.07020735740662</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.97958207130432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97074031829834</t>
+    <t xml:space="preserve">2.97074055671692</t>
   </si>
   <si>
     <t xml:space="preserve">2.91548109054565</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.93316435813904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92874360084534</t>
+    <t xml:space="preserve">2.92874336242676</t>
   </si>
   <si>
     <t xml:space="preserve">2.90221905708313</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">2.90000867843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87790489196777</t>
+    <t xml:space="preserve">2.87790513038635</t>
   </si>
   <si>
     <t xml:space="preserve">2.86464262008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83369731903076</t>
+    <t xml:space="preserve">2.83369755744934</t>
   </si>
   <si>
     <t xml:space="preserve">2.81822490692139</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">2.69002318382263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60160827636719</t>
+    <t xml:space="preserve">2.60160851478577</t>
   </si>
   <si>
     <t xml:space="preserve">2.66791939735413</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">2.68560242652893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62813282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65023636817932</t>
+    <t xml:space="preserve">2.62813305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6502366065979</t>
   </si>
   <si>
     <t xml:space="preserve">2.60381865501404</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">2.5551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47340679168701</t>
+    <t xml:space="preserve">2.47340655326843</t>
   </si>
   <si>
     <t xml:space="preserve">2.44909262657166</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">2.47119641304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47782731056213</t>
+    <t xml:space="preserve">2.47782754898071</t>
   </si>
   <si>
     <t xml:space="preserve">2.46014451980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624245643616</t>
+    <t xml:space="preserve">2.56624221801758</t>
   </si>
   <si>
     <t xml:space="preserve">2.55961132049561</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">2.54855942726135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50877261161804</t>
+    <t xml:space="preserve">2.50877285003662</t>
   </si>
   <si>
     <t xml:space="preserve">2.53087639808655</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">2.32531189918518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24529647827148</t>
+    <t xml:space="preserve">2.24529623985291</t>
   </si>
   <si>
     <t xml:space="preserve">2.19932055473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15422916412354</t>
+    <t xml:space="preserve">2.15422892570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.14715576171875</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">2.17633247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29746127128601</t>
+    <t xml:space="preserve">2.29746103286743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38720226287842</t>
@@ -4367,40 +4367,40 @@
     <t xml:space="preserve">2.33813214302063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51894044876099</t>
+    <t xml:space="preserve">2.51894021034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.46854400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42345237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51319336891174</t>
+    <t xml:space="preserve">2.42345213890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51319360733032</t>
   </si>
   <si>
     <t xml:space="preserve">2.57287359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52026677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56712651252747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5507698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53794956207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54723310470581</t>
+    <t xml:space="preserve">2.52026653289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56712675094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55076956748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53794980049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54723334312439</t>
   </si>
   <si>
     <t xml:space="preserve">2.70461177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78109049797058</t>
+    <t xml:space="preserve">2.78109073638916</t>
   </si>
   <si>
     <t xml:space="preserve">2.75854468345642</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">2.79302644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75633454322815</t>
+    <t xml:space="preserve">2.75633430480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.77357530593872</t>
@@ -4436,13 +4436,13 @@
     <t xml:space="preserve">2.91327095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84253907203674</t>
+    <t xml:space="preserve">2.84253883361816</t>
   </si>
   <si>
     <t xml:space="preserve">2.93935322761536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94112157821655</t>
+    <t xml:space="preserve">2.94112133979797</t>
   </si>
   <si>
     <t xml:space="preserve">2.92343854904175</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">2.94554233551025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785930633545</t>
+    <t xml:space="preserve">2.92785954475403</t>
   </si>
   <si>
     <t xml:space="preserve">2.93537449836731</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">2.89249348640442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88851475715637</t>
+    <t xml:space="preserve">2.88851451873779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93006944656372</t>
@@ -4475,25 +4475,25 @@
     <t xml:space="preserve">2.88011527061462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92741751670837</t>
+    <t xml:space="preserve">2.92741727828979</t>
   </si>
   <si>
     <t xml:space="preserve">3.02378964424133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03926205635071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03086256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96189904212952</t>
+    <t xml:space="preserve">3.03926229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03086280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96189880371094</t>
   </si>
   <si>
     <t xml:space="preserve">2.93493247032166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89824056625366</t>
+    <t xml:space="preserve">2.89824032783508</t>
   </si>
   <si>
     <t xml:space="preserve">2.91724944114685</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">2.9106183052063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91769170761108</t>
+    <t xml:space="preserve">2.9176914691925</t>
   </si>
   <si>
     <t xml:space="preserve">2.9256489276886</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">2.98444485664368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02246308326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00168561935425</t>
+    <t xml:space="preserve">3.02246332168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00168585777283</t>
   </si>
   <si>
     <t xml:space="preserve">2.95438385009766</t>
@@ -4538,13 +4538,13 @@
     <t xml:space="preserve">2.73865151405334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67101383209229</t>
+    <t xml:space="preserve">2.67101407051086</t>
   </si>
   <si>
     <t xml:space="preserve">2.68737077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6608464717865</t>
+    <t xml:space="preserve">2.66084623336792</t>
   </si>
   <si>
     <t xml:space="preserve">2.68869686126709</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.64537382125854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72052645683289</t>
+    <t xml:space="preserve">2.72052621841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.70947456359863</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">2.62327003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5870201587677</t>
+    <t xml:space="preserve">2.58701992034912</t>
   </si>
   <si>
     <t xml:space="preserve">2.60426068305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57729434967041</t>
+    <t xml:space="preserve">2.57729411125183</t>
   </si>
   <si>
     <t xml:space="preserve">2.58171510696411</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">2.58083081245422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59497714042664</t>
+    <t xml:space="preserve">2.59497737884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.65288901329041</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">2.69488620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69223356246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6413950920105</t>
+    <t xml:space="preserve">2.69223380088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64139485359192</t>
   </si>
   <si>
     <t xml:space="preserve">2.58480954170227</t>
@@ -4622,19 +4622,19 @@
     <t xml:space="preserve">2.70549583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7116847038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67985558509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85049605369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84342312812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93183779716492</t>
+    <t xml:space="preserve">2.71168494224548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67985534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85049629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84342336654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9318380355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.91946005821228</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">2.94952082633972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87878918647766</t>
+    <t xml:space="preserve">2.87878894805908</t>
   </si>
   <si>
     <t xml:space="preserve">3.13872885704041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">3.30671715736389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42519330978394</t>
+    <t xml:space="preserve">3.42519307136536</t>
   </si>
   <si>
     <t xml:space="preserve">3.41988825798035</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">3.34561967849731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33501005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43933963775635</t>
+    <t xml:space="preserve">3.33500981330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43933939933777</t>
   </si>
   <si>
     <t xml:space="preserve">3.36507105827332</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">3.29787564277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30848550796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32793664932251</t>
+    <t xml:space="preserve">3.30848574638367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32793688774109</t>
   </si>
   <si>
     <t xml:space="preserve">3.41458320617676</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">3.41104674339294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57019376754761</t>
+    <t xml:space="preserve">3.49592518806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57019352912903</t>
   </si>
   <si>
     <t xml:space="preserve">3.57372999191284</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">3.50123000144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5259861946106</t>
+    <t xml:space="preserve">3.50653481483459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52598595619202</t>
   </si>
   <si>
     <t xml:space="preserve">3.61616945266724</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">3.61793756484985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59848642349243</t>
+    <t xml:space="preserve">3.59848666191101</t>
   </si>
   <si>
     <t xml:space="preserve">3.63031578063965</t>
@@ -4748,28 +4748,28 @@
     <t xml:space="preserve">3.7045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77708411216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82129192352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84074306488037</t>
+    <t xml:space="preserve">3.77708435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84074282646179</t>
   </si>
   <si>
     <t xml:space="preserve">3.84781646728516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85488939285278</t>
+    <t xml:space="preserve">3.85488963127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.87610912322998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8584258556366</t>
+    <t xml:space="preserve">3.75232815742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85842609405518</t>
   </si>
   <si>
     <t xml:space="preserve">3.65860843658447</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">3.46409559249878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57903480529785</t>
+    <t xml:space="preserve">3.57903504371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.52775454521179</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">3.4941565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52952289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62324237823486</t>
+    <t xml:space="preserve">3.52952265739441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62324261665344</t>
   </si>
   <si>
     <t xml:space="preserve">3.61440086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6869010925293</t>
+    <t xml:space="preserve">3.68690133094788</t>
   </si>
   <si>
     <t xml:space="preserve">3.65684032440186</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">3.6957426071167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7452552318573</t>
+    <t xml:space="preserve">3.74525499343872</t>
   </si>
   <si>
     <t xml:space="preserve">3.75056004524231</t>
@@ -4826,19 +4826,19 @@
     <t xml:space="preserve">3.80714583396912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05824422836304</t>
+    <t xml:space="preserve">4.20501232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05824375152588</t>
   </si>
   <si>
     <t xml:space="preserve">4.09184122085571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1201343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16787815093994</t>
+    <t xml:space="preserve">4.12013387680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1678786277771</t>
   </si>
   <si>
     <t xml:space="preserve">4.07592678070068</t>
@@ -5655,6 +5655,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.92199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89599990844727</t>
   </si>
 </sst>
 </file>
@@ -71695,7 +71698,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6912384259</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>283676</v>
@@ -71716,6 +71719,32 @@
         <v>1880</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6911458333</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>429423</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>3.96600008010864</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>3.88199996948242</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>3.89599990844727</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1881</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356538772583</t>
+    <t xml:space="preserve">12.2356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">10.9101800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.076696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1366443634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6770582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3107194900513</t>
+    <t xml:space="preserve">11.0766973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.136643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302526473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6770572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3107204437256</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907381057739</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65797328948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2507734298706</t>
+    <t xml:space="preserve">9.65797424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2507743835449</t>
   </si>
   <si>
     <t xml:space="preserve">10.7370042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3906488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5438442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.257435798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2707567214966</t>
+    <t xml:space="preserve">10.3906478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5438432693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2707557678223</t>
   </si>
   <si>
     <t xml:space="preserve">10.4838972091675</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">9.9110803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54474449157715</t>
+    <t xml:space="preserve">9.54474258422852</t>
   </si>
   <si>
     <t xml:space="preserve">9.77120494842529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2174701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639158248901</t>
+    <t xml:space="preserve">10.2174711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639148712158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6171102523804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172916412354</t>
+    <t xml:space="preserve">10.417290687561</t>
   </si>
   <si>
     <t xml:space="preserve">10.7703065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9301633834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96436500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4905586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7236814498901</t>
+    <t xml:space="preserve">10.9301624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96436595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4905576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7236833572388</t>
   </si>
   <si>
     <t xml:space="preserve">10.9434843063354</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">11.3431243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6495141983032</t>
+    <t xml:space="preserve">11.6495161056519</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898397445679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0624771118164</t>
+    <t xml:space="preserve">12.0624761581421</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289934158325</t>
+    <t xml:space="preserve">12.2289943695068</t>
   </si>
   <si>
     <t xml:space="preserve">12.475438117981</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">12.4554576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3422269821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4621171951294</t>
+    <t xml:space="preserve">12.3422241210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4621181488037</t>
   </si>
   <si>
     <t xml:space="preserve">12.5553665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019906997681</t>
+    <t xml:space="preserve">12.6019926071167</t>
   </si>
   <si>
     <t xml:space="preserve">12.1823701858521</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">11.696138381958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695867538452</t>
+    <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0757970809937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.915940284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1890296936035</t>
+    <t xml:space="preserve">11.9159421920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1890287399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">11.0633764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6561756134033</t>
+    <t xml:space="preserve">11.656174659729</t>
   </si>
   <si>
     <t xml:space="preserve">11.955906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8217935562134</t>
+    <t xml:space="preserve">12.2689580917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217926025391</t>
   </si>
   <si>
     <t xml:space="preserve">12.9217023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350252151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.101541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1281843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2480764389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1947917938232</t>
+    <t xml:space="preserve">12.9350261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1015424728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2480773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1947898864746</t>
   </si>
   <si>
     <t xml:space="preserve">13.1814708709717</t>
@@ -257,73 +257,73 @@
     <t xml:space="preserve">13.16148853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3613061904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882205963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9816484451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5620288848877</t>
+    <t xml:space="preserve">13.3613080978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882196426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9816493988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6885805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5620279312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.8817405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8617582321167</t>
+    <t xml:space="preserve">12.8617572784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.8884000778198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0482559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4088315963745</t>
+    <t xml:space="preserve">13.0482578277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4088306427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7218837738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685098648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9150428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221435546875</t>
+    <t xml:space="preserve">12.4221534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7218828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9150419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2214336395264</t>
   </si>
   <si>
     <t xml:space="preserve">13.1344079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3887948989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159883499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6230974197388</t>
+    <t xml:space="preserve">13.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6230983734131</t>
   </si>
   <si>
     <t xml:space="preserve">13.5226821899414</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">13.5561532974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4222660064697</t>
+    <t xml:space="preserve">13.4222640991211</t>
   </si>
   <si>
     <t xml:space="preserve">13.3620147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3553218841553</t>
+    <t xml:space="preserve">13.3553228378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
@@ -347,46 +347,46 @@
     <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3017663955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2749891281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156099319458</t>
+    <t xml:space="preserve">13.3017673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2749900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194655418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6591053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833864212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156108856201</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620553970337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766916275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524105072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4515771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1411008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850898742676</t>
+    <t xml:space="preserve">11.7218894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524095535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4515790939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850889205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.1487054824829</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">10.4834251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7177286148071</t>
+    <t xml:space="preserve">10.7177295684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0482883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4432601928711</t>
+    <t xml:space="preserve">10.0482902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">11.1193933486938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4741954803467</t>
+    <t xml:space="preserve">11.474196434021</t>
   </si>
   <si>
     <t xml:space="preserve">11.2599744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260890960693</t>
+    <t xml:space="preserve">11.126088142395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">10.9252548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783941268921</t>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0616788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1754817962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88762378692627</t>
+    <t xml:space="preserve">10.0616779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
     <t xml:space="preserve">9.06421375274658</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">8.93032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80313205718994</t>
+    <t xml:space="preserve">8.67593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479679107666</t>
+    <t xml:space="preserve">9.20479583740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.37215518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25835037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33868312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23826885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31860065460205</t>
+    <t xml:space="preserve">9.25835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23826789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13115787506104</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">9.2315731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6332368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55959987640381</t>
+    <t xml:space="preserve">9.63323783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79390335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
@@ -518,31 +518,31 @@
     <t xml:space="preserve">9.43909931182861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56629276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265575408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53951549530029</t>
+    <t xml:space="preserve">9.56629371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53951644897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.8273754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76042938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78720760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87423610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6734037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760334014893</t>
+    <t xml:space="preserve">9.76043128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78720855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87423419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67340469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.17132377624512</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">9.07090759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08429622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31190586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36546230316162</t>
+    <t xml:space="preserve">9.08429527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31190490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35207366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36546039581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.3855447769165</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">9.24496269226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03743648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70941066741943</t>
+    <t xml:space="preserve">9.03743553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">8.72279930114746</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.76965999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74957656860352</t>
+    <t xml:space="preserve">8.74957752227783</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78974437713623</t>
+    <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.71610450744629</t>
@@ -605,61 +605,61 @@
     <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2006368637085</t>
+    <t xml:space="preserve">8.20063591003418</t>
   </si>
   <si>
     <t xml:space="preserve">8.10022068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1203031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82574939727783</t>
+    <t xml:space="preserve">8.12030410766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82574987411499</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583425521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63161277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62491846084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66508483886719</t>
+    <t xml:space="preserve">7.86591672897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6316123008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62491798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
     <t xml:space="preserve">7.74541664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71194553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6918625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48433589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64500141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.651695728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68516778945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95963716506958</t>
+    <t xml:space="preserve">7.7119460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48433542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64500093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68516731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9596381187439</t>
   </si>
   <si>
     <t xml:space="preserve">8.12699794769287</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9236307144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2114896774292</t>
+    <t xml:space="preserve">8.92363166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21149063110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.09768581390381</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">11.9963598251343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1168594360352</t>
+    <t xml:space="preserve">12.1168575286865</t>
   </si>
   <si>
     <t xml:space="preserve">11.9294147491455</t>
@@ -689,100 +689,100 @@
     <t xml:space="preserve">11.8691654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0499153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833061218262</t>
+    <t xml:space="preserve">12.0499134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833080291748</t>
   </si>
   <si>
     <t xml:space="preserve">13.7971525192261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6967344284058</t>
+    <t xml:space="preserve">13.6967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">13.7569856643677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8975677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8908729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9578170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6004791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0180692672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0582332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9712085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0917053222656</t>
+    <t xml:space="preserve">13.8975687026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8908739089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904577255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6004800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0180673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582342147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9712076187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0917043685913</t>
   </si>
   <si>
     <t xml:space="preserve">14.3126201629639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2858438491821</t>
+    <t xml:space="preserve">14.2858428955078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1385679244995</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817234992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.455738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544904708862</t>
+    <t xml:space="preserve">14.1251783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8172359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544895172119</t>
   </si>
   <si>
     <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.208044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9268808364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7528257369995</t>
+    <t xml:space="preserve">13.2080450057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9268798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7528266906738</t>
   </si>
   <si>
     <t xml:space="preserve">12.8264646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9737415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067983627319</t>
+    <t xml:space="preserve">12.9737405776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067974090576</t>
   </si>
   <si>
     <t xml:space="preserve">13.1611843109131</t>
@@ -800,64 +800,64 @@
     <t xml:space="preserve">13.1879634857178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3419351577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339918136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8599348068237</t>
+    <t xml:space="preserve">13.3419322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339908599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.859935760498</t>
   </si>
   <si>
     <t xml:space="preserve">12.9871292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0072135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0473785400391</t>
+    <t xml:space="preserve">13.007212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0473794937134</t>
   </si>
   <si>
     <t xml:space="preserve">13.0206031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9201850891113</t>
+    <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
     <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3754043579102</t>
+    <t xml:space="preserve">13.3754062652588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3486289978027</t>
+    <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
     <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1745719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406847000122</t>
+    <t xml:space="preserve">13.1745729446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406856536865</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867139816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8398542404175</t>
+    <t xml:space="preserve">12.8867130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.933575630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8398532867432</t>
   </si>
   <si>
     <t xml:space="preserve">12.9001035690308</t>
@@ -866,25 +866,25 @@
     <t xml:space="preserve">12.9536581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8532419204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858835220337</t>
+    <t xml:space="preserve">12.8532438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858825683594</t>
   </si>
   <si>
     <t xml:space="preserve">12.5386047363281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.310996055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3310785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4047193527222</t>
+    <t xml:space="preserve">12.3109951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3310794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4047164916992</t>
   </si>
   <si>
     <t xml:space="preserve">12.2708301544189</t>
@@ -899,40 +899,40 @@
     <t xml:space="preserve">11.8624706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1771087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1436367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800210952759</t>
+    <t xml:space="preserve">12.1771078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862977981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.946964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653839111328</t>
+    <t xml:space="preserve">12.5653848648071</t>
   </si>
   <si>
     <t xml:space="preserve">12.4448833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637191772461</t>
+    <t xml:space="preserve">12.1637201309204</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.558690071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649686813354</t>
+    <t xml:space="preserve">12.3913297653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5586891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649667739868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189384460449</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2842178344727</t>
+    <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181060791016</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">12.1034698486328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0900821685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0633029937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5519933700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6724939346313</t>
+    <t xml:space="preserve">12.0900802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0633039474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5519943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6724948883057</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176898956299</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">12.0030536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813064575195</t>
+    <t xml:space="preserve">11.5813074111938</t>
   </si>
   <si>
     <t xml:space="preserve">11.6147785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076694488525</t>
+    <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7084989547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6817235946655</t>
+    <t xml:space="preserve">11.5880002975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7085008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6817226409912</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942789077759</t>
@@ -1001,19 +1001,19 @@
     <t xml:space="preserve">11.5210571289062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.634861946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7687501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7018060684204</t>
+    <t xml:space="preserve">11.7151937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6348609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7018051147461</t>
   </si>
   <si>
     <t xml:space="preserve">11.4474191665649</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2265033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7043409347534</t>
+    <t xml:space="preserve">11.2265043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7779808044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7043399810791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7980613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9453401565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.139476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1930322647095</t>
+    <t xml:space="preserve">10.9453392028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1394758224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1930313110352</t>
   </si>
   <si>
     <t xml:space="preserve">11.1461706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0658388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1327810287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528654098511</t>
+    <t xml:space="preserve">11.0658397674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1327819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528663635254</t>
   </si>
   <si>
     <t xml:space="preserve">11.0993099212646</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112699508667</t>
+    <t xml:space="preserve">11.1126985549927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206399917603</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2198104858398</t>
+    <t xml:space="preserve">11.2198095321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.300142288208</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">11.4005575180054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541139602661</t>
+    <t xml:space="preserve">11.4608087539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541130065918</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336143493652</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">11.0524492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721155166626</t>
+    <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3897047042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1620950698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2156505584717</t>
+    <t xml:space="preserve">10.3897037506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1620941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2156496047974</t>
   </si>
   <si>
     <t xml:space="preserve">10.3361482620239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2625112533569</t>
+    <t xml:space="preserve">10.4901208877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3428430557251</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">10.3562326431274</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076404571533</t>
+    <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">9.80059719085693</t>
@@ -1148,25 +1148,25 @@
     <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68679428100586</t>
+    <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
     <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72026538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74704265594482</t>
+    <t xml:space="preserve">9.72026443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70018100738525</t>
+    <t xml:space="preserve">9.75373554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70018196105957</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
@@ -1175,25 +1175,25 @@
     <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650785446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700374603271</t>
+    <t xml:space="preserve">10.6507863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700365066528</t>
   </si>
   <si>
     <t xml:space="preserve">10.6708679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6641750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3763151168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1888723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.275899887085</t>
+    <t xml:space="preserve">10.664174079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.376314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2759008407593</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357320785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570640563965</t>
+    <t xml:space="preserve">10.2357330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570650100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.5102033615112</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65332126617432</t>
+    <t xml:space="preserve">10.2089557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65331935882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.52612686157227</t>
@@ -1229,31 +1229,31 @@
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8474588394165</t>
+    <t xml:space="preserve">9.84745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">10.2959823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436754226685</t>
+    <t xml:space="preserve">10.5436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.7712850570679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5972309112549</t>
+    <t xml:space="preserve">10.5972299575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.8583116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855060577393</t>
+    <t xml:space="preserve">10.9855051040649</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587278366089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7311191558838</t>
+    <t xml:space="preserve">10.7311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">10.82483959198</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">11.1796426773071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2465858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.2465867996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9118671417236</t>
+    <t xml:space="preserve">10.9118661880493</t>
   </si>
   <si>
     <t xml:space="preserve">10.9051733016968</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">10.7277708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4633417129517</t>
+    <t xml:space="preserve">10.463342666626</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871877670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.289288520813</t>
+    <t xml:space="preserve">10.5871887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2892875671387</t>
   </si>
   <si>
     <t xml:space="preserve">10.2658576965332</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">10.3696212768555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135498046875</t>
+    <t xml:space="preserve">10.5135507583618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6206607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8616590499878</t>
+    <t xml:space="preserve">10.8616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.6407442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106195449829</t>
+    <t xml:space="preserve">10.6106185913086</t>
   </si>
   <si>
     <t xml:space="preserve">10.5503702163696</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139650344849</t>
+    <t xml:space="preserve">10.533634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139659881592</t>
   </si>
   <si>
     <t xml:space="preserve">10.6240072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4097871780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1729497909546</t>
+    <t xml:space="preserve">10.4097881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
     <t xml:space="preserve">10.9821586608887</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">10.5269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261070251465</t>
+    <t xml:space="preserve">10.3261079788208</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3394956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.36292552948</t>
+    <t xml:space="preserve">10.3394947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1520528793335</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">9.94452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0349016189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0951499938965</t>
+    <t xml:space="preserve">10.0349006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0951509475708</t>
   </si>
   <si>
     <t xml:space="preserve">10.9788103103638</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">11.0357131958008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1762962341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8717002868652</t>
+    <t xml:space="preserve">11.1762952804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8717012405396</t>
   </si>
   <si>
     <t xml:space="preserve">10.868353843689</t>
@@ -1412,70 +1412,70 @@
     <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0223245620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.025671005249</t>
+    <t xml:space="preserve">11.0223255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9553813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
     <t xml:space="preserve">11.082573890686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.952033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0290193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0758800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.28675365448</t>
+    <t xml:space="preserve">10.9520330429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0290184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0758790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9352970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5068559646606</t>
+    <t xml:space="preserve">10.9352960586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.506856918335</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729677200317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1721353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.245774269104</t>
+    <t xml:space="preserve">10.1721363067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2457752227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683736801147</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74369621276855</t>
+    <t xml:space="preserve">9.74369525909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.28847503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6700553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72695732116699</t>
+    <t xml:space="preserve">9.34537887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67005634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72695922851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633399963379</t>
+    <t xml:space="preserve">9.57633495330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.48596096038818</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6165018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54286289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57298755645752</t>
+    <t xml:space="preserve">9.61650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57298851013184</t>
   </si>
   <si>
     <t xml:space="preserve">9.56964015960693</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49600315093994</t>
+    <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.62319564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60980606079102</t>
+    <t xml:space="preserve">9.60980701446533</t>
   </si>
   <si>
     <t xml:space="preserve">8.83660411834717</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949409484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350700378418</t>
+    <t xml:space="preserve">8.68932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72949314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350605010986</t>
   </si>
   <si>
     <t xml:space="preserve">9.14119911193848</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">9.13785171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45583629608154</t>
+    <t xml:space="preserve">9.45583534240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28178024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61315441131592</t>
+    <t xml:space="preserve">9.28178119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.71691799163818</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">9.46922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37550258636475</t>
+    <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.54621028900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31525230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7328405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80647850036621</t>
+    <t xml:space="preserve">9.31525325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26504611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73284149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80647945404053</t>
   </si>
   <si>
     <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02070045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8533411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338138580322</t>
+    <t xml:space="preserve">9.02070140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338043212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003398895264</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.88011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82656192779541</t>
+    <t xml:space="preserve">8.82656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27427387237549</t>
+    <t xml:space="preserve">8.2742748260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.24080276489258</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5387020111084</t>
+    <t xml:space="preserve">8.47175884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870296478271</t>
   </si>
   <si>
     <t xml:space="preserve">8.78639602661133</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13450527191162</t>
+    <t xml:space="preserve">9.1345043182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00731086730957</t>
@@ -1655,31 +1655,31 @@
     <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01400661468506</t>
+    <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
     <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22822666168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94706153869629</t>
+    <t xml:space="preserve">9.22822570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94706058502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.0006160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12780952453613</t>
+    <t xml:space="preserve">9.01735210418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.03408813476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66589546203613</t>
+    <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75292491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90689563751221</t>
+    <t xml:space="preserve">8.62907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75292301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90689468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.29517078399658</t>
@@ -1712,43 +1712,43 @@
     <t xml:space="preserve">9.30855941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46587753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11107444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.294358253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31109428405762</t>
+    <t xml:space="preserve">9.50604343414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46587657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11107349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3110933303833</t>
   </si>
   <si>
     <t xml:space="preserve">8.34456539154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32448291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24749755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48514842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49184226989746</t>
+    <t xml:space="preserve">8.32448387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24749660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48514747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.93367290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19810104370117</t>
+    <t xml:space="preserve">9.19810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">8.25753879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56548118591309</t>
+    <t xml:space="preserve">8.56548023223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.50188446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75627136230469</t>
+    <t xml:space="preserve">8.75627040863037</t>
   </si>
   <si>
     <t xml:space="preserve">8.82321548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84329795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74622821807861</t>
+    <t xml:space="preserve">8.84329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74622917175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.18471240997314</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">9.42236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26169872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29851818084717</t>
+    <t xml:space="preserve">9.26169681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.44914054870605</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">9.91105461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84411144256592</t>
+    <t xml:space="preserve">9.8441104888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.522780418396</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">9.45918273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44244575500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41901588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.44244766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41901683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456886291504</t>
@@ -1820,31 +1820,31 @@
     <t xml:space="preserve">9.41566848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35876655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27174091339111</t>
+    <t xml:space="preserve">9.35876750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2717399597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.54874515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7127571105957</t>
+    <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.8098258972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10437965393066</t>
+    <t xml:space="preserve">9.10438060760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52947330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51943302154541</t>
+    <t xml:space="preserve">9.52947425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51943206787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.42905902862549</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">9.24830913543701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47257041931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55625247955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4257116317749</t>
+    <t xml:space="preserve">9.47257137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55625152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42571067810059</t>
   </si>
   <si>
     <t xml:space="preserve">9.15124034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789295196533</t>
+    <t xml:space="preserve">9.16128349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789390563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.43240547180176</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">9.33533668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24161434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.24161624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">9.50939083099365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73700046539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9210958480835</t>
+    <t xml:space="preserve">9.73699951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79725074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92109680175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.90770816802979</t>
@@ -1919,70 +1919,70 @@
     <t xml:space="preserve">9.77716636657715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71022319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62988948822021</t>
+    <t xml:space="preserve">9.7102222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62989044189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.38889217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76631355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62573146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73953533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77300643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961875915527</t>
+    <t xml:space="preserve">9.45248794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76631259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62573051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73953628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7730073928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961780548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.02404689788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4056282043457</t>
+    <t xml:space="preserve">9.40562725067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.63993167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70687484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94787311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76712608337402</t>
+    <t xml:space="preserve">9.70687580108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94787406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76712512969971</t>
   </si>
   <si>
     <t xml:space="preserve">9.66670894622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53282165527344</t>
+    <t xml:space="preserve">9.53282070159912</t>
   </si>
   <si>
     <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35542011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20144939422607</t>
+    <t xml:space="preserve">9.35541915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20144844055176</t>
   </si>
   <si>
     <t xml:space="preserve">9.10103321075439</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9437141418457</t>
+    <t xml:space="preserve">8.94371318817139</t>
   </si>
   <si>
     <t xml:space="preserve">8.98053359985352</t>
@@ -2000,28 +2000,28 @@
     <t xml:space="preserve">8.99057579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9035472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68263339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67928504943848</t>
+    <t xml:space="preserve">8.87342357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90354824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67928600311279</t>
   </si>
   <si>
     <t xml:space="preserve">10.0415954589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86084651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8240270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81063842773438</t>
+    <t xml:space="preserve">9.86084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82402801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81063938140869</t>
   </si>
   <si>
     <t xml:space="preserve">9.82067966461182</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">8.74288272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79308986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65250778198242</t>
+    <t xml:space="preserve">8.7930908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65250873565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87677001953125</t>
+    <t xml:space="preserve">8.87677097320557</t>
   </si>
   <si>
     <t xml:space="preserve">8.88681221008301</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">9.060866355896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1545877456665</t>
+    <t xml:space="preserve">9.15458869934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.97383880615234</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">8.99726867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92697811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06756019592285</t>
+    <t xml:space="preserve">8.92697906494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06756114959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.829909324646</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">8.33787155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28431606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377616882324</t>
+    <t xml:space="preserve">8.28431701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377521514893</t>
   </si>
   <si>
     <t xml:space="preserve">7.9897632598877</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624948501587</t>
+    <t xml:space="preserve">7.94624900817871</t>
   </si>
   <si>
     <t xml:space="preserve">7.95629119873047</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02323532104492</t>
+    <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
     <t xml:space="preserve">7.96633148193359</t>
@@ -2162,40 +2162,40 @@
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94290256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67177820205688</t>
+    <t xml:space="preserve">7.94290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6717791557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.12953186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22325420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300487518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87514543533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72786903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25256681442261</t>
+    <t xml:space="preserve">7.22325372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300439834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07263040542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87514638900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72786951065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25256586074829</t>
   </si>
   <si>
     <t xml:space="preserve">6.15884494781494</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">5.57978010177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45091247558594</t>
+    <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
     <t xml:space="preserve">4.58566188812256</t>
@@ -2216,31 +2216,31 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05928993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27183771133423</t>
+    <t xml:space="preserve">4.74800109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05929040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27183723449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.69023752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69693231582642</t>
+    <t xml:space="preserve">5.69693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.98311710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05842971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29440689086914</t>
+    <t xml:space="preserve">6.05842876434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23917818069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29440641403198</t>
   </si>
   <si>
     <t xml:space="preserve">6.47515487670898</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">6.49356460571289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741161346436</t>
+    <t xml:space="preserve">6.36637210845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741065979004</t>
   </si>
   <si>
     <t xml:space="preserve">6.5303840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.647536277771</t>
+    <t xml:space="preserve">6.64753723144531</t>
   </si>
   <si>
     <t xml:space="preserve">6.56720399856567</t>
@@ -2267,37 +2267,37 @@
     <t xml:space="preserve">6.54377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4266209602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3596773147583</t>
+    <t xml:space="preserve">6.42662191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
     <t xml:space="preserve">6.0919017791748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834581375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85759735107422</t>
+    <t xml:space="preserve">6.03834676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1789288520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85759687423706</t>
   </si>
   <si>
     <t xml:space="preserve">6.00487422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20235967636108</t>
+    <t xml:space="preserve">6.20235824584961</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628820419312</t>
+    <t xml:space="preserve">6.32620477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628772735596</t>
   </si>
   <si>
     <t xml:space="preserve">6.28603887557983</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">6.01826286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08520650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776468276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813724517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05508232116699</t>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89776372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.87433290481567</t>
@@ -2342,34 +2342,34 @@
     <t xml:space="preserve">4.87017393112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75302124023438</t>
+    <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
     <t xml:space="preserve">4.91368770599365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08774089813232</t>
+    <t xml:space="preserve">5.08774137496948</t>
   </si>
   <si>
     <t xml:space="preserve">5.17142152786255</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18815755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34212827682495</t>
+    <t xml:space="preserve">5.188157081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34212923049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22163009643555</t>
+    <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74379301071167</t>
+    <t xml:space="preserve">5.74379253387451</t>
   </si>
   <si>
     <t xml:space="preserve">5.74044561386108</t>
@@ -2381,49 +2381,49 @@
     <t xml:space="preserve">5.94127750396729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82077836990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60655689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2952675819397</t>
+    <t xml:space="preserve">5.82077789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60655736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1981987953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29861545562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28522682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196285247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.238365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33208751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27853202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23167085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35886430740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3253927230835</t>
+    <t xml:space="preserve">5.19819927215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29861497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2852258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196237564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23836517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33208703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2785325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23167133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35886478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204580307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32539319992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.28187894821167</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">5.04422807693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97059011459351</t>
+    <t xml:space="preserve">4.97058963775635</t>
   </si>
   <si>
     <t xml:space="preserve">4.94046497344971</t>
@@ -2444,34 +2444,34 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104753494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13125562667847</t>
+    <t xml:space="preserve">5.08104705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13125514984131</t>
   </si>
   <si>
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790822982788</t>
+    <t xml:space="preserve">5.12790775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11786603927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12121391296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05092287063599</t>
+    <t xml:space="preserve">5.11786651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12121343612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05092191696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1044774055481</t>
+    <t xml:space="preserve">5.10447788238525</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
@@ -2483,19 +2483,19 @@
     <t xml:space="preserve">5.41576719284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38898944854736</t>
+    <t xml:space="preserve">5.38899040222168</t>
   </si>
   <si>
     <t xml:space="preserve">5.48940515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36890697479248</t>
+    <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57643270492554</t>
+    <t xml:space="preserve">5.5764331817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961324691772</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">5.38229513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36555957794189</t>
+    <t xml:space="preserve">5.36555910110474</t>
   </si>
   <si>
     <t xml:space="preserve">5.3454761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30530977249146</t>
+    <t xml:space="preserve">5.3053092956543</t>
   </si>
   <si>
     <t xml:space="preserve">5.27518510818481</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">5.60321044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12537336349487</t>
+    <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
     <t xml:space="preserve">6.15215110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27934503555298</t>
+    <t xml:space="preserve">6.27934455871582</t>
   </si>
   <si>
     <t xml:space="preserve">6.22244167327881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1956639289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14880323410034</t>
+    <t xml:space="preserve">6.19566488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14880418777466</t>
   </si>
   <si>
     <t xml:space="preserve">6.09524822235107</t>
@@ -2555,31 +2555,31 @@
     <t xml:space="preserve">5.7069730758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89441633224487</t>
+    <t xml:space="preserve">5.89441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.73375034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62664079666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4860577583313</t>
+    <t xml:space="preserve">5.62664031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61325216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48605823516846</t>
   </si>
   <si>
     <t xml:space="preserve">5.48271083831787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65341758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040390014648</t>
+    <t xml:space="preserve">5.52287721633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65341806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040437698364</t>
   </si>
   <si>
     <t xml:space="preserve">5.70027875900269</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5563497543335</t>
+    <t xml:space="preserve">5.55634927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262741088867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47267007827759</t>
+    <t xml:space="preserve">5.47266960144043</t>
   </si>
   <si>
     <t xml:space="preserve">5.50948858261108</t>
@@ -2606,46 +2606,46 @@
     <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37894821166992</t>
+    <t xml:space="preserve">5.37894773483276</t>
   </si>
   <si>
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372941970825</t>
+    <t xml:space="preserve">4.92372894287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.95385408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88021469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94381189346313</t>
+    <t xml:space="preserve">4.88021564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94381237030029</t>
   </si>
   <si>
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2182822227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468597412109</t>
+    <t xml:space="preserve">5.21828269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468549728394</t>
   </si>
   <si>
     <t xml:space="preserve">5.55300235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86094427108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02830505371094</t>
+    <t xml:space="preserve">5.8609447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02830410003662</t>
   </si>
   <si>
     <t xml:space="preserve">6.09859561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335699081421</t>
+    <t xml:space="preserve">6.44335651397705</t>
   </si>
   <si>
     <t xml:space="preserve">6.59398174285889</t>
@@ -2654,34 +2654,34 @@
     <t xml:space="preserve">6.8082013130188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6374945640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5872859954834</t>
+    <t xml:space="preserve">6.63749504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58728647232056</t>
   </si>
   <si>
     <t xml:space="preserve">6.72117471694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67766094207764</t>
+    <t xml:space="preserve">6.67766141891479</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323232650757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
+    <t xml:space="preserve">6.64418888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.7613410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383676528931</t>
+    <t xml:space="preserve">7.10275459289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
     <t xml:space="preserve">7.19647693634033</t>
@@ -2690,88 +2690,88 @@
     <t xml:space="preserve">7.12283849716187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0893669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556161880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986604690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05589485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00233840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175727844238</t>
+    <t xml:space="preserve">7.08936595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20986652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14961528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05589437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0023398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175632476807</t>
   </si>
   <si>
     <t xml:space="preserve">7.06928396224976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10944890975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07597732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9822564125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14292192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09606075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9688663482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90192365646362</t>
+    <t xml:space="preserve">7.10944986343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07597780227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98225688934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14292144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09606122970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92200660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96886730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90192270278931</t>
   </si>
   <si>
     <t xml:space="preserve">7.11614465713501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01572751998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18978309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03581142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90861749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08267164230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622713088989</t>
+    <t xml:space="preserve">7.01572799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18978214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03581047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90861797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08267211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622665405273</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2500319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2701153755188</t>
+    <t xml:space="preserve">7.25003242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011394500732</t>
   </si>
   <si>
     <t xml:space="preserve">7.32366991043091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55127906799316</t>
+    <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
@@ -2786,40 +2786,40 @@
     <t xml:space="preserve">7.470947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56466960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51111268997192</t>
+    <t xml:space="preserve">7.56466865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.53789138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61152935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61822319030762</t>
+    <t xml:space="preserve">7.6115288734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61822462081909</t>
   </si>
   <si>
     <t xml:space="preserve">7.7588062286377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8525276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07344436645508</t>
+    <t xml:space="preserve">7.85252714157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07344245910645</t>
   </si>
   <si>
     <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1805534362793</t>
+    <t xml:space="preserve">8.18055438995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66254997253418</t>
+    <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.89685344696045</t>
@@ -2840,67 +2840,67 @@
     <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28766345977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45502376556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.28766250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45502281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18724822998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758098602295</t>
+    <t xml:space="preserve">8.26758003234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.32783031463623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81236124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77888917922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277647018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938831329346</t>
+    <t xml:space="preserve">7.81236171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77888870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938879013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049140930176</t>
+    <t xml:space="preserve">8.97049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55290412902832</t>
+    <t xml:space="preserve">9.55290508270264</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473476409912</t>
+    <t xml:space="preserve">9.99473571777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94118022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0081233978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0282068252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85415172576904</t>
+    <t xml:space="preserve">9.9411792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0081224441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.028205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
     <t xml:space="preserve">9.77381992340088</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">9.73365306854248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.476731300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6775636672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440906524658</t>
+    <t xml:space="preserve">10.5168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039247512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4767303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.677562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440916061401</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">10.3346567153931</t>
   </si>
   <si>
-    <t xml:space="preserve">10.186595916748</t>
+    <t xml:space="preserve">10.1865968704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.0755491256714</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93489265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94969749450684</t>
+    <t xml:space="preserve">9.93489170074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94969654083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.9052791595459</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">9.67578506469727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76462078094482</t>
+    <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.79423332214355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83865261077881</t>
+    <t xml:space="preserve">9.83865165710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">9.98671245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0903558731079</t>
+    <t xml:space="preserve">10.0903549194336</t>
   </si>
   <si>
     <t xml:space="preserve">9.89047241210938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7572193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80904006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.75721836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80904102325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77202415466309</t>
+    <t xml:space="preserve">9.7720251083374</t>
   </si>
   <si>
     <t xml:space="preserve">10.0533399581909</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">9.7202033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60175514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5499324798584</t>
+    <t xml:space="preserve">9.6017541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54993343353271</t>
   </si>
   <si>
     <t xml:space="preserve">9.52032089233398</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524513244629</t>
+    <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14276599884033</t>
+    <t xml:space="preserve">9.14276504516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.10575008392334</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">8.99655532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34634876251221</t>
+    <t xml:space="preserve">9.34634971618652</t>
   </si>
   <si>
     <t xml:space="preserve">9.3500509262085</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">9.37225914001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4166784286499</t>
+    <t xml:space="preserve">9.41667938232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.30563259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17237854003906</t>
+    <t xml:space="preserve">9.17237758636475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2464075088501</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1131534576416</t>
+    <t xml:space="preserve">9.11315250396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
+    <t xml:space="preserve">9.15757179260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.31303691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35745429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26861667633057</t>
+    <t xml:space="preserve">9.35745525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
     <t xml:space="preserve">9.15016841888428</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98730278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09834671020508</t>
+    <t xml:space="preserve">8.98730182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09834766387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">9.52772331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885261535645</t>
+    <t xml:space="preserve">8.86885166168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.75040340423584</t>
@@ -3146,19 +3146,19 @@
     <t xml:space="preserve">8.92067432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93547916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8096284866333</t>
+    <t xml:space="preserve">8.93548011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33078336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40481424331665</t>
+    <t xml:space="preserve">4.33078384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40481376647949</t>
   </si>
   <si>
     <t xml:space="preserve">4.51585960388184</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5824875831604</t>
+    <t xml:space="preserve">4.69723415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58248710632324</t>
   </si>
   <si>
     <t xml:space="preserve">4.31227588653564</t>
@@ -3182,19 +3182,19 @@
     <t xml:space="preserve">4.10128927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13090181350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27155876159668</t>
+    <t xml:space="preserve">4.13090133666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
     <t xml:space="preserve">4.1938271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1679162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17161846160889</t>
+    <t xml:space="preserve">4.16791677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17161798477173</t>
   </si>
   <si>
     <t xml:space="preserve">4.2456488609314</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12720012664795</t>
+    <t xml:space="preserve">4.12719964981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018468856812</t>
+    <t xml:space="preserve">4.09018516540527</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233510971069</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41962051391602</t>
+    <t xml:space="preserve">4.41962003707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.35669422149658</t>
@@ -3230,52 +3230,52 @@
     <t xml:space="preserve">4.39741086959839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36039590835571</t>
+    <t xml:space="preserve">4.36039543151855</t>
   </si>
   <si>
     <t xml:space="preserve">4.15311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499048233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09758758544922</t>
+    <t xml:space="preserve">4.10499095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09758710861206</t>
   </si>
   <si>
     <t xml:space="preserve">4.17902088165283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93842196464539</t>
+    <t xml:space="preserve">3.93842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057262420654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87549638748169</t>
+    <t xml:space="preserve">4.05687093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
     <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85328674316406</t>
+    <t xml:space="preserve">3.85328698158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.58862781524658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51644802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86069011688232</t>
+    <t xml:space="preserve">3.51644825935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86069059371948</t>
   </si>
   <si>
     <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206514358521</t>
+    <t xml:space="preserve">4.04206466674805</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3284,70 +3284,70 @@
     <t xml:space="preserve">4.34558963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27526140213013</t>
+    <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.94952654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90510821342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433329582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98654222488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95322823524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05316877365112</t>
+    <t xml:space="preserve">3.90510845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433305740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98654246330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95322799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05316925048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86439156532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79036116600037</t>
+    <t xml:space="preserve">4.01985502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8643913269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79036092758179</t>
   </si>
   <si>
     <t xml:space="preserve">3.73483824729919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50164198875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53310513496399</t>
+    <t xml:space="preserve">3.50164246559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53310489654541</t>
   </si>
   <si>
     <t xml:space="preserve">3.55716466903687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52014994621277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48313450813293</t>
+    <t xml:space="preserve">3.52015018463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48313426971436</t>
   </si>
   <si>
     <t xml:space="preserve">3.51459765434265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57382154464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6200909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638951301575</t>
+    <t xml:space="preserve">3.5738217830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62009072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638975143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.70152449607849</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.33137178421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358119010925</t>
+    <t xml:space="preserve">3.35358095169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">3.14999747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20181846618652</t>
+    <t xml:space="preserve">3.2018187046051</t>
   </si>
   <si>
     <t xml:space="preserve">3.26474452018738</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">3.0130410194397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92050290107727</t>
+    <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
     <t xml:space="preserve">2.88718914985657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05005621910095</t>
+    <t xml:space="preserve">3.05005598068237</t>
   </si>
   <si>
     <t xml:space="preserve">3.00748872756958</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">2.98342871665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93345832824707</t>
+    <t xml:space="preserve">2.93345808982849</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">2.87238311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81130790710449</t>
+    <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
     <t xml:space="preserve">2.86497974395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683058738708</t>
+    <t xml:space="preserve">2.86683082580566</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503896713257</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">2.92420434951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014433860779</t>
+    <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82981562614441</t>
+    <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059102058411</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">2.82426309585571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83721828460693</t>
+    <t xml:space="preserve">2.83721852302551</t>
   </si>
   <si>
     <t xml:space="preserve">2.763188123703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772395133972</t>
+    <t xml:space="preserve">2.6077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">2.52999210357666</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">2.46706604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47817087173462</t>
+    <t xml:space="preserve">2.47817063331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.45596170425415</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742437362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2727358341217</t>
+    <t xml:space="preserve">2.48742413520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27273607254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.25792980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34861731529236</t>
+    <t xml:space="preserve">2.34861707687378</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133939743042</t>
@@ -3524,22 +3524,22 @@
     <t xml:space="preserve">2.19685482978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13577938079834</t>
+    <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.18760085105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29679584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28569149971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30234813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35416960716248</t>
+    <t xml:space="preserve">2.29679560661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2856912612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30234837532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35416984558105</t>
   </si>
   <si>
     <t xml:space="preserve">2.34121417999268</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458667755127</t>
+    <t xml:space="preserve">2.27458691596985</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3566,49 +3566,49 @@
     <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276544570923</t>
+    <t xml:space="preserve">2.22276568412781</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18204879760742</t>
+    <t xml:space="preserve">2.18204855918884</t>
   </si>
   <si>
     <t xml:space="preserve">2.2653329372406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2912437915802</t>
+    <t xml:space="preserve">2.29124355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.24867606163025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21351146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13022756576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15798878669739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14873480796814</t>
+    <t xml:space="preserve">2.21351170539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1302273273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15798902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14873504638672</t>
   </si>
   <si>
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13763070106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14688420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0839581489563</t>
+    <t xml:space="preserve">2.08765959739685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13763046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14688444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08395838737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.10246586799622</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">1.95810651779175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86186671257019</t>
+    <t xml:space="preserve">1.86186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
@@ -71753,7 +71753,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.691099537</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>350007</v>
@@ -71774,6 +71774,32 @@
         <v>1788</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6911111111</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>369237</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>3.95799994468689</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>3.89400005340576</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>3.93600010871887</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="1882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="1883">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1956901550293</t>
+    <t xml:space="preserve">12.195689201355</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5895700454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097290039062</t>
+    <t xml:space="preserve">11.5895709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097299575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.076696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1366424560547</t>
+    <t xml:space="preserve">11.0766973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.136643409729</t>
   </si>
   <si>
     <t xml:space="preserve">10.8302526473999</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6770572662354</t>
+    <t xml:space="preserve">10.6770582199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.3107194900513</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2907371520996</t>
+    <t xml:space="preserve">10.2907381057739</t>
   </si>
   <si>
     <t xml:space="preserve">9.65797424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2507743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3906497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4239521026611</t>
+    <t xml:space="preserve">10.2507753372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7370042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3906488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4239511489868</t>
   </si>
   <si>
     <t xml:space="preserve">10.5438432693481</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">10.4838972091675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.297399520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1042394638062</t>
+    <t xml:space="preserve">10.2973985671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1042385101318</t>
   </si>
   <si>
     <t xml:space="preserve">10.8702173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7170209884644</t>
+    <t xml:space="preserve">10.7170219421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.77786636352539</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.91107940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54474258422852</t>
+    <t xml:space="preserve">9.54474353790283</t>
   </si>
   <si>
     <t xml:space="preserve">9.77120590209961</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.6171112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4172916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7703075408936</t>
+    <t xml:space="preserve">10.417290687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7703065872192</t>
   </si>
   <si>
     <t xml:space="preserve">10.9301633834839</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">10.4905595779419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7236814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9434833526611</t>
+    <t xml:space="preserve">10.7236824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9434843063354</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363737106323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3431253433228</t>
+    <t xml:space="preserve">11.3431243896484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6495161056519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898397445679</t>
+    <t xml:space="preserve">11.2898387908936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0624780654907</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7627487182617</t>
+    <t xml:space="preserve">11.7627468109131</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289943695068</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">12.475438117981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4554586410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4621162414551</t>
+    <t xml:space="preserve">12.4554576873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422250747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4621171951294</t>
   </si>
   <si>
     <t xml:space="preserve">12.5553665161133</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">12.6019916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1823711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6961402893066</t>
+    <t xml:space="preserve">12.1823692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.696138381958</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0757970809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9159421920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1890287399292</t>
+    <t xml:space="preserve">12.075798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.915943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1890296936035</t>
   </si>
   <si>
     <t xml:space="preserve">11.4963188171387</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">11.955906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2689561843872</t>
+    <t xml:space="preserve">12.2689590454102</t>
   </si>
   <si>
     <t xml:space="preserve">12.8217935562134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9217052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9350252151489</t>
+    <t xml:space="preserve">12.9217042922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9350261688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.101541519165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1281824111938</t>
+    <t xml:space="preserve">13.1281833648682</t>
   </si>
   <si>
     <t xml:space="preserve">13.2480754852295</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">13.1614875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3613080978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882186889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.981650352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6885805130005</t>
+    <t xml:space="preserve">13.361307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882196426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9816493988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6885814666748</t>
   </si>
   <si>
     <t xml:space="preserve">12.5620269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881739616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8617572784424</t>
+    <t xml:space="preserve">12.8817386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8617563247681</t>
   </si>
   <si>
     <t xml:space="preserve">12.8884000778198</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">13.0482559204102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4088315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221534729004</t>
+    <t xml:space="preserve">12.4088306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221525192261</t>
   </si>
   <si>
     <t xml:space="preserve">12.3488864898682</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">12.9150428771973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2214326858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1344089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887948989868</t>
+    <t xml:space="preserve">13.2214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1344060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.5159883499146</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">13.5226831436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5561552047729</t>
+    <t xml:space="preserve">13.5561532974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.4222650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3620157241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3553228378296</t>
+    <t xml:space="preserve">13.3620147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3553237915039</t>
   </si>
   <si>
     <t xml:space="preserve">13.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9938230514526</t>
+    <t xml:space="preserve">12.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">13.3017673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2749881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.194655418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833854675293</t>
+    <t xml:space="preserve">13.2749891281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1946544647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6591053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833864212036</t>
   </si>
   <si>
     <t xml:space="preserve">11.8156099319458</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">12.0766916275024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6524095535278</t>
+    <t xml:space="preserve">12.6524085998535</t>
   </si>
   <si>
     <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4515771865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1410999298096</t>
+    <t xml:space="preserve">12.4515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1411008834839</t>
   </si>
   <si>
     <t xml:space="preserve">10.8850898742676</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">10.2290382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.416482925415</t>
+    <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
     <t xml:space="preserve">10.0482902526855</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193933486938</t>
+    <t xml:space="preserve">11.1193943023682</t>
   </si>
   <si>
     <t xml:space="preserve">11.4741954803467</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">11.2599744796753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126088142395</t>
+    <t xml:space="preserve">11.1260871887207</t>
   </si>
   <si>
     <t xml:space="preserve">11.0189771652222</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">10.8114500045776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9252548217773</t>
+    <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
     <t xml:space="preserve">10.8783950805664</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0642147064209</t>
+    <t xml:space="preserve">9.06421375274658</t>
   </si>
   <si>
     <t xml:space="preserve">8.93032550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67593860626221</t>
+    <t xml:space="preserve">8.67593765258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.80313110351562</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">8.93702030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20479583740234</t>
+    <t xml:space="preserve">9.20479488372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.37215518951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25835037231445</t>
+    <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.33868312835693</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.23826789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31860065460205</t>
+    <t xml:space="preserve">9.31860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">9.13115787506104</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">9.2315731048584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63323783874512</t>
+    <t xml:space="preserve">9.6332368850708</t>
   </si>
   <si>
     <t xml:space="preserve">9.79390335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55959892272949</t>
+    <t xml:space="preserve">9.55959796905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.51273822784424</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">9.43910026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56629276275635</t>
+    <t xml:space="preserve">9.56629371643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">9.78720855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87423610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6734037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07760143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1713228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08429527282715</t>
+    <t xml:space="preserve">9.87423515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67340469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07760238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17132377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07090759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
     <t xml:space="preserve">9.31190586090088</t>
@@ -569,31 +569,31 @@
     <t xml:space="preserve">9.38554573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24496364593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03743648529053</t>
+    <t xml:space="preserve">9.24496269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03743553161621</t>
   </si>
   <si>
     <t xml:space="preserve">8.70940971374512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72279930114746</t>
+    <t xml:space="preserve">8.72280025482178</t>
   </si>
   <si>
     <t xml:space="preserve">8.87007617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76965999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74957752227783</t>
+    <t xml:space="preserve">8.7696590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.78304958343506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78974342346191</t>
+    <t xml:space="preserve">8.7897424697876</t>
   </si>
   <si>
     <t xml:space="preserve">8.71610546112061</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">8.33452415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20063591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12030410766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79227733612061</t>
+    <t xml:space="preserve">8.2006368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1203031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79227828979492</t>
   </si>
   <si>
     <t xml:space="preserve">7.82574939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83913946151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86591768264771</t>
+    <t xml:space="preserve">7.83913850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86591672897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.84583377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6316123008728</t>
+    <t xml:space="preserve">7.63161182403564</t>
   </si>
   <si>
     <t xml:space="preserve">7.62491798400879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66508436203003</t>
+    <t xml:space="preserve">7.66508340835571</t>
   </si>
   <si>
     <t xml:space="preserve">7.74541759490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71194553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6918625831604</t>
+    <t xml:space="preserve">7.71194648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69186067581177</t>
   </si>
   <si>
     <t xml:space="preserve">7.48433589935303</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">8.12699794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38138580322266</t>
+    <t xml:space="preserve">8.38138484954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.9236307144165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2114896774292</t>
+    <t xml:space="preserve">9.21149063110352</t>
   </si>
   <si>
     <t xml:space="preserve">9.09768581390381</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">11.8691654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0499143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615617752075</t>
+    <t xml:space="preserve">12.0499134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615598678589</t>
   </si>
   <si>
     <t xml:space="preserve">15.2833080291748</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">13.6967344284058</t>
   </si>
   <si>
-    <t xml:space="preserve">13.756986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975677490234</t>
+    <t xml:space="preserve">13.756983757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975696563721</t>
   </si>
   <si>
     <t xml:space="preserve">13.7235145568848</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">13.8908729553223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9578170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7904577255249</t>
+    <t xml:space="preserve">13.9578189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7904596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.6004791259766</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">14.0180683135986</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0582323074341</t>
+    <t xml:space="preserve">14.0582342147827</t>
   </si>
   <si>
     <t xml:space="preserve">13.9712057113647</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">14.1385669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1251783370972</t>
+    <t xml:space="preserve">14.1251764297485</t>
   </si>
   <si>
     <t xml:space="preserve">13.817234992981</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">13.7101249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2415189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544904708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2549066543579</t>
+    <t xml:space="preserve">13.455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2415180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.2080450057983</t>
@@ -773,43 +773,43 @@
     <t xml:space="preserve">12.9268808364868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7528247833252</t>
+    <t xml:space="preserve">12.7528276443481</t>
   </si>
   <si>
     <t xml:space="preserve">12.8264636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9737424850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067964553833</t>
+    <t xml:space="preserve">12.9737405776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067983627319</t>
   </si>
   <si>
     <t xml:space="preserve">13.1611843109131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0540742874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9134912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2147397994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1879625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3419332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812658309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.859935760498</t>
+    <t xml:space="preserve">13.0540733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9134931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2147388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1879634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3419322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812686920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8599367141724</t>
   </si>
   <si>
     <t xml:space="preserve">12.9871301651001</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.9201860427856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8934087753296</t>
+    <t xml:space="preserve">12.8934097290039</t>
   </si>
   <si>
     <t xml:space="preserve">13.3754053115845</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1745729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406856536865</t>
+    <t xml:space="preserve">13.1745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406847000122</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666296005249</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">12.9001035690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9536581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197708129883</t>
+    <t xml:space="preserve">12.9536590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532438278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197689056396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858835220337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5386047363281</t>
+    <t xml:space="preserve">12.5386056900024</t>
   </si>
   <si>
     <t xml:space="preserve">12.310996055603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3310785293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4047193527222</t>
+    <t xml:space="preserve">12.3310794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4047183990479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2708292007446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1570253372192</t>
+    <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
     <t xml:space="preserve">11.6750288009644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8624715805054</t>
+    <t xml:space="preserve">11.8624706268311</t>
   </si>
   <si>
     <t xml:space="preserve">12.1771078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1436367034912</t>
+    <t xml:space="preserve">12.1436357498169</t>
   </si>
   <si>
     <t xml:space="preserve">12.7862987518311</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">12.8800201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9469633102417</t>
+    <t xml:space="preserve">12.946964263916</t>
   </si>
   <si>
     <t xml:space="preserve">12.5653839111328</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">12.4448823928833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1637201309204</t>
+    <t xml:space="preserve">12.1637191772461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3043012619019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3913278579712</t>
+    <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.5586891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4649686813354</t>
+    <t xml:space="preserve">12.4649677276611</t>
   </si>
   <si>
     <t xml:space="preserve">12.6189384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2574405670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2842178344727</t>
+    <t xml:space="preserve">12.2574396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1971912384033</t>
+    <t xml:space="preserve">12.197190284729</t>
   </si>
   <si>
     <t xml:space="preserve">12.1034698486328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0900812149048</t>
+    <t xml:space="preserve">12.0900802612305</t>
   </si>
   <si>
     <t xml:space="preserve">12.063304901123</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">12.5519933700562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6724939346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8089160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030546188354</t>
+    <t xml:space="preserve">12.6724920272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3176889419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8089170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030555725098</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813064575195</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">11.6147794723511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076694488525</t>
+    <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">11.6549444198608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5880012512207</t>
+    <t xml:space="preserve">11.5880002975464</t>
   </si>
   <si>
     <t xml:space="preserve">11.7085008621216</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">11.6817235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942798614502</t>
+    <t xml:space="preserve">11.4942789077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.5210571289062</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">11.7018051147461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4474182128906</t>
+    <t xml:space="preserve">11.4474191665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.3804740905762</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">11.2265043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.777979850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7043418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7980623245239</t>
+    <t xml:space="preserve">10.7779788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7980632781982</t>
   </si>
   <si>
     <t xml:space="preserve">10.9453392028809</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">11.1461715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0658388137817</t>
+    <t xml:space="preserve">11.0658378601074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1327810287476</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">11.1997261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9921998977661</t>
+    <t xml:space="preserve">10.9922008514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.112699508667</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">11.4206409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5411396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5679187774658</t>
+    <t xml:space="preserve">11.5411405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5679178237915</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">11.4005584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4608087539673</t>
+    <t xml:space="preserve">11.4608097076416</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541130065918</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">11.3336153030396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1595602035522</t>
+    <t xml:space="preserve">11.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1595592498779</t>
   </si>
   <si>
     <t xml:space="preserve">11.0524501800537</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">10.5302858352661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093719482422</t>
+    <t xml:space="preserve">10.3897047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093709945679</t>
   </si>
   <si>
     <t xml:space="preserve">10.1620950698853</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">10.3428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3562316894531</t>
+    <t xml:space="preserve">10.3562326431274</t>
   </si>
   <si>
     <t xml:space="preserve">9.84076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80059623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80729007720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68679237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71356964111328</t>
+    <t xml:space="preserve">9.80059719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80729103088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68679141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">9.72026443481445</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">9.74704170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74034786224365</t>
+    <t xml:space="preserve">9.74034690856934</t>
   </si>
   <si>
     <t xml:space="preserve">9.75373649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70018196105957</t>
+    <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">10.5235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7110347747803</t>
+    <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
     <t xml:space="preserve">10.650785446167</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">10.1888723373413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2758989334106</t>
+    <t xml:space="preserve">10.275899887085</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">10.2223443984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5570640563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5102043151855</t>
+    <t xml:space="preserve">10.2357339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5570650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5102033615112</t>
   </si>
   <si>
     <t xml:space="preserve">10.3160648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089557647705</t>
+    <t xml:space="preserve">10.2089548110962</t>
   </si>
   <si>
     <t xml:space="preserve">9.65331935882568</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">9.52612590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62654209136963</t>
+    <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">9.8474588394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2959823608398</t>
+    <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436754226685</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">10.8583126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855051040649</t>
+    <t xml:space="preserve">10.9855060577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587287902832</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">11.0725326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9988946914673</t>
+    <t xml:space="preserve">10.998893737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1796426773071</t>
+    <t xml:space="preserve">11.1796436309814</t>
   </si>
   <si>
     <t xml:space="preserve">11.2465867996216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0859203338623</t>
+    <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
     <t xml:space="preserve">10.9185609817505</t>
@@ -1283,34 +1283,34 @@
     <t xml:space="preserve">10.9118661880493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8917837142944</t>
+    <t xml:space="preserve">10.9051733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8917846679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0390605926514</t>
+    <t xml:space="preserve">11.0390596389771</t>
   </si>
   <si>
     <t xml:space="preserve">10.7277708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4633417129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554002761841</t>
+    <t xml:space="preserve">10.463342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553993225098</t>
   </si>
   <si>
     <t xml:space="preserve">10.5871887207031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.289288520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2658576965332</t>
+    <t xml:space="preserve">10.2892875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2658586502075</t>
   </si>
   <si>
     <t xml:space="preserve">10.3696212768555</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5336322784424</t>
+    <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139659881592</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">10.6240081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4097871780396</t>
+    <t xml:space="preserve">10.4097862243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.1729497909546</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">10.3261079788208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4030923843384</t>
+    <t xml:space="preserve">10.4030933380127</t>
   </si>
   <si>
     <t xml:space="preserve">10.3394966125488</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">10.3629264831543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1520547866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
+    <t xml:space="preserve">10.1520538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1821775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94452667236328</t>
+    <t xml:space="preserve">9.9445276260376</t>
   </si>
   <si>
     <t xml:space="preserve">10.0349006652832</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620752334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.025671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0825729370117</t>
+    <t xml:space="preserve">10.9620742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0223245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9553813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0256719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.082573890686</t>
   </si>
   <si>
     <t xml:space="preserve">10.952033996582</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.28675365448</t>
+    <t xml:space="preserve">11.2867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">10.5068559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1721353530884</t>
+    <t xml:space="preserve">10.3729686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1721363067627</t>
   </si>
   <si>
     <t xml:space="preserve">10.2457752227783</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">10.0683736801147</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74369525909424</t>
+    <t xml:space="preserve">9.74369621276855</t>
   </si>
   <si>
     <t xml:space="preserve">9.28847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34537792205811</t>
+    <t xml:space="preserve">9.34537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.6700553894043</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">9.66336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57633495330811</t>
+    <t xml:space="preserve">9.57633590698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.48596000671387</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">9.58637619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61650085449219</t>
+    <t xml:space="preserve">9.6165018081665</t>
   </si>
   <si>
     <t xml:space="preserve">9.54286289215088</t>
@@ -1493,16 +1493,16 @@
     <t xml:space="preserve">9.56964015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5026969909668</t>
+    <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.47926616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49600219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62319564819336</t>
+    <t xml:space="preserve">9.49600124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62319469451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.60980606079102</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">9.14120006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186557769775</t>
+    <t xml:space="preserve">9.30186462402344</t>
   </si>
   <si>
     <t xml:space="preserve">9.22487926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28512859344482</t>
+    <t xml:space="preserve">9.28512954711914</t>
   </si>
   <si>
     <t xml:space="preserve">9.21483707427979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13785171508789</t>
+    <t xml:space="preserve">9.13785076141357</t>
   </si>
   <si>
     <t xml:space="preserve">9.45583629608154</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">9.28178119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61315441131592</t>
+    <t xml:space="preserve">9.6131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.71691799163818</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">9.37550354003906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54620933532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31525325775146</t>
+    <t xml:space="preserve">9.54621028900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31525421142578</t>
   </si>
   <si>
     <t xml:space="preserve">9.26504516601562</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">8.80647850036621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89015865325928</t>
+    <t xml:space="preserve">8.89015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02070045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8533411026001</t>
+    <t xml:space="preserve">8.85334014892578</t>
   </si>
   <si>
     <t xml:space="preserve">8.86338138580322</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">8.86003494262695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92028331756592</t>
+    <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.88011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82656288146973</t>
+    <t xml:space="preserve">8.82656383514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">8.29770565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27427387237549</t>
+    <t xml:space="preserve">8.2742748260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.24080371856689</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">8.35795497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47845458984375</t>
+    <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.47175884246826</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">9.00730991363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01065921783447</t>
+    <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
     <t xml:space="preserve">9.01400566101074</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22822666168213</t>
+    <t xml:space="preserve">9.22822570800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.94706153869629</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">9.01735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12781047821045</t>
+    <t xml:space="preserve">9.12780952453613</t>
   </si>
   <si>
     <t xml:space="preserve">9.03408813476562</t>
@@ -1679,22 +1679,22 @@
     <t xml:space="preserve">8.66589641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59560680389404</t>
+    <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.8499927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53535556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47510623931885</t>
+    <t xml:space="preserve">8.53535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47510528564453</t>
   </si>
   <si>
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
+    <t xml:space="preserve">8.62907886505127</t>
   </si>
   <si>
     <t xml:space="preserve">8.7529239654541</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">9.29516983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30855941772461</t>
+    <t xml:space="preserve">9.30855846405029</t>
   </si>
   <si>
     <t xml:space="preserve">9.50604438781738</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">8.294358253479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31109428405762</t>
+    <t xml:space="preserve">8.3110933303833</t>
   </si>
   <si>
     <t xml:space="preserve">8.34456539154053</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">8.49184322357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93367290496826</t>
+    <t xml:space="preserve">8.93367195129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.19810104370117</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">8.25753879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56548023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5018835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.756272315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82321453094482</t>
+    <t xml:space="preserve">8.56548118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50188446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82321548461914</t>
   </si>
   <si>
     <t xml:space="preserve">8.84329891204834</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">9.26169776916504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29851818084717</t>
+    <t xml:space="preserve">9.29851722717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.44914054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91105461120605</t>
+    <t xml:space="preserve">9.91105556488037</t>
   </si>
   <si>
     <t xml:space="preserve">9.8441104888916</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">9.52277946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45918273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44244575500488</t>
+    <t xml:space="preserve">9.4591817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4424467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.41901683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60645961761475</t>
+    <t xml:space="preserve">9.60646057128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456886291504</t>
@@ -1844,34 +1844,34 @@
     <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42905902862549</t>
+    <t xml:space="preserve">9.42905807495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24831008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47257137298584</t>
+    <t xml:space="preserve">9.24830913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47257232666016</t>
   </si>
   <si>
     <t xml:space="preserve">9.55625152587891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4257116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128158569336</t>
+    <t xml:space="preserve">9.42570972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15124130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128253936768</t>
   </si>
   <si>
     <t xml:space="preserve">9.14789390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43240451812744</t>
+    <t xml:space="preserve">9.43240547180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.39223861694336</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.73030471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69014072418213</t>
+    <t xml:space="preserve">9.69013977050781</t>
   </si>
   <si>
     <t xml:space="preserve">9.50939083099365</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">9.9210958480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90770721435547</t>
+    <t xml:space="preserve">9.90770816802979</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">9.77716732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7102222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62988948822021</t>
+    <t xml:space="preserve">9.71022319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62989044189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.38889122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45248794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
+    <t xml:space="preserve">9.45248889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.76631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62573051452637</t>
+    <t xml:space="preserve">8.62573146820068</t>
   </si>
   <si>
     <t xml:space="preserve">8.73953533172607</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">8.75961875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02404594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4056282043457</t>
+    <t xml:space="preserve">9.02404689788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40562725067139</t>
   </si>
   <si>
     <t xml:space="preserve">9.63993167877197</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">9.70687580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94787406921387</t>
+    <t xml:space="preserve">9.94787311553955</t>
   </si>
   <si>
     <t xml:space="preserve">9.76712512969971</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">9.53282165527344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60311317443848</t>
+    <t xml:space="preserve">9.60311222076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.35541915893555</t>
@@ -1988,28 +1988,28 @@
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9437141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9805326461792</t>
+    <t xml:space="preserve">8.94371318817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98053359985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.99057483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87342357635498</t>
+    <t xml:space="preserve">8.87342262268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.90354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68263339996338</t>
+    <t xml:space="preserve">8.68263244628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.67928600311279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0415954589844</t>
+    <t xml:space="preserve">10.0415964126587</t>
   </si>
   <si>
     <t xml:space="preserve">9.86084651947021</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">8.88346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74288177490234</t>
+    <t xml:space="preserve">8.74288272857666</t>
   </si>
   <si>
     <t xml:space="preserve">8.7930908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65250873565674</t>
+    <t xml:space="preserve">8.65250778198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.84664535522461</t>
@@ -2066,43 +2066,43 @@
     <t xml:space="preserve">8.88681221008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00396347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05417156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06086730957031</t>
+    <t xml:space="preserve">9.0039644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05417251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.060866355896</t>
   </si>
   <si>
     <t xml:space="preserve">9.1545877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383975982666</t>
+    <t xml:space="preserve">8.97383880615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.11776828765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08094882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9671459197998</t>
+    <t xml:space="preserve">9.0809497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96714496612549</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90019989013672</t>
+    <t xml:space="preserve">8.90020084381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99726867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92697811126709</t>
+    <t xml:space="preserve">8.99726963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92697906494141</t>
   </si>
   <si>
     <t xml:space="preserve">9.06756019592285</t>
@@ -2114,25 +2114,25 @@
     <t xml:space="preserve">8.64246559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40146923065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33787155151367</t>
+    <t xml:space="preserve">8.40146827697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33787250518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.28431606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23410892486572</t>
+    <t xml:space="preserve">8.23410797119141</t>
   </si>
   <si>
     <t xml:space="preserve">8.15377616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98976230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06005477905273</t>
+    <t xml:space="preserve">7.9897632598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06005382537842</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">8.03327655792236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94624996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95629119873047</t>
+    <t xml:space="preserve">7.94624900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95629024505615</t>
   </si>
   <si>
     <t xml:space="preserve">7.93286037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02323532104492</t>
+    <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
     <t xml:space="preserve">7.96633243560791</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">8.03997135162354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9429030418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558397293091</t>
+    <t xml:space="preserve">7.94290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558301925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.6717791557312</t>
@@ -2186,34 +2186,34 @@
     <t xml:space="preserve">6.87514591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72786855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57222509384155</t>
+    <t xml:space="preserve">6.72786903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57222461700439</t>
   </si>
   <si>
     <t xml:space="preserve">6.25256633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1588454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55802297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57978010177612</t>
+    <t xml:space="preserve">6.15884447097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55802249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.4509129524231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5856614112854</t>
+    <t xml:space="preserve">4.58566188812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800109863281</t>
+    <t xml:space="preserve">4.74800062179565</t>
   </si>
   <si>
     <t xml:space="preserve">5.05929040908813</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">5.69693231582642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98311758041382</t>
+    <t xml:space="preserve">5.98311710357666</t>
   </si>
   <si>
     <t xml:space="preserve">6.05842971801758</t>
@@ -2240,31 +2240,31 @@
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47515535354614</t>
+    <t xml:space="preserve">6.47515487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.49356508255005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36637163162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61741209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53038454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56720447540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662143707275</t>
+    <t xml:space="preserve">6.36637115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61741065979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5303840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56720304489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42662191390991</t>
   </si>
   <si>
     <t xml:space="preserve">6.3596773147583</t>
@@ -2285,43 +2285,43 @@
     <t xml:space="preserve">6.00487422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20235967636108</t>
+    <t xml:space="preserve">6.20235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.25926160812378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32620477676392</t>
+    <t xml:space="preserve">6.32620429992676</t>
   </si>
   <si>
     <t xml:space="preserve">6.34628820419312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28603935241699</t>
+    <t xml:space="preserve">6.28603839874268</t>
   </si>
   <si>
     <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01826333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08520650863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01156806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89776420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813772201538</t>
+    <t xml:space="preserve">6.01826286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08520746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01156854629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8977632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813819885254</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433338165283</t>
+    <t xml:space="preserve">5.87433385848999</t>
   </si>
   <si>
     <t xml:space="preserve">5.82747220993042</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">5.68354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66011238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08439445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87017393112183</t>
+    <t xml:space="preserve">5.6601128578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08439493179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87017345428467</t>
   </si>
   <si>
     <t xml:space="preserve">4.75302219390869</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">5.74379301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74044513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89106941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94127798080444</t>
+    <t xml:space="preserve">5.74044561386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89106893539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94127702713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.82077789306641</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">5.60655736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2952675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20824146270752</t>
+    <t xml:space="preserve">5.29526805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20824098587036</t>
   </si>
   <si>
     <t xml:space="preserve">5.19819927215576</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">5.33208703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27853202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23167085647583</t>
+    <t xml:space="preserve">5.2785325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23167133331299</t>
   </si>
   <si>
     <t xml:space="preserve">5.35886430740356</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">4.94046545028687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02079772949219</t>
+    <t xml:space="preserve">5.02079820632935</t>
   </si>
   <si>
     <t xml:space="preserve">5.08104753494263</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">5.12790822982788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12456130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11786651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12121391296387</t>
+    <t xml:space="preserve">5.12456083297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11786699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12121343612671</t>
   </si>
   <si>
     <t xml:space="preserve">5.05092287063599</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">4.98063135147095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10447788238525</t>
+    <t xml:space="preserve">5.1044774055481</t>
   </si>
   <si>
     <t xml:space="preserve">5.03753423690796</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">5.41576719284058</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38898992538452</t>
+    <t xml:space="preserve">5.38898944854736</t>
   </si>
   <si>
     <t xml:space="preserve">5.48940515518188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36890697479248</t>
+    <t xml:space="preserve">5.36890649795532</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53961324691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49609994888306</t>
+    <t xml:space="preserve">5.53961372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49610042572021</t>
   </si>
   <si>
     <t xml:space="preserve">5.39568424224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36221170425415</t>
+    <t xml:space="preserve">5.36221218109131</t>
   </si>
   <si>
     <t xml:space="preserve">5.38229560852051</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">5.09108877182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60320997238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12537336349487</t>
+    <t xml:space="preserve">5.60321044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
     <t xml:space="preserve">6.15215063095093</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">6.22244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1956639289856</t>
+    <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
     <t xml:space="preserve">6.1488037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09524726867676</t>
+    <t xml:space="preserve">6.09524822235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.7069730758667</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">5.65341806411743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73040437698364</t>
+    <t xml:space="preserve">5.7304048538208</t>
   </si>
   <si>
     <t xml:space="preserve">5.70027923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70362663269043</t>
+    <t xml:space="preserve">5.70362615585327</t>
   </si>
   <si>
     <t xml:space="preserve">5.65676546096802</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46262741088867</t>
+    <t xml:space="preserve">5.46262788772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.47266960144043</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">5.50948858261108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45258617401123</t>
+    <t xml:space="preserve">5.45258665084839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894773483276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10113000869751</t>
+    <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
     <t xml:space="preserve">4.92372941970825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95385360717773</t>
+    <t xml:space="preserve">4.95385408401489</t>
   </si>
   <si>
     <t xml:space="preserve">4.88021564483643</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">4.94381237030029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07770013809204</t>
+    <t xml:space="preserve">5.07769966125488</t>
   </si>
   <si>
     <t xml:space="preserve">5.2182822227478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15468597412109</t>
+    <t xml:space="preserve">5.15468549728394</t>
   </si>
   <si>
     <t xml:space="preserve">5.55300235748291</t>
@@ -2636,55 +2636,55 @@
     <t xml:space="preserve">5.8609447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02830505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09859561920166</t>
+    <t xml:space="preserve">6.02830457687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0985951423645</t>
   </si>
   <si>
     <t xml:space="preserve">6.44335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59398126602173</t>
+    <t xml:space="preserve">6.59398174285889</t>
   </si>
   <si>
     <t xml:space="preserve">6.8082013130188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63749408721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58728647232056</t>
+    <t xml:space="preserve">6.6374945640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5872859954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.72117519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67766141891479</t>
+    <t xml:space="preserve">6.67766189575195</t>
   </si>
   <si>
     <t xml:space="preserve">6.41323184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64418983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7814245223999</t>
+    <t xml:space="preserve">6.64418935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78142404556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.76134157180786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275411605835</t>
+    <t xml:space="preserve">7.10275506973267</t>
   </si>
   <si>
     <t xml:space="preserve">7.36383628845215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19647741317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283849716187</t>
+    <t xml:space="preserve">7.19647645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283945083618</t>
   </si>
   <si>
     <t xml:space="preserve">7.08936643600464</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">7.20986604690552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14961671829224</t>
+    <t xml:space="preserve">7.14961576461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.05589437484741</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">7.10944890975952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07597684860229</t>
+    <t xml:space="preserve">7.07597780227661</t>
   </si>
   <si>
     <t xml:space="preserve">6.98225688934326</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581190109253</t>
+    <t xml:space="preserve">7.03581142425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.90861749649048</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">7.08267211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13622808456421</t>
+    <t xml:space="preserve">7.13622713088989</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631055831909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25003147125244</t>
+    <t xml:space="preserve">7.25003242492676</t>
   </si>
   <si>
     <t xml:space="preserve">7.27011489868164</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">7.32367038726807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55127954483032</t>
+    <t xml:space="preserve">7.55128049850464</t>
   </si>
   <si>
     <t xml:space="preserve">7.47764158248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41069746017456</t>
+    <t xml:space="preserve">7.4106969833374</t>
   </si>
   <si>
     <t xml:space="preserve">7.39061403274536</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">7.61152982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61822319030762</t>
+    <t xml:space="preserve">7.61822414398193</t>
   </si>
   <si>
     <t xml:space="preserve">7.75880575180054</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">7.85252666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07344245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113647460938</t>
+    <t xml:space="preserve">8.07344341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.18055438995361</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89685249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91693592071533</t>
+    <t xml:space="preserve">8.89685344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91693687438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.48849487304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73618793487549</t>
+    <t xml:space="preserve">8.73618698120117</t>
   </si>
   <si>
     <t xml:space="preserve">8.41485691070557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21402549743652</t>
+    <t xml:space="preserve">8.21402454376221</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
@@ -2849,28 +2849,28 @@
     <t xml:space="preserve">8.20733070373535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32782936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81236028671265</t>
+    <t xml:space="preserve">8.26758098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32783031463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81236219406128</t>
   </si>
   <si>
     <t xml:space="preserve">7.77888917922974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91277599334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938879013062</t>
+    <t xml:space="preserve">7.91277694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938974380493</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049236297607</t>
+    <t xml:space="preserve">8.97049140930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.68009853363037</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">9.93448543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99473476409912</t>
+    <t xml:space="preserve">9.99473571777344</t>
   </si>
   <si>
     <t xml:space="preserve">9.96126270294189</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85415267944336</t>
+    <t xml:space="preserve">9.85415172576904</t>
   </si>
   <si>
     <t xml:space="preserve">9.77381992340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73365306854248</t>
+    <t xml:space="preserve">9.7336540222168</t>
   </si>
   <si>
     <t xml:space="preserve">10.5168981552124</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">10.476731300354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6775636672974</t>
+    <t xml:space="preserve">10.677562713623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6440906524658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.038535118103</t>
+    <t xml:space="preserve">10.0385360717773</t>
   </si>
   <si>
     <t xml:space="preserve">9.84605503082275</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">10.1865949630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0755500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93489170074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94969844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90528011322021</t>
+    <t xml:space="preserve">10.0755491256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93489265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94969749450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9052791595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.63877010345459</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">9.79423332214355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83865261077881</t>
+    <t xml:space="preserve">9.83865165710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">10.0903558731079</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89047336578369</t>
+    <t xml:space="preserve">9.89047241210938</t>
   </si>
   <si>
     <t xml:space="preserve">9.75721836090088</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">9.80904006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85345840454102</t>
+    <t xml:space="preserve">9.85345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">10.0533409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72020435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60175514221191</t>
+    <t xml:space="preserve">9.7202033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6017541885376</t>
   </si>
   <si>
     <t xml:space="preserve">9.5499324798584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52031993865967</t>
+    <t xml:space="preserve">9.52032089233398</t>
   </si>
   <si>
     <t xml:space="preserve">9.4018726348877</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">9.40927505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33524417877197</t>
+    <t xml:space="preserve">9.33524513244629</t>
   </si>
   <si>
     <t xml:space="preserve">9.26121425628662</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">9.10574913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655437469482</t>
+    <t xml:space="preserve">8.99655532836914</t>
   </si>
   <si>
     <t xml:space="preserve">9.34634876251221</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">9.3500509262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37226104736328</t>
+    <t xml:space="preserve">9.37226009368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.4166784286499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30563259124756</t>
+    <t xml:space="preserve">9.30563163757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.17237854003906</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">9.17978000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11315441131592</t>
+    <t xml:space="preserve">9.1131534576416</t>
   </si>
   <si>
     <t xml:space="preserve">9.23160266876221</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31303596496582</t>
+    <t xml:space="preserve">9.15757179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31303691864014</t>
   </si>
   <si>
     <t xml:space="preserve">9.35745525360107</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016746520996</t>
+    <t xml:space="preserve">9.15016841888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.03172016143799</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">9.02431678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98730182647705</t>
+    <t xml:space="preserve">8.98730278015137</t>
   </si>
   <si>
     <t xml:space="preserve">9.09834671020508</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66838264465332</t>
+    <t xml:space="preserve">9.66838359832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">9.43148326873779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52772331237793</t>
+    <t xml:space="preserve">9.52772426605225</t>
   </si>
   <si>
     <t xml:space="preserve">8.86885261535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75040340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92067337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93548011779785</t>
+    <t xml:space="preserve">8.75040245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92067432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93547916412354</t>
   </si>
   <si>
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261352539062</t>
+    <t xml:space="preserve">8.77261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">4.33078384399414</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128879547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090133666992</t>
+    <t xml:space="preserve">4.10128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090181350708</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018421173096</t>
+    <t xml:space="preserve">4.09018468856812</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46033668518066</t>
+    <t xml:space="preserve">4.46033716201782</t>
   </si>
   <si>
     <t xml:space="preserve">4.41962003707886</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">4.15311098098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10499095916748</t>
+    <t xml:space="preserve">4.10499048233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.09758710861206</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">3.87549662590027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576683044434</t>
+    <t xml:space="preserve">4.04576635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.85328698158264</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.07537841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206418991089</t>
+    <t xml:space="preserve">4.04206466674805</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">4.34558963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27526044845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94952630996704</t>
+    <t xml:space="preserve">4.27526092529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9495267868042</t>
   </si>
   <si>
     <t xml:space="preserve">3.9051079750061</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">3.53310537338257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55716466903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52014970779419</t>
+    <t xml:space="preserve">3.55716490745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52015018463135</t>
   </si>
   <si>
     <t xml:space="preserve">3.48313450813293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51459717750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57382130622864</t>
+    <t xml:space="preserve">3.51459765434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
     <t xml:space="preserve">3.62009072303772</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137202262878</t>
+    <t xml:space="preserve">3.33137178421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358166694641</t>
+    <t xml:space="preserve">3.35358119010925</t>
   </si>
   <si>
     <t xml:space="preserve">3.10928058624268</t>
@@ -3371,25 +3371,25 @@
     <t xml:space="preserve">3.14999747276306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20181894302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26474475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10187745094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0130410194397</t>
+    <t xml:space="preserve">3.2018187046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26474452018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10187768936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01304125785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88718891143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05005621910095</t>
+    <t xml:space="preserve">2.88718914985657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05005598068237</t>
   </si>
   <si>
     <t xml:space="preserve">3.00748872756958</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">2.98342871665955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93345808982849</t>
+    <t xml:space="preserve">2.93345832824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.93530893325806</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">2.9242045879364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90014457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85387563705444</t>
+    <t xml:space="preserve">2.90014433860779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85387539863586</t>
   </si>
   <si>
     <t xml:space="preserve">2.82981562614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059102058411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82426333427429</t>
+    <t xml:space="preserve">2.77059125900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82426309585571</t>
   </si>
   <si>
     <t xml:space="preserve">2.83721852302551</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">2.60772395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52999186515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49852919578552</t>
+    <t xml:space="preserve">2.52999210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49852895736694</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297690391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56515645980835</t>
+    <t xml:space="preserve">2.49297666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56515622138977</t>
   </si>
   <si>
     <t xml:space="preserve">2.6151270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57811164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888751983643</t>
+    <t xml:space="preserve">2.57811188697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.44855833053589</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">2.52629041671753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48742461204529</t>
+    <t xml:space="preserve">2.48742437362671</t>
   </si>
   <si>
     <t xml:space="preserve">2.2727358341217</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">2.34861731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41339421272278</t>
+    <t xml:space="preserve">2.4133939743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676671028137</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18760085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29679608345032</t>
+    <t xml:space="preserve">2.18760061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29679584503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.28569149971008</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">2.26718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28754186630249</t>
+    <t xml:space="preserve">2.28754210472107</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">2.08765983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13763022422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14688444137573</t>
+    <t xml:space="preserve">2.13763046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14688420295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434632301331</t>
+    <t xml:space="preserve">2.05434608459473</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">2.01362919807434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810627937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186695098877</t>
+    <t xml:space="preserve">1.95810651779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186671257019</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
@@ -3647,28 +3647,28 @@
     <t xml:space="preserve">1.90132355690002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83638429641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87255322933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91036558151245</t>
+    <t xml:space="preserve">1.83638441562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87255299091339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91036581993103</t>
   </si>
   <si>
     <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84953653812408</t>
+    <t xml:space="preserve">1.84953641891479</t>
   </si>
   <si>
     <t xml:space="preserve">1.78377532958984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70814979076385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86679875850677</t>
+    <t xml:space="preserve">1.70814990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
@@ -3683,40 +3683,40 @@
     <t xml:space="preserve">1.8372061252594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78541910648346</t>
+    <t xml:space="preserve">1.78541922569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.7615807056427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.770623087883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556234836578</t>
+    <t xml:space="preserve">1.77062296867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556222915649</t>
   </si>
   <si>
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85857880115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90625560283661</t>
+    <t xml:space="preserve">1.85857856273651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90625584125519</t>
   </si>
   <si>
     <t xml:space="preserve">1.95311057567596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.958864569664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00078749656677</t>
+    <t xml:space="preserve">1.95886480808258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00078725814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.03695607185364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98023700714111</t>
+    <t xml:space="preserve">1.98023724555969</t>
   </si>
   <si>
     <t xml:space="preserve">2.03942227363586</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559132575989</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07970118522644</t>
+    <t xml:space="preserve">2.07970094680786</t>
   </si>
   <si>
     <t xml:space="preserve">2.0048975944519</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">1.99749958515167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11258172988892</t>
+    <t xml:space="preserve">2.11258149147034</t>
   </si>
   <si>
     <t xml:space="preserve">2.09203147888184</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24204921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23382925987244</t>
+    <t xml:space="preserve">2.2420494556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
     <t xml:space="preserve">2.14135217666626</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">2.19889330863953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28520512580872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34480118751526</t>
+    <t xml:space="preserve">2.28520488739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">2.2728750705719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27904033660889</t>
+    <t xml:space="preserve">2.27904009819031</t>
   </si>
   <si>
     <t xml:space="preserve">2.30781030654907</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25848937034607</t>
+    <t xml:space="preserve">2.25848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">2.19067311286926</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">2.22766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16190266609192</t>
+    <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
     <t xml:space="preserve">2.14546251296997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21944379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24615955352783</t>
+    <t xml:space="preserve">2.21944403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24615931510925</t>
   </si>
   <si>
     <t xml:space="preserve">2.26670980453491</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">2.25437951087952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30986547470093</t>
+    <t xml:space="preserve">2.30986571311951</t>
   </si>
   <si>
     <t xml:space="preserve">2.3550763130188</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">2.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54003000259399</t>
+    <t xml:space="preserve">2.54003024101257</t>
   </si>
   <si>
     <t xml:space="preserve">2.45988368988037</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">2.52153491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54208493232727</t>
+    <t xml:space="preserve">2.54208517074585</t>
   </si>
   <si>
     <t xml:space="preserve">2.51125955581665</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">2.43933320045471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48454427719116</t>
+    <t xml:space="preserve">2.48454403877258</t>
   </si>
   <si>
     <t xml:space="preserve">2.45577335357666</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786447525024</t>
+    <t xml:space="preserve">2.75786471366882</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
@@ -3926,19 +3926,19 @@
     <t xml:space="preserve">2.68799304962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68182802200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74142408370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70443344116211</t>
+    <t xml:space="preserve">2.68182778358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7414243221283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70443320274353</t>
   </si>
   <si>
     <t xml:space="preserve">2.72498393058777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70854353904724</t>
+    <t xml:space="preserve">2.70854377746582</t>
   </si>
   <si>
     <t xml:space="preserve">2.7784149646759</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">2.71881866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78663516044617</t>
+    <t xml:space="preserve">2.78663539886475</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869009017944</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63867211341858</t>
+    <t xml:space="preserve">2.63867235183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.67360782623291</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">2.62017679214478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58524107933044</t>
+    <t xml:space="preserve">2.58524131774902</t>
   </si>
   <si>
     <t xml:space="preserve">2.58935117721558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57907605171204</t>
+    <t xml:space="preserve">2.57907581329346</t>
   </si>
   <si>
     <t xml:space="preserve">2.69621324539185</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">2.98597383499146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95925831794739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035953521729</t>
+    <t xml:space="preserve">2.95925855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035929679871</t>
   </si>
   <si>
     <t xml:space="preserve">2.99419403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99830436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89760756492615</t>
+    <t xml:space="preserve">2.99830412864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89760732650757</t>
   </si>
   <si>
     <t xml:space="preserve">2.84006595611572</t>
@@ -4046,22 +4046,22 @@
     <t xml:space="preserve">2.82773590087891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74553418159485</t>
+    <t xml:space="preserve">2.74553394317627</t>
   </si>
   <si>
     <t xml:space="preserve">2.61606669425964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68388295173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6982684135437</t>
+    <t xml:space="preserve">2.68388319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69826817512512</t>
   </si>
   <si>
     <t xml:space="preserve">2.70237827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66538786888123</t>
+    <t xml:space="preserve">2.66538763046265</t>
   </si>
   <si>
     <t xml:space="preserve">2.79896521568298</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979106903076</t>
+    <t xml:space="preserve">2.82979083061218</t>
   </si>
   <si>
     <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10927629470825</t>
+    <t xml:space="preserve">3.10927653312683</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">2.90582752227783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9633686542511</t>
+    <t xml:space="preserve">2.96336841583252</t>
   </si>
   <si>
     <t xml:space="preserve">2.93665313720703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89966225624084</t>
+    <t xml:space="preserve">2.89966201782227</t>
   </si>
   <si>
     <t xml:space="preserve">2.85856151580811</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">3.02296471595764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06612062454224</t>
+    <t xml:space="preserve">3.06612038612366</t>
   </si>
   <si>
     <t xml:space="preserve">3.05995559692383</t>
@@ -5658,6 +5658,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.98399996757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96399998664856</t>
   </si>
 </sst>
 </file>
@@ -71802,7 +71805,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.691087963</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>231886</v>
@@ -71823,6 +71826,32 @@
         <v>1881</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6910763889</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>208671</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>3.99600005149841</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>3.94799995422363</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>3.99600005149841</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>3.96399998664856</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2356567382812</t>
+    <t xml:space="preserve">12.2356538772583</t>
   </si>
   <si>
     <t xml:space="preserve">MFEB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.195689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027997970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5895681381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4097318649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101791381836</t>
+    <t xml:space="preserve">12.1956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027988433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5895690917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101800918579</t>
   </si>
   <si>
     <t xml:space="preserve">11.0766973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1366424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8302536010742</t>
+    <t xml:space="preserve">11.136643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8302545547485</t>
   </si>
   <si>
     <t xml:space="preserve">10.6770572662354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3107204437256</t>
+    <t xml:space="preserve">10.3107213973999</t>
   </si>
   <si>
     <t xml:space="preserve">10.2907390594482</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">10.2707567214966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4838972091675</t>
+    <t xml:space="preserve">10.4838962554932</t>
   </si>
   <si>
     <t xml:space="preserve">10.2973985671997</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">9.77120590209961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2174711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4639158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6171102523804</t>
+    <t xml:space="preserve">10.217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4639139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6171112060547</t>
   </si>
   <si>
     <t xml:space="preserve">10.4172916412354</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">10.9301624298096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96436595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4905576705933</t>
+    <t xml:space="preserve">9.9643669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4905586242676</t>
   </si>
   <si>
     <t xml:space="preserve">10.7236824035645</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">11.6495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898397445679</t>
+    <t xml:space="preserve">11.2898387908936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0624771118164</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">12.2289934158325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.475438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4554576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3422250747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4621162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5553665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823692321777</t>
+    <t xml:space="preserve">12.4754390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4554567337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3422260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4621181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823701858521</t>
   </si>
   <si>
     <t xml:space="preserve">11.6961402893066</t>
@@ -209,37 +209,37 @@
     <t xml:space="preserve">12.075798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9159421920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1890296936035</t>
+    <t xml:space="preserve">11.915940284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1890287399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.496319770813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0633764266968</t>
+    <t xml:space="preserve">11.0633773803711</t>
   </si>
   <si>
     <t xml:space="preserve">11.6561756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9559078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2689580917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.821795463562</t>
+    <t xml:space="preserve">11.9559049606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8217926025391</t>
   </si>
   <si>
     <t xml:space="preserve">12.921703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9350261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1015434265137</t>
+    <t xml:space="preserve">12.9350252151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.101541519165</t>
   </si>
   <si>
     <t xml:space="preserve">13.1281843185425</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">13.2480764389038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1947917938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1814699172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3613090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2347555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3946123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0882196426392</t>
+    <t xml:space="preserve">13.1947908401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.16148853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.361307144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2347564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3946113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0882205963135</t>
   </si>
   <si>
     <t xml:space="preserve">12.981650352478</t>
@@ -275,55 +275,55 @@
     <t xml:space="preserve">12.6885786056519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5620288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8817386627197</t>
+    <t xml:space="preserve">12.5620269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8817405700684</t>
   </si>
   <si>
     <t xml:space="preserve">12.8617582321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8884000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0482568740845</t>
+    <t xml:space="preserve">12.8884010314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0482587814331</t>
   </si>
   <si>
     <t xml:space="preserve">12.4088315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755292892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3488864898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7218837738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7685079574585</t>
+    <t xml:space="preserve">12.3755283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3488874435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.721884727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7685089111328</t>
   </si>
   <si>
     <t xml:space="preserve">12.9150428771973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2214336395264</t>
+    <t xml:space="preserve">13.2214345932007</t>
   </si>
   <si>
     <t xml:space="preserve">13.134407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3887939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5159864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6230993270874</t>
+    <t xml:space="preserve">13.3887929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5159883499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6230983734131</t>
   </si>
   <si>
     <t xml:space="preserve">13.5226821899414</t>
@@ -332,64 +332,64 @@
     <t xml:space="preserve">13.5561542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4222640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3620157241821</t>
+    <t xml:space="preserve">13.4222650527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3620166778564</t>
   </si>
   <si>
     <t xml:space="preserve">13.3553218841553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0741567611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2749891281128</t>
+    <t xml:space="preserve">13.0741586685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9938249588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017683029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2749900817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.1946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6591033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0833873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8156108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7218894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6524095535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6925754547119</t>
+    <t xml:space="preserve">12.6591053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0833864212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8156099319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7218885421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6524105072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6925764083862</t>
   </si>
   <si>
     <t xml:space="preserve">12.4515800476074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8850889205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1487054824829</t>
+    <t xml:space="preserve">13.1411008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8850908279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1487064361572</t>
   </si>
   <si>
     <t xml:space="preserve">10.4231758117676</t>
@@ -398,43 +398,43 @@
     <t xml:space="preserve">10.8382291793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4834251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7177305221558</t>
+    <t xml:space="preserve">10.4834260940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7177295684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.2290382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4164810180664</t>
+    <t xml:space="preserve">10.4164819717407</t>
   </si>
   <si>
     <t xml:space="preserve">10.0482892990112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4432601928711</t>
+    <t xml:space="preserve">10.4432592391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.7445068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1193933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.474196434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2599754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1260890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0189771652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0122842788696</t>
+    <t xml:space="preserve">11.1193943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4741954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2599763870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126088142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0189762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0122833251953</t>
   </si>
   <si>
     <t xml:space="preserve">10.811450958252</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">10.9252557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8783960342407</t>
+    <t xml:space="preserve">10.8783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">10.7645902633667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0616788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1754846572876</t>
+    <t xml:space="preserve">10.0616779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1754837036133</t>
   </si>
   <si>
     <t xml:space="preserve">9.88762474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06421375274658</t>
+    <t xml:space="preserve">9.06421279907227</t>
   </si>
   <si>
     <t xml:space="preserve">8.93032550811768</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">9.25835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23826885223389</t>
+    <t xml:space="preserve">9.33868312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23826789855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.31860065460205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13115787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37885093688965</t>
+    <t xml:space="preserve">9.13115692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37884998321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.19140720367432</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">9.63323783874512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79390335083008</t>
+    <t xml:space="preserve">9.79390239715576</t>
   </si>
   <si>
     <t xml:space="preserve">9.55959892272949</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">9.51273918151855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43909931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56629276275635</t>
+    <t xml:space="preserve">9.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56629371643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">9.53951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82737636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76043128967285</t>
+    <t xml:space="preserve">9.8273754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76043033599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.78720855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87423515319824</t>
+    <t xml:space="preserve">9.87423610687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.6734037399292</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">9.17132377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07090759277344</t>
+    <t xml:space="preserve">9.07090854644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.08429622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31190586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17801761627197</t>
+    <t xml:space="preserve">9.3119068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17801856994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.35207271575928</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">9.3855447769165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24496269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03743553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72279930114746</t>
+    <t xml:space="preserve">9.24496173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03743457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70941066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72280025482178</t>
   </si>
   <si>
     <t xml:space="preserve">8.87007617950439</t>
@@ -590,79 +590,79 @@
     <t xml:space="preserve">8.74957656860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78304958343506</t>
+    <t xml:space="preserve">8.78304862976074</t>
   </si>
   <si>
     <t xml:space="preserve">8.78974342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71610546112061</t>
+    <t xml:space="preserve">8.71610450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.66924381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33452415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20063591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10022068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12030410766602</t>
+    <t xml:space="preserve">8.33452320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2006368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1002197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1203031539917</t>
   </si>
   <si>
     <t xml:space="preserve">7.79227781295776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82575082778931</t>
+    <t xml:space="preserve">7.82575035095215</t>
   </si>
   <si>
     <t xml:space="preserve">7.83913898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86591577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583473205566</t>
+    <t xml:space="preserve">7.86591625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.6316123008728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62491798400879</t>
+    <t xml:space="preserve">7.62491750717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.66508436203003</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74541759490967</t>
+    <t xml:space="preserve">7.74541711807251</t>
   </si>
   <si>
     <t xml:space="preserve">7.71194553375244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69186210632324</t>
+    <t xml:space="preserve">7.69186162948608</t>
   </si>
   <si>
     <t xml:space="preserve">7.48433542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64500188827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65169620513916</t>
+    <t xml:space="preserve">7.64500141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65169525146484</t>
   </si>
   <si>
     <t xml:space="preserve">7.68516731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95963907241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12699890136719</t>
+    <t xml:space="preserve">7.95963764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12699794769287</t>
   </si>
   <si>
     <t xml:space="preserve">8.38138484954834</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">9.09768676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99635887146</t>
+    <t xml:space="preserve">11.9963598251343</t>
   </si>
   <si>
     <t xml:space="preserve">12.1168594360352</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">11.9294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8691654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0499143600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2833080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7971515655518</t>
+    <t xml:space="preserve">11.8691644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0499134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615617752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2833089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7971534729004</t>
   </si>
   <si>
     <t xml:space="preserve">13.6967363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7569847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8975687026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7235126495361</t>
+    <t xml:space="preserve">13.7569856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8975667953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7235145568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.8908739089966</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">14.6004800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0180683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.058235168457</t>
+    <t xml:space="preserve">14.0180673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0582332611084</t>
   </si>
   <si>
     <t xml:space="preserve">13.9712066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0917062759399</t>
+    <t xml:space="preserve">14.0917053222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.3126201629639</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">14.2858438491821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1385650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1251783370972</t>
+    <t xml:space="preserve">14.1385669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1251773834229</t>
   </si>
   <si>
     <t xml:space="preserve">13.817234992981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101240158081</t>
+    <t xml:space="preserve">13.7101230621338</t>
   </si>
   <si>
     <t xml:space="preserve">13.4557371139526</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">13.1544904708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2549047470093</t>
+    <t xml:space="preserve">13.2549057006836</t>
   </si>
   <si>
     <t xml:space="preserve">13.208044052124</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">12.7528247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8264636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9737415313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9067974090576</t>
+    <t xml:space="preserve">12.8264656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9737405776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9067983627319</t>
   </si>
   <si>
     <t xml:space="preserve">13.1611852645874</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">13.3419332504272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812686920166</t>
+    <t xml:space="preserve">13.1812696456909</t>
   </si>
   <si>
     <t xml:space="preserve">13.033989906311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8599348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9871292114258</t>
+    <t xml:space="preserve">12.8599367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9871301651001</t>
   </si>
   <si>
     <t xml:space="preserve">13.0072135925293</t>
@@ -824,61 +824,61 @@
     <t xml:space="preserve">13.0206031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9201860427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8934087753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3754034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4758214950562</t>
+    <t xml:space="preserve">12.920184135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3754043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">13.3486280441284</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1745729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0406847000122</t>
+    <t xml:space="preserve">13.1745719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0406866073608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8666305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8867139816284</t>
+    <t xml:space="preserve">12.8867130279541</t>
   </si>
   <si>
     <t xml:space="preserve">12.9335746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9001035690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9536581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8197689056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858835220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5386047363281</t>
+    <t xml:space="preserve">12.8398523330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9001045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9536590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5386056900024</t>
   </si>
   <si>
     <t xml:space="preserve">12.3109951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3310794830322</t>
+    <t xml:space="preserve">12.3310804367065</t>
   </si>
   <si>
     <t xml:space="preserve">12.4047183990479</t>
@@ -890,55 +890,55 @@
     <t xml:space="preserve">12.1570243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6750288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8624706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1771087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1436347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8800210952759</t>
+    <t xml:space="preserve">11.6750297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8624715805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1771078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862997055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8800191879272</t>
   </si>
   <si>
     <t xml:space="preserve">12.946964263916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5653839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1637191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3043003082275</t>
+    <t xml:space="preserve">12.5653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1637201309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3043012619019</t>
   </si>
   <si>
     <t xml:space="preserve">12.3913288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5586881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4649677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6189384460449</t>
+    <t xml:space="preserve">12.5586891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4649667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6189393997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.2574405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2842178344727</t>
+    <t xml:space="preserve">12.284218788147</t>
   </si>
   <si>
     <t xml:space="preserve">12.4181060791016</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">12.1971921920776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1034708023071</t>
+    <t xml:space="preserve">12.1034698486328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0900802612305</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">12.0633029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5519952774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6724939346313</t>
+    <t xml:space="preserve">12.5519943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.672492980957</t>
   </si>
   <si>
     <t xml:space="preserve">12.3176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8089160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813064575195</t>
+    <t xml:space="preserve">11.8089151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030527114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5813055038452</t>
   </si>
   <si>
     <t xml:space="preserve">11.6147785186768</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">11.5076684951782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6549453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5880002975464</t>
+    <t xml:space="preserve">11.6549444198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5880012512207</t>
   </si>
   <si>
     <t xml:space="preserve">11.7084999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6817216873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942789077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5210571289062</t>
+    <t xml:space="preserve">11.6817235946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5210561752319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151947021484</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">11.7687501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7018060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4474191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3804759979248</t>
+    <t xml:space="preserve">11.7018051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3804750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.2265043258667</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">11.1394758224487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1930322647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461706161499</t>
+    <t xml:space="preserve">11.1930313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658388137817</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">11.1327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1528663635254</t>
+    <t xml:space="preserve">11.0591440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1528654098511</t>
   </si>
   <si>
     <t xml:space="preserve">11.0993099212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1997261047363</t>
+    <t xml:space="preserve">11.199725151062</t>
   </si>
   <si>
     <t xml:space="preserve">10.9921998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1126985549927</t>
+    <t xml:space="preserve">11.112699508667</t>
   </si>
   <si>
     <t xml:space="preserve">11.4206409454346</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">11.5411405563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5679197311401</t>
+    <t xml:space="preserve">11.5679187774658</t>
   </si>
   <si>
     <t xml:space="preserve">11.2198095321655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3001413345337</t>
+    <t xml:space="preserve">11.300142288208</t>
   </si>
   <si>
     <t xml:space="preserve">11.4005584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.460807800293</t>
+    <t xml:space="preserve">11.4608087539673</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3536958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1595602035522</t>
+    <t xml:space="preserve">11.3336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3536968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1595592498779</t>
   </si>
   <si>
     <t xml:space="preserve">11.0524492263794</t>
@@ -1106,52 +1106,52 @@
     <t xml:space="preserve">10.9721164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5302858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3897037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3093719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1620941162109</t>
+    <t xml:space="preserve">10.5302867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3897047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3093709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1620950698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.2156505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3361492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901208877563</t>
+    <t xml:space="preserve">10.3361482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.490119934082</t>
   </si>
   <si>
     <t xml:space="preserve">10.2625102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3428430557251</t>
+    <t xml:space="preserve">10.3428440093994</t>
   </si>
   <si>
     <t xml:space="preserve">10.3562316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80059719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80729198455811</t>
+    <t xml:space="preserve">9.84076404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80059814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80729103088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.68679237365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7135705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72026443481445</t>
+    <t xml:space="preserve">9.71356964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72026538848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.74704265594482</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">9.74034786224365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75373554229736</t>
+    <t xml:space="preserve">9.75373649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.70018100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5235919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7110347747803</t>
+    <t xml:space="preserve">10.5235929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7110357284546</t>
   </si>
   <si>
     <t xml:space="preserve">10.650785446167</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">10.4700374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6708679199219</t>
+    <t xml:space="preserve">10.6708688735962</t>
   </si>
   <si>
     <t xml:space="preserve">10.664174079895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3763151168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.275899887085</t>
+    <t xml:space="preserve">10.3763160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1888723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2758989334106</t>
   </si>
   <si>
     <t xml:space="preserve">10.128623008728</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">10.316065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2089557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65332126617432</t>
+    <t xml:space="preserve">10.2089548110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6533203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.52612590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62654209136963</t>
+    <t xml:space="preserve">9.62654304504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.83406829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2959823608398</t>
+    <t xml:space="preserve">9.8474588394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2959833145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436754226685</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7712850570679</t>
+    <t xml:space="preserve">10.7712841033936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5972299575806</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">10.8583116531372</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9855041503906</t>
+    <t xml:space="preserve">10.9855051040649</t>
   </si>
   <si>
     <t xml:space="preserve">10.9587278366089</t>
@@ -1256,34 +1256,34 @@
     <t xml:space="preserve">10.82483959198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725326538086</t>
+    <t xml:space="preserve">10.9654216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725336074829</t>
   </si>
   <si>
     <t xml:space="preserve">10.9988946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0926160812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1796426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2465877532959</t>
+    <t xml:space="preserve">11.0926151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1796436309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2465858459473</t>
   </si>
   <si>
     <t xml:space="preserve">11.0859212875366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9185619354248</t>
+    <t xml:space="preserve">10.9185609817505</t>
   </si>
   <si>
     <t xml:space="preserve">10.9118661880493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9051733016968</t>
+    <t xml:space="preserve">10.9051742553711</t>
   </si>
   <si>
     <t xml:space="preserve">10.8917837142944</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">10.7512006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0390605926514</t>
+    <t xml:space="preserve">11.0390596389771</t>
   </si>
   <si>
     <t xml:space="preserve">10.7277708053589</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">10.1554002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871877670288</t>
+    <t xml:space="preserve">10.5871887207031</t>
   </si>
   <si>
     <t xml:space="preserve">10.2892875671387</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">10.3696203231812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6206607818604</t>
+    <t xml:space="preserve">10.5135507583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.620659828186</t>
   </si>
   <si>
     <t xml:space="preserve">10.8616590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6407451629639</t>
+    <t xml:space="preserve">10.6407432556152</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106185913086</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">10.5503702163696</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5771465301514</t>
+    <t xml:space="preserve">10.5771474838257</t>
   </si>
   <si>
     <t xml:space="preserve">10.5336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6139659881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6240091323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4097881317139</t>
+    <t xml:space="preserve">10.6139669418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6240072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4097871780396</t>
   </si>
   <si>
     <t xml:space="preserve">11.1729488372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.982159614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269403457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261079788208</t>
+    <t xml:space="preserve">10.9821586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261070251465</t>
   </si>
   <si>
     <t xml:space="preserve">10.4030933380127</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">10.3394956588745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3629264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1520528793335</t>
+    <t xml:space="preserve">10.3629274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1520519256592</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">10.0349016189575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0951499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9788103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1060056686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0357131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1762952804565</t>
+    <t xml:space="preserve">10.0951509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9788112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0357141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.8717002868652</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">10.868353843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620742797852</t>
+    <t xml:space="preserve">10.9620752334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.0223245620728</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">10.9553804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025671005249</t>
+    <t xml:space="preserve">11.0256719589233</t>
   </si>
   <si>
     <t xml:space="preserve">11.0825748443604</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">10.952033996582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0290193557739</t>
+    <t xml:space="preserve">11.0290203094482</t>
   </si>
   <si>
     <t xml:space="preserve">11.0758800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2867546081543</t>
+    <t xml:space="preserve">11.28675365448</t>
   </si>
   <si>
     <t xml:space="preserve">11.313530921936</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">10.1721353530884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.245774269104</t>
+    <t xml:space="preserve">10.2457733154297</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683727264404</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">9.34537792205811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67005634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72695827484131</t>
+    <t xml:space="preserve">9.6700553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72695922851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.66336250305176</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">9.48596000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58637619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6165018081665</t>
+    <t xml:space="preserve">9.58637714385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">9.54286289215088</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.50269603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49600315093994</t>
+    <t xml:space="preserve">9.47926616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49600219726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.62319564819336</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">8.60564708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68932819366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72949314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89350700378418</t>
+    <t xml:space="preserve">8.68932628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89350605010986</t>
   </si>
   <si>
     <t xml:space="preserve">9.14119911193848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30186557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22487926483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28512859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2148380279541</t>
+    <t xml:space="preserve">9.30186462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22487831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28512954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21483707427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.13785171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45583629608154</t>
+    <t xml:space="preserve">9.45583438873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.39558601379395</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">9.61315441131592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71691703796387</t>
+    <t xml:space="preserve">9.71691799163818</t>
   </si>
   <si>
     <t xml:space="preserve">9.46922397613525</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">9.31525421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26504611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73284149169922</t>
+    <t xml:space="preserve">9.26504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7328405380249</t>
   </si>
   <si>
     <t xml:space="preserve">8.80647945404053</t>
@@ -1580,34 +1580,34 @@
     <t xml:space="preserve">8.89015865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02070045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86338043212891</t>
+    <t xml:space="preserve">9.0206995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85334014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86338138580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.86003398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92028331756592</t>
+    <t xml:space="preserve">8.92028427124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.88011741638184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82656288146973</t>
+    <t xml:space="preserve">8.82656383514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.58891105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29770469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2742748260498</t>
+    <t xml:space="preserve">8.29770565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27427387237549</t>
   </si>
   <si>
     <t xml:space="preserve">8.24080276489258</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">8.25084400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64581298828125</t>
+    <t xml:space="preserve">8.64581394195557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795497894287</t>
@@ -1625,16 +1625,16 @@
     <t xml:space="preserve">8.47845363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47175884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53870296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78639507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71945095062256</t>
+    <t xml:space="preserve">8.47175979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53870391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78639602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71945190429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635383605957</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">9.16462898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1345043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00731086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01065921783447</t>
+    <t xml:space="preserve">9.13450527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00731182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01065826416016</t>
   </si>
   <si>
     <t xml:space="preserve">9.01400566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20814418792725</t>
+    <t xml:space="preserve">9.20814323425293</t>
   </si>
   <si>
     <t xml:space="preserve">9.22822570800781</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">8.94706153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0006160736084</t>
+    <t xml:space="preserve">9.00061511993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735210418701</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">9.12781047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03408813476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66589641571045</t>
+    <t xml:space="preserve">9.03408908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66589736938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.59560585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84999370574951</t>
+    <t xml:space="preserve">8.84999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.53535652160645</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">8.30105209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62907791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7529239654541</t>
+    <t xml:space="preserve">8.62907886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75292491912842</t>
   </si>
   <si>
     <t xml:space="preserve">8.90689563751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29516983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30855846405029</t>
+    <t xml:space="preserve">9.29517078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30855751037598</t>
   </si>
   <si>
     <t xml:space="preserve">9.50604343414307</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">9.46587753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12111663818359</t>
+    <t xml:space="preserve">9.12111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.11107349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29435729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3110933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34456539154053</t>
+    <t xml:space="preserve">8.294358253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31109428405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34456634521484</t>
   </si>
   <si>
     <t xml:space="preserve">8.32448387145996</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">8.48514842987061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93367385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19810199737549</t>
+    <t xml:space="preserve">8.49184322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93367290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19810104370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.23492050170898</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">8.25753879547119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5654821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50188446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.756272315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82321548461914</t>
+    <t xml:space="preserve">8.56548118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5018835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75627040863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82321453094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.84329795837402</t>
@@ -1778,25 +1778,25 @@
     <t xml:space="preserve">9.18471240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26169776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29851722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44914054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91105556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84411144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.522780418396</t>
+    <t xml:space="preserve">9.42236423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26169872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29851818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91105461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45918273925781</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">9.4424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41901683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60646057128906</t>
+    <t xml:space="preserve">9.41901588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60645961761475</t>
   </si>
   <si>
     <t xml:space="preserve">9.95456790924072</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">8.71275806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80982685089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10438060760498</t>
+    <t xml:space="preserve">8.8098258972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10437965393066</t>
   </si>
   <si>
     <t xml:space="preserve">9.27843379974365</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">9.51943302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42905902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36211490631104</t>
+    <t xml:space="preserve">9.42905807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">9.24830913543701</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">9.47257137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55625152587891</t>
+    <t xml:space="preserve">9.55625247955322</t>
   </si>
   <si>
     <t xml:space="preserve">9.42571067810059</t>
@@ -1865,37 +1865,37 @@
     <t xml:space="preserve">9.15124034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128253936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14789390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43240547180176</t>
+    <t xml:space="preserve">9.16128158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14789295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43240451812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.39223861694336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33533668518066</t>
+    <t xml:space="preserve">9.33533573150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.24161529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14454650878906</t>
+    <t xml:space="preserve">9.14454555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.2516565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73030662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69014072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50938987731934</t>
+    <t xml:space="preserve">9.73030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69013977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50939083099365</t>
   </si>
   <si>
     <t xml:space="preserve">9.73700046539307</t>
@@ -1907,31 +1907,31 @@
     <t xml:space="preserve">9.92109680175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90770721435547</t>
+    <t xml:space="preserve">9.90770816802979</t>
   </si>
   <si>
     <t xml:space="preserve">9.92779064178467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77716732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7102222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62989044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38889122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45248794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25500392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76296520233154</t>
+    <t xml:space="preserve">9.77716541290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71022319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62988948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38889217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45248889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25500297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.76631259918213</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">8.73953628540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7730073928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75961780548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02404594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40562725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63993072509766</t>
+    <t xml:space="preserve">8.77300643920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75961875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02404689788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63993263244629</t>
   </si>
   <si>
     <t xml:space="preserve">9.70687580108643</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">9.76712512969971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66670989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53282070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60311222076416</t>
+    <t xml:space="preserve">9.66670894622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53282165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60311317443848</t>
   </si>
   <si>
     <t xml:space="preserve">9.35542011260986</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">9.20144844055176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10103225708008</t>
+    <t xml:space="preserve">9.10103321075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.02739429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9437141418457</t>
+    <t xml:space="preserve">8.94371318817139</t>
   </si>
   <si>
     <t xml:space="preserve">8.98053359985352</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">8.90354824066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68263244628906</t>
+    <t xml:space="preserve">8.68263339996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.67928600311279</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">9.82402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063938140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82067966461182</t>
+    <t xml:space="preserve">9.81063842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068061828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.30521202087402</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">9.1746711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08764362335205</t>
+    <t xml:space="preserve">9.08764457702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.04413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09099102020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74288177490234</t>
+    <t xml:space="preserve">9.09099006652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88346576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74288272857666</t>
   </si>
   <si>
     <t xml:space="preserve">8.7930908203125</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">8.65250778198242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84664535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87677097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88681125640869</t>
+    <t xml:space="preserve">8.84664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87677001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88681221008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.00396347045898</t>
@@ -2072,28 +2072,28 @@
     <t xml:space="preserve">9.05417156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06086540222168</t>
+    <t xml:space="preserve">9.060866355896</t>
   </si>
   <si>
     <t xml:space="preserve">9.15458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97383975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11776733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0809497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96714496612549</t>
+    <t xml:space="preserve">8.97383880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08094882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9671459197998</t>
   </si>
   <si>
     <t xml:space="preserve">8.95040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90020084381104</t>
+    <t xml:space="preserve">8.90020179748535</t>
   </si>
   <si>
     <t xml:space="preserve">8.94036674499512</t>
@@ -2102,88 +2102,88 @@
     <t xml:space="preserve">8.99726867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92697906494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06756114959717</t>
+    <t xml:space="preserve">8.92697811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06756019592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.829909324646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40146923065186</t>
+    <t xml:space="preserve">8.64246559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40146827697754</t>
   </si>
   <si>
     <t xml:space="preserve">8.33787155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28431606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15377616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98976230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06005477905273</t>
+    <t xml:space="preserve">8.28431701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15377521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98976278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0600528717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.01654052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03327751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94624900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95629119873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93286037445068</t>
+    <t xml:space="preserve">8.03327655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94624948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95629024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93286085128784</t>
   </si>
   <si>
     <t xml:space="preserve">8.02323436737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96633148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03997039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6717791557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12953233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22325468063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54793262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16300535202026</t>
+    <t xml:space="preserve">7.96633291244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03997135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94290161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558397293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67177867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12953186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2232551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54793214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16300487518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.07262992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87514591217041</t>
+    <t xml:space="preserve">6.87514543533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.72786855697632</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">6.1588454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55802297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57978010177612</t>
+    <t xml:space="preserve">5.55802345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.45091247558594</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">4.96556901931763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74800157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05929040908813</t>
+    <t xml:space="preserve">4.74800109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05929088592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.27183771133423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6902379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6969313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98311805725098</t>
+    <t xml:space="preserve">5.69023752212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69693231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98311758041382</t>
   </si>
   <si>
     <t xml:space="preserve">6.05842971801758</t>
@@ -2240,91 +2240,91 @@
     <t xml:space="preserve">6.29440689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4751558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49356460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36637210845947</t>
+    <t xml:space="preserve">6.47515487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49356508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36637163162231</t>
   </si>
   <si>
     <t xml:space="preserve">6.61741161346436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5303840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64753675460815</t>
+    <t xml:space="preserve">6.53038454055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.647536277771</t>
   </si>
   <si>
     <t xml:space="preserve">6.56720352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42662143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3596773147583</t>
+    <t xml:space="preserve">6.54377269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35967683792114</t>
   </si>
   <si>
     <t xml:space="preserve">6.09190130233765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03834629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17892837524414</t>
+    <t xml:space="preserve">6.03834676742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17892789840698</t>
   </si>
   <si>
     <t xml:space="preserve">5.85759735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00487375259399</t>
+    <t xml:space="preserve">6.00487422943115</t>
   </si>
   <si>
     <t xml:space="preserve">6.20235919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25926160812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32620477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34628772735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28603839874268</t>
+    <t xml:space="preserve">6.25926113128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32620525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34628820419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28603935241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.20905303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01826286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08520698547363</t>
+    <t xml:space="preserve">6.01826333999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08520650863647</t>
   </si>
   <si>
     <t xml:space="preserve">6.01156806945801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89776372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98813772201538</t>
+    <t xml:space="preserve">5.89776420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98813724517822</t>
   </si>
   <si>
     <t xml:space="preserve">6.05508184432983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87433338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82747268676758</t>
+    <t xml:space="preserve">5.87433290481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82747220993042</t>
   </si>
   <si>
     <t xml:space="preserve">5.68354272842407</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">5.66011238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08439445495605</t>
+    <t xml:space="preserve">5.0843939781189</t>
   </si>
   <si>
     <t xml:space="preserve">4.87017393112183</t>
@@ -2342,25 +2342,25 @@
     <t xml:space="preserve">4.75302171707153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91368818283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0877423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17142152786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18815755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34212923049927</t>
+    <t xml:space="preserve">4.91368770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08774185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17142200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18815803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34212875366211</t>
   </si>
   <si>
     <t xml:space="preserve">5.15803289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22163009643555</t>
+    <t xml:space="preserve">5.22162961959839</t>
   </si>
   <si>
     <t xml:space="preserve">5.37225341796875</t>
@@ -2372,34 +2372,34 @@
     <t xml:space="preserve">5.74044513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89106893539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94127798080444</t>
+    <t xml:space="preserve">5.89106941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94127702713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.82077741622925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60655689239502</t>
+    <t xml:space="preserve">5.60655736923218</t>
   </si>
   <si>
     <t xml:space="preserve">5.29526805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2082405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19819927215576</t>
+    <t xml:space="preserve">5.20824098587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1981987953186</t>
   </si>
   <si>
     <t xml:space="preserve">5.29861497879028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2852258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30196237564087</t>
+    <t xml:space="preserve">5.28522634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30196285247803</t>
   </si>
   <si>
     <t xml:space="preserve">5.23836517333984</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">5.23167133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35886526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32204580307007</t>
+    <t xml:space="preserve">5.35886478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32204532623291</t>
   </si>
   <si>
     <t xml:space="preserve">5.3253927230835</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">5.04422807693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97059011459351</t>
+    <t xml:space="preserve">4.97058963775635</t>
   </si>
   <si>
     <t xml:space="preserve">4.94046497344971</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">5.02079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08104705810547</t>
+    <t xml:space="preserve">5.08104753494263</t>
   </si>
   <si>
     <t xml:space="preserve">5.13125514984131</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">5.1145191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12790775299072</t>
+    <t xml:space="preserve">5.12790822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.12456083297729</t>
@@ -2462,13 +2462,13 @@
     <t xml:space="preserve">5.12121391296387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05092287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98063135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10447788238525</t>
+    <t xml:space="preserve">5.05092239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98063182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1044774055481</t>
   </si>
   <si>
     <t xml:space="preserve">5.0375337600708</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">4.96389532089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41576719284058</t>
+    <t xml:space="preserve">5.41576766967773</t>
   </si>
   <si>
     <t xml:space="preserve">5.38898992538452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48940515518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36890649795532</t>
+    <t xml:space="preserve">5.48940563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36890697479248</t>
   </si>
   <si>
     <t xml:space="preserve">5.32874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5764331817627</t>
+    <t xml:space="preserve">5.57643270492554</t>
   </si>
   <si>
     <t xml:space="preserve">5.53961277008057</t>
@@ -2525,37 +2525,37 @@
     <t xml:space="preserve">5.09108877182007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60320997238159</t>
+    <t xml:space="preserve">5.60321044921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.12537288665771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27934408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22244167327881</t>
+    <t xml:space="preserve">6.15215063095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27934455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22244215011597</t>
   </si>
   <si>
     <t xml:space="preserve">6.19566440582275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14880418777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09524774551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7069730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89441728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73375129699707</t>
+    <t xml:space="preserve">6.14880323410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09524822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70697259902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89441633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73375082015991</t>
   </si>
   <si>
     <t xml:space="preserve">5.62664031982422</t>
@@ -2567,16 +2567,16 @@
     <t xml:space="preserve">5.48605823516846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48271131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52287721633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65341806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73040390014648</t>
+    <t xml:space="preserve">5.48271083831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65341758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73040437698364</t>
   </si>
   <si>
     <t xml:space="preserve">5.70027923583984</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">5.65676546096802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55634927749634</t>
+    <t xml:space="preserve">5.5563497543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.46262788772583</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">5.47266960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50948858261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45258665084839</t>
+    <t xml:space="preserve">5.50948810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45258712768555</t>
   </si>
   <si>
     <t xml:space="preserve">5.37894773483276</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">5.10113048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92372894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95385360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88021564483643</t>
+    <t xml:space="preserve">4.92372941970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95385408401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88021516799927</t>
   </si>
   <si>
     <t xml:space="preserve">4.94381237030029</t>
@@ -2624,49 +2624,49 @@
     <t xml:space="preserve">5.07770013809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2182822227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15468597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55300283432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8609447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02830410003662</t>
+    <t xml:space="preserve">5.21828269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15468549728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55300235748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86094427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02830457687378</t>
   </si>
   <si>
     <t xml:space="preserve">6.09859609603882</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44335699081421</t>
+    <t xml:space="preserve">6.44335651397705</t>
   </si>
   <si>
     <t xml:space="preserve">6.59398126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80820178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6374945640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58728647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72117376327515</t>
+    <t xml:space="preserve">6.80820226669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63749504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72117471694946</t>
   </si>
   <si>
     <t xml:space="preserve">6.67766094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41323184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64418888092041</t>
+    <t xml:space="preserve">6.41323280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64418935775757</t>
   </si>
   <si>
     <t xml:space="preserve">6.7814245223999</t>
@@ -2675,49 +2675,49 @@
     <t xml:space="preserve">6.7613410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10275459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19647693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12283897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08936595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97556114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20986557006836</t>
+    <t xml:space="preserve">7.10275554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36383581161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19647598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12283802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08936548233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97556209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2098650932312</t>
   </si>
   <si>
     <t xml:space="preserve">7.14961576461792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05589437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86175632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06928253173828</t>
+    <t xml:space="preserve">7.05589389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00233888626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86175727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0692834854126</t>
   </si>
   <si>
     <t xml:space="preserve">7.10944890975952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07597732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9822564125061</t>
+    <t xml:space="preserve">7.07597684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98225545883179</t>
   </si>
   <si>
     <t xml:space="preserve">7.14292192459106</t>
@@ -2726,73 +2726,73 @@
     <t xml:space="preserve">7.09606170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92200708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96886730194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90192317962646</t>
+    <t xml:space="preserve">6.92200660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96886777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90192365646362</t>
   </si>
   <si>
     <t xml:space="preserve">7.11614465713501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01572751998901</t>
+    <t xml:space="preserve">7.01572799682617</t>
   </si>
   <si>
     <t xml:space="preserve">7.18978214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03581094741821</t>
+    <t xml:space="preserve">7.03581142425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.90861749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08267211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13622617721558</t>
+    <t xml:space="preserve">7.08267164230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13622665405273</t>
   </si>
   <si>
     <t xml:space="preserve">7.15631008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25003099441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27011489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32366991043091</t>
+    <t xml:space="preserve">7.25003147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27011442184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">7.55127954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47764158248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41069746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39061403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.470947265625</t>
+    <t xml:space="preserve">7.47764110565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4106969833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39061498641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47094631195068</t>
   </si>
   <si>
     <t xml:space="preserve">7.56466865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51111459732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53789091110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61152982711792</t>
+    <t xml:space="preserve">7.5111141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53789138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6115288734436</t>
   </si>
   <si>
     <t xml:space="preserve">7.61822414398193</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">7.8525276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07344341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32113456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18055248260498</t>
+    <t xml:space="preserve">8.07344245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32113647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1805534362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.37469100952148</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">8.66254901885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89685344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91693782806396</t>
+    <t xml:space="preserve">8.89685249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91693592071533</t>
   </si>
   <si>
     <t xml:space="preserve">8.48849582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73618793487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21402645111084</t>
+    <t xml:space="preserve">8.7361888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21402549743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.28766345977783</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">8.45502281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18724727630615</t>
+    <t xml:space="preserve">8.18724632263184</t>
   </si>
   <si>
     <t xml:space="preserve">8.20733070373535</t>
@@ -2858,67 +2858,67 @@
     <t xml:space="preserve">7.8123607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77888965606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91277694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89938831329346</t>
+    <t xml:space="preserve">7.77888917922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91277742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89938879013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.99980354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97049236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68009757995605</t>
+    <t xml:space="preserve">8.97049140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68009853363037</t>
   </si>
   <si>
     <t xml:space="preserve">9.55290508270264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93448448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99473476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96126270294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94118022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0081224441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.028205871582</t>
+    <t xml:space="preserve">9.93448543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96126365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9411792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0081233978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0282068252563</t>
   </si>
   <si>
     <t xml:space="preserve">9.85415267944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73365306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5168972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039247512817</t>
+    <t xml:space="preserve">9.77381992340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7336540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5168962478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039257049561</t>
   </si>
   <si>
     <t xml:space="preserve">10.4767303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6775636672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6440916061401</t>
+    <t xml:space="preserve">10.677562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6440906524658</t>
   </si>
   <si>
     <t xml:space="preserve">10.038535118103</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.84605503082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3346567153931</t>
+    <t xml:space="preserve">10.3346557617188</t>
   </si>
   <si>
     <t xml:space="preserve">10.186595916748</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">9.94969749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9052791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63877010345459</t>
+    <t xml:space="preserve">9.90528011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63876914978027</t>
   </si>
   <si>
     <t xml:space="preserve">9.55733585357666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59435081481934</t>
+    <t xml:space="preserve">9.59435176849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.43888759613037</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">9.57954502105713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67578506469727</t>
+    <t xml:space="preserve">9.67578411102295</t>
   </si>
   <si>
     <t xml:space="preserve">9.76462173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79423332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83865261077881</t>
+    <t xml:space="preserve">9.79423236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83865165710449</t>
   </si>
   <si>
     <t xml:space="preserve">9.89787673950195</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">9.89047336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75721836090088</t>
+    <t xml:space="preserve">9.7572193145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.80904006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85345935821533</t>
+    <t xml:space="preserve">9.85345840454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.86086082458496</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.77202415466309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0533409118652</t>
+    <t xml:space="preserve">10.0533399581909</t>
   </si>
   <si>
     <t xml:space="preserve">9.7202033996582</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">9.4018726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40927505493164</t>
+    <t xml:space="preserve">9.40927600860596</t>
   </si>
   <si>
     <t xml:space="preserve">9.33524417877197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26121425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14276504516602</t>
+    <t xml:space="preserve">9.26121520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14276599884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.10575008392334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99655532836914</t>
+    <t xml:space="preserve">8.99655437469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.34634971618652</t>
@@ -3056,40 +3056,40 @@
     <t xml:space="preserve">9.17237758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2464075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20199012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17978096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11315250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23160171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01691436767578</t>
+    <t xml:space="preserve">9.24640846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20199108123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17978000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1131534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23160266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01691341400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.03912258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15757179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31303596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35745429992676</t>
+    <t xml:space="preserve">9.15757083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3130350112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35745334625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.26861763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15016841888428</t>
+    <t xml:space="preserve">9.15016746520996</t>
   </si>
   <si>
     <t xml:space="preserve">9.03171920776367</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">8.98730182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09834766387939</t>
+    <t xml:space="preserve">9.09834671020508</t>
   </si>
   <si>
     <t xml:space="preserve">8.994704246521</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">9.9571008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.668381690979</t>
+    <t xml:space="preserve">9.66838264465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.60915756225586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32784271240234</t>
+    <t xml:space="preserve">9.32784175872803</t>
   </si>
   <si>
     <t xml:space="preserve">9.46109676361084</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">9.52772426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86885166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75040340423584</t>
+    <t xml:space="preserve">8.86885261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75040435791016</t>
   </si>
   <si>
     <t xml:space="preserve">8.92067432403564</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">8.80962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77261257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33078384399414</t>
+    <t xml:space="preserve">8.77261352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33078336715698</t>
   </si>
   <si>
     <t xml:space="preserve">4.40481376647949</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">4.51585960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5898904800415</t>
+    <t xml:space="preserve">4.58989000320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.62690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69723415374756</t>
+    <t xml:space="preserve">4.69723463058472</t>
   </si>
   <si>
     <t xml:space="preserve">4.5824875831604</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">4.31227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13090133666992</t>
+    <t xml:space="preserve">4.10128879547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13090085983276</t>
   </si>
   <si>
     <t xml:space="preserve">4.27155923843384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19382667541504</t>
+    <t xml:space="preserve">4.1938271522522</t>
   </si>
   <si>
     <t xml:space="preserve">4.16791677474976</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">4.20493173599243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12720012664795</t>
+    <t xml:space="preserve">4.12719964981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.14570760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09018468856812</t>
+    <t xml:space="preserve">4.09018421173096</t>
   </si>
   <si>
     <t xml:space="preserve">4.21233510971069</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">4.35669469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39741086959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36039543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15311050415039</t>
+    <t xml:space="preserve">4.39741134643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36039590835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15311098098755</t>
   </si>
   <si>
     <t xml:space="preserve">4.10499095916748</t>
@@ -3239,28 +3239,28 @@
     <t xml:space="preserve">4.09758758544922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17902088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93842220306396</t>
+    <t xml:space="preserve">4.17902135848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93842196464539</t>
   </si>
   <si>
     <t xml:space="preserve">4.06057214736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05687093734741</t>
+    <t xml:space="preserve">4.05687046051025</t>
   </si>
   <si>
     <t xml:space="preserve">3.87549614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04576683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58862781524658</t>
+    <t xml:space="preserve">4.04576635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85328722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58862805366516</t>
   </si>
   <si>
     <t xml:space="preserve">3.51644825935364</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">4.07537889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04206418991089</t>
+    <t xml:space="preserve">4.04206466674805</t>
   </si>
   <si>
     <t xml:space="preserve">4.15681171417236</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">4.27526092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94952654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90510845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96433281898499</t>
+    <t xml:space="preserve">3.94952702522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90510821342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96433258056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.98654198646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95322799682617</t>
+    <t xml:space="preserve">3.95322823524475</t>
   </si>
   <si>
     <t xml:space="preserve">4.05316925048828</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">4.01615428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01985549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88660097122192</t>
+    <t xml:space="preserve">4.01985502243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88660049438477</t>
   </si>
   <si>
     <t xml:space="preserve">3.86439180374146</t>
@@ -3323,46 +3323,46 @@
     <t xml:space="preserve">3.50164246559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53310513496399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55716514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52015018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48313474655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51459765434265</t>
+    <t xml:space="preserve">3.53310537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55716490745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52014994621277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48313450813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51459717750549</t>
   </si>
   <si>
     <t xml:space="preserve">3.5738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6200909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61638975143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70152449607849</t>
+    <t xml:space="preserve">3.62009072303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61638951301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70152425765991</t>
   </si>
   <si>
     <t xml:space="preserve">3.42391014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33137226104736</t>
+    <t xml:space="preserve">3.33137178421021</t>
   </si>
   <si>
     <t xml:space="preserve">3.32026743888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35358095169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10928058624268</t>
+    <t xml:space="preserve">3.35358119010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1092803478241</t>
   </si>
   <si>
     <t xml:space="preserve">3.24623703956604</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">3.2647442817688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10187745094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01304125785828</t>
+    <t xml:space="preserve">3.10187768936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0130410194397</t>
   </si>
   <si>
     <t xml:space="preserve">2.92050266265869</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">3.007488489151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98342895507812</t>
+    <t xml:space="preserve">2.98342871665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.93345808982849</t>
@@ -3404,25 +3404,25 @@
     <t xml:space="preserve">2.93530893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87238311767578</t>
+    <t xml:space="preserve">2.8723828792572</t>
   </si>
   <si>
     <t xml:space="preserve">2.81130766868591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86497974395752</t>
+    <t xml:space="preserve">2.8649799823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683058738708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503896713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90569663047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86868143081665</t>
+    <t xml:space="preserve">2.76503872871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90569686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86868166923523</t>
   </si>
   <si>
     <t xml:space="preserve">2.92420434951782</t>
@@ -3431,22 +3431,22 @@
     <t xml:space="preserve">2.90014457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85387539863586</t>
+    <t xml:space="preserve">2.85387563705444</t>
   </si>
   <si>
     <t xml:space="preserve">2.82981538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059102058411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82426309585571</t>
+    <t xml:space="preserve">2.77059125900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82426333427429</t>
   </si>
   <si>
     <t xml:space="preserve">2.83721852302551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.763188123703</t>
+    <t xml:space="preserve">2.76318788528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.60772395133972</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">2.52999186515808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49852895736694</t>
+    <t xml:space="preserve">2.49852871894836</t>
   </si>
   <si>
     <t xml:space="preserve">2.60032105445862</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.56515645980835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6151270866394</t>
+    <t xml:space="preserve">2.61512732505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.57811188697815</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">2.51888728141785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44855833053589</t>
+    <t xml:space="preserve">2.44855809211731</t>
   </si>
   <si>
     <t xml:space="preserve">2.47446918487549</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">2.48927521705627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52629041671753</t>
+    <t xml:space="preserve">2.52629065513611</t>
   </si>
   <si>
     <t xml:space="preserve">2.48742437362671</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">2.25792980194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34861707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4133939743042</t>
+    <t xml:space="preserve">2.34861731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41339373588562</t>
   </si>
   <si>
     <t xml:space="preserve">2.34676671028137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790042877197</t>
+    <t xml:space="preserve">2.30790066719055</t>
   </si>
   <si>
     <t xml:space="preserve">2.19685482978821</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">2.13577961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18760085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29679584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2856912612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30234813690186</t>
+    <t xml:space="preserve">2.18760108947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29679608345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28569149971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30234837532043</t>
   </si>
   <si>
     <t xml:space="preserve">2.35416984558105</t>
@@ -3542,19 +3542,19 @@
     <t xml:space="preserve">2.34121417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25422859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26718378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28754210472107</t>
+    <t xml:space="preserve">2.25422835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26718401908875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28754186630249</t>
   </si>
   <si>
     <t xml:space="preserve">2.32085585594177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27458691596985</t>
+    <t xml:space="preserve">2.27458667755127</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461628913879</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">2.25607919692993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22276568412781</t>
+    <t xml:space="preserve">2.22276544570923</t>
   </si>
   <si>
     <t xml:space="preserve">2.24312376976013</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">2.18204879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2653329372406</t>
+    <t xml:space="preserve">2.26533317565918</t>
   </si>
   <si>
     <t xml:space="preserve">2.2912437915802</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">2.117271900177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08765959739685</t>
+    <t xml:space="preserve">2.08765983581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.13763046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14688444137573</t>
+    <t xml:space="preserve">2.14688420295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.08395838737488</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">2.07470440864563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05434608459473</t>
+    <t xml:space="preserve">2.05434632301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.05989837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11912274360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12652564048767</t>
+    <t xml:space="preserve">2.11912250518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12652587890625</t>
   </si>
   <si>
     <t xml:space="preserve">2.07285380363464</t>
@@ -3635,28 +3635,28 @@
     <t xml:space="preserve">2.01362943649292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95810651779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86186683177948</t>
+    <t xml:space="preserve">1.95810639858246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86186695098877</t>
   </si>
   <si>
     <t xml:space="preserve">2.01393985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90132355690002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83638417720795</t>
+    <t xml:space="preserve">1.90132367610931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83638429641724</t>
   </si>
   <si>
     <t xml:space="preserve">1.87255311012268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91036570072174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88077330589294</t>
+    <t xml:space="preserve">1.91036558151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88077318668365</t>
   </si>
   <si>
     <t xml:space="preserve">1.84953665733337</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">1.70814979076385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86679899692535</t>
+    <t xml:space="preserve">1.86679887771606</t>
   </si>
   <si>
     <t xml:space="preserve">1.93338215351105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89556932449341</t>
+    <t xml:space="preserve">1.8955694437027</t>
   </si>
   <si>
     <t xml:space="preserve">1.83967220783234</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">1.76158058643341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77062296867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83556222915649</t>
+    <t xml:space="preserve">1.770623087883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83556234836578</t>
   </si>
   <si>
     <t xml:space="preserve">1.79199540615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85857880115509</t>
+    <t xml:space="preserve">1.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">1.90625560283661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95311069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.958864569664</t>
+    <t xml:space="preserve">1.95311045646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95886468887329</t>
   </si>
   <si>
     <t xml:space="preserve">2.00078773498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03695607185364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98023724555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03942251205444</t>
+    <t xml:space="preserve">2.03695631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03942203521729</t>
   </si>
   <si>
     <t xml:space="preserve">2.02873587608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07559108734131</t>
+    <t xml:space="preserve">2.07559084892273</t>
   </si>
   <si>
     <t xml:space="preserve">2.08381128311157</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">2.25643444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2420494556427</t>
+    <t xml:space="preserve">2.24204897880554</t>
   </si>
   <si>
     <t xml:space="preserve">2.23382902145386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14135241508484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15573763847351</t>
+    <t xml:space="preserve">2.14135217666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15573740005493</t>
   </si>
   <si>
     <t xml:space="preserve">2.14751744270325</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">2.30781054496765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34685659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35096621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34274625778198</t>
+    <t xml:space="preserve">2.34685635566711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35096645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3427460193634</t>
   </si>
   <si>
     <t xml:space="preserve">2.30164551734924</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">2.25026941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24821424484253</t>
+    <t xml:space="preserve">2.24821448326111</t>
   </si>
   <si>
     <t xml:space="preserve">2.25848960876465</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">2.1619029045105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14546251296997</t>
+    <t xml:space="preserve">2.14546227455139</t>
   </si>
   <si>
     <t xml:space="preserve">2.21944379806519</t>
@@ -3833,37 +3833,37 @@
     <t xml:space="preserve">2.30986547470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35507655143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41056251525879</t>
+    <t xml:space="preserve">2.3550763130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41056227684021</t>
   </si>
   <si>
     <t xml:space="preserve">2.51536965370178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54619526863098</t>
+    <t xml:space="preserve">2.54619550704956</t>
   </si>
   <si>
     <t xml:space="preserve">2.52769994735718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55236029624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53797507286072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54003024101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45988368988037</t>
+    <t xml:space="preserve">2.55236053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5379753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54003000259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45988345146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.41261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52153491973877</t>
+    <t xml:space="preserve">2.52153468132019</t>
   </si>
   <si>
     <t xml:space="preserve">2.54208517074585</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">2.50920462608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55852556228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55647039413452</t>
+    <t xml:space="preserve">2.5585253238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55647015571594</t>
   </si>
   <si>
     <t xml:space="preserve">2.56674551963806</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">2.81540560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75786447525024</t>
+    <t xml:space="preserve">2.75786423683167</t>
   </si>
   <si>
     <t xml:space="preserve">2.7475893497467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72087359428406</t>
+    <t xml:space="preserve">2.72087383270264</t>
   </si>
   <si>
     <t xml:space="preserve">2.63661694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63250708580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66744256019592</t>
+    <t xml:space="preserve">2.63250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6674427986145</t>
   </si>
   <si>
     <t xml:space="preserve">2.67155265808105</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">2.68182802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7414243221283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70443320274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72498393058777</t>
+    <t xml:space="preserve">2.74142408370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70443344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72498369216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.70854353904724</t>
@@ -3953,25 +3953,25 @@
     <t xml:space="preserve">2.78663516044617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78868985176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77019476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72703909873962</t>
+    <t xml:space="preserve">2.78869009017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77019453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72703886032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.65922236442566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6078462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62634181976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70648860931396</t>
+    <t xml:space="preserve">2.60784649848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6263415813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70648837089539</t>
   </si>
   <si>
     <t xml:space="preserve">2.63867211341858</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">2.67360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62428712844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59757137298584</t>
+    <t xml:space="preserve">2.62428689002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59757161140442</t>
   </si>
   <si>
     <t xml:space="preserve">2.6057915687561</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">2.58524107933044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58935141563416</t>
+    <t xml:space="preserve">2.58935117721558</t>
   </si>
   <si>
     <t xml:space="preserve">2.57907605171204</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">2.86678171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93048787117004</t>
+    <t xml:space="preserve">2.93048810958862</t>
   </si>
   <si>
     <t xml:space="preserve">2.97158861160278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91404747962952</t>
+    <t xml:space="preserve">2.9140477180481</t>
   </si>
   <si>
     <t xml:space="preserve">2.94487309455872</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">2.95925831794739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035929679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99419403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99830412864685</t>
+    <t xml:space="preserve">3.00035953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99419379234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99830436706543</t>
   </si>
   <si>
     <t xml:space="preserve">2.89760732650757</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">2.84006595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82773590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74553418159485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61606645584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68388295173645</t>
+    <t xml:space="preserve">2.82773566246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74553442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61606669425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68388319015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.6982684135437</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">2.66538786888123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79896521568298</t>
+    <t xml:space="preserve">2.79896545410156</t>
   </si>
   <si>
     <t xml:space="preserve">2.7907452583313</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.99008417129517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9345977306366</t>
+    <t xml:space="preserve">2.93459796905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.84212112426758</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">2.77224969863892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78457975387573</t>
+    <t xml:space="preserve">2.78457999229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.65305733680725</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">2.69210314750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82979083061218</t>
+    <t xml:space="preserve">2.82979106903076</t>
   </si>
   <si>
     <t xml:space="preserve">2.89555215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10927653312683</t>
+    <t xml:space="preserve">3.10927629470825</t>
   </si>
   <si>
     <t xml:space="preserve">3.03324007987976</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">2.85856151580811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85034108161926</t>
+    <t xml:space="preserve">2.85034132003784</t>
   </si>
   <si>
     <t xml:space="preserve">2.86883687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82568097114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92226767539978</t>
+    <t xml:space="preserve">2.82568073272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92226791381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.88733220100403</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">3.06612062454224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05995535850525</t>
+    <t xml:space="preserve">3.05995559692383</t>
   </si>
   <si>
     <t xml:space="preserve">2.9818639755249</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">3.0126895904541</t>
   </si>
   <si